--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\batuhan.helvaci\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAE420B-4637-4144-AC8C-F1E0E2661DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD737ECC-76A0-45A6-B978-84BDBDF1F0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="19" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
-    <sheet name="Bitfinex P2P Daily Lending Avr " sheetId="11" state="hidden" r:id="rId2"/>
+    <sheet name="Bitfinex P2P Daily Lending Avr " sheetId="11" r:id="rId2"/>
     <sheet name="Günlük taslak" sheetId="17" state="hidden" r:id="rId3"/>
     <sheet name="Günlük" sheetId="18" r:id="rId4"/>
     <sheet name="Daily Data" sheetId="10" r:id="rId5"/>
@@ -42,6 +42,7 @@
     <sheet name="13.04.2026" sheetId="47" r:id="rId27"/>
     <sheet name="14.04.2026" sheetId="48" r:id="rId28"/>
     <sheet name="15.04.2026" sheetId="49" r:id="rId29"/>
+    <sheet name="16.04.2026" sheetId="51" r:id="rId30"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -876,6 +877,43 @@
 </comments>
 </file>
 
+<file path=xl/comments26.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{04D58333-62FC-4627-A2DD-DE4145F871CC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1136,7 +1174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3216" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3251" uniqueCount="68">
   <si>
     <t>3.46%</t>
   </si>
@@ -1352,7 +1390,7 @@
     <numFmt numFmtId="166" formatCode="0.00000%"/>
     <numFmt numFmtId="167" formatCode="0.000000%"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1461,6 +1499,13 @@
       <charset val="162"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1560,10 +1605,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1802,11 +1848,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="25">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2066,10 +2121,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Margin Borrow Rates'!$A$2:$A$74</c:f>
+              <c:f>'Margin Borrow Rates'!$A$2:$A$90</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="89"/>
                 <c:pt idx="0">
                   <c:v>46054.125</c:v>
                 </c:pt>
@@ -2288,16 +2343,64 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46126.125</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46127.125</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46128.125</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46129.125</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46130.125</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>46131.125</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>46132.125</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>46133.125</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>46134.125</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>46135.125</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>46136.125</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>46137.125</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>46138.125</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>46139.125</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>46140.125</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>46141.125</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>46142.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Margin Borrow Rates'!$B$2:$B$74</c:f>
+              <c:f>'Margin Borrow Rates'!$B$2:$B$90</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="89"/>
                 <c:pt idx="0">
                   <c:v>4.1399999999999999E-2</c:v>
                 </c:pt>
@@ -2515,6 +2618,12 @@
                   <c:v>2.9499999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="72">
+                  <c:v>2.9499999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2.9499999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="74">
                   <c:v>2.9499999999999998E-2</c:v>
                 </c:pt>
               </c:numCache>
@@ -2555,10 +2664,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Margin Borrow Rates'!$A$2:$A$74</c:f>
+              <c:f>'Margin Borrow Rates'!$A$2:$A$90</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="89"/>
                 <c:pt idx="0">
                   <c:v>46054.125</c:v>
                 </c:pt>
@@ -2777,16 +2886,64 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46126.125</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46127.125</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46128.125</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46129.125</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46130.125</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>46131.125</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>46132.125</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>46133.125</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>46134.125</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>46135.125</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>46136.125</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>46137.125</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>46138.125</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>46139.125</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>46140.125</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>46141.125</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>46142.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Margin Borrow Rates'!$C$2:$C$74</c:f>
+              <c:f>'Margin Borrow Rates'!$C$2:$C$90</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="89"/>
                 <c:pt idx="0">
                   <c:v>3.7499999999999999E-2</c:v>
                 </c:pt>
@@ -3004,6 +3161,12 @@
                   <c:v>2.47E-2</c:v>
                 </c:pt>
                 <c:pt idx="72">
+                  <c:v>2.47E-2</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2.47E-2</c:v>
+                </c:pt>
+                <c:pt idx="74">
                   <c:v>2.47E-2</c:v>
                 </c:pt>
               </c:numCache>
@@ -3044,10 +3207,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Margin Borrow Rates'!$A$2:$A$74</c:f>
+              <c:f>'Margin Borrow Rates'!$A$2:$A$90</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="89"/>
                 <c:pt idx="0">
                   <c:v>46054.125</c:v>
                 </c:pt>
@@ -3266,16 +3429,64 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46126.125</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46127.125</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46128.125</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46129.125</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46130.125</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>46131.125</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>46132.125</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>46133.125</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>46134.125</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>46135.125</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>46136.125</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>46137.125</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>46138.125</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>46139.125</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>46140.125</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>46141.125</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>46142.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Margin Borrow Rates'!$D$2:$D$74</c:f>
+              <c:f>'Margin Borrow Rates'!$D$2:$D$90</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="89"/>
                 <c:pt idx="0">
                   <c:v>4.99E-2</c:v>
                 </c:pt>
@@ -3493,6 +3704,12 @@
                   <c:v>3.2500000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="72">
+                  <c:v>3.2500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>3.2500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="74">
                   <c:v>3.2500000000000001E-2</c:v>
                 </c:pt>
               </c:numCache>
@@ -3533,10 +3750,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Margin Borrow Rates'!$A$2:$A$74</c:f>
+              <c:f>'Margin Borrow Rates'!$A$2:$A$90</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="89"/>
                 <c:pt idx="0">
                   <c:v>46054.125</c:v>
                 </c:pt>
@@ -3755,16 +3972,64 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46126.125</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46127.125</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46128.125</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46129.125</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46130.125</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>46131.125</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>46132.125</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>46133.125</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>46134.125</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>46135.125</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>46136.125</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>46137.125</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>46138.125</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>46139.125</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>46140.125</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>46141.125</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>46142.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Margin Borrow Rates'!$E$2:$E$74</c:f>
+              <c:f>'Margin Borrow Rates'!$E$2:$E$90</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="89"/>
                 <c:pt idx="0">
                   <c:v>4.6899999999999997E-2</c:v>
                 </c:pt>
@@ -3982,6 +4247,12 @@
                   <c:v>3.1099999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="72">
+                  <c:v>3.1099999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>3.1099999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="74">
                   <c:v>3.1099999999999999E-2</c:v>
                 </c:pt>
               </c:numCache>
@@ -4022,10 +4293,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Margin Borrow Rates'!$A$2:$A$74</c:f>
+              <c:f>'Margin Borrow Rates'!$A$2:$A$90</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="89"/>
                 <c:pt idx="0">
                   <c:v>46054.125</c:v>
                 </c:pt>
@@ -4244,16 +4515,64 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46126.125</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46127.125</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46128.125</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46129.125</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46130.125</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>46131.125</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>46132.125</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>46133.125</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>46134.125</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>46135.125</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>46136.125</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>46137.125</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>46138.125</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>46139.125</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>46140.125</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>46141.125</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>46142.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Margin Borrow Rates'!$F$2:$F$74</c:f>
+              <c:f>'Margin Borrow Rates'!$F$2:$F$90</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="89"/>
                 <c:pt idx="0">
                   <c:v>5.0500000000000003E-2</c:v>
                 </c:pt>
@@ -4472,6 +4791,12 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>3.1600000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>3.2500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>3.2500000000000001E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5294,7 +5619,7 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>665339</xdr:colOff>
       <xdr:row>136</xdr:row>
-      <xdr:rowOff>107294</xdr:rowOff>
+      <xdr:rowOff>104119</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7200,21 +7525,41 @@
       <c r="A75" s="82">
         <v>46127.125</v>
       </c>
-      <c r="B75" s="82"/>
-      <c r="C75" s="10"/>
-      <c r="D75" s="10"/>
-      <c r="E75" s="10"/>
-      <c r="F75" s="10"/>
+      <c r="B75" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C75" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D75" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E75" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F75" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="82">
         <v>46128.125</v>
       </c>
-      <c r="B76" s="82"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="10"/>
-      <c r="F76" s="10"/>
+      <c r="B76" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C76" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D76" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E76" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F76" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="82">
@@ -8037,7 +8382,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8373,7 +8718,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8711,7 +9056,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9047,7 +9392,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9381,7 +9726,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9717,7 +10062,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10053,7 +10398,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10389,7 +10734,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10725,7 +11070,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11061,7 +11406,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12109,9 +12454,15 @@
       <c r="A75" s="12">
         <v>46127</v>
       </c>
-      <c r="B75" s="13"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="13"/>
+      <c r="B75" s="13">
+        <v>3.0700000000000002E-2</v>
+      </c>
+      <c r="C75" s="13">
+        <v>0.1018</v>
+      </c>
+      <c r="D75" s="13">
+        <v>4.7399999999999998E-2</v>
+      </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="12">
@@ -12505,7 +12856,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12841,7 +13192,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13179,7 +13530,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13517,7 +13868,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13855,7 +14206,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14223,7 +14574,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14591,7 +14942,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14959,7 +15310,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15330,7 +15681,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -15711,7 +16062,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -15725,7 +16076,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB57D633-B910-43FF-A74D-AABABC541E07}">
-  <dimension ref="A1:AR122"/>
+  <dimension ref="A1:BA122"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.7265625" style="26" bestFit="1" customWidth="1"/>
@@ -15751,6 +16102,7 @@
     <col min="33" max="34" width="8.7265625" style="24"/>
     <col min="35" max="35" width="10.08984375" style="24" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="10.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.35">
@@ -20379,7 +20731,7 @@
       <c r="AQ48" s="10"/>
       <c r="AR48" s="10"/>
     </row>
-    <row r="49" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A49" s="15" t="s">
         <v>15</v>
       </c>
@@ -20529,7 +20881,7 @@
         <v>2.8497416706523726E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A50" s="15"/>
       <c r="B50" s="35"/>
       <c r="C50" s="34">
@@ -20581,7 +20933,7 @@
       <c r="AH50" s="10"/>
       <c r="AI50" s="35"/>
     </row>
-    <row r="51" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A51" s="15" t="s">
         <v>17</v>
       </c>
@@ -20695,7 +21047,7 @@
         <v>3.0144199258958837E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A53" s="25">
         <v>46082</v>
       </c>
@@ -20817,7 +21169,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="54" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A54" s="15"/>
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
@@ -20859,7 +21211,7 @@
       <c r="AQ54" s="10"/>
       <c r="AR54" s="10"/>
     </row>
-    <row r="55" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A55" s="15"/>
       <c r="B55" s="34">
         <f>B56*(365/B53)</f>
@@ -20975,7 +21327,7 @@
         <v>2.7161339183711553E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A56" s="15" t="s">
         <v>12</v>
       </c>
@@ -21100,7 +21452,7 @@
         <v>3.3445657100777071E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A57" s="15" t="s">
         <v>59</v>
       </c>
@@ -21220,7 +21572,7 @@
       <c r="AQ57" s="10"/>
       <c r="AR57" s="10"/>
     </row>
-    <row r="58" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A58" s="15"/>
       <c r="B58" s="23"/>
       <c r="C58" s="23"/>
@@ -21284,7 +21636,7 @@
         <v>2.5314242726610869E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A59" s="15"/>
       <c r="B59" s="34">
         <f>B60*(365/B53)</f>
@@ -21356,7 +21708,7 @@
       <c r="AQ59" s="10"/>
       <c r="AR59" s="10"/>
     </row>
-    <row r="60" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A60" s="15" t="s">
         <v>15</v>
       </c>
@@ -21506,7 +21858,7 @@
         <v>2.8291753567093458E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A61" s="15"/>
       <c r="B61" s="35"/>
       <c r="C61" s="34">
@@ -21558,7 +21910,7 @@
       <c r="AH61" s="10"/>
       <c r="AI61" s="16"/>
     </row>
-    <row r="62" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A62" s="15" t="s">
         <v>17</v>
       </c>
@@ -21695,8 +22047,32 @@
       <c r="AR62" s="17" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="63" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT62" s="25">
+        <v>46128</v>
+      </c>
+      <c r="AU62" s="17">
+        <v>7</v>
+      </c>
+      <c r="AV62" s="17">
+        <v>14</v>
+      </c>
+      <c r="AW62" s="17">
+        <v>30</v>
+      </c>
+      <c r="AX62" s="17">
+        <v>60</v>
+      </c>
+      <c r="AY62" s="17">
+        <v>90</v>
+      </c>
+      <c r="AZ62" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="BA62" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="1:53" x14ac:dyDescent="0.35">
       <c r="AK63" s="15"/>
       <c r="AL63" s="10"/>
       <c r="AM63" s="10"/>
@@ -21705,8 +22081,16 @@
       <c r="AP63" s="10"/>
       <c r="AQ63" s="10"/>
       <c r="AR63" s="10"/>
-    </row>
-    <row r="64" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT63" s="15"/>
+      <c r="AU63" s="10"/>
+      <c r="AV63" s="10"/>
+      <c r="AW63" s="10"/>
+      <c r="AX63" s="10"/>
+      <c r="AY63" s="10"/>
+      <c r="AZ63" s="10"/>
+      <c r="BA63" s="10"/>
+    </row>
+    <row r="64" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A64" s="25">
         <v>46083</v>
       </c>
@@ -21833,27 +22217,57 @@
         <f>(1+AQ64/365)^365-1</f>
         <v>2.6750586738331306E-2</v>
       </c>
-    </row>
-    <row r="65" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT64" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="AU64" s="34">
+        <f>((1+$BA64)^(AU62/365)-1)*365/AU62</f>
+        <v>2.7406171402247135E-2</v>
+      </c>
+      <c r="AV64" s="34">
+        <f t="shared" ref="AV64:AY64" si="71">((1+$BA64)^(AV62/365)-1)*365/AV62</f>
+        <v>2.7413373714052343E-2</v>
+      </c>
+      <c r="AW64" s="34">
+        <f t="shared" si="71"/>
+        <v>2.7429845619310389E-2</v>
+      </c>
+      <c r="AX64" s="34">
+        <f t="shared" si="71"/>
+        <v>2.7460766020571663E-2</v>
+      </c>
+      <c r="AY64" s="34">
+        <f t="shared" si="71"/>
+        <v>2.7491732895357952E-2</v>
+      </c>
+      <c r="AZ64" s="23">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="BA64" s="34">
+        <f>(1+AZ64/365)^365-1</f>
+        <v>2.7777775131269555E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A65" s="15"/>
       <c r="B65" s="34">
         <f>B66*(365/B64)</f>
         <v>3.1308053397499487E-2</v>
       </c>
       <c r="C65" s="34">
-        <f t="shared" ref="C65:F65" si="71">C66*(365/C64)</f>
+        <f t="shared" ref="C65:F65" si="72">C66*(365/C64)</f>
         <v>3.1317452520042227E-2</v>
       </c>
       <c r="D65" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>3.13389503593711E-2</v>
       </c>
       <c r="E65" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>3.137931185839702E-2</v>
       </c>
       <c r="F65" s="34">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>3.1419742666299495E-2</v>
       </c>
       <c r="G65" s="16"/>
@@ -21864,19 +22278,19 @@
         <v>3.1308053397499487E-2</v>
       </c>
       <c r="L65" s="34">
-        <f t="shared" ref="L65:O65" si="72">L66*365/L64</f>
+        <f t="shared" ref="L65:O65" si="73">L66*365/L64</f>
         <v>3.131745252004222E-2</v>
       </c>
       <c r="M65" s="34">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3.13389503593711E-2</v>
       </c>
       <c r="N65" s="34">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3.137931185839702E-2</v>
       </c>
       <c r="O65" s="34">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3.1419742666299495E-2</v>
       </c>
       <c r="P65" s="10"/>
@@ -21922,8 +22336,33 @@
         <f>(1+AQ65/365)^365-1</f>
         <v>3.334232700144435E-2</v>
       </c>
-    </row>
-    <row r="66" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT65" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="AU65" s="23">
+        <v>0.03</v>
+      </c>
+      <c r="AV65" s="23">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="AW65" s="23">
+        <v>4.2900000000000001E-2</v>
+      </c>
+      <c r="AX65" s="23">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="AY65" s="23">
+        <v>6.4899999999999999E-2</v>
+      </c>
+      <c r="AZ65" s="23">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA65" s="34">
+        <f>(1+AZ65/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A66" s="15" t="s">
         <v>12</v>
       </c>
@@ -21992,19 +22431,19 @@
         <v>2.8306583508236022E-2</v>
       </c>
       <c r="U66" s="34">
-        <f t="shared" ref="U66:X66" si="73">((1+$Z66)^(U64/365)-1)*365/U64</f>
+        <f t="shared" ref="U66:X66" si="74">((1+$Z66)^(U64/365)-1)*365/U64</f>
         <v>2.8314266848908365E-2</v>
       </c>
       <c r="V66" s="34">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>2.8331839214008798E-2</v>
       </c>
       <c r="W66" s="34">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>2.8364826602223003E-2</v>
       </c>
       <c r="X66" s="34">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>2.8397865201035391E-2</v>
       </c>
       <c r="Y66" s="23">
@@ -22022,19 +22461,19 @@
         <v>3.0507646955369054E-2</v>
       </c>
       <c r="AD66" s="34">
-        <f t="shared" ref="AD66:AG66" si="74">((1+$AI66)^(AD64/365)-1)*365/AD64</f>
+        <f t="shared" ref="AD66:AG66" si="75">((1+$AI66)^(AD64/365)-1)*365/AD64</f>
         <v>3.0516571634355998E-2</v>
       </c>
       <c r="AE66" s="34">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>3.0536983974912595E-2</v>
       </c>
       <c r="AF66" s="34">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>3.0575306196430729E-2</v>
       </c>
       <c r="AG66" s="34">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>3.0613692540966575E-2</v>
       </c>
       <c r="AH66" s="23">
@@ -22052,8 +22491,16 @@
       <c r="AP66" s="10"/>
       <c r="AQ66" s="10"/>
       <c r="AR66" s="10"/>
-    </row>
-    <row r="67" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT66" s="15"/>
+      <c r="AU66" s="10"/>
+      <c r="AV66" s="10"/>
+      <c r="AW66" s="10"/>
+      <c r="AX66" s="10"/>
+      <c r="AY66" s="10"/>
+      <c r="AZ66" s="10"/>
+      <c r="BA66" s="10"/>
+    </row>
+    <row r="67" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A67" s="15" t="s">
         <v>59</v>
       </c>
@@ -22167,19 +22614,19 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="AM67" s="34">
-        <f t="shared" ref="AM67:AP67" si="75">((1+$AR67)^(AM62/365)-1)*365/AM62</f>
+        <f t="shared" ref="AM67:AP67" si="76">((1+$AR67)^(AM62/365)-1)*365/AM62</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="AN67" s="34">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="AO67" s="34">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="AP67" s="34">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="AQ67" s="23">
@@ -22189,8 +22636,38 @@
         <f>(1+AQ67/365)^365-1</f>
         <v>2.5314242726610869E-2</v>
       </c>
-    </row>
-    <row r="68" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT67" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="AU67" s="34">
+        <f>((1+$BA67)^(AU62/365)-1)*365/AU62</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="AV67" s="34">
+        <f t="shared" ref="AV67:AY67" si="77">((1+$BA67)^(AV62/365)-1)*365/AV62</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="AW67" s="34">
+        <f t="shared" si="77"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="AX67" s="34">
+        <f t="shared" si="77"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="AY67" s="34">
+        <f t="shared" si="77"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="AZ67" s="23">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="BA67" s="34">
+        <f>(1+AZ67/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A68" s="15"/>
       <c r="B68" s="23"/>
       <c r="C68" s="23"/>
@@ -22231,27 +22708,35 @@
       <c r="AP68" s="10"/>
       <c r="AQ68" s="10"/>
       <c r="AR68" s="10"/>
-    </row>
-    <row r="69" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT68" s="15"/>
+      <c r="AU68" s="10"/>
+      <c r="AV68" s="10"/>
+      <c r="AW68" s="10"/>
+      <c r="AX68" s="10"/>
+      <c r="AY68" s="10"/>
+      <c r="AZ68" s="10"/>
+      <c r="BA68" s="10"/>
+    </row>
+    <row r="69" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A69" s="15"/>
       <c r="B69" s="34">
         <f>B70*(365/B64)</f>
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="C69" s="34">
-        <f t="shared" ref="C69:F69" si="76">C70*(365/C64)</f>
+        <f t="shared" ref="C69:F69" si="78">C70*(365/C64)</f>
         <v>2.501113318692437E-2</v>
       </c>
       <c r="D69" s="34">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>2.5024844646748069E-2</v>
       </c>
       <c r="E69" s="34">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="F69" s="34">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>2.5076351951623114E-2</v>
       </c>
       <c r="G69" s="16"/>
@@ -22262,19 +22747,19 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="L69" s="34">
-        <f t="shared" ref="L69:O69" si="77">L70*365/L64</f>
+        <f t="shared" ref="L69:O69" si="79">L70*365/L64</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="M69" s="34">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="N69" s="34">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="O69" s="34">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="P69" s="27"/>
@@ -22323,8 +22808,36 @@
         <f>(1+AQ69/365)^365-1</f>
         <v>2.8600263658591585E-2</v>
       </c>
-    </row>
-    <row r="70" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT69" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU69" s="23">
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="AV69" s="34">
+        <f>((1+$BA69)^(AV62/365)-1)*365/AV62</f>
+        <v>2.751347152523961E-2</v>
+      </c>
+      <c r="AW69" s="23">
+        <v>5.4800000000000001E-2</v>
+      </c>
+      <c r="AX69" s="34">
+        <f>((1+$BA69)^(AX62/365)-1)*365/AX62</f>
+        <v>2.7561210701938343E-2</v>
+      </c>
+      <c r="AY69" s="34">
+        <f>((1+$BA69)^(AY62/365)-1)*365/AY62</f>
+        <v>2.7592404443735931E-2</v>
+      </c>
+      <c r="AZ69" s="23">
+        <v>2.75E-2</v>
+      </c>
+      <c r="BA69" s="34">
+        <f>(1+AZ69/365)^365-1</f>
+        <v>2.7880550318131858E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A70" s="15" t="s">
         <v>15</v>
       </c>
@@ -22393,19 +22906,19 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="U70" s="34">
-        <f t="shared" ref="U70:X70" si="78">((1+$Z70)^(U64/365)-1)*365/U64</f>
+        <f t="shared" ref="U70:X70" si="80">((1+$Z70)^(U64/365)-1)*365/U64</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="V70" s="34">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="W70" s="34">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="X70" s="34">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="Y70" s="23">
@@ -22423,30 +22936,30 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="AD70" s="34">
-        <f t="shared" ref="AD70:AG70" si="79">((1+$AI70)^(AD64/365)-1)*365/AD64</f>
+        <f t="shared" ref="AD70:AG70" si="81">((1+$AI70)^(AD64/365)-1)*365/AD64</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="AE70" s="34">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="AF70" s="34">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="AG70" s="34">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="AH70" s="23">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="AI70" s="34">
-        <f t="shared" ref="AI70:AI72" si="80">(1+AH70/365)^365-1</f>
+        <f t="shared" ref="AI70:AI72" si="82">(1+AH70/365)^365-1</f>
         <v>2.5314242726610869E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A71" s="15"/>
       <c r="B71" s="35"/>
       <c r="C71" s="34">
@@ -22521,8 +23034,32 @@
       <c r="AR71" s="17" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="72" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT71" s="25">
+        <v>46129</v>
+      </c>
+      <c r="AU71" s="17">
+        <v>7</v>
+      </c>
+      <c r="AV71" s="17">
+        <v>14</v>
+      </c>
+      <c r="AW71" s="17">
+        <v>30</v>
+      </c>
+      <c r="AX71" s="17">
+        <v>60</v>
+      </c>
+      <c r="AY71" s="17">
+        <v>90</v>
+      </c>
+      <c r="AZ71" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="BA71" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="72" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A72" s="15" t="s">
         <v>17</v>
       </c>
@@ -22632,7 +23169,7 @@
         <v>3.0599999999999999E-2</v>
       </c>
       <c r="AI72" s="34">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>3.1071669725747597E-2</v>
       </c>
       <c r="AK72" s="15"/>
@@ -22643,8 +23180,16 @@
       <c r="AP72" s="10"/>
       <c r="AQ72" s="10"/>
       <c r="AR72" s="10"/>
-    </row>
-    <row r="73" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT72" s="15"/>
+      <c r="AU72" s="10"/>
+      <c r="AV72" s="10"/>
+      <c r="AW72" s="10"/>
+      <c r="AX72" s="10"/>
+      <c r="AY72" s="10"/>
+      <c r="AZ72" s="10"/>
+      <c r="BA72" s="10"/>
+    </row>
+    <row r="73" spans="1:53" x14ac:dyDescent="0.35">
       <c r="AK73" s="15" t="s">
         <v>12</v>
       </c>
@@ -22653,19 +23198,19 @@
         <v>2.650577261626081E-2</v>
       </c>
       <c r="AM73" s="34">
-        <f t="shared" ref="AM73:AP73" si="81">((1+$AR73)^(AM71/365)-1)*365/AM71</f>
+        <f t="shared" ref="AM73:AP73" si="83">((1+$AR73)^(AM71/365)-1)*365/AM71</f>
         <v>2.6512509454446293E-2</v>
       </c>
       <c r="AN73" s="34">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>2.6527916516109307E-2</v>
       </c>
       <c r="AO73" s="34">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>2.6556836941645196E-2</v>
       </c>
       <c r="AP73" s="34">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>2.6585799405461893E-2</v>
       </c>
       <c r="AQ73" s="23">
@@ -22675,8 +23220,18 @@
         <f>(1+AQ73/365)^365-1</f>
         <v>2.6853259490220882E-2</v>
       </c>
-    </row>
-    <row r="74" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT73" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="AU73" s="34"/>
+      <c r="AV73" s="34"/>
+      <c r="AW73" s="34"/>
+      <c r="AX73" s="34"/>
+      <c r="AY73" s="34"/>
+      <c r="AZ73" s="23"/>
+      <c r="BA73" s="34"/>
+    </row>
+    <row r="74" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A74" s="25">
         <v>46084</v>
       </c>
@@ -22798,8 +23353,18 @@
         <f>(1+AQ74/365)^365-1</f>
         <v>3.3445657100777071E-2</v>
       </c>
-    </row>
-    <row r="75" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT74" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="AU74" s="23"/>
+      <c r="AV74" s="23"/>
+      <c r="AW74" s="23"/>
+      <c r="AX74" s="23"/>
+      <c r="AY74" s="23"/>
+      <c r="AZ74" s="23"/>
+      <c r="BA74" s="34"/>
+    </row>
+    <row r="75" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A75" s="15"/>
       <c r="B75" s="10"/>
       <c r="C75" s="10"/>
@@ -22840,27 +23405,35 @@
       <c r="AP75" s="10"/>
       <c r="AQ75" s="10"/>
       <c r="AR75" s="10"/>
-    </row>
-    <row r="76" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT75" s="15"/>
+      <c r="AU75" s="10"/>
+      <c r="AV75" s="10"/>
+      <c r="AW75" s="10"/>
+      <c r="AX75" s="10"/>
+      <c r="AY75" s="10"/>
+      <c r="AZ75" s="10"/>
+      <c r="BA75" s="10"/>
+    </row>
+    <row r="76" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A76" s="15"/>
       <c r="B76" s="34">
         <f>B77*365/B74</f>
         <v>3.1208002016684468E-2</v>
       </c>
       <c r="C76" s="34">
-        <f t="shared" ref="C76:F76" si="82">C77*365/C74</f>
+        <f t="shared" ref="C76:F76" si="84">C77*365/C74</f>
         <v>3.121734116151758E-2</v>
       </c>
       <c r="D76" s="34">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>3.1238701773908639E-2</v>
       </c>
       <c r="E76" s="34">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>3.1278805465217829E-2</v>
       </c>
       <c r="F76" s="34">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>3.1318977802404467E-2</v>
       </c>
       <c r="G76" s="16"/>
@@ -22871,19 +23444,19 @@
         <v>3.06076971850027E-2</v>
       </c>
       <c r="L76" s="34">
-        <f t="shared" ref="L76:O76" si="83">L77*365/L74</f>
+        <f t="shared" ref="L76:O76" si="85">L77*365/L74</f>
         <v>3.0616680497176203E-2</v>
       </c>
       <c r="M76" s="34">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>3.063722698551748E-2</v>
       </c>
       <c r="N76" s="34">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>3.0675801218832937E-2</v>
       </c>
       <c r="O76" s="34">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>3.071444020872649E-2</v>
       </c>
       <c r="P76" s="10"/>
@@ -22912,19 +23485,19 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="AM76" s="34">
-        <f t="shared" ref="AM76:AP76" si="84">((1+$AR76)^(AM71/365)-1)*365/AM71</f>
+        <f t="shared" ref="AM76:AP76" si="86">((1+$AR76)^(AM71/365)-1)*365/AM71</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="AN76" s="34">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="AO76" s="34">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="AP76" s="34">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="AQ76" s="23">
@@ -22934,8 +23507,18 @@
         <f>(1+AQ76/365)^365-1</f>
         <v>2.5314242726610869E-2</v>
       </c>
-    </row>
-    <row r="77" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT76" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="AU76" s="34"/>
+      <c r="AV76" s="34"/>
+      <c r="AW76" s="34"/>
+      <c r="AX76" s="34"/>
+      <c r="AY76" s="34"/>
+      <c r="AZ76" s="23"/>
+      <c r="BA76" s="34"/>
+    </row>
+    <row r="77" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A77" s="15" t="s">
         <v>12</v>
       </c>
@@ -23004,19 +23587,19 @@
         <v>2.8806818211650764E-2</v>
       </c>
       <c r="U77" s="76">
-        <f t="shared" ref="U77:X77" si="85">((1+$Z77)^(U74/365)-1)*365/U74</f>
+        <f t="shared" ref="U77:X77" si="87">((1+$Z77)^(U74/365)-1)*365/U74</f>
         <v>2.8814775512232469E-2</v>
       </c>
       <c r="V77" s="76">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>2.8832974634983022E-2</v>
       </c>
       <c r="W77" s="76">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>2.8867139310035983E-2</v>
       </c>
       <c r="X77" s="76">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>2.8901357961484207E-2</v>
       </c>
       <c r="Y77" s="23">
@@ -23034,19 +23617,19 @@
         <v>3.0807798137726067E-2</v>
       </c>
       <c r="AD77" s="34">
-        <f t="shared" ref="AD77:AG77" si="86">((1+$AI77)^(AD74/365)-1)*365/AD74</f>
+        <f t="shared" ref="AD77:AG77" si="88">((1+$AI77)^(AD74/365)-1)*365/AD74</f>
         <v>3.0816899292500168E-2</v>
       </c>
       <c r="AE77" s="34">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>3.0837715396014837E-2</v>
       </c>
       <c r="AF77" s="34">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>3.087679613673544E-2</v>
       </c>
       <c r="AG77" s="34">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>3.0915942913661267E-2</v>
       </c>
       <c r="AH77" s="23">
@@ -23064,8 +23647,16 @@
       <c r="AP77" s="10"/>
       <c r="AQ77" s="10"/>
       <c r="AR77" s="10"/>
-    </row>
-    <row r="78" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT77" s="15"/>
+      <c r="AU77" s="10"/>
+      <c r="AV77" s="10"/>
+      <c r="AW77" s="10"/>
+      <c r="AX77" s="10"/>
+      <c r="AY77" s="10"/>
+      <c r="AZ77" s="10"/>
+      <c r="BA77" s="10"/>
+    </row>
+    <row r="78" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A78" s="15"/>
       <c r="B78" s="10"/>
       <c r="C78" s="10"/>
@@ -23126,8 +23717,18 @@
         <f>(1+AQ78/365)^365-1</f>
         <v>2.7366776854136576E-2</v>
       </c>
-    </row>
-    <row r="79" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT78" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU78" s="23"/>
+      <c r="AV78" s="34"/>
+      <c r="AW78" s="23"/>
+      <c r="AX78" s="34"/>
+      <c r="AY78" s="34"/>
+      <c r="AZ78" s="23"/>
+      <c r="BA78" s="34"/>
+    </row>
+    <row r="79" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A79" s="15" t="s">
         <v>59</v>
       </c>
@@ -23234,7 +23835,7 @@
         <v>3.3548997504548206E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A80" s="15"/>
       <c r="B80" s="35"/>
       <c r="C80" s="35"/>
@@ -23299,19 +23900,19 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="C81" s="34">
-        <f t="shared" ref="C81:F81" si="87">C82*365/C74</f>
+        <f t="shared" ref="C81:F81" si="89">C82*365/C74</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="D81" s="34">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="E81" s="34">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="F81" s="34">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="G81" s="16"/>
@@ -23322,19 +23923,19 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="L81" s="14">
-        <f t="shared" ref="L81:O81" si="88">L82*365/L74</f>
+        <f t="shared" ref="L81:O81" si="90">L82*365/L74</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="M81" s="14">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="N81" s="14">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="O81" s="14">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="P81" s="10"/>
@@ -23433,19 +24034,19 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="U82" s="34">
-        <f t="shared" ref="U82:X82" si="89">((1+$Z82)^(U74/365)-1)*365/U74</f>
+        <f t="shared" ref="U82:X82" si="91">((1+$Z82)^(U74/365)-1)*365/U74</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="V82" s="34">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="W82" s="34">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="X82" s="34">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="Y82" s="23">
@@ -23463,19 +24064,19 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="AD82" s="34">
-        <f t="shared" ref="AD82:AG82" si="90">((1+$AI82)^(AD74/365)-1)*365/AD74</f>
+        <f t="shared" ref="AD82:AG82" si="92">((1+$AI82)^(AD74/365)-1)*365/AD74</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="AE82" s="34">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="AF82" s="34">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="AG82" s="34">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="AH82" s="23">
@@ -23493,19 +24094,19 @@
         <v>2.650577261626081E-2</v>
       </c>
       <c r="AM82" s="34">
-        <f t="shared" ref="AM82:AP82" si="91">((1+$AR82)^(AM80/365)-1)*365/AM80</f>
+        <f t="shared" ref="AM82:AP82" si="93">((1+$AR82)^(AM80/365)-1)*365/AM80</f>
         <v>2.6512509454446293E-2</v>
       </c>
       <c r="AN82" s="34">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>2.6527916516109307E-2</v>
       </c>
       <c r="AO82" s="34">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>2.6556836941645196E-2</v>
       </c>
       <c r="AP82" s="34">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>2.6585799405461893E-2</v>
       </c>
       <c r="AQ82" s="23">
@@ -23724,19 +24325,19 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="AM85" s="34">
-        <f t="shared" ref="AM85:AP85" si="92">((1+$AR85)^(AM80/365)-1)*365/AM80</f>
+        <f t="shared" ref="AM85:AP85" si="94">((1+$AR85)^(AM80/365)-1)*365/AM80</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="AN85" s="34">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="AO85" s="34">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="AP85" s="34">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="AQ85" s="23">
@@ -23860,19 +24461,19 @@
         <v>3.0407596890108839E-2</v>
       </c>
       <c r="C87" s="34">
-        <f t="shared" ref="C87:F87" si="93">C88*365/C86</f>
+        <f t="shared" ref="C87:F87" si="95">C88*365/C86</f>
         <v>3.0416463127971544E-2</v>
       </c>
       <c r="D87" s="34">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>3.0436741760606328E-2</v>
       </c>
       <c r="E87" s="34">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>3.0474812798236512E-2</v>
       </c>
       <c r="F87" s="34">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>3.0512947329474491E-2</v>
       </c>
       <c r="G87" s="16"/>
@@ -23883,19 +24484,19 @@
         <v>2.9907349030706052E-2</v>
       </c>
       <c r="L87" s="34">
-        <f t="shared" ref="L87:O87" si="94">L88*365/L86</f>
+        <f t="shared" ref="L87:O87" si="96">L88*365/L86</f>
         <v>2.9915925943969159E-2</v>
       </c>
       <c r="M87" s="34">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>2.9935542634702439E-2</v>
       </c>
       <c r="N87" s="34">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>2.9972370170845902E-2</v>
       </c>
       <c r="O87" s="34">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>3.0009258115333635E-2</v>
       </c>
       <c r="P87" s="10"/>
@@ -24014,19 +24615,19 @@
         <v>2.9207008934516918E-2</v>
       </c>
       <c r="U88" s="34">
-        <f t="shared" ref="U88:X88" si="95">((1+$Z88)^(U86/365)-1)*365/U86</f>
+        <f t="shared" ref="U88:X88" si="97">((1+$Z88)^(U86/365)-1)*365/U86</f>
         <v>2.9215188859992698E-2</v>
       </c>
       <c r="V88" s="34">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>2.9233897304799861E-2</v>
       </c>
       <c r="W88" s="34">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>2.9269018705551892E-2</v>
       </c>
       <c r="X88" s="34">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>2.9304196365779224E-2</v>
       </c>
       <c r="Y88" s="23">
@@ -24044,19 +24645,19 @@
         <v>3.0907848860827362E-2</v>
       </c>
       <c r="AD88" s="34">
-        <f t="shared" ref="AD88:AG88" si="96">((1+$AI88)^(AD86/365)-1)*365/AD86</f>
+        <f t="shared" ref="AD88:AG88" si="98">((1+$AI88)^(AD86/365)-1)*365/AD86</f>
         <v>3.0917009225003924E-2</v>
       </c>
       <c r="AE88" s="34">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>3.0937960795912711E-2</v>
       </c>
       <c r="AF88" s="34">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>3.0977296032276263E-2</v>
       </c>
       <c r="AG88" s="34">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>3.1016697950943278E-2</v>
       </c>
       <c r="AH88" s="23">
@@ -24228,7 +24829,7 @@
         <v>3.1E-2</v>
       </c>
       <c r="AI90" s="34">
-        <f t="shared" ref="AI90:AI95" si="97">(1+AH90/365)^365-1</f>
+        <f t="shared" ref="AI90:AI95" si="99">(1+AH90/365)^365-1</f>
         <v>3.1484146077251696E-2</v>
       </c>
       <c r="AK90" s="15"/>
@@ -24281,19 +24882,19 @@
         <v>2.8506676896215315E-2</v>
       </c>
       <c r="AM91" s="34">
-        <f t="shared" ref="AM91:AP91" si="98">((1+$AR91)^(AM89/365)-1)*365/AM89</f>
+        <f t="shared" ref="AM91:AP91" si="100">((1+$AR91)^(AM89/365)-1)*365/AM89</f>
         <v>2.8514469244696868E-2</v>
       </c>
       <c r="AN91" s="34">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>2.8532290993570169E-2</v>
       </c>
       <c r="AO91" s="34">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>2.8565746813953425E-2</v>
       </c>
       <c r="AP91" s="34">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>2.8599254939608972E-2</v>
       </c>
       <c r="AQ91" s="23">
@@ -24311,19 +24912,19 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="C92" s="34">
-        <f t="shared" ref="C92:F92" si="99">C93*365/C86</f>
+        <f t="shared" ref="C92:F92" si="101">C93*365/C86</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="D92" s="34">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="E92" s="34">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="F92" s="34">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="G92" s="16"/>
@@ -24334,19 +24935,19 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="L92" s="34">
-        <f t="shared" ref="L92:O92" si="100">L93*365/L86</f>
+        <f t="shared" ref="L92:O92" si="102">L93*365/L86</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="M92" s="34">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="N92" s="34">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="O92" s="34">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="P92" s="10"/>
@@ -24462,19 +25063,19 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="U93" s="34">
-        <f t="shared" ref="U93:X93" si="101">((1+$Z93)^(U86/365)-1)*365/U86</f>
+        <f t="shared" ref="U93:X93" si="103">((1+$Z93)^(U86/365)-1)*365/U86</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="V93" s="34">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="W93" s="34">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="X93" s="34">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="Y93" s="23">
@@ -24492,26 +25093,26 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="AD93" s="34">
-        <f t="shared" ref="AD93:AG93" si="102">((1+$AI93)^(AD86/365)-1)*365/AD86</f>
+        <f t="shared" ref="AD93:AG93" si="104">((1+$AI93)^(AD86/365)-1)*365/AD86</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="AE93" s="34">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="AF93" s="34">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="AG93" s="34">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="AH93" s="23">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="AI93" s="34">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>2.5314242726610869E-2</v>
       </c>
       <c r="AK93" s="15"/>
@@ -24582,19 +25183,19 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="AM94" s="34">
-        <f t="shared" ref="AM94:AP94" si="103">((1+$AR94)^(AM89/365)-1)*365/AM89</f>
+        <f t="shared" ref="AM94:AP94" si="105">((1+$AR94)^(AM89/365)-1)*365/AM89</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="AN94" s="34">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="AO94" s="34">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="AP94" s="34">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="AQ94" s="23">
@@ -24715,7 +25316,7 @@
         <v>3.1800000000000002E-2</v>
       </c>
       <c r="AI95" s="34">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>3.230959251755694E-2</v>
       </c>
       <c r="AK95" s="15"/>
@@ -24862,19 +25463,19 @@
         <v>3.1708260565512791E-2</v>
       </c>
       <c r="C98" s="34">
-        <f t="shared" ref="C98:F98" si="104">C99*365/C97</f>
+        <f t="shared" ref="C98:F98" si="106">C99*365/C97</f>
         <v>3.1717901519644563E-2</v>
       </c>
       <c r="D98" s="34">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>3.1739952665787552E-2</v>
       </c>
       <c r="E98" s="34">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>3.1781353676550363E-2</v>
       </c>
       <c r="F98" s="34">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>3.1822826690937146E-2</v>
       </c>
       <c r="G98" s="16"/>
@@ -24885,19 +25486,19 @@
         <v>3.2108470364739912E-2</v>
       </c>
       <c r="L98" s="34">
-        <f t="shared" ref="L98:O98" si="105">L99*365/L97</f>
+        <f t="shared" ref="L98:O98" si="107">L99*365/L97</f>
         <v>3.2118356223753065E-2</v>
       </c>
       <c r="M98" s="34">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>3.2140967715421409E-2</v>
       </c>
       <c r="N98" s="34">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>3.2183421488258611E-2</v>
       </c>
       <c r="O98" s="34">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>3.2225950028510517E-2</v>
       </c>
       <c r="P98" s="10"/>
@@ -25012,19 +25613,19 @@
         <v>2.8806818211650764E-2</v>
       </c>
       <c r="U99" s="34">
-        <f t="shared" ref="U99:X99" si="106">((1+$Z99)^(U97/365)-1)*365/U97</f>
+        <f t="shared" ref="U99:X99" si="108">((1+$Z99)^(U97/365)-1)*365/U97</f>
         <v>2.8814775512232469E-2</v>
       </c>
       <c r="V99" s="34">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>2.8832974634983022E-2</v>
       </c>
       <c r="W99" s="34">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>2.8867139310035983E-2</v>
       </c>
       <c r="X99" s="34">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>2.8901357961484207E-2</v>
       </c>
       <c r="Y99" s="23">
@@ -25042,19 +25643,19 @@
         <v>3.1007899748336825E-2</v>
       </c>
       <c r="AD99" s="34">
-        <f t="shared" ref="AD99:AG99" si="107">((1+$AI99)^(AD97/365)-1)*365/AD97</f>
+        <f t="shared" ref="AD99:AG99" si="109">((1+$AI99)^(AD97/365)-1)*365/AD97</f>
         <v>3.1017119513989746E-2</v>
       </c>
       <c r="AE99" s="34">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>3.103820699217404E-2</v>
       </c>
       <c r="AF99" s="34">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>3.1077797552172309E-2</v>
       </c>
       <c r="AG99" s="34">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>3.1117455444773193E-2</v>
       </c>
       <c r="AH99" s="23">
@@ -25151,7 +25752,7 @@
         <v>3.3300000000000003E-2</v>
       </c>
       <c r="Z100" s="34">
-        <f t="shared" ref="Z100:Z104" si="108">(1+$Y100/365)^365-1</f>
+        <f t="shared" ref="Z100:Z104" si="110">(1+$Y100/365)^365-1</f>
         <v>3.3859080551566834E-2</v>
       </c>
       <c r="AB100" s="15" t="s">
@@ -25187,19 +25788,19 @@
         <v>2.7206081631976988E-2</v>
       </c>
       <c r="AM100" s="34">
-        <f t="shared" ref="AM100:AP100" si="109">((1+$AR100)^(AM98/365)-1)*365/AM98</f>
+        <f t="shared" ref="AM100:AP100" si="111">((1+$AR100)^(AM98/365)-1)*365/AM98</f>
         <v>2.721317916094455E-2</v>
       </c>
       <c r="AN100" s="34">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>2.7229411356470796E-2</v>
       </c>
       <c r="AO100" s="34">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>2.7259881528093017E-2</v>
       </c>
       <c r="AP100" s="34">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>2.7290397161898836E-2</v>
       </c>
       <c r="AQ100" s="23">
@@ -25217,19 +25818,19 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="C101" s="34">
-        <f t="shared" ref="C101:F101" si="110">C102*365/C97</f>
+        <f t="shared" ref="C101:F101" si="112">C102*365/C97</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="D101" s="34">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="E101" s="34">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="F101" s="34">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="G101" s="16"/>
@@ -25240,19 +25841,19 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="L101" s="34">
-        <f t="shared" ref="L101:O101" si="111">L102*365/L97</f>
+        <f t="shared" ref="L101:O101" si="113">L102*365/L97</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="M101" s="34">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="N101" s="34">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="O101" s="34">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="P101" s="10"/>
@@ -25373,26 +25974,26 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="U102" s="34">
-        <f t="shared" ref="U102:X102" si="112">((1+$Z102)^(U97/365)-1)*365/U97</f>
+        <f t="shared" ref="U102:X102" si="114">((1+$Z102)^(U97/365)-1)*365/U97</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="V102" s="34">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="W102" s="34">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="X102" s="34">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="Y102" s="23">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="Z102" s="34">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>2.5314242726610869E-2</v>
       </c>
       <c r="AB102" s="15" t="s">
@@ -25403,19 +26004,19 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="AD102" s="34">
-        <f t="shared" ref="AD102:AG102" si="113">((1+$AI102)^(AD97/365)-1)*365/AD97</f>
+        <f t="shared" ref="AD102:AG102" si="115">((1+$AI102)^(AD97/365)-1)*365/AD97</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="AE102" s="34">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="AF102" s="34">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="AG102" s="34">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="AH102" s="23">
@@ -25493,19 +26094,19 @@
         <v>2.5005137572765568E-2</v>
       </c>
       <c r="AM103" s="34">
-        <f t="shared" ref="AM103:AP103" si="114">((1+$AR103)^(AM98/365)-1)*365/AM98</f>
+        <f t="shared" ref="AM103:AP103" si="116">((1+$AR103)^(AM98/365)-1)*365/AM98</f>
         <v>2.5011133186924366E-2</v>
       </c>
       <c r="AN103" s="34">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>2.5024844646748073E-2</v>
       </c>
       <c r="AO103" s="34">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>2.5050580654265259E-2</v>
       </c>
       <c r="AP103" s="34">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>2.5076351951623117E-2</v>
       </c>
       <c r="AQ103" s="23">
@@ -25598,7 +26199,7 @@
         <v>2.9899999999999999E-2</v>
       </c>
       <c r="Z104" s="34">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>3.0350231880070799E-2</v>
       </c>
       <c r="AB104" s="15" t="s">
@@ -25822,6 +26423,350 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64930BE0-5361-4236-B759-D5C263D71056}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46128</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.03</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>4.2900000000000001E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>6.4899999999999999E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR55</f>
+        <v>2.52E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z55</f>
+        <v>1.2600000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="57">
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f>((1+I5)^(C2/365)-1)*365/C2</f>
+        <v>2.751347152523961E-2</v>
+      </c>
+      <c r="D5" s="57">
+        <v>5.4800000000000001E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f>((1+$I5)^(E2/365)-1)*365/E2</f>
+        <v>2.7561210701938343E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" ref="F5:G5" si="2">((1+$I5)^(F2/365)-1)*365/F2</f>
+        <v>2.7592404443735931E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.7686268375885618E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.75E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>2.7880550318131858E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ55</f>
+        <v>2.07E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="55">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f>((1+I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="55">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f>((1+$I6)^(E2/365)-1)*365/E2</f>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" ref="F6:G6" si="3">((1+$I6)^(F2/365)-1)*365/F2</f>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="55">
+        <v>0.02</v>
+      </c>
+      <c r="C7" s="52">
+        <f>((1+I7)^(C2/365)-1)*365/C2</f>
+        <v>1.9106497976434694E-2</v>
+      </c>
+      <c r="D7" s="55">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f>((1+$I7)^(E2/365)-1)*365/E2</f>
+        <v>1.9129514495355309E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" ref="F7:G7" si="4">((1+$I7)^(F2/365)-1)*365/F2</f>
+        <v>1.9144545184274515E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>1.9189731793765021E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>1.9099999999999999E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>1.9283062519709127E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-0.91%</f>
+        <v>9.9999999999999985E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.7406171402247135E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.7413373714052343E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7429845619310389E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7460766020571663E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7491732895357952E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7584913147389555E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>2.7777775131269555E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H55</f>
+        <v>1.9300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -29960,6 +30905,30 @@
       <c r="DC13" s="17" t="s">
         <v>58</v>
       </c>
+      <c r="DE13" s="25">
+        <v>46128</v>
+      </c>
+      <c r="DF13" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="DG13" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="DH13" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="DI13" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="DJ13" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="DK13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="DL13" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="14" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
@@ -30329,6 +31298,37 @@
         <f>'Günlük taslak'!AR73</f>
         <v>2.6853259490220882E-2</v>
       </c>
+      <c r="DE14" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="DF14" s="34">
+        <f>'Günlük taslak'!AU64</f>
+        <v>2.7406171402247135E-2</v>
+      </c>
+      <c r="DG14" s="34">
+        <f>'Günlük taslak'!AV64</f>
+        <v>2.7413373714052343E-2</v>
+      </c>
+      <c r="DH14" s="34">
+        <f>'Günlük taslak'!AW64</f>
+        <v>2.7429845619310389E-2</v>
+      </c>
+      <c r="DI14" s="34">
+        <f>'Günlük taslak'!AX64</f>
+        <v>2.7460766020571663E-2</v>
+      </c>
+      <c r="DJ14" s="34">
+        <f>'Günlük taslak'!AY64</f>
+        <v>2.7491732895357952E-2</v>
+      </c>
+      <c r="DK14" s="23">
+        <f>'Günlük taslak'!AZ64</f>
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="DL14" s="34">
+        <f>'Günlük taslak'!BA64</f>
+        <v>2.7777775131269555E-2</v>
+      </c>
     </row>
     <row r="15" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
@@ -30673,6 +31673,37 @@
         <f>'Günlük taslak'!AR74</f>
         <v>3.3445657100777071E-2</v>
       </c>
+      <c r="DE15" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="DF15" s="23">
+        <f>'Günlük taslak'!AU65</f>
+        <v>0.03</v>
+      </c>
+      <c r="DG15" s="23">
+        <f>'Günlük taslak'!AV65</f>
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="DH15" s="23">
+        <f>'Günlük taslak'!AW65</f>
+        <v>4.2900000000000001E-2</v>
+      </c>
+      <c r="DI15" s="23">
+        <f>'Günlük taslak'!AX65</f>
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="DJ15" s="23">
+        <f>'Günlük taslak'!AY65</f>
+        <v>6.4899999999999999E-2</v>
+      </c>
+      <c r="DK15" s="23">
+        <f>'Günlük taslak'!AZ65</f>
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="DL15" s="34">
+        <f>'Günlük taslak'!BA65</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
     </row>
     <row r="16" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
@@ -31042,8 +32073,39 @@
         <f>'Günlük taslak'!AR76</f>
         <v>2.5314242726610869E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:107" x14ac:dyDescent="0.35">
+      <c r="DE16" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="DF16" s="34">
+        <f>'Günlük taslak'!AU67</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="DG16" s="34">
+        <f>'Günlük taslak'!AV67</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="DH16" s="34">
+        <f>'Günlük taslak'!AW67</f>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="DI16" s="34">
+        <f>'Günlük taslak'!AX67</f>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="DJ16" s="34">
+        <f>'Günlük taslak'!AY67</f>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="DK16" s="23">
+        <f>'Günlük taslak'!AZ67</f>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="DL16" s="34">
+        <f>'Günlük taslak'!BA67</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
         <v>17</v>
       </c>
@@ -31401,8 +32463,39 @@
         <f>'Günlük taslak'!AR78</f>
         <v>2.7366776854136576E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:107" x14ac:dyDescent="0.35">
+      <c r="DE17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="DF17" s="23">
+        <f>'Günlük taslak'!AU69</f>
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="DG17" s="34">
+        <f>'Günlük taslak'!AV69</f>
+        <v>2.751347152523961E-2</v>
+      </c>
+      <c r="DH17" s="23">
+        <f>'Günlük taslak'!AW69</f>
+        <v>5.4800000000000001E-2</v>
+      </c>
+      <c r="DI17" s="34">
+        <f>'Günlük taslak'!AX69</f>
+        <v>2.7561210701938343E-2</v>
+      </c>
+      <c r="DJ17" s="34">
+        <f>'Günlük taslak'!AY69</f>
+        <v>2.7592404443735931E-2</v>
+      </c>
+      <c r="DK17" s="23">
+        <f>'Günlük taslak'!AZ69</f>
+        <v>2.75E-2</v>
+      </c>
+      <c r="DL17" s="34">
+        <f>'Günlük taslak'!BA69</f>
+        <v>2.7880550318131858E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:116" x14ac:dyDescent="0.35">
       <c r="J18" s="26"/>
       <c r="K18" s="24"/>
       <c r="L18" s="24"/>
@@ -31476,7 +32569,7 @@
       <c r="CJ18" s="24"/>
       <c r="CK18" s="24"/>
     </row>
-    <row r="19" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A19" s="25">
         <v>46080</v>
       </c>
@@ -31766,7 +32859,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
         <v>12</v>
       </c>
@@ -32135,7 +33228,7 @@
         <v>2.6853259490220882E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A21" s="15" t="s">
         <v>59</v>
       </c>
@@ -32479,7 +33572,7 @@
         <v>3.3445657100777071E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A22" s="15" t="s">
         <v>15</v>
       </c>
@@ -32848,7 +33941,7 @@
         <v>2.5314242726610869E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:116" x14ac:dyDescent="0.35">
       <c r="A23" s="15" t="s">
         <v>17</v>
       </c>
@@ -33207,7 +34300,7 @@
         <v>2.7469511054885043E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:116" x14ac:dyDescent="0.35">
       <c r="J24" s="26"/>
       <c r="K24" s="24"/>
       <c r="L24" s="24"/>
@@ -33233,7 +34326,7 @@
       <c r="BR24" s="24"/>
       <c r="BS24" s="24"/>
     </row>
-    <row r="25" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:116" x14ac:dyDescent="0.35">
       <c r="J25" s="44"/>
       <c r="K25" s="45"/>
       <c r="L25" s="45"/>
@@ -33243,7 +34336,7 @@
       <c r="P25" s="45"/>
       <c r="Q25" s="45"/>
     </row>
-    <row r="26" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:116" x14ac:dyDescent="0.35">
       <c r="B26" s="47"/>
       <c r="J26" s="26"/>
       <c r="K26" s="24"/>
@@ -33254,7 +34347,7 @@
       <c r="P26" s="24"/>
       <c r="Q26" s="24"/>
     </row>
-    <row r="27" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:116" x14ac:dyDescent="0.35">
       <c r="B27" s="47"/>
       <c r="J27" s="26"/>
       <c r="K27" s="24"/>
@@ -33265,7 +34358,7 @@
       <c r="P27" s="24"/>
       <c r="Q27" s="24"/>
     </row>
-    <row r="28" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:116" x14ac:dyDescent="0.35">
       <c r="J28" s="26"/>
       <c r="K28" s="24"/>
       <c r="L28" s="24"/>
@@ -33275,7 +34368,7 @@
       <c r="P28" s="24"/>
       <c r="Q28" s="24"/>
     </row>
-    <row r="29" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:116" x14ac:dyDescent="0.35">
       <c r="J29" s="26"/>
       <c r="K29" s="24"/>
       <c r="L29" s="24"/>
@@ -33372,7 +34465,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1323899-2C0B-4B24-87C6-64610CA5A78F}">
-  <dimension ref="A1:BS86"/>
+  <dimension ref="A1:BS1048576"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -34067,7 +35160,7 @@
         <v>0.03</v>
       </c>
       <c r="AI5" s="13">
-        <f t="shared" ref="AI5:AI54" si="1">AH5-Z5</f>
+        <f t="shared" ref="AI5:AI55" si="1">AH5-Z5</f>
         <v>1.8700000000000001E-2</v>
       </c>
       <c r="AK5" s="4">
@@ -34113,7 +35206,7 @@
         <v>3.44E-2</v>
       </c>
       <c r="BA5" s="13">
-        <f t="shared" ref="BA5:BA54" si="2">AZ5-AR5</f>
+        <f t="shared" ref="BA5:BA55" si="2">AZ5-AR5</f>
         <v>2.8400000000000002E-2</v>
       </c>
       <c r="BC5" s="4">
@@ -34151,7 +35244,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS54" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS55" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -41425,7 +42518,7 @@
         <v>3.1E-2</v>
       </c>
       <c r="Q44" s="60">
-        <f t="shared" ref="Q44:Q54" si="4">P44-H44</f>
+        <f t="shared" ref="Q44:Q55" si="4">P44-H44</f>
         <v>2.2499999999999999E-2</v>
       </c>
       <c r="S44" s="4">
@@ -43134,7 +44227,7 @@
       <c r="P53" s="58">
         <v>2.8500000000000001E-2</v>
       </c>
-      <c r="Q53" s="11">
+      <c r="Q53" s="90">
         <f t="shared" si="4"/>
         <v>1.9900000000000001E-2</v>
       </c>
@@ -43324,7 +44417,7 @@
       <c r="P54" s="58">
         <v>2.7199999999999998E-2</v>
       </c>
-      <c r="Q54" s="11">
+      <c r="Q54" s="90">
         <f t="shared" si="4"/>
         <v>1.9299999999999998E-2</v>
       </c>
@@ -43487,7 +44580,9 @@
       <c r="G55" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H55" s="9"/>
+      <c r="H55" s="9">
+        <v>8.0999999999999996E-3</v>
+      </c>
       <c r="I55" s="2">
         <v>46128</v>
       </c>
@@ -43509,8 +44604,13 @@
       <c r="O55" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P55" s="58"/>
-      <c r="Q55" s="11"/>
+      <c r="P55" s="58">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="Q55" s="90">
+        <f t="shared" si="4"/>
+        <v>1.9300000000000001E-2</v>
+      </c>
       <c r="S55" s="4">
         <v>46128</v>
       </c>
@@ -43526,11 +44626,15 @@
       <c r="W55" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X55" s="6"/>
+      <c r="X55" s="6">
+        <v>0.03</v>
+      </c>
       <c r="Y55" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z55" s="6"/>
+      <c r="Z55" s="6">
+        <v>1.24E-2</v>
+      </c>
       <c r="AA55" s="2">
         <v>46128</v>
       </c>
@@ -43552,50 +44656,97 @@
       <c r="AG55" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH55" s="58"/>
-      <c r="AI55" s="13"/>
+      <c r="AH55" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI55" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2600000000000002E-2</v>
+      </c>
       <c r="AK55" s="4">
         <v>46128</v>
       </c>
-      <c r="AL55" s="3"/>
+      <c r="AL55" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
-      <c r="AP55" s="3"/>
-      <c r="AQ55" s="6"/>
-      <c r="AR55" s="6"/>
+      <c r="AP55" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ55" s="6">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AR55" s="6">
+        <v>7.7000000000000002E-3</v>
+      </c>
       <c r="AS55" s="2">
         <v>46128</v>
       </c>
-      <c r="AT55" s="14"/>
-      <c r="AU55" s="14"/>
-      <c r="AV55" s="14"/>
-      <c r="AW55" s="14"/>
-      <c r="AX55" s="14"/>
-      <c r="AY55" s="14"/>
-      <c r="AZ55" s="14"/>
-      <c r="BA55" s="13"/>
+      <c r="AT55" s="14">
+        <v>0.03</v>
+      </c>
+      <c r="AU55" s="14">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="AV55" s="14">
+        <v>4.2900000000000001E-2</v>
+      </c>
+      <c r="AW55" s="14">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="AX55" s="14">
+        <v>6.4899999999999999E-2</v>
+      </c>
+      <c r="AY55" s="14">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="AZ55" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA55" s="13">
+        <f t="shared" si="2"/>
+        <v>2.52E-2</v>
+      </c>
       <c r="BC55" s="4">
         <v>46128</v>
       </c>
-      <c r="BD55" s="6"/>
-      <c r="BE55" s="6"/>
-      <c r="BF55" s="6"/>
+      <c r="BD55" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE55" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF55" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG55" s="3"/>
       <c r="BH55" s="3"/>
       <c r="BI55" s="3"/>
-      <c r="BJ55" s="6"/>
+      <c r="BJ55" s="6">
+        <v>6.7999999999999996E-3</v>
+      </c>
       <c r="BK55" s="2">
         <v>46128</v>
       </c>
-      <c r="BL55" s="58"/>
+      <c r="BL55" s="58">
+        <v>3.5700000000000003E-2</v>
+      </c>
       <c r="BM55" s="1"/>
-      <c r="BN55" s="58"/>
+      <c r="BN55" s="58">
+        <v>5.4800000000000001E-2</v>
+      </c>
       <c r="BO55" s="1"/>
       <c r="BP55" s="1"/>
       <c r="BQ55" s="1"/>
-      <c r="BR55" s="58"/>
-      <c r="BS55" s="13"/>
+      <c r="BR55" s="58">
+        <v>2.75E-2</v>
+      </c>
+      <c r="BS55" s="13">
+        <f t="shared" si="3"/>
+        <v>2.07E-2</v>
+      </c>
     </row>
     <row r="56" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A56" s="4">
@@ -47688,6 +48839,9 @@
       <c r="BQ86" s="1"/>
       <c r="BR86" s="58"/>
       <c r="BS86" s="13"/>
+    </row>
+    <row r="1048576" spans="42:42" x14ac:dyDescent="0.35">
+      <c r="AP1048576" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -48055,7 +49209,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -48418,7 +49572,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48779,7 +49933,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -49137,7 +50291,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4C1FA9-A796-4209-A2BC-8E5419C0C3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124F8ABE-A55F-46BD-AB97-4B0778941775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="1830" windowWidth="29040" windowHeight="15720" firstSheet="24" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -44,6 +44,9 @@
     <sheet name="15.04.2026" sheetId="49" r:id="rId29"/>
     <sheet name="16.04.2026" sheetId="51" r:id="rId30"/>
     <sheet name="17.04.2026" sheetId="52" r:id="rId31"/>
+    <sheet name="18.04.2026" sheetId="53" r:id="rId32"/>
+    <sheet name="19.04.2026" sheetId="54" r:id="rId33"/>
+    <sheet name="20.04.2026" sheetId="55" r:id="rId34"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -952,6 +955,80 @@
 </comments>
 </file>
 
+<file path=xl/comments28.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{5C391A5D-4962-4978-9589-1739097B62FA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments29.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{566F298B-D4B6-4A5D-BA8F-0DEF9171ED1E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -959,6 +1036,43 @@
   </authors>
   <commentList>
     <comment ref="H9" authorId="0" shapeId="0" xr:uid="{70DEC24D-99E0-4094-AAC8-40C91A2A2BA4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments30.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{D539A7F4-75E4-4AF4-A969-6EC18F13ABEC}">
       <text>
         <r>
           <rPr>
@@ -1212,7 +1326,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3264" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3300" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -1426,11 +1540,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0000%"/>
     <numFmt numFmtId="165" formatCode="0.000%"/>
     <numFmt numFmtId="166" formatCode="0.00000%"/>
     <numFmt numFmtId="167" formatCode="0.000000%"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -1655,11 +1769,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1893,8 +2008,6 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1910,12 +2023,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="29">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2171,7 +2312,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>487484</xdr:colOff>
+      <xdr:colOff>484309</xdr:colOff>
       <xdr:row>121</xdr:row>
       <xdr:rowOff>20630</xdr:rowOff>
     </xdr:to>
@@ -2499,7 +2640,7 @@
   <cols>
     <col min="1" max="2" width="15.6328125" style="81" customWidth="1"/>
     <col min="3" max="6" width="15.6328125" style="24" customWidth="1"/>
-    <col min="7" max="7" width="11.81640625" customWidth="1"/>
+    <col min="7" max="7" width="11.81640625" style="97" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -2521,7 +2662,7 @@
       <c r="F1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="95" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2532,20 +2673,20 @@
       <c r="B2" s="88">
         <v>4.36E-2</v>
       </c>
-      <c r="C2" s="91">
+      <c r="C2" s="89">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="D2" s="91">
+      <c r="D2" s="89">
         <v>3.85E-2</v>
       </c>
-      <c r="E2" s="91">
+      <c r="E2" s="89">
         <v>4.5400000000000003E-2</v>
       </c>
-      <c r="F2" s="91">
+      <c r="F2" s="89">
         <v>4.4299999999999999E-2</v>
       </c>
-      <c r="G2" s="89">
-        <v>88.727999999999994</v>
+      <c r="G2" s="94">
+        <v>88728</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -2555,20 +2696,20 @@
       <c r="B3" s="88">
         <v>4.4600000000000001E-2</v>
       </c>
-      <c r="C3" s="91">
+      <c r="C3" s="89">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="D3" s="91">
+      <c r="D3" s="89">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="E3" s="91">
+      <c r="E3" s="89">
         <v>4.6199999999999998E-2</v>
       </c>
-      <c r="F3" s="91">
+      <c r="F3" s="89">
         <v>4.36E-2</v>
       </c>
-      <c r="G3" s="89">
-        <v>89.926000000000002</v>
+      <c r="G3" s="94">
+        <v>89926</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -2578,20 +2719,20 @@
       <c r="B4" s="88">
         <v>4.5900000000000003E-2</v>
       </c>
-      <c r="C4" s="91">
+      <c r="C4" s="89">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="D4" s="91">
+      <c r="D4" s="89">
         <v>3.9699999999999999E-2</v>
       </c>
-      <c r="E4" s="91">
+      <c r="E4" s="89">
         <v>4.7199999999999999E-2</v>
       </c>
-      <c r="F4" s="91">
+      <c r="F4" s="89">
         <v>4.2700000000000002E-2</v>
       </c>
-      <c r="G4" s="89">
-        <v>90.593999999999994</v>
+      <c r="G4" s="94">
+        <v>90594</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -2601,20 +2742,20 @@
       <c r="B5" s="88">
         <v>4.5900000000000003E-2</v>
       </c>
-      <c r="C5" s="91">
+      <c r="C5" s="89">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="D5" s="91">
+      <c r="D5" s="89">
         <v>3.9600000000000003E-2</v>
       </c>
-      <c r="E5" s="91">
+      <c r="E5" s="89">
         <v>4.7800000000000002E-2</v>
       </c>
-      <c r="F5" s="91">
+      <c r="F5" s="89">
         <v>4.0399999999999998E-2</v>
       </c>
-      <c r="G5" s="89">
-        <v>91.373000000000005</v>
+      <c r="G5" s="94">
+        <v>91373</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -2624,20 +2765,20 @@
       <c r="B6" s="88">
         <v>4.6199999999999998E-2</v>
       </c>
-      <c r="C6" s="91">
+      <c r="C6" s="89">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="D6" s="91">
+      <c r="D6" s="89">
         <v>3.95E-2</v>
       </c>
-      <c r="E6" s="91">
+      <c r="E6" s="89">
         <v>4.7899999999999998E-2</v>
       </c>
-      <c r="F6" s="91">
+      <c r="F6" s="89">
         <v>4.8899999999999999E-2</v>
       </c>
-      <c r="G6" s="89">
-        <v>93.927000000000007</v>
+      <c r="G6" s="94">
+        <v>93927</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -2647,20 +2788,20 @@
       <c r="B7" s="88">
         <v>4.58E-2</v>
       </c>
-      <c r="C7" s="91">
+      <c r="C7" s="89">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="D7" s="91">
+      <c r="D7" s="89">
         <v>3.9699999999999999E-2</v>
       </c>
-      <c r="E7" s="91">
+      <c r="E7" s="89">
         <v>4.7E-2</v>
       </c>
-      <c r="F7" s="91">
+      <c r="F7" s="89">
         <v>5.0299999999999997E-2</v>
       </c>
-      <c r="G7" s="89">
-        <v>93.667000000000002</v>
+      <c r="G7" s="94">
+        <v>93667</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -2670,20 +2811,20 @@
       <c r="B8" s="88">
         <v>4.5600000000000002E-2</v>
       </c>
-      <c r="C8" s="91">
+      <c r="C8" s="89">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="D8" s="91">
+      <c r="D8" s="89">
         <v>3.9800000000000002E-2</v>
       </c>
-      <c r="E8" s="91">
+      <c r="E8" s="89">
         <v>4.7500000000000001E-2</v>
       </c>
-      <c r="F8" s="91">
+      <c r="F8" s="89">
         <v>5.1400000000000001E-2</v>
       </c>
-      <c r="G8" s="89">
-        <v>91.257000000000005</v>
+      <c r="G8" s="94">
+        <v>91257</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -2693,20 +2834,20 @@
       <c r="B9" s="88">
         <v>4.6100000000000002E-2</v>
       </c>
-      <c r="C9" s="91">
+      <c r="C9" s="89">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="D9" s="91">
+      <c r="D9" s="89">
         <v>3.8399999999999997E-2</v>
       </c>
-      <c r="E9" s="91">
+      <c r="E9" s="89">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="F9" s="91">
+      <c r="F9" s="89">
         <v>5.0599999999999999E-2</v>
       </c>
-      <c r="G9" s="89">
-        <v>90.983999999999995</v>
+      <c r="G9" s="94">
+        <v>90984</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -2716,20 +2857,20 @@
       <c r="B10" s="88">
         <v>4.6100000000000002E-2</v>
       </c>
-      <c r="C10" s="91">
+      <c r="C10" s="89">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="D10" s="91">
+      <c r="D10" s="89">
         <v>3.73E-2</v>
       </c>
-      <c r="E10" s="91">
+      <c r="E10" s="89">
         <v>4.8599999999999997E-2</v>
       </c>
-      <c r="F10" s="91">
+      <c r="F10" s="89">
         <v>5.1700000000000003E-2</v>
       </c>
-      <c r="G10" s="89">
-        <v>90.504999999999995</v>
+      <c r="G10" s="94">
+        <v>90505</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -2739,20 +2880,20 @@
       <c r="B11" s="88">
         <v>4.65E-2</v>
       </c>
-      <c r="C11" s="91">
+      <c r="C11" s="89">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="D11" s="91">
+      <c r="D11" s="89">
         <v>3.7100000000000001E-2</v>
       </c>
-      <c r="E11" s="91">
+      <c r="E11" s="89">
         <v>4.7500000000000001E-2</v>
       </c>
-      <c r="F11" s="91">
+      <c r="F11" s="89">
         <v>5.1799999999999999E-2</v>
       </c>
-      <c r="G11" s="89">
-        <v>90.441999999999993</v>
+      <c r="G11" s="94">
+        <v>90442</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -2762,20 +2903,20 @@
       <c r="B12" s="88">
         <v>4.6600000000000003E-2</v>
       </c>
-      <c r="C12" s="91">
+      <c r="C12" s="89">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="D12" s="91">
+      <c r="D12" s="89">
         <v>3.73E-2</v>
       </c>
-      <c r="E12" s="91">
+      <c r="E12" s="89">
         <v>4.8099999999999997E-2</v>
       </c>
-      <c r="F12" s="91">
+      <c r="F12" s="89">
         <v>5.21E-2</v>
       </c>
-      <c r="G12" s="89">
-        <v>90.819000000000003</v>
+      <c r="G12" s="94">
+        <v>90819</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -2785,20 +2926,20 @@
       <c r="B13" s="88">
         <v>4.7100000000000003E-2</v>
       </c>
-      <c r="C13" s="91">
+      <c r="C13" s="89">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="D13" s="91">
+      <c r="D13" s="89">
         <v>3.8300000000000001E-2</v>
       </c>
-      <c r="E13" s="91">
+      <c r="E13" s="89">
         <v>4.8899999999999999E-2</v>
       </c>
-      <c r="F13" s="91">
+      <c r="F13" s="89">
         <v>5.2200000000000003E-2</v>
       </c>
-      <c r="G13" s="89">
-        <v>91.135000000000005</v>
+      <c r="G13" s="94">
+        <v>91135</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -2808,20 +2949,20 @@
       <c r="B14" s="88">
         <v>4.6600000000000003E-2</v>
       </c>
-      <c r="C14" s="91">
+      <c r="C14" s="89">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="D14" s="91">
+      <c r="D14" s="89">
         <v>3.8699999999999998E-2</v>
       </c>
-      <c r="E14" s="91">
+      <c r="E14" s="89">
         <v>4.9200000000000001E-2</v>
       </c>
-      <c r="F14" s="91">
+      <c r="F14" s="89">
         <v>5.0799999999999998E-2</v>
       </c>
-      <c r="G14" s="89">
-        <v>95.26</v>
+      <c r="G14" s="94">
+        <v>95260</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -2831,20 +2972,20 @@
       <c r="B15" s="88">
         <v>4.9399999999999999E-2</v>
       </c>
-      <c r="C15" s="91">
+      <c r="C15" s="89">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="D15" s="91">
+      <c r="D15" s="89">
         <v>4.2500000000000003E-2</v>
       </c>
-      <c r="E15" s="91">
+      <c r="E15" s="89">
         <v>5.0200000000000002E-2</v>
       </c>
-      <c r="F15" s="91">
+      <c r="F15" s="89">
         <v>4.7399999999999998E-2</v>
       </c>
-      <c r="G15" s="89">
-        <v>97.007999999999996</v>
+      <c r="G15" s="94">
+        <v>97008</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -2854,20 +2995,20 @@
       <c r="B16" s="88">
         <v>4.99E-2</v>
       </c>
-      <c r="C16" s="91">
+      <c r="C16" s="89">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="D16" s="91">
+      <c r="D16" s="89">
         <v>4.3900000000000002E-2</v>
       </c>
-      <c r="E16" s="91">
+      <c r="E16" s="89">
         <v>5.11E-2</v>
       </c>
-      <c r="F16" s="91">
+      <c r="F16" s="89">
         <v>5.3800000000000001E-2</v>
       </c>
-      <c r="G16" s="89">
-        <v>95.584999999999994</v>
+      <c r="G16" s="94">
+        <v>95585</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -2877,20 +3018,20 @@
       <c r="B17" s="88">
         <v>4.9299999999999997E-2</v>
       </c>
-      <c r="C17" s="91">
+      <c r="C17" s="89">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D17" s="91">
+      <c r="D17" s="89">
         <v>5.3699999999999998E-2</v>
       </c>
-      <c r="E17" s="91">
+      <c r="E17" s="89">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="F17" s="91">
+      <c r="F17" s="89">
         <v>5.8799999999999998E-2</v>
       </c>
-      <c r="G17" s="89">
-        <v>95.516000000000005</v>
+      <c r="G17" s="94">
+        <v>95516</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -2900,20 +3041,20 @@
       <c r="B18" s="88">
         <v>4.7199999999999999E-2</v>
       </c>
-      <c r="C18" s="91">
+      <c r="C18" s="89">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D18" s="91">
+      <c r="D18" s="89">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="E18" s="91">
+      <c r="E18" s="89">
         <v>4.8899999999999999E-2</v>
       </c>
-      <c r="F18" s="91">
+      <c r="F18" s="89">
         <v>5.7299999999999997E-2</v>
       </c>
-      <c r="G18" s="89">
-        <v>95.1</v>
+      <c r="G18" s="94">
+        <v>95100</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -2923,20 +3064,20 @@
       <c r="B19" s="88">
         <v>4.5699999999999998E-2</v>
       </c>
-      <c r="C19" s="91">
+      <c r="C19" s="89">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D19" s="91">
+      <c r="D19" s="89">
         <v>5.0799999999999998E-2</v>
       </c>
-      <c r="E19" s="91">
+      <c r="E19" s="89">
         <v>4.8300000000000003E-2</v>
       </c>
-      <c r="F19" s="91">
+      <c r="F19" s="89">
         <v>5.6099999999999997E-2</v>
       </c>
-      <c r="G19" s="89">
-        <v>93.753</v>
+      <c r="G19" s="94">
+        <v>93753</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -2946,20 +3087,20 @@
       <c r="B20" s="88">
         <v>4.53E-2</v>
       </c>
-      <c r="C20" s="91">
+      <c r="C20" s="89">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D20" s="91">
+      <c r="D20" s="89">
         <v>4.9700000000000001E-2</v>
       </c>
-      <c r="E20" s="91">
+      <c r="E20" s="89">
         <v>4.7199999999999999E-2</v>
       </c>
-      <c r="F20" s="91">
+      <c r="F20" s="89">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="G20" s="89">
-        <v>92.558000000000007</v>
+      <c r="G20" s="94">
+        <v>92558</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -2969,20 +3110,20 @@
       <c r="B21" s="88">
         <v>4.4200000000000003E-2</v>
       </c>
-      <c r="C21" s="91">
+      <c r="C21" s="89">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D21" s="91">
+      <c r="D21" s="89">
         <v>4.8599999999999997E-2</v>
       </c>
-      <c r="E21" s="91">
+      <c r="E21" s="89">
         <v>4.6100000000000002E-2</v>
       </c>
-      <c r="F21" s="91">
+      <c r="F21" s="89">
         <v>5.5899999999999998E-2</v>
       </c>
-      <c r="G21" s="89">
-        <v>88.313000000000002</v>
+      <c r="G21" s="94">
+        <v>88313</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -2992,20 +3133,20 @@
       <c r="B22" s="88">
         <v>4.4699999999999997E-2</v>
       </c>
-      <c r="C22" s="91">
+      <c r="C22" s="89">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D22" s="91">
+      <c r="D22" s="89">
         <v>4.9099999999999998E-2</v>
       </c>
-      <c r="E22" s="91">
+      <c r="E22" s="89">
         <v>4.6699999999999998E-2</v>
       </c>
-      <c r="F22" s="91">
+      <c r="F22" s="89">
         <v>5.91E-2</v>
       </c>
-      <c r="G22" s="89">
-        <v>89.353999999999999</v>
+      <c r="G22" s="94">
+        <v>89354</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -3015,20 +3156,20 @@
       <c r="B23" s="88">
         <v>4.41E-2</v>
       </c>
-      <c r="C23" s="91">
+      <c r="C23" s="89">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D23" s="91">
+      <c r="D23" s="89">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="E23" s="91">
+      <c r="E23" s="89">
         <v>4.6600000000000003E-2</v>
       </c>
-      <c r="F23" s="91">
+      <c r="F23" s="89">
         <v>5.8099999999999999E-2</v>
       </c>
-      <c r="G23" s="89">
-        <v>89.442999999999998</v>
+      <c r="G23" s="94">
+        <v>89443</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -3038,20 +3179,20 @@
       <c r="B24" s="88">
         <v>4.4299999999999999E-2</v>
       </c>
-      <c r="C24" s="91">
+      <c r="C24" s="89">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D24" s="91">
+      <c r="D24" s="89">
         <v>4.8399999999999999E-2</v>
       </c>
-      <c r="E24" s="91">
+      <c r="E24" s="89">
         <v>4.6100000000000002E-2</v>
       </c>
-      <c r="F24" s="91">
+      <c r="F24" s="89">
         <v>5.8299999999999998E-2</v>
       </c>
-      <c r="G24" s="89">
-        <v>89.412000000000006</v>
+      <c r="G24" s="94">
+        <v>89412</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -3061,20 +3202,20 @@
       <c r="B25" s="88">
         <v>4.5400000000000003E-2</v>
       </c>
-      <c r="C25" s="91">
+      <c r="C25" s="89">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D25" s="91">
+      <c r="D25" s="89">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="E25" s="91">
+      <c r="E25" s="89">
         <v>4.7100000000000003E-2</v>
       </c>
-      <c r="F25" s="91">
+      <c r="F25" s="89">
         <v>5.7200000000000001E-2</v>
       </c>
-      <c r="G25" s="89">
-        <v>89.171000000000006</v>
+      <c r="G25" s="94">
+        <v>89171</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -3084,20 +3225,20 @@
       <c r="B26" s="88">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="C26" s="91">
+      <c r="C26" s="89">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D26" s="91">
+      <c r="D26" s="89">
         <v>5.0500000000000003E-2</v>
       </c>
-      <c r="E26" s="91">
+      <c r="E26" s="89">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="F26" s="91">
+      <c r="F26" s="89">
         <v>5.6800000000000003E-2</v>
       </c>
-      <c r="G26" s="89">
-        <v>86.548000000000002</v>
+      <c r="G26" s="94">
+        <v>86548</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -3107,20 +3248,20 @@
       <c r="B27" s="88">
         <v>4.58E-2</v>
       </c>
-      <c r="C27" s="91">
+      <c r="C27" s="89">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D27" s="91">
+      <c r="D27" s="89">
         <v>5.0299999999999997E-2</v>
       </c>
-      <c r="E27" s="91">
+      <c r="E27" s="89">
         <v>4.7699999999999999E-2</v>
       </c>
-      <c r="F27" s="91">
+      <c r="F27" s="89">
         <v>5.7700000000000001E-2</v>
       </c>
-      <c r="G27" s="89">
-        <v>88.308000000000007</v>
+      <c r="G27" s="94">
+        <v>88308</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -3130,20 +3271,20 @@
       <c r="B28" s="88">
         <v>4.65E-2</v>
       </c>
-      <c r="C28" s="91">
+      <c r="C28" s="89">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D28" s="91">
+      <c r="D28" s="89">
         <v>5.0900000000000001E-2</v>
       </c>
-      <c r="E28" s="91">
+      <c r="E28" s="89">
         <v>4.8399999999999999E-2</v>
       </c>
-      <c r="F28" s="91">
+      <c r="F28" s="89">
         <v>5.0500000000000003E-2</v>
       </c>
-      <c r="G28" s="89">
-        <v>89.203999999999994</v>
+      <c r="G28" s="94">
+        <v>89204</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -3153,20 +3294,20 @@
       <c r="B29" s="88">
         <v>4.7E-2</v>
       </c>
-      <c r="C29" s="91">
+      <c r="C29" s="89">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D29" s="91">
+      <c r="D29" s="89">
         <v>5.0900000000000001E-2</v>
       </c>
-      <c r="E29" s="91">
+      <c r="E29" s="89">
         <v>4.8399999999999999E-2</v>
       </c>
-      <c r="F29" s="91">
+      <c r="F29" s="89">
         <v>5.5399999999999998E-2</v>
       </c>
-      <c r="G29" s="89">
-        <v>89.162000000000006</v>
+      <c r="G29" s="94">
+        <v>89162</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -3176,20 +3317,20 @@
       <c r="B30" s="88">
         <v>4.8099999999999997E-2</v>
       </c>
-      <c r="C30" s="91">
+      <c r="C30" s="89">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D30" s="91">
+      <c r="D30" s="89">
         <v>5.21E-2</v>
       </c>
-      <c r="E30" s="91">
+      <c r="E30" s="89">
         <v>4.99E-2</v>
       </c>
-      <c r="F30" s="91">
+      <c r="F30" s="89">
         <v>5.5399999999999998E-2</v>
       </c>
-      <c r="G30" s="89">
-        <v>84.57</v>
+      <c r="G30" s="94">
+        <v>84570</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
@@ -3199,20 +3340,20 @@
       <c r="B31" s="88">
         <v>4.6699999999999998E-2</v>
       </c>
-      <c r="C31" s="91">
+      <c r="C31" s="89">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D31" s="91">
+      <c r="D31" s="89">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="E31" s="91">
+      <c r="E31" s="89">
         <v>4.8800000000000003E-2</v>
       </c>
-      <c r="F31" s="91">
+      <c r="F31" s="89">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="G31" s="89">
-        <v>84.141999999999996</v>
+      <c r="G31" s="94">
+        <v>84142</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
@@ -3222,20 +3363,20 @@
       <c r="B32" s="88">
         <v>4.4699999999999997E-2</v>
       </c>
-      <c r="C32" s="91">
+      <c r="C32" s="89">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D32" s="91">
+      <c r="D32" s="89">
         <v>4.8899999999999999E-2</v>
       </c>
-      <c r="E32" s="91">
+      <c r="E32" s="89">
         <v>4.65E-2</v>
       </c>
-      <c r="F32" s="91">
+      <c r="F32" s="89">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="G32" s="89">
-        <v>78.725999999999999</v>
+      <c r="G32" s="94">
+        <v>78726</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -3257,8 +3398,8 @@
       <c r="F33" s="23">
         <v>5.0500000000000003E-2</v>
       </c>
-      <c r="G33" s="89">
-        <v>76.936999999999998</v>
+      <c r="G33" s="94">
+        <v>76937</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -3280,8 +3421,8 @@
       <c r="F34" s="23">
         <v>5.0799999999999998E-2</v>
       </c>
-      <c r="G34" s="89">
-        <v>78.768000000000001</v>
+      <c r="G34" s="94">
+        <v>78768</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
@@ -3303,8 +3444,8 @@
       <c r="F35" s="23">
         <v>4.9799999999999997E-2</v>
       </c>
-      <c r="G35" s="89">
-        <v>75.638999999999996</v>
+      <c r="G35" s="94">
+        <v>75639</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -3326,8 +3467,8 @@
       <c r="F36" s="23">
         <v>4.7899999999999998E-2</v>
       </c>
-      <c r="G36" s="89">
-        <v>73.171999999999997</v>
+      <c r="G36" s="94">
+        <v>73172</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
@@ -3349,8 +3490,8 @@
       <c r="F37" s="23">
         <v>4.7500000000000001E-2</v>
       </c>
-      <c r="G37" s="89">
-        <v>62.853999999999999</v>
+      <c r="G37" s="94">
+        <v>62854</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
@@ -3372,8 +3513,8 @@
       <c r="F38" s="23">
         <v>4.24E-2</v>
       </c>
-      <c r="G38" s="89">
-        <v>70.524000000000001</v>
+      <c r="G38" s="94">
+        <v>70524</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
@@ -3395,8 +3536,8 @@
       <c r="F39" s="23">
         <v>4.5699999999999998E-2</v>
       </c>
-      <c r="G39" s="89">
-        <v>69.296999999999997</v>
+      <c r="G39" s="94">
+        <v>69297</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
@@ -3418,8 +3559,8 @@
       <c r="F40" s="23">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="G40" s="89">
-        <v>70.542000000000002</v>
+      <c r="G40" s="94">
+        <v>70542</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
@@ -3441,8 +3582,8 @@
       <c r="F41" s="23">
         <v>4.4200000000000003E-2</v>
       </c>
-      <c r="G41" s="89">
-        <v>70.096000000000004</v>
+      <c r="G41" s="94">
+        <v>70096</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
@@ -3464,8 +3605,8 @@
       <c r="F42" s="23">
         <v>4.0300000000000002E-2</v>
       </c>
-      <c r="G42" s="89">
-        <v>68.78</v>
+      <c r="G42" s="94">
+        <v>68780</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
@@ -3487,8 +3628,8 @@
       <c r="F43" s="23">
         <v>4.0899999999999999E-2</v>
       </c>
-      <c r="G43" s="89">
-        <v>66.938000000000002</v>
+      <c r="G43" s="94">
+        <v>66938</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
@@ -3510,8 +3651,8 @@
       <c r="F44" s="23">
         <v>4.07E-2</v>
       </c>
-      <c r="G44" s="89">
-        <v>66.185000000000002</v>
+      <c r="G44" s="94">
+        <v>66185</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
@@ -3533,8 +3674,8 @@
       <c r="F45" s="23">
         <v>4.0800000000000003E-2</v>
       </c>
-      <c r="G45" s="89">
-        <v>68.838999999999999</v>
+      <c r="G45" s="94">
+        <v>68839</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
@@ -3556,8 +3697,8 @@
       <c r="F46" s="23">
         <v>4.0899999999999999E-2</v>
       </c>
-      <c r="G46" s="89">
-        <v>69.766000000000005</v>
+      <c r="G46" s="94">
+        <v>69766</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
@@ -3579,8 +3720,8 @@
       <c r="F47" s="23">
         <v>4.07E-2</v>
       </c>
-      <c r="G47" s="89">
-        <v>68.716999999999999</v>
+      <c r="G47" s="94">
+        <v>68717</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
@@ -3602,8 +3743,8 @@
       <c r="F48" s="23">
         <v>4.0899999999999999E-2</v>
       </c>
-      <c r="G48" s="89">
-        <v>68.908000000000001</v>
+      <c r="G48" s="94">
+        <v>68908</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
@@ -3625,8 +3766,8 @@
       <c r="F49" s="23">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="G49" s="89">
-        <v>67.489000000000004</v>
+      <c r="G49" s="94">
+        <v>67489</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
@@ -3648,8 +3789,8 @@
       <c r="F50" s="23">
         <v>4.1200000000000001E-2</v>
       </c>
-      <c r="G50" s="89">
-        <v>66.456000000000003</v>
+      <c r="G50" s="94">
+        <v>66456</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
@@ -3671,8 +3812,8 @@
       <c r="F51" s="23">
         <v>4.1700000000000001E-2</v>
       </c>
-      <c r="G51" s="89">
-        <v>66.918999999999997</v>
+      <c r="G51" s="94">
+        <v>66919</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
@@ -3694,8 +3835,8 @@
       <c r="F52" s="23">
         <v>4.2500000000000003E-2</v>
       </c>
-      <c r="G52" s="89">
-        <v>67.97</v>
+      <c r="G52" s="94">
+        <v>67970</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
@@ -3717,8 +3858,8 @@
       <c r="F53" s="23">
         <v>4.2700000000000002E-2</v>
       </c>
-      <c r="G53" s="89">
-        <v>67.977999999999994</v>
+      <c r="G53" s="94">
+        <v>67978</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
@@ -3740,8 +3881,8 @@
       <c r="F54" s="23">
         <v>3.7199999999999997E-2</v>
       </c>
-      <c r="G54" s="89">
-        <v>67.584999999999994</v>
+      <c r="G54" s="94">
+        <v>67585</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
@@ -3763,8 +3904,8 @@
       <c r="F55" s="23">
         <v>3.6700000000000003E-2</v>
       </c>
-      <c r="G55" s="89">
-        <v>64.578000000000003</v>
+      <c r="G55" s="94">
+        <v>64578</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
@@ -3786,8 +3927,8 @@
       <c r="F56" s="23">
         <v>3.6900000000000002E-2</v>
       </c>
-      <c r="G56" s="89">
-        <v>64.073999999999998</v>
+      <c r="G56" s="94">
+        <v>64074</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
@@ -3809,8 +3950,8 @@
       <c r="F57" s="23">
         <v>3.6799999999999999E-2</v>
       </c>
-      <c r="G57" s="89">
-        <v>67.947000000000003</v>
+      <c r="G57" s="94">
+        <v>67947</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
@@ -3832,8 +3973,8 @@
       <c r="F58" s="23">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="G58" s="89">
-        <v>67.468999999999994</v>
+      <c r="G58" s="94">
+        <v>67469</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
@@ -3855,8 +3996,8 @@
       <c r="F59" s="23">
         <v>3.61E-2</v>
       </c>
-      <c r="G59" s="89">
-        <v>65.884</v>
+      <c r="G59" s="94">
+        <v>65884</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
@@ -3878,8 +4019,8 @@
       <c r="F60" s="23">
         <v>3.56E-2</v>
       </c>
-      <c r="G60" s="89">
-        <v>67.007999999999996</v>
+      <c r="G60" s="94">
+        <v>67008</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
@@ -3901,8 +4042,8 @@
       <c r="F61" s="23">
         <v>3.56E-2</v>
       </c>
-      <c r="G61" s="89">
-        <v>65.712999999999994</v>
+      <c r="G61" s="94">
+        <v>65713</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
@@ -3924,8 +4065,8 @@
       <c r="F62" s="23">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="G62" s="89">
-        <v>68.864000000000004</v>
+      <c r="G62" s="94">
+        <v>68864</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
@@ -3947,8 +4088,8 @@
       <c r="F63" s="23">
         <v>3.6499999999999998E-2</v>
       </c>
-      <c r="G63" s="89">
-        <v>68.322000000000003</v>
+      <c r="G63" s="94">
+        <v>68322</v>
       </c>
       <c r="H63" s="47"/>
     </row>
@@ -3971,8 +4112,8 @@
       <c r="F64" s="23">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="G64" s="89">
-        <v>72.67</v>
+      <c r="G64" s="94">
+        <v>72670</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
@@ -3994,8 +4135,8 @@
       <c r="F65" s="23">
         <v>3.49E-2</v>
       </c>
-      <c r="G65" s="89">
-        <v>70.875</v>
+      <c r="G65" s="94">
+        <v>70875</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
@@ -4017,8 +4158,8 @@
       <c r="F66" s="23">
         <v>3.85E-2</v>
       </c>
-      <c r="G66" s="89">
-        <v>68.147999999999996</v>
+      <c r="G66" s="94">
+        <v>68148</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
@@ -4040,8 +4181,8 @@
       <c r="F67" s="23">
         <v>3.85E-2</v>
       </c>
-      <c r="G67" s="89">
-        <v>67.271000000000001</v>
+      <c r="G67" s="94">
+        <v>67271</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
@@ -4063,8 +4204,8 @@
       <c r="F68" s="23">
         <v>3.8199999999999998E-2</v>
       </c>
-      <c r="G68" s="89">
-        <v>66.036000000000001</v>
+      <c r="G68" s="94">
+        <v>66036</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
@@ -4086,8 +4227,8 @@
       <c r="F69" s="23">
         <v>3.8199999999999998E-2</v>
       </c>
-      <c r="G69" s="89">
-        <v>68.459000000000003</v>
+      <c r="G69" s="94">
+        <v>68459</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
@@ -4109,8 +4250,8 @@
       <c r="F70" s="23">
         <v>3.8300000000000001E-2</v>
       </c>
-      <c r="G70" s="89">
-        <v>69.882999999999996</v>
+      <c r="G70" s="94">
+        <v>69883</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
@@ -4132,8 +4273,8 @@
       <c r="F71" s="23">
         <v>3.7400000000000003E-2</v>
       </c>
-      <c r="G71" s="89">
-        <v>70.227000000000004</v>
+      <c r="G71" s="94">
+        <v>70227</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
@@ -4155,8 +4296,8 @@
       <c r="F72" s="23">
         <v>3.73E-2</v>
       </c>
-      <c r="G72" s="89">
-        <v>70.543999999999997</v>
+      <c r="G72" s="94">
+        <v>70544</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
@@ -4178,8 +4319,8 @@
       <c r="F73" s="23">
         <v>3.73E-2</v>
       </c>
-      <c r="G73" s="89">
-        <v>70.965000000000003</v>
+      <c r="G73" s="94">
+        <v>70965</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
@@ -4201,8 +4342,8 @@
       <c r="F74" s="23">
         <v>3.7600000000000001E-2</v>
       </c>
-      <c r="G74" s="89">
-        <v>71.216999999999999</v>
+      <c r="G74" s="94">
+        <v>71217</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
@@ -4224,8 +4365,8 @@
       <c r="F75" s="23">
         <v>3.7900000000000003E-2</v>
       </c>
-      <c r="G75" s="89">
-        <v>72.682000000000002</v>
+      <c r="G75" s="94">
+        <v>72682</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
@@ -4247,8 +4388,8 @@
       <c r="F76" s="23">
         <v>3.8300000000000001E-2</v>
       </c>
-      <c r="G76" s="89">
-        <v>74.858000000000004</v>
+      <c r="G76" s="94">
+        <v>74858</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
@@ -4270,8 +4411,8 @@
       <c r="F77" s="23">
         <v>3.6499999999999998E-2</v>
       </c>
-      <c r="G77" s="89">
-        <v>73.926000000000002</v>
+      <c r="G77" s="94">
+        <v>73926</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
@@ -4293,8 +4434,8 @@
       <c r="F78" s="23">
         <v>3.7400000000000003E-2</v>
       </c>
-      <c r="G78" s="89">
-        <v>71.256</v>
+      <c r="G78" s="94">
+        <v>71256</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
@@ -4316,8 +4457,8 @@
       <c r="F79" s="23">
         <v>3.6799999999999999E-2</v>
       </c>
-      <c r="G79" s="89">
-        <v>69.870999999999995</v>
+      <c r="G79" s="94">
+        <v>69871</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
@@ -4339,8 +4480,8 @@
       <c r="F80" s="23">
         <v>3.7100000000000001E-2</v>
       </c>
-      <c r="G80" s="89">
-        <v>70.552999999999997</v>
+      <c r="G80" s="94">
+        <v>70553</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
@@ -4362,8 +4503,8 @@
       <c r="F81" s="23">
         <v>3.7699999999999997E-2</v>
       </c>
-      <c r="G81" s="89">
-        <v>68.733999999999995</v>
+      <c r="G81" s="94">
+        <v>68734</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
@@ -4385,8 +4526,8 @@
       <c r="F82" s="23">
         <v>3.3500000000000002E-2</v>
       </c>
-      <c r="G82" s="89">
-        <v>67.849000000000004</v>
+      <c r="G82" s="94">
+        <v>67849</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
@@ -4408,8 +4549,8 @@
       <c r="F83" s="23">
         <v>3.3399999999999999E-2</v>
       </c>
-      <c r="G83" s="89">
-        <v>70.893000000000001</v>
+      <c r="G83" s="94">
+        <v>70893</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
@@ -4431,8 +4572,8 @@
       <c r="F84" s="23">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="G84" s="89">
-        <v>70.525000000000006</v>
+      <c r="G84" s="94">
+        <v>70525</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
@@ -4454,8 +4595,8 @@
       <c r="F85" s="23">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="G85" s="89">
-        <v>71.308999999999997</v>
+      <c r="G85" s="94">
+        <v>71309</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
@@ -4477,8 +4618,8 @@
       <c r="F86" s="23">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="G86" s="89">
-        <v>68.790999999999997</v>
+      <c r="G86" s="94">
+        <v>68791</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
@@ -4500,8 +4641,8 @@
       <c r="F87" s="23">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="G87" s="89">
-        <v>66.320999999999998</v>
+      <c r="G87" s="94">
+        <v>66321</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
@@ -4523,8 +4664,8 @@
       <c r="F88" s="23">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="G88" s="89">
-        <v>66.320999999999998</v>
+      <c r="G88" s="94">
+        <v>66321</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
@@ -4546,8 +4687,8 @@
       <c r="F89" s="23">
         <v>3.4799999999999998E-2</v>
       </c>
-      <c r="G89" s="89">
-        <v>65.97</v>
+      <c r="G89" s="94">
+        <v>65970</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
@@ -4569,8 +4710,8 @@
       <c r="F90" s="23">
         <v>3.49E-2</v>
       </c>
-      <c r="G90" s="89">
-        <v>66.698999999999998</v>
+      <c r="G90" s="94">
+        <v>66699</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
@@ -4592,8 +4733,8 @@
       <c r="F91" s="23">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="G91" s="89">
-        <v>68.231999999999999</v>
+      <c r="G91" s="94">
+        <v>68232</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
@@ -4615,8 +4756,8 @@
       <c r="F92" s="23">
         <v>3.6799999999999999E-2</v>
       </c>
-      <c r="G92" s="89">
-        <v>68.088999999999999</v>
+      <c r="G92" s="94">
+        <v>68089</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
@@ -4638,8 +4779,8 @@
       <c r="F93" s="23">
         <v>3.56E-2</v>
       </c>
-      <c r="G93" s="89">
-        <v>66.891999999999996</v>
+      <c r="G93" s="94">
+        <v>66892</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
@@ -4661,8 +4802,8 @@
       <c r="F94" s="23">
         <v>3.6799999999999999E-2</v>
       </c>
-      <c r="G94" s="89">
-        <v>66.94</v>
+      <c r="G94" s="94">
+        <v>66940</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
@@ -4684,8 +4825,8 @@
       <c r="F95" s="23">
         <v>3.7199999999999997E-2</v>
       </c>
-      <c r="G95" s="89">
-        <v>67.304000000000002</v>
+      <c r="G95" s="94">
+        <v>67304</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
@@ -4707,8 +4848,8 @@
       <c r="F96" s="23">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="G96" s="89">
-        <v>68.986000000000004</v>
+      <c r="G96" s="94">
+        <v>68986</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
@@ -4730,8 +4871,8 @@
       <c r="F97" s="23">
         <v>3.5799999999999998E-2</v>
       </c>
-      <c r="G97" s="89">
-        <v>68.864000000000004</v>
+      <c r="G97" s="94">
+        <v>68864</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
@@ -4753,8 +4894,8 @@
       <c r="F98" s="23">
         <v>3.5700000000000003E-2</v>
       </c>
-      <c r="G98" s="89">
-        <v>71.975999999999999</v>
+      <c r="G98" s="94">
+        <v>71976</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
@@ -4776,8 +4917,8 @@
       <c r="F99" s="23">
         <v>3.7400000000000003E-2</v>
       </c>
-      <c r="G99" s="89">
-        <v>71.117000000000004</v>
+      <c r="G99" s="94">
+        <v>71117</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
@@ -4799,8 +4940,8 @@
       <c r="F100" s="23">
         <v>3.9E-2</v>
       </c>
-      <c r="G100" s="89">
-        <v>71.771000000000001</v>
+      <c r="G100" s="94">
+        <v>71771</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
@@ -4822,8 +4963,8 @@
       <c r="F101" s="23">
         <v>3.2899999999999999E-2</v>
       </c>
-      <c r="G101" s="89">
-        <v>72.972999999999999</v>
+      <c r="G101" s="94">
+        <v>72973</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
@@ -4845,8 +4986,8 @@
       <c r="F102" s="23">
         <v>3.27E-2</v>
       </c>
-      <c r="G102" s="89">
-        <v>73.054000000000002</v>
+      <c r="G102" s="94">
+        <v>73054</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
@@ -4868,8 +5009,8 @@
       <c r="F103" s="23">
         <v>3.2599999999999997E-2</v>
       </c>
-      <c r="G103" s="89">
-        <v>70.757000000000005</v>
+      <c r="G103" s="94">
+        <v>70757</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
@@ -4891,8 +5032,8 @@
       <c r="F104" s="23">
         <v>3.1099999999999999E-2</v>
       </c>
-      <c r="G104" s="89">
-        <v>74.515000000000001</v>
+      <c r="G104" s="94">
+        <v>74515</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
@@ -4914,8 +5055,8 @@
       <c r="F105" s="23">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="G105" s="89">
-        <v>74.180999999999997</v>
+      <c r="G105" s="94">
+        <v>74181</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
@@ -4937,8 +5078,8 @@
       <c r="F106" s="23">
         <v>3.2500000000000001E-2</v>
       </c>
-      <c r="G106" s="89">
-        <v>74.834000000000003</v>
+      <c r="G106" s="94">
+        <v>74834</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
@@ -4960,8 +5101,8 @@
       <c r="F107" s="23">
         <v>3.2500000000000001E-2</v>
       </c>
-      <c r="G107" s="89">
-        <v>74.81</v>
+      <c r="G107" s="94">
+        <v>74810</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
@@ -4983,40 +5124,66 @@
       <c r="F108" s="23">
         <v>3.2099999999999997E-2</v>
       </c>
-      <c r="G108" s="89"/>
+      <c r="G108" s="96">
+        <v>77154</v>
+      </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="82">
         <v>46130.125</v>
       </c>
-      <c r="B109" s="82"/>
-      <c r="C109" s="10"/>
-      <c r="D109" s="10"/>
-      <c r="E109" s="10"/>
-      <c r="F109" s="10"/>
-      <c r="G109" s="89"/>
+      <c r="B109" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C109" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D109" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E109" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F109" s="23">
+        <v>3.27E-2</v>
+      </c>
+      <c r="G109" s="96">
+        <v>77072</v>
+      </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="82">
         <v>46131.125</v>
       </c>
-      <c r="B110" s="82"/>
-      <c r="C110" s="10"/>
-      <c r="D110" s="10"/>
-      <c r="E110" s="10"/>
-      <c r="F110" s="10"/>
-      <c r="G110" s="89"/>
+      <c r="B110" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C110" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D110" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E110" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F110" s="23">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="G110" s="96">
+        <v>75691</v>
+      </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="82">
         <v>46132.125</v>
       </c>
-      <c r="B111" s="82"/>
+      <c r="B111" s="83"/>
       <c r="C111" s="10"/>
       <c r="D111" s="10"/>
       <c r="E111" s="10"/>
       <c r="F111" s="10"/>
-      <c r="G111" s="89"/>
+      <c r="G111" s="94"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="82">
@@ -5027,7 +5194,7 @@
       <c r="D112" s="10"/>
       <c r="E112" s="10"/>
       <c r="F112" s="10"/>
-      <c r="G112" s="89"/>
+      <c r="G112" s="94"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="82">
@@ -5038,7 +5205,7 @@
       <c r="D113" s="10"/>
       <c r="E113" s="10"/>
       <c r="F113" s="10"/>
-      <c r="G113" s="89"/>
+      <c r="G113" s="96"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="82">
@@ -5049,7 +5216,7 @@
       <c r="D114" s="10"/>
       <c r="E114" s="10"/>
       <c r="F114" s="10"/>
-      <c r="G114" s="89"/>
+      <c r="G114" s="94"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="82">
@@ -5060,7 +5227,7 @@
       <c r="D115" s="10"/>
       <c r="E115" s="10"/>
       <c r="F115" s="10"/>
-      <c r="G115" s="89"/>
+      <c r="G115" s="94"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="82">
@@ -5071,7 +5238,7 @@
       <c r="D116" s="10"/>
       <c r="E116" s="10"/>
       <c r="F116" s="10"/>
-      <c r="G116" s="89"/>
+      <c r="G116" s="94"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="82">
@@ -5082,7 +5249,7 @@
       <c r="D117" s="10"/>
       <c r="E117" s="10"/>
       <c r="F117" s="10"/>
-      <c r="G117" s="89"/>
+      <c r="G117" s="94"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="82">
@@ -5093,7 +5260,7 @@
       <c r="D118" s="10"/>
       <c r="E118" s="10"/>
       <c r="F118" s="10"/>
-      <c r="G118" s="89"/>
+      <c r="G118" s="94"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="82">
@@ -5104,7 +5271,7 @@
       <c r="D119" s="10"/>
       <c r="E119" s="10"/>
       <c r="F119" s="10"/>
-      <c r="G119" s="89"/>
+      <c r="G119" s="94"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="82">
@@ -5115,7 +5282,7 @@
       <c r="D120" s="10"/>
       <c r="E120" s="10"/>
       <c r="F120" s="10"/>
-      <c r="G120" s="89"/>
+      <c r="G120" s="94"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="82">
@@ -5126,12 +5293,11 @@
       <c r="D121" s="10"/>
       <c r="E121" s="10"/>
       <c r="F121" s="10"/>
-      <c r="G121" s="89"/>
+      <c r="G121" s="94"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="80"/>
       <c r="B122" s="80"/>
-      <c r="G122" s="90"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="80"/>
@@ -5809,7 +5975,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6145,7 +6311,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6483,7 +6649,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6819,7 +6985,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7153,7 +7319,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7489,7 +7655,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7825,7 +7991,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8161,7 +8327,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8497,7 +8663,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8833,7 +8999,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8851,11 +9017,11 @@
       <c r="A1" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="92" t="s">
+      <c r="B1" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="11"/>
@@ -10289,7 +10455,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10625,7 +10791,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10963,7 +11129,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11301,7 +11467,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11639,7 +11805,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12007,7 +12173,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12375,7 +12541,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12743,7 +12909,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13114,7 +13280,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -13495,7 +13661,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -24191,7 +24357,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -24493,6 +24659,1038 @@
       <c r="K8" s="68">
         <f>H8-'Daily Data'!H56</f>
         <v>1.9500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0583F2FA-CC65-4AD3-B78A-2F0172C1B511}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46130</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.03</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.44E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>5.5E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5.8900000000000001E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>5.5E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR57</f>
+        <v>2.5799999999999997E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z57</f>
+        <v>1.2100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="57">
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="C5" s="57">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.791386633517404E-2</v>
+      </c>
+      <c r="D5" s="57">
+        <v>5.4800000000000001E-2</v>
+      </c>
+      <c r="E5" s="57">
+        <f t="shared" si="2"/>
+        <v>2.7963005663145801E-2</v>
+      </c>
+      <c r="F5" s="57">
+        <f t="shared" si="2"/>
+        <v>2.7995115183913229E-2</v>
+      </c>
+      <c r="G5" s="57">
+        <f t="shared" si="2"/>
+        <v>2.8091738995796145E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>2.8291753567093458E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ57</f>
+        <v>1.9800000000000002E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="55">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="55">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="55">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="55">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="55">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="55">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="55">
+        <v>2.0899999999999998E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.0007124849186049E-2</v>
+      </c>
+      <c r="D7" s="55">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.0032363041720885E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.0048845600492471E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.0098401845550402E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>0.02</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.0200781032909898E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.08%</f>
+        <v>9.1999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.750621653395394E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.751347152523961E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7530063944917416E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7561210701938343E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7592404443735931E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7686268375885618E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.75E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>2.7880550318131858E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H57</f>
+        <v>1.95E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F1455F4-1EC2-49DE-97C4-3BE0393A97FE}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46131</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.03</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.44E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>5.5E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5.8900000000000001E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>5.5E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR58</f>
+        <v>2.5799999999999997E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z58</f>
+        <v>1.2100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="57">
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="C5" s="57">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.7613569693030509E-2</v>
+      </c>
+      <c r="D5" s="57">
+        <v>5.4800000000000001E-2</v>
+      </c>
+      <c r="E5" s="57">
+        <f t="shared" si="2"/>
+        <v>2.7661657006941637E-2</v>
+      </c>
+      <c r="F5" s="57">
+        <f t="shared" si="2"/>
+        <v>2.7693078446810349E-2</v>
+      </c>
+      <c r="G5" s="57">
+        <f t="shared" si="2"/>
+        <v>2.7787628574820866E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.76E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>2.7983335754216743E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ58</f>
+        <v>1.9200000000000002E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="55">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="55">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="55">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="55">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="55">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="55">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="55">
+        <v>2.0899999999999998E-2</v>
+      </c>
+      <c r="C7" s="55">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.0007124849186049E-2</v>
+      </c>
+      <c r="D7" s="55">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="E7" s="55">
+        <f t="shared" si="4"/>
+        <v>2.0032363041720885E-2</v>
+      </c>
+      <c r="F7" s="55">
+        <f t="shared" si="4"/>
+        <v>2.0048845600492471E-2</v>
+      </c>
+      <c r="G7" s="55">
+        <f t="shared" si="4"/>
+        <v>2.0098401845550402E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>0.02</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.0200781032909898E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.08%</f>
+        <v>9.1999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.7005992519582658E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.7012986033863436E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7028980278442066E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7059003529465182E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7089071246125033E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7179541931450679E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.7E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>2.7366776854136576E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H58</f>
+        <v>1.9099999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B31185A9-0BD0-4791-8C95-34E7EF9BB056}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46132</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.03</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.44E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>5.5E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5.8900000000000001E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>5.5E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR59</f>
+        <v>2.5700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z59</f>
+        <v>1.1900000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="57">
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.791386633517404E-2</v>
+      </c>
+      <c r="D5" s="57">
+        <v>5.4800000000000001E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.7963005663145801E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.7995115183913229E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8091738995796145E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>2.8291753567093458E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ59</f>
+        <v>1.9700000000000002E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="55">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="55">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="55">
+        <v>2.0899999999999998E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.0007124849186049E-2</v>
+      </c>
+      <c r="D7" s="55">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.0032363041720885E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.0048845600492471E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.0098401845550402E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>0.02</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.0200781032909898E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-0.92%</f>
+        <v>1.0800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.7005992519582658E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.7012986033863436E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7028980278442066E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7059003529465182E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7089071246125033E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7179541931450679E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.7E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>2.7366776854136576E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H59</f>
+        <v>1.9099999999999999E-2</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
@@ -32290,78 +33488,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" x14ac:dyDescent="0.35">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="91" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="94"/>
-      <c r="P1" s="95"/>
-      <c r="S1" s="93" t="s">
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92"/>
+      <c r="P1" s="93"/>
+      <c r="S1" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="94"/>
-      <c r="U1" s="94"/>
-      <c r="V1" s="94"/>
-      <c r="W1" s="94"/>
-      <c r="X1" s="94"/>
-      <c r="Y1" s="94"/>
-      <c r="Z1" s="94"/>
-      <c r="AA1" s="94"/>
-      <c r="AB1" s="94"/>
-      <c r="AC1" s="94"/>
-      <c r="AD1" s="94"/>
-      <c r="AE1" s="94"/>
-      <c r="AF1" s="94"/>
-      <c r="AG1" s="94"/>
-      <c r="AH1" s="95"/>
-      <c r="AK1" s="93" t="s">
+      <c r="T1" s="92"/>
+      <c r="U1" s="92"/>
+      <c r="V1" s="92"/>
+      <c r="W1" s="92"/>
+      <c r="X1" s="92"/>
+      <c r="Y1" s="92"/>
+      <c r="Z1" s="92"/>
+      <c r="AA1" s="92"/>
+      <c r="AB1" s="92"/>
+      <c r="AC1" s="92"/>
+      <c r="AD1" s="92"/>
+      <c r="AE1" s="92"/>
+      <c r="AF1" s="92"/>
+      <c r="AG1" s="92"/>
+      <c r="AH1" s="93"/>
+      <c r="AK1" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="AL1" s="94"/>
-      <c r="AM1" s="94"/>
-      <c r="AN1" s="94"/>
-      <c r="AO1" s="94"/>
-      <c r="AP1" s="94"/>
-      <c r="AQ1" s="94"/>
-      <c r="AR1" s="94"/>
-      <c r="AS1" s="94"/>
-      <c r="AT1" s="94"/>
-      <c r="AU1" s="94"/>
-      <c r="AV1" s="94"/>
-      <c r="AW1" s="94"/>
-      <c r="AX1" s="94"/>
-      <c r="AY1" s="94"/>
-      <c r="AZ1" s="95"/>
-      <c r="BC1" s="93" t="s">
+      <c r="AL1" s="92"/>
+      <c r="AM1" s="92"/>
+      <c r="AN1" s="92"/>
+      <c r="AO1" s="92"/>
+      <c r="AP1" s="92"/>
+      <c r="AQ1" s="92"/>
+      <c r="AR1" s="92"/>
+      <c r="AS1" s="92"/>
+      <c r="AT1" s="92"/>
+      <c r="AU1" s="92"/>
+      <c r="AV1" s="92"/>
+      <c r="AW1" s="92"/>
+      <c r="AX1" s="92"/>
+      <c r="AY1" s="92"/>
+      <c r="AZ1" s="93"/>
+      <c r="BC1" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="BD1" s="94"/>
-      <c r="BE1" s="94"/>
-      <c r="BF1" s="94"/>
-      <c r="BG1" s="94"/>
-      <c r="BH1" s="94"/>
-      <c r="BI1" s="94"/>
-      <c r="BJ1" s="94"/>
-      <c r="BK1" s="94"/>
-      <c r="BL1" s="94"/>
-      <c r="BM1" s="94"/>
-      <c r="BN1" s="94"/>
-      <c r="BO1" s="94"/>
-      <c r="BP1" s="94"/>
-      <c r="BQ1" s="94"/>
-      <c r="BR1" s="95"/>
+      <c r="BD1" s="92"/>
+      <c r="BE1" s="92"/>
+      <c r="BF1" s="92"/>
+      <c r="BG1" s="92"/>
+      <c r="BH1" s="92"/>
+      <c r="BI1" s="92"/>
+      <c r="BJ1" s="92"/>
+      <c r="BK1" s="92"/>
+      <c r="BL1" s="92"/>
+      <c r="BM1" s="92"/>
+      <c r="BN1" s="92"/>
+      <c r="BO1" s="92"/>
+      <c r="BP1" s="92"/>
+      <c r="BQ1" s="92"/>
+      <c r="BR1" s="93"/>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
@@ -32937,7 +34135,7 @@
         <v>0.03</v>
       </c>
       <c r="AI5" s="13">
-        <f t="shared" ref="AI5:AI56" si="1">AH5-Z5</f>
+        <f t="shared" ref="AI5:AI59" si="1">AH5-Z5</f>
         <v>1.8700000000000001E-2</v>
       </c>
       <c r="AK5" s="4">
@@ -32983,7 +34181,7 @@
         <v>3.44E-2</v>
       </c>
       <c r="BA5" s="13">
-        <f t="shared" ref="BA5:BA56" si="2">AZ5-AR5</f>
+        <f t="shared" ref="BA5:BA59" si="2">AZ5-AR5</f>
         <v>2.8400000000000002E-2</v>
       </c>
       <c r="BC5" s="4">
@@ -33021,7 +34219,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS56" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS59" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -40295,7 +41493,7 @@
         <v>3.1E-2</v>
       </c>
       <c r="Q44" s="60">
-        <f t="shared" ref="Q44:Q56" si="4">P44-H44</f>
+        <f t="shared" ref="Q44:Q86" si="4">P44-H44</f>
         <v>2.2499999999999999E-2</v>
       </c>
       <c r="S44" s="4">
@@ -42737,7 +43935,9 @@
       <c r="G57" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H57" s="9"/>
+      <c r="H57" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
       <c r="I57" s="2">
         <v>46130</v>
       </c>
@@ -42759,8 +43959,13 @@
       <c r="O57" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P57" s="58"/>
-      <c r="Q57" s="11"/>
+      <c r="P57" s="58">
+        <v>2.75E-2</v>
+      </c>
+      <c r="Q57" s="86">
+        <f t="shared" si="4"/>
+        <v>1.95E-2</v>
+      </c>
       <c r="S57" s="4">
         <v>46130</v>
       </c>
@@ -42776,11 +43981,15 @@
       <c r="W57" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X57" s="6"/>
+      <c r="X57" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y57" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z57" s="6"/>
+      <c r="Z57" s="6">
+        <v>1.29E-2</v>
+      </c>
       <c r="AA57" s="2">
         <v>46130</v>
       </c>
@@ -42802,50 +44011,97 @@
       <c r="AG57" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH57" s="58"/>
-      <c r="AI57" s="13"/>
+      <c r="AH57" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI57" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2100000000000001E-2</v>
+      </c>
       <c r="AK57" s="4">
         <v>46130</v>
       </c>
-      <c r="AL57" s="3"/>
+      <c r="AL57" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM57" s="3"/>
       <c r="AN57" s="3"/>
       <c r="AO57" s="3"/>
-      <c r="AP57" s="3"/>
-      <c r="AQ57" s="6"/>
-      <c r="AR57" s="6"/>
+      <c r="AP57" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ57" s="6">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AR57" s="6">
+        <v>7.1000000000000004E-3</v>
+      </c>
       <c r="AS57" s="2">
         <v>46130</v>
       </c>
-      <c r="AT57" s="14"/>
-      <c r="AU57" s="14"/>
-      <c r="AV57" s="14"/>
-      <c r="AW57" s="14"/>
-      <c r="AX57" s="14"/>
-      <c r="AY57" s="14"/>
-      <c r="AZ57" s="14"/>
-      <c r="BA57" s="13"/>
+      <c r="AT57" s="14">
+        <v>0.03</v>
+      </c>
+      <c r="AU57" s="14">
+        <v>3.44E-2</v>
+      </c>
+      <c r="AV57" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AW57" s="14">
+        <v>5.5E-2</v>
+      </c>
+      <c r="AX57" s="14">
+        <v>5.8900000000000001E-2</v>
+      </c>
+      <c r="AY57" s="14">
+        <v>5.5E-2</v>
+      </c>
+      <c r="AZ57" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA57" s="13">
+        <f t="shared" si="2"/>
+        <v>2.5799999999999997E-2</v>
+      </c>
       <c r="BC57" s="4">
         <v>46130</v>
       </c>
-      <c r="BD57" s="6"/>
-      <c r="BE57" s="6"/>
-      <c r="BF57" s="6"/>
+      <c r="BD57" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE57" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF57" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG57" s="3"/>
       <c r="BH57" s="3"/>
       <c r="BI57" s="3"/>
-      <c r="BJ57" s="6"/>
+      <c r="BJ57" s="6">
+        <v>8.0999999999999996E-3</v>
+      </c>
       <c r="BK57" s="2">
         <v>46130</v>
       </c>
-      <c r="BL57" s="58"/>
+      <c r="BL57" s="58">
+        <v>3.5700000000000003E-2</v>
+      </c>
       <c r="BM57" s="1"/>
-      <c r="BN57" s="58"/>
+      <c r="BN57" s="58">
+        <v>5.4800000000000001E-2</v>
+      </c>
       <c r="BO57" s="1"/>
       <c r="BP57" s="1"/>
       <c r="BQ57" s="1"/>
-      <c r="BR57" s="58"/>
-      <c r="BS57" s="13"/>
+      <c r="BR57" s="58">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="BS57" s="13">
+        <f t="shared" si="3"/>
+        <v>1.9800000000000002E-2</v>
+      </c>
     </row>
     <row r="58" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A58" s="4">
@@ -42869,7 +44125,9 @@
       <c r="G58" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H58" s="9"/>
+      <c r="H58" s="9">
+        <v>7.9000000000000008E-3</v>
+      </c>
       <c r="I58" s="2">
         <v>46131</v>
       </c>
@@ -42891,8 +44149,13 @@
       <c r="O58" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P58" s="58"/>
-      <c r="Q58" s="11"/>
+      <c r="P58" s="58">
+        <v>2.7E-2</v>
+      </c>
+      <c r="Q58" s="86">
+        <f t="shared" si="4"/>
+        <v>1.9099999999999999E-2</v>
+      </c>
       <c r="S58" s="4">
         <v>46131</v>
       </c>
@@ -42908,11 +44171,15 @@
       <c r="W58" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X58" s="6"/>
+      <c r="X58" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y58" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z58" s="6"/>
+      <c r="Z58" s="6">
+        <v>1.29E-2</v>
+      </c>
       <c r="AA58" s="2">
         <v>46131</v>
       </c>
@@ -42934,50 +44201,97 @@
       <c r="AG58" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH58" s="58"/>
-      <c r="AI58" s="13"/>
+      <c r="AH58" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI58" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2100000000000001E-2</v>
+      </c>
       <c r="AK58" s="4">
         <v>46131</v>
       </c>
-      <c r="AL58" s="3"/>
+      <c r="AL58" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM58" s="3"/>
       <c r="AN58" s="3"/>
       <c r="AO58" s="3"/>
-      <c r="AP58" s="3"/>
-      <c r="AQ58" s="6"/>
-      <c r="AR58" s="6"/>
+      <c r="AP58" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ58" s="6">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AR58" s="6">
+        <v>7.1000000000000004E-3</v>
+      </c>
       <c r="AS58" s="2">
         <v>46131</v>
       </c>
-      <c r="AT58" s="14"/>
-      <c r="AU58" s="14"/>
-      <c r="AV58" s="14"/>
-      <c r="AW58" s="14"/>
-      <c r="AX58" s="14"/>
-      <c r="AY58" s="14"/>
-      <c r="AZ58" s="14"/>
-      <c r="BA58" s="13"/>
+      <c r="AT58" s="14">
+        <v>0.03</v>
+      </c>
+      <c r="AU58" s="14">
+        <v>3.44E-2</v>
+      </c>
+      <c r="AV58" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AW58" s="14">
+        <v>5.5E-2</v>
+      </c>
+      <c r="AX58" s="14">
+        <v>5.8900000000000001E-2</v>
+      </c>
+      <c r="AY58" s="14">
+        <v>5.5E-2</v>
+      </c>
+      <c r="AZ58" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA58" s="13">
+        <f t="shared" si="2"/>
+        <v>2.5799999999999997E-2</v>
+      </c>
       <c r="BC58" s="4">
         <v>46131</v>
       </c>
-      <c r="BD58" s="6"/>
-      <c r="BE58" s="6"/>
-      <c r="BF58" s="6"/>
+      <c r="BD58" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE58" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF58" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG58" s="3"/>
       <c r="BH58" s="3"/>
       <c r="BI58" s="3"/>
-      <c r="BJ58" s="6"/>
+      <c r="BJ58" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
       <c r="BK58" s="2">
         <v>46131</v>
       </c>
-      <c r="BL58" s="58"/>
+      <c r="BL58" s="58">
+        <v>3.5700000000000003E-2</v>
+      </c>
       <c r="BM58" s="1"/>
-      <c r="BN58" s="58"/>
+      <c r="BN58" s="58">
+        <v>5.4800000000000001E-2</v>
+      </c>
       <c r="BO58" s="1"/>
       <c r="BP58" s="1"/>
       <c r="BQ58" s="1"/>
-      <c r="BR58" s="58"/>
-      <c r="BS58" s="13"/>
+      <c r="BR58" s="58">
+        <v>2.76E-2</v>
+      </c>
+      <c r="BS58" s="13">
+        <f t="shared" si="3"/>
+        <v>1.9200000000000002E-2</v>
+      </c>
     </row>
     <row r="59" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A59" s="4">
@@ -43001,7 +44315,9 @@
       <c r="G59" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H59" s="9"/>
+      <c r="H59" s="9">
+        <v>7.9000000000000008E-3</v>
+      </c>
       <c r="I59" s="2">
         <v>46132</v>
       </c>
@@ -43023,8 +44339,13 @@
       <c r="O59" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P59" s="58"/>
-      <c r="Q59" s="11"/>
+      <c r="P59" s="58">
+        <v>2.7E-2</v>
+      </c>
+      <c r="Q59" s="86">
+        <f t="shared" si="4"/>
+        <v>1.9099999999999999E-2</v>
+      </c>
       <c r="S59" s="4">
         <v>46132</v>
       </c>
@@ -43040,11 +44361,15 @@
       <c r="W59" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X59" s="6"/>
+      <c r="X59" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y59" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z59" s="6"/>
+      <c r="Z59" s="6">
+        <v>1.3100000000000001E-2</v>
+      </c>
       <c r="AA59" s="2">
         <v>46132</v>
       </c>
@@ -43066,50 +44391,97 @@
       <c r="AG59" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH59" s="58"/>
-      <c r="AI59" s="13"/>
+      <c r="AH59" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI59" s="13">
+        <f t="shared" si="1"/>
+        <v>1.1900000000000001E-2</v>
+      </c>
       <c r="AK59" s="4">
         <v>46132</v>
       </c>
-      <c r="AL59" s="3"/>
+      <c r="AL59" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM59" s="3"/>
       <c r="AN59" s="3"/>
       <c r="AO59" s="3"/>
-      <c r="AP59" s="3"/>
-      <c r="AQ59" s="6"/>
-      <c r="AR59" s="6"/>
+      <c r="AP59" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ59" s="6">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AR59" s="6">
+        <v>7.1999999999999998E-3</v>
+      </c>
       <c r="AS59" s="2">
         <v>46132</v>
       </c>
-      <c r="AT59" s="14"/>
-      <c r="AU59" s="14"/>
-      <c r="AV59" s="14"/>
-      <c r="AW59" s="14"/>
-      <c r="AX59" s="14"/>
-      <c r="AY59" s="14"/>
-      <c r="AZ59" s="14"/>
-      <c r="BA59" s="13"/>
+      <c r="AT59" s="14">
+        <v>0.03</v>
+      </c>
+      <c r="AU59" s="14">
+        <v>3.44E-2</v>
+      </c>
+      <c r="AV59" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AW59" s="14">
+        <v>5.5E-2</v>
+      </c>
+      <c r="AX59" s="14">
+        <v>5.8900000000000001E-2</v>
+      </c>
+      <c r="AY59" s="14">
+        <v>5.5E-2</v>
+      </c>
+      <c r="AZ59" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA59" s="13">
+        <f t="shared" si="2"/>
+        <v>2.5700000000000001E-2</v>
+      </c>
       <c r="BC59" s="4">
         <v>46132</v>
       </c>
-      <c r="BD59" s="6"/>
-      <c r="BE59" s="6"/>
-      <c r="BF59" s="6"/>
+      <c r="BD59" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE59" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF59" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG59" s="3"/>
       <c r="BH59" s="3"/>
       <c r="BI59" s="3"/>
-      <c r="BJ59" s="6"/>
+      <c r="BJ59" s="6">
+        <v>8.2000000000000007E-3</v>
+      </c>
       <c r="BK59" s="2">
         <v>46132</v>
       </c>
-      <c r="BL59" s="58"/>
+      <c r="BL59" s="58">
+        <v>3.5700000000000003E-2</v>
+      </c>
       <c r="BM59" s="1"/>
-      <c r="BN59" s="58"/>
+      <c r="BN59" s="58">
+        <v>5.4800000000000001E-2</v>
+      </c>
       <c r="BO59" s="1"/>
       <c r="BP59" s="1"/>
       <c r="BQ59" s="1"/>
-      <c r="BR59" s="58"/>
-      <c r="BS59" s="13"/>
+      <c r="BR59" s="58">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="BS59" s="13">
+        <f t="shared" si="3"/>
+        <v>1.9700000000000002E-2</v>
+      </c>
     </row>
     <row r="60" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A60" s="4">
@@ -43156,7 +44528,10 @@
         <v>32</v>
       </c>
       <c r="P60" s="58"/>
-      <c r="Q60" s="11"/>
+      <c r="Q60" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S60" s="4">
         <v>46133</v>
       </c>
@@ -43288,7 +44663,10 @@
         <v>32</v>
       </c>
       <c r="P61" s="58"/>
-      <c r="Q61" s="11"/>
+      <c r="Q61" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S61" s="4">
         <v>46134</v>
       </c>
@@ -43420,7 +44798,10 @@
         <v>32</v>
       </c>
       <c r="P62" s="58"/>
-      <c r="Q62" s="11"/>
+      <c r="Q62" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S62" s="4">
         <v>46135</v>
       </c>
@@ -43552,7 +44933,10 @@
         <v>32</v>
       </c>
       <c r="P63" s="58"/>
-      <c r="Q63" s="11"/>
+      <c r="Q63" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S63" s="4">
         <v>46136</v>
       </c>
@@ -43684,7 +45068,10 @@
         <v>32</v>
       </c>
       <c r="P64" s="58"/>
-      <c r="Q64" s="11"/>
+      <c r="Q64" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S64" s="4">
         <v>46137</v>
       </c>
@@ -43816,7 +45203,10 @@
         <v>32</v>
       </c>
       <c r="P65" s="58"/>
-      <c r="Q65" s="11"/>
+      <c r="Q65" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S65" s="4">
         <v>46138</v>
       </c>
@@ -43948,7 +45338,10 @@
         <v>32</v>
       </c>
       <c r="P66" s="58"/>
-      <c r="Q66" s="11"/>
+      <c r="Q66" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S66" s="4">
         <v>46139</v>
       </c>
@@ -44080,7 +45473,10 @@
         <v>32</v>
       </c>
       <c r="P67" s="58"/>
-      <c r="Q67" s="11"/>
+      <c r="Q67" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S67" s="4">
         <v>46140</v>
       </c>
@@ -44212,7 +45608,10 @@
         <v>32</v>
       </c>
       <c r="P68" s="58"/>
-      <c r="Q68" s="11"/>
+      <c r="Q68" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S68" s="4">
         <v>46141</v>
       </c>
@@ -44344,7 +45743,10 @@
         <v>32</v>
       </c>
       <c r="P69" s="58"/>
-      <c r="Q69" s="11"/>
+      <c r="Q69" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S69" s="4">
         <v>46142</v>
       </c>
@@ -44476,7 +45878,10 @@
         <v>32</v>
       </c>
       <c r="P70" s="58"/>
-      <c r="Q70" s="11"/>
+      <c r="Q70" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S70" s="4">
         <v>46143</v>
       </c>
@@ -44608,7 +46013,10 @@
         <v>32</v>
       </c>
       <c r="P71" s="58"/>
-      <c r="Q71" s="11"/>
+      <c r="Q71" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S71" s="4">
         <v>46144</v>
       </c>
@@ -44740,7 +46148,10 @@
         <v>32</v>
       </c>
       <c r="P72" s="58"/>
-      <c r="Q72" s="11"/>
+      <c r="Q72" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S72" s="4">
         <v>46145</v>
       </c>
@@ -44872,7 +46283,10 @@
         <v>32</v>
       </c>
       <c r="P73" s="58"/>
-      <c r="Q73" s="11"/>
+      <c r="Q73" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S73" s="4">
         <v>46146</v>
       </c>
@@ -45004,7 +46418,10 @@
         <v>32</v>
       </c>
       <c r="P74" s="58"/>
-      <c r="Q74" s="11"/>
+      <c r="Q74" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S74" s="4">
         <v>46147</v>
       </c>
@@ -45136,7 +46553,10 @@
         <v>32</v>
       </c>
       <c r="P75" s="58"/>
-      <c r="Q75" s="11"/>
+      <c r="Q75" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S75" s="4">
         <v>46148</v>
       </c>
@@ -45268,7 +46688,10 @@
         <v>32</v>
       </c>
       <c r="P76" s="58"/>
-      <c r="Q76" s="11"/>
+      <c r="Q76" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S76" s="4">
         <v>46149</v>
       </c>
@@ -45400,7 +46823,10 @@
         <v>32</v>
       </c>
       <c r="P77" s="58"/>
-      <c r="Q77" s="11"/>
+      <c r="Q77" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S77" s="4">
         <v>46150</v>
       </c>
@@ -45532,7 +46958,10 @@
         <v>32</v>
       </c>
       <c r="P78" s="58"/>
-      <c r="Q78" s="11"/>
+      <c r="Q78" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S78" s="4">
         <v>46151</v>
       </c>
@@ -45664,7 +47093,10 @@
         <v>32</v>
       </c>
       <c r="P79" s="58"/>
-      <c r="Q79" s="11"/>
+      <c r="Q79" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S79" s="4">
         <v>46152</v>
       </c>
@@ -45796,7 +47228,10 @@
         <v>32</v>
       </c>
       <c r="P80" s="58"/>
-      <c r="Q80" s="11"/>
+      <c r="Q80" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S80" s="4">
         <v>46153</v>
       </c>
@@ -45928,7 +47363,10 @@
         <v>32</v>
       </c>
       <c r="P81" s="58"/>
-      <c r="Q81" s="11"/>
+      <c r="Q81" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S81" s="4">
         <v>46154</v>
       </c>
@@ -46060,7 +47498,10 @@
         <v>32</v>
       </c>
       <c r="P82" s="58"/>
-      <c r="Q82" s="11"/>
+      <c r="Q82" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S82" s="4">
         <v>46155</v>
       </c>
@@ -46192,7 +47633,10 @@
         <v>32</v>
       </c>
       <c r="P83" s="58"/>
-      <c r="Q83" s="11"/>
+      <c r="Q83" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S83" s="4">
         <v>46156</v>
       </c>
@@ -46324,7 +47768,10 @@
         <v>32</v>
       </c>
       <c r="P84" s="58"/>
-      <c r="Q84" s="11"/>
+      <c r="Q84" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S84" s="4">
         <v>46157</v>
       </c>
@@ -46456,7 +47903,10 @@
         <v>32</v>
       </c>
       <c r="P85" s="58"/>
-      <c r="Q85" s="11"/>
+      <c r="Q85" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S85" s="4">
         <v>46158</v>
       </c>
@@ -46588,7 +48038,10 @@
         <v>32</v>
       </c>
       <c r="P86" s="58"/>
-      <c r="Q86" s="11"/>
+      <c r="Q86" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="S86" s="4">
         <v>46159</v>
       </c>
@@ -47044,7 +48497,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47407,7 +48860,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47768,7 +49221,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48123,7 +49576,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124F8ABE-A55F-46BD-AB97-4B0778941775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58CCF8F5-69C6-4B8B-B45A-F98ADF1A7B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="1830" windowWidth="29040" windowHeight="15720" firstSheet="24" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="25" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -47,6 +47,7 @@
     <sheet name="18.04.2026" sheetId="53" r:id="rId32"/>
     <sheet name="19.04.2026" sheetId="54" r:id="rId33"/>
     <sheet name="20.04.2026" sheetId="55" r:id="rId34"/>
+    <sheet name="21.04.2026" sheetId="56" r:id="rId35"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1103,6 +1104,43 @@
 </comments>
 </file>
 
+<file path=xl/comments31.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{FF35EDB8-9BD3-4133-B21E-26FBB0842709}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1326,7 +1364,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3300" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3312" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -2011,6 +2049,12 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2023,19 +2067,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="30">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2640,7 +2685,7 @@
   <cols>
     <col min="1" max="2" width="15.6328125" style="81" customWidth="1"/>
     <col min="3" max="6" width="15.6328125" style="24" customWidth="1"/>
-    <col min="7" max="7" width="11.81640625" style="97" customWidth="1"/>
+    <col min="7" max="7" width="11.81640625" style="93" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -2662,7 +2707,7 @@
       <c r="F1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="95" t="s">
+      <c r="G1" s="91" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2685,7 +2730,7 @@
       <c r="F2" s="89">
         <v>4.4299999999999999E-2</v>
       </c>
-      <c r="G2" s="94">
+      <c r="G2" s="90">
         <v>88728</v>
       </c>
     </row>
@@ -2708,7 +2753,7 @@
       <c r="F3" s="89">
         <v>4.36E-2</v>
       </c>
-      <c r="G3" s="94">
+      <c r="G3" s="90">
         <v>89926</v>
       </c>
     </row>
@@ -2731,7 +2776,7 @@
       <c r="F4" s="89">
         <v>4.2700000000000002E-2</v>
       </c>
-      <c r="G4" s="94">
+      <c r="G4" s="90">
         <v>90594</v>
       </c>
     </row>
@@ -2754,7 +2799,7 @@
       <c r="F5" s="89">
         <v>4.0399999999999998E-2</v>
       </c>
-      <c r="G5" s="94">
+      <c r="G5" s="90">
         <v>91373</v>
       </c>
     </row>
@@ -2777,7 +2822,7 @@
       <c r="F6" s="89">
         <v>4.8899999999999999E-2</v>
       </c>
-      <c r="G6" s="94">
+      <c r="G6" s="90">
         <v>93927</v>
       </c>
     </row>
@@ -2800,7 +2845,7 @@
       <c r="F7" s="89">
         <v>5.0299999999999997E-2</v>
       </c>
-      <c r="G7" s="94">
+      <c r="G7" s="90">
         <v>93667</v>
       </c>
     </row>
@@ -2823,7 +2868,7 @@
       <c r="F8" s="89">
         <v>5.1400000000000001E-2</v>
       </c>
-      <c r="G8" s="94">
+      <c r="G8" s="90">
         <v>91257</v>
       </c>
     </row>
@@ -2846,7 +2891,7 @@
       <c r="F9" s="89">
         <v>5.0599999999999999E-2</v>
       </c>
-      <c r="G9" s="94">
+      <c r="G9" s="90">
         <v>90984</v>
       </c>
     </row>
@@ -2869,7 +2914,7 @@
       <c r="F10" s="89">
         <v>5.1700000000000003E-2</v>
       </c>
-      <c r="G10" s="94">
+      <c r="G10" s="90">
         <v>90505</v>
       </c>
     </row>
@@ -2892,7 +2937,7 @@
       <c r="F11" s="89">
         <v>5.1799999999999999E-2</v>
       </c>
-      <c r="G11" s="94">
+      <c r="G11" s="90">
         <v>90442</v>
       </c>
     </row>
@@ -2915,7 +2960,7 @@
       <c r="F12" s="89">
         <v>5.21E-2</v>
       </c>
-      <c r="G12" s="94">
+      <c r="G12" s="90">
         <v>90819</v>
       </c>
     </row>
@@ -2938,7 +2983,7 @@
       <c r="F13" s="89">
         <v>5.2200000000000003E-2</v>
       </c>
-      <c r="G13" s="94">
+      <c r="G13" s="90">
         <v>91135</v>
       </c>
     </row>
@@ -2961,7 +3006,7 @@
       <c r="F14" s="89">
         <v>5.0799999999999998E-2</v>
       </c>
-      <c r="G14" s="94">
+      <c r="G14" s="90">
         <v>95260</v>
       </c>
     </row>
@@ -2984,7 +3029,7 @@
       <c r="F15" s="89">
         <v>4.7399999999999998E-2</v>
       </c>
-      <c r="G15" s="94">
+      <c r="G15" s="90">
         <v>97008</v>
       </c>
     </row>
@@ -3007,7 +3052,7 @@
       <c r="F16" s="89">
         <v>5.3800000000000001E-2</v>
       </c>
-      <c r="G16" s="94">
+      <c r="G16" s="90">
         <v>95585</v>
       </c>
     </row>
@@ -3030,7 +3075,7 @@
       <c r="F17" s="89">
         <v>5.8799999999999998E-2</v>
       </c>
-      <c r="G17" s="94">
+      <c r="G17" s="90">
         <v>95516</v>
       </c>
     </row>
@@ -3053,7 +3098,7 @@
       <c r="F18" s="89">
         <v>5.7299999999999997E-2</v>
       </c>
-      <c r="G18" s="94">
+      <c r="G18" s="90">
         <v>95100</v>
       </c>
     </row>
@@ -3076,7 +3121,7 @@
       <c r="F19" s="89">
         <v>5.6099999999999997E-2</v>
       </c>
-      <c r="G19" s="94">
+      <c r="G19" s="90">
         <v>93753</v>
       </c>
     </row>
@@ -3099,7 +3144,7 @@
       <c r="F20" s="89">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="G20" s="94">
+      <c r="G20" s="90">
         <v>92558</v>
       </c>
     </row>
@@ -3122,7 +3167,7 @@
       <c r="F21" s="89">
         <v>5.5899999999999998E-2</v>
       </c>
-      <c r="G21" s="94">
+      <c r="G21" s="90">
         <v>88313</v>
       </c>
     </row>
@@ -3145,7 +3190,7 @@
       <c r="F22" s="89">
         <v>5.91E-2</v>
       </c>
-      <c r="G22" s="94">
+      <c r="G22" s="90">
         <v>89354</v>
       </c>
     </row>
@@ -3168,7 +3213,7 @@
       <c r="F23" s="89">
         <v>5.8099999999999999E-2</v>
       </c>
-      <c r="G23" s="94">
+      <c r="G23" s="90">
         <v>89443</v>
       </c>
     </row>
@@ -3191,7 +3236,7 @@
       <c r="F24" s="89">
         <v>5.8299999999999998E-2</v>
       </c>
-      <c r="G24" s="94">
+      <c r="G24" s="90">
         <v>89412</v>
       </c>
     </row>
@@ -3214,7 +3259,7 @@
       <c r="F25" s="89">
         <v>5.7200000000000001E-2</v>
       </c>
-      <c r="G25" s="94">
+      <c r="G25" s="90">
         <v>89171</v>
       </c>
     </row>
@@ -3237,7 +3282,7 @@
       <c r="F26" s="89">
         <v>5.6800000000000003E-2</v>
       </c>
-      <c r="G26" s="94">
+      <c r="G26" s="90">
         <v>86548</v>
       </c>
     </row>
@@ -3260,7 +3305,7 @@
       <c r="F27" s="89">
         <v>5.7700000000000001E-2</v>
       </c>
-      <c r="G27" s="94">
+      <c r="G27" s="90">
         <v>88308</v>
       </c>
     </row>
@@ -3283,7 +3328,7 @@
       <c r="F28" s="89">
         <v>5.0500000000000003E-2</v>
       </c>
-      <c r="G28" s="94">
+      <c r="G28" s="90">
         <v>89204</v>
       </c>
     </row>
@@ -3306,7 +3351,7 @@
       <c r="F29" s="89">
         <v>5.5399999999999998E-2</v>
       </c>
-      <c r="G29" s="94">
+      <c r="G29" s="90">
         <v>89162</v>
       </c>
     </row>
@@ -3329,7 +3374,7 @@
       <c r="F30" s="89">
         <v>5.5399999999999998E-2</v>
       </c>
-      <c r="G30" s="94">
+      <c r="G30" s="90">
         <v>84570</v>
       </c>
     </row>
@@ -3352,7 +3397,7 @@
       <c r="F31" s="89">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="G31" s="94">
+      <c r="G31" s="90">
         <v>84142</v>
       </c>
     </row>
@@ -3375,7 +3420,7 @@
       <c r="F32" s="89">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="G32" s="94">
+      <c r="G32" s="90">
         <v>78726</v>
       </c>
     </row>
@@ -3398,7 +3443,7 @@
       <c r="F33" s="23">
         <v>5.0500000000000003E-2</v>
       </c>
-      <c r="G33" s="94">
+      <c r="G33" s="90">
         <v>76937</v>
       </c>
     </row>
@@ -3421,7 +3466,7 @@
       <c r="F34" s="23">
         <v>5.0799999999999998E-2</v>
       </c>
-      <c r="G34" s="94">
+      <c r="G34" s="90">
         <v>78768</v>
       </c>
     </row>
@@ -3444,7 +3489,7 @@
       <c r="F35" s="23">
         <v>4.9799999999999997E-2</v>
       </c>
-      <c r="G35" s="94">
+      <c r="G35" s="90">
         <v>75639</v>
       </c>
     </row>
@@ -3467,7 +3512,7 @@
       <c r="F36" s="23">
         <v>4.7899999999999998E-2</v>
       </c>
-      <c r="G36" s="94">
+      <c r="G36" s="90">
         <v>73172</v>
       </c>
     </row>
@@ -3490,7 +3535,7 @@
       <c r="F37" s="23">
         <v>4.7500000000000001E-2</v>
       </c>
-      <c r="G37" s="94">
+      <c r="G37" s="90">
         <v>62854</v>
       </c>
     </row>
@@ -3513,7 +3558,7 @@
       <c r="F38" s="23">
         <v>4.24E-2</v>
       </c>
-      <c r="G38" s="94">
+      <c r="G38" s="90">
         <v>70524</v>
       </c>
     </row>
@@ -3536,7 +3581,7 @@
       <c r="F39" s="23">
         <v>4.5699999999999998E-2</v>
       </c>
-      <c r="G39" s="94">
+      <c r="G39" s="90">
         <v>69297</v>
       </c>
     </row>
@@ -3559,7 +3604,7 @@
       <c r="F40" s="23">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="G40" s="94">
+      <c r="G40" s="90">
         <v>70542</v>
       </c>
     </row>
@@ -3582,7 +3627,7 @@
       <c r="F41" s="23">
         <v>4.4200000000000003E-2</v>
       </c>
-      <c r="G41" s="94">
+      <c r="G41" s="90">
         <v>70096</v>
       </c>
     </row>
@@ -3605,7 +3650,7 @@
       <c r="F42" s="23">
         <v>4.0300000000000002E-2</v>
       </c>
-      <c r="G42" s="94">
+      <c r="G42" s="90">
         <v>68780</v>
       </c>
     </row>
@@ -3628,7 +3673,7 @@
       <c r="F43" s="23">
         <v>4.0899999999999999E-2</v>
       </c>
-      <c r="G43" s="94">
+      <c r="G43" s="90">
         <v>66938</v>
       </c>
     </row>
@@ -3651,7 +3696,7 @@
       <c r="F44" s="23">
         <v>4.07E-2</v>
       </c>
-      <c r="G44" s="94">
+      <c r="G44" s="90">
         <v>66185</v>
       </c>
     </row>
@@ -3674,7 +3719,7 @@
       <c r="F45" s="23">
         <v>4.0800000000000003E-2</v>
       </c>
-      <c r="G45" s="94">
+      <c r="G45" s="90">
         <v>68839</v>
       </c>
     </row>
@@ -3697,7 +3742,7 @@
       <c r="F46" s="23">
         <v>4.0899999999999999E-2</v>
       </c>
-      <c r="G46" s="94">
+      <c r="G46" s="90">
         <v>69766</v>
       </c>
     </row>
@@ -3720,7 +3765,7 @@
       <c r="F47" s="23">
         <v>4.07E-2</v>
       </c>
-      <c r="G47" s="94">
+      <c r="G47" s="90">
         <v>68717</v>
       </c>
     </row>
@@ -3743,7 +3788,7 @@
       <c r="F48" s="23">
         <v>4.0899999999999999E-2</v>
       </c>
-      <c r="G48" s="94">
+      <c r="G48" s="90">
         <v>68908</v>
       </c>
     </row>
@@ -3766,7 +3811,7 @@
       <c r="F49" s="23">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="G49" s="94">
+      <c r="G49" s="90">
         <v>67489</v>
       </c>
     </row>
@@ -3789,7 +3834,7 @@
       <c r="F50" s="23">
         <v>4.1200000000000001E-2</v>
       </c>
-      <c r="G50" s="94">
+      <c r="G50" s="90">
         <v>66456</v>
       </c>
     </row>
@@ -3812,7 +3857,7 @@
       <c r="F51" s="23">
         <v>4.1700000000000001E-2</v>
       </c>
-      <c r="G51" s="94">
+      <c r="G51" s="90">
         <v>66919</v>
       </c>
     </row>
@@ -3835,7 +3880,7 @@
       <c r="F52" s="23">
         <v>4.2500000000000003E-2</v>
       </c>
-      <c r="G52" s="94">
+      <c r="G52" s="90">
         <v>67970</v>
       </c>
     </row>
@@ -3858,7 +3903,7 @@
       <c r="F53" s="23">
         <v>4.2700000000000002E-2</v>
       </c>
-      <c r="G53" s="94">
+      <c r="G53" s="90">
         <v>67978</v>
       </c>
     </row>
@@ -3881,7 +3926,7 @@
       <c r="F54" s="23">
         <v>3.7199999999999997E-2</v>
       </c>
-      <c r="G54" s="94">
+      <c r="G54" s="90">
         <v>67585</v>
       </c>
     </row>
@@ -3904,7 +3949,7 @@
       <c r="F55" s="23">
         <v>3.6700000000000003E-2</v>
       </c>
-      <c r="G55" s="94">
+      <c r="G55" s="90">
         <v>64578</v>
       </c>
     </row>
@@ -3927,7 +3972,7 @@
       <c r="F56" s="23">
         <v>3.6900000000000002E-2</v>
       </c>
-      <c r="G56" s="94">
+      <c r="G56" s="90">
         <v>64074</v>
       </c>
     </row>
@@ -3950,7 +3995,7 @@
       <c r="F57" s="23">
         <v>3.6799999999999999E-2</v>
       </c>
-      <c r="G57" s="94">
+      <c r="G57" s="90">
         <v>67947</v>
       </c>
     </row>
@@ -3973,7 +4018,7 @@
       <c r="F58" s="23">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="G58" s="94">
+      <c r="G58" s="90">
         <v>67469</v>
       </c>
     </row>
@@ -3996,7 +4041,7 @@
       <c r="F59" s="23">
         <v>3.61E-2</v>
       </c>
-      <c r="G59" s="94">
+      <c r="G59" s="90">
         <v>65884</v>
       </c>
     </row>
@@ -4019,7 +4064,7 @@
       <c r="F60" s="23">
         <v>3.56E-2</v>
       </c>
-      <c r="G60" s="94">
+      <c r="G60" s="90">
         <v>67008</v>
       </c>
     </row>
@@ -4042,7 +4087,7 @@
       <c r="F61" s="23">
         <v>3.56E-2</v>
       </c>
-      <c r="G61" s="94">
+      <c r="G61" s="90">
         <v>65713</v>
       </c>
     </row>
@@ -4065,7 +4110,7 @@
       <c r="F62" s="23">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="G62" s="94">
+      <c r="G62" s="90">
         <v>68864</v>
       </c>
     </row>
@@ -4088,7 +4133,7 @@
       <c r="F63" s="23">
         <v>3.6499999999999998E-2</v>
       </c>
-      <c r="G63" s="94">
+      <c r="G63" s="90">
         <v>68322</v>
       </c>
       <c r="H63" s="47"/>
@@ -4112,7 +4157,7 @@
       <c r="F64" s="23">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="G64" s="94">
+      <c r="G64" s="90">
         <v>72670</v>
       </c>
     </row>
@@ -4135,7 +4180,7 @@
       <c r="F65" s="23">
         <v>3.49E-2</v>
       </c>
-      <c r="G65" s="94">
+      <c r="G65" s="90">
         <v>70875</v>
       </c>
     </row>
@@ -4158,7 +4203,7 @@
       <c r="F66" s="23">
         <v>3.85E-2</v>
       </c>
-      <c r="G66" s="94">
+      <c r="G66" s="90">
         <v>68148</v>
       </c>
     </row>
@@ -4181,7 +4226,7 @@
       <c r="F67" s="23">
         <v>3.85E-2</v>
       </c>
-      <c r="G67" s="94">
+      <c r="G67" s="90">
         <v>67271</v>
       </c>
     </row>
@@ -4204,7 +4249,7 @@
       <c r="F68" s="23">
         <v>3.8199999999999998E-2</v>
       </c>
-      <c r="G68" s="94">
+      <c r="G68" s="90">
         <v>66036</v>
       </c>
     </row>
@@ -4227,7 +4272,7 @@
       <c r="F69" s="23">
         <v>3.8199999999999998E-2</v>
       </c>
-      <c r="G69" s="94">
+      <c r="G69" s="90">
         <v>68459</v>
       </c>
     </row>
@@ -4250,7 +4295,7 @@
       <c r="F70" s="23">
         <v>3.8300000000000001E-2</v>
       </c>
-      <c r="G70" s="94">
+      <c r="G70" s="90">
         <v>69883</v>
       </c>
     </row>
@@ -4273,7 +4318,7 @@
       <c r="F71" s="23">
         <v>3.7400000000000003E-2</v>
       </c>
-      <c r="G71" s="94">
+      <c r="G71" s="90">
         <v>70227</v>
       </c>
     </row>
@@ -4296,7 +4341,7 @@
       <c r="F72" s="23">
         <v>3.73E-2</v>
       </c>
-      <c r="G72" s="94">
+      <c r="G72" s="90">
         <v>70544</v>
       </c>
     </row>
@@ -4319,7 +4364,7 @@
       <c r="F73" s="23">
         <v>3.73E-2</v>
       </c>
-      <c r="G73" s="94">
+      <c r="G73" s="90">
         <v>70965</v>
       </c>
     </row>
@@ -4342,7 +4387,7 @@
       <c r="F74" s="23">
         <v>3.7600000000000001E-2</v>
       </c>
-      <c r="G74" s="94">
+      <c r="G74" s="90">
         <v>71217</v>
       </c>
     </row>
@@ -4365,7 +4410,7 @@
       <c r="F75" s="23">
         <v>3.7900000000000003E-2</v>
       </c>
-      <c r="G75" s="94">
+      <c r="G75" s="90">
         <v>72682</v>
       </c>
     </row>
@@ -4388,7 +4433,7 @@
       <c r="F76" s="23">
         <v>3.8300000000000001E-2</v>
       </c>
-      <c r="G76" s="94">
+      <c r="G76" s="90">
         <v>74858</v>
       </c>
     </row>
@@ -4411,7 +4456,7 @@
       <c r="F77" s="23">
         <v>3.6499999999999998E-2</v>
       </c>
-      <c r="G77" s="94">
+      <c r="G77" s="90">
         <v>73926</v>
       </c>
     </row>
@@ -4434,7 +4479,7 @@
       <c r="F78" s="23">
         <v>3.7400000000000003E-2</v>
       </c>
-      <c r="G78" s="94">
+      <c r="G78" s="90">
         <v>71256</v>
       </c>
     </row>
@@ -4457,7 +4502,7 @@
       <c r="F79" s="23">
         <v>3.6799999999999999E-2</v>
       </c>
-      <c r="G79" s="94">
+      <c r="G79" s="90">
         <v>69871</v>
       </c>
     </row>
@@ -4480,7 +4525,7 @@
       <c r="F80" s="23">
         <v>3.7100000000000001E-2</v>
       </c>
-      <c r="G80" s="94">
+      <c r="G80" s="90">
         <v>70553</v>
       </c>
     </row>
@@ -4503,7 +4548,7 @@
       <c r="F81" s="23">
         <v>3.7699999999999997E-2</v>
       </c>
-      <c r="G81" s="94">
+      <c r="G81" s="90">
         <v>68734</v>
       </c>
     </row>
@@ -4526,7 +4571,7 @@
       <c r="F82" s="23">
         <v>3.3500000000000002E-2</v>
       </c>
-      <c r="G82" s="94">
+      <c r="G82" s="90">
         <v>67849</v>
       </c>
     </row>
@@ -4549,7 +4594,7 @@
       <c r="F83" s="23">
         <v>3.3399999999999999E-2</v>
       </c>
-      <c r="G83" s="94">
+      <c r="G83" s="90">
         <v>70893</v>
       </c>
     </row>
@@ -4572,7 +4617,7 @@
       <c r="F84" s="23">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="G84" s="94">
+      <c r="G84" s="90">
         <v>70525</v>
       </c>
     </row>
@@ -4595,7 +4640,7 @@
       <c r="F85" s="23">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="G85" s="94">
+      <c r="G85" s="90">
         <v>71309</v>
       </c>
     </row>
@@ -4618,7 +4663,7 @@
       <c r="F86" s="23">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="G86" s="94">
+      <c r="G86" s="90">
         <v>68791</v>
       </c>
     </row>
@@ -4641,7 +4686,7 @@
       <c r="F87" s="23">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="G87" s="94">
+      <c r="G87" s="90">
         <v>66321</v>
       </c>
     </row>
@@ -4664,7 +4709,7 @@
       <c r="F88" s="23">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="G88" s="94">
+      <c r="G88" s="90">
         <v>66321</v>
       </c>
     </row>
@@ -4687,7 +4732,7 @@
       <c r="F89" s="23">
         <v>3.4799999999999998E-2</v>
       </c>
-      <c r="G89" s="94">
+      <c r="G89" s="90">
         <v>65970</v>
       </c>
     </row>
@@ -4710,7 +4755,7 @@
       <c r="F90" s="23">
         <v>3.49E-2</v>
       </c>
-      <c r="G90" s="94">
+      <c r="G90" s="90">
         <v>66699</v>
       </c>
     </row>
@@ -4733,7 +4778,7 @@
       <c r="F91" s="23">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="G91" s="94">
+      <c r="G91" s="90">
         <v>68232</v>
       </c>
     </row>
@@ -4756,7 +4801,7 @@
       <c r="F92" s="23">
         <v>3.6799999999999999E-2</v>
       </c>
-      <c r="G92" s="94">
+      <c r="G92" s="90">
         <v>68089</v>
       </c>
     </row>
@@ -4779,7 +4824,7 @@
       <c r="F93" s="23">
         <v>3.56E-2</v>
       </c>
-      <c r="G93" s="94">
+      <c r="G93" s="90">
         <v>66892</v>
       </c>
     </row>
@@ -4802,7 +4847,7 @@
       <c r="F94" s="23">
         <v>3.6799999999999999E-2</v>
       </c>
-      <c r="G94" s="94">
+      <c r="G94" s="90">
         <v>66940</v>
       </c>
     </row>
@@ -4825,7 +4870,7 @@
       <c r="F95" s="23">
         <v>3.7199999999999997E-2</v>
       </c>
-      <c r="G95" s="94">
+      <c r="G95" s="90">
         <v>67304</v>
       </c>
     </row>
@@ -4848,7 +4893,7 @@
       <c r="F96" s="23">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="G96" s="94">
+      <c r="G96" s="90">
         <v>68986</v>
       </c>
     </row>
@@ -4871,7 +4916,7 @@
       <c r="F97" s="23">
         <v>3.5799999999999998E-2</v>
       </c>
-      <c r="G97" s="94">
+      <c r="G97" s="90">
         <v>68864</v>
       </c>
     </row>
@@ -4894,7 +4939,7 @@
       <c r="F98" s="23">
         <v>3.5700000000000003E-2</v>
       </c>
-      <c r="G98" s="94">
+      <c r="G98" s="90">
         <v>71976</v>
       </c>
     </row>
@@ -4917,7 +4962,7 @@
       <c r="F99" s="23">
         <v>3.7400000000000003E-2</v>
       </c>
-      <c r="G99" s="94">
+      <c r="G99" s="90">
         <v>71117</v>
       </c>
     </row>
@@ -4940,7 +4985,7 @@
       <c r="F100" s="23">
         <v>3.9E-2</v>
       </c>
-      <c r="G100" s="94">
+      <c r="G100" s="90">
         <v>71771</v>
       </c>
     </row>
@@ -4963,7 +5008,7 @@
       <c r="F101" s="23">
         <v>3.2899999999999999E-2</v>
       </c>
-      <c r="G101" s="94">
+      <c r="G101" s="90">
         <v>72973</v>
       </c>
     </row>
@@ -4986,7 +5031,7 @@
       <c r="F102" s="23">
         <v>3.27E-2</v>
       </c>
-      <c r="G102" s="94">
+      <c r="G102" s="90">
         <v>73054</v>
       </c>
     </row>
@@ -5009,7 +5054,7 @@
       <c r="F103" s="23">
         <v>3.2599999999999997E-2</v>
       </c>
-      <c r="G103" s="94">
+      <c r="G103" s="90">
         <v>70757</v>
       </c>
     </row>
@@ -5032,7 +5077,7 @@
       <c r="F104" s="23">
         <v>3.1099999999999999E-2</v>
       </c>
-      <c r="G104" s="94">
+      <c r="G104" s="90">
         <v>74515</v>
       </c>
     </row>
@@ -5055,7 +5100,7 @@
       <c r="F105" s="23">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="G105" s="94">
+      <c r="G105" s="90">
         <v>74181</v>
       </c>
     </row>
@@ -5078,7 +5123,7 @@
       <c r="F106" s="23">
         <v>3.2500000000000001E-2</v>
       </c>
-      <c r="G106" s="94">
+      <c r="G106" s="90">
         <v>74834</v>
       </c>
     </row>
@@ -5101,7 +5146,7 @@
       <c r="F107" s="23">
         <v>3.2500000000000001E-2</v>
       </c>
-      <c r="G107" s="94">
+      <c r="G107" s="90">
         <v>74810</v>
       </c>
     </row>
@@ -5124,7 +5169,7 @@
       <c r="F108" s="23">
         <v>3.2099999999999997E-2</v>
       </c>
-      <c r="G108" s="96">
+      <c r="G108" s="92">
         <v>77154</v>
       </c>
     </row>
@@ -5147,7 +5192,7 @@
       <c r="F109" s="23">
         <v>3.27E-2</v>
       </c>
-      <c r="G109" s="96">
+      <c r="G109" s="92">
         <v>77072</v>
       </c>
     </row>
@@ -5170,7 +5215,7 @@
       <c r="F110" s="23">
         <v>3.2199999999999999E-2</v>
       </c>
-      <c r="G110" s="96">
+      <c r="G110" s="92">
         <v>75691</v>
       </c>
     </row>
@@ -5178,23 +5223,45 @@
       <c r="A111" s="82">
         <v>46132.125</v>
       </c>
-      <c r="B111" s="83"/>
-      <c r="C111" s="10"/>
-      <c r="D111" s="10"/>
-      <c r="E111" s="10"/>
-      <c r="F111" s="10"/>
-      <c r="G111" s="94"/>
+      <c r="B111" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C111" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D111" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E111" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F111" s="23">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="G111" s="90">
+        <v>75965.25</v>
+      </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="82">
         <v>46133.125</v>
       </c>
-      <c r="B112" s="82"/>
-      <c r="C112" s="10"/>
-      <c r="D112" s="10"/>
-      <c r="E112" s="10"/>
-      <c r="F112" s="10"/>
-      <c r="G112" s="94"/>
+      <c r="B112" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C112" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D112" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E112" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F112" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="G112" s="90"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="82">
@@ -5205,7 +5272,7 @@
       <c r="D113" s="10"/>
       <c r="E113" s="10"/>
       <c r="F113" s="10"/>
-      <c r="G113" s="96"/>
+      <c r="G113" s="92"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="82">
@@ -5216,7 +5283,7 @@
       <c r="D114" s="10"/>
       <c r="E114" s="10"/>
       <c r="F114" s="10"/>
-      <c r="G114" s="94"/>
+      <c r="G114" s="90"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="82">
@@ -5227,7 +5294,7 @@
       <c r="D115" s="10"/>
       <c r="E115" s="10"/>
       <c r="F115" s="10"/>
-      <c r="G115" s="94"/>
+      <c r="G115" s="90"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="82">
@@ -5238,7 +5305,7 @@
       <c r="D116" s="10"/>
       <c r="E116" s="10"/>
       <c r="F116" s="10"/>
-      <c r="G116" s="94"/>
+      <c r="G116" s="90"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="82">
@@ -5249,7 +5316,7 @@
       <c r="D117" s="10"/>
       <c r="E117" s="10"/>
       <c r="F117" s="10"/>
-      <c r="G117" s="94"/>
+      <c r="G117" s="90"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="82">
@@ -5260,7 +5327,7 @@
       <c r="D118" s="10"/>
       <c r="E118" s="10"/>
       <c r="F118" s="10"/>
-      <c r="G118" s="94"/>
+      <c r="G118" s="90"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="82">
@@ -5271,7 +5338,7 @@
       <c r="D119" s="10"/>
       <c r="E119" s="10"/>
       <c r="F119" s="10"/>
-      <c r="G119" s="94"/>
+      <c r="G119" s="90"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="82">
@@ -5282,7 +5349,7 @@
       <c r="D120" s="10"/>
       <c r="E120" s="10"/>
       <c r="F120" s="10"/>
-      <c r="G120" s="94"/>
+      <c r="G120" s="90"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="82">
@@ -5293,7 +5360,7 @@
       <c r="D121" s="10"/>
       <c r="E121" s="10"/>
       <c r="F121" s="10"/>
-      <c r="G121" s="94"/>
+      <c r="G121" s="90"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="80"/>
@@ -5975,7 +6042,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6311,7 +6378,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6649,7 +6716,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6985,7 +7052,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7319,7 +7386,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7655,7 +7722,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7991,7 +8058,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8327,7 +8394,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8663,7 +8730,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8999,7 +9066,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9017,11 +9084,11 @@
       <c r="A1" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="90" t="s">
+      <c r="B1" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="11"/>
@@ -10455,7 +10522,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10791,7 +10858,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11129,7 +11196,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11467,7 +11534,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11805,7 +11872,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12173,7 +12240,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12541,7 +12608,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12909,7 +12976,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13280,7 +13347,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -13661,7 +13728,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -24357,7 +24424,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -24701,7 +24768,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -25045,7 +25112,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -25389,7 +25456,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -25691,6 +25758,338 @@
       <c r="K8" s="68">
         <f>H8-'Daily Data'!H59</f>
         <v>1.9099999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B44002C-376C-42C5-9335-B49848550553}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46133</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.44E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="E3" s="55">
+        <v>5.5E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR60</f>
+        <v>2.5899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z60</f>
+        <v>1.2100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="57"/>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.8013965928817948E-2</v>
+      </c>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8063458462371366E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8095799005777876E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8193119078325148E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>2.8394580009664327E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ60</f>
+        <v>1.9799999999999998E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="55"/>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.1908543050180623E-2</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.1938808003552523E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.1958576046921283E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.201802278059398E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.2140893683114893E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-0.92%</f>
+        <v>1.2699999999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.7406171402247135E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.7413373714052343E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7429845619310389E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7460766020571663E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7491732895357952E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7584913147389555E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>2.7777775131269555E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H60</f>
+        <v>1.9300000000000001E-2</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
@@ -33488,78 +33887,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="93"/>
-      <c r="S1" s="91" t="s">
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="96"/>
+      <c r="P1" s="97"/>
+      <c r="S1" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="92"/>
-      <c r="U1" s="92"/>
-      <c r="V1" s="92"/>
-      <c r="W1" s="92"/>
-      <c r="X1" s="92"/>
-      <c r="Y1" s="92"/>
-      <c r="Z1" s="92"/>
-      <c r="AA1" s="92"/>
-      <c r="AB1" s="92"/>
-      <c r="AC1" s="92"/>
-      <c r="AD1" s="92"/>
-      <c r="AE1" s="92"/>
-      <c r="AF1" s="92"/>
-      <c r="AG1" s="92"/>
-      <c r="AH1" s="93"/>
-      <c r="AK1" s="91" t="s">
+      <c r="T1" s="96"/>
+      <c r="U1" s="96"/>
+      <c r="V1" s="96"/>
+      <c r="W1" s="96"/>
+      <c r="X1" s="96"/>
+      <c r="Y1" s="96"/>
+      <c r="Z1" s="96"/>
+      <c r="AA1" s="96"/>
+      <c r="AB1" s="96"/>
+      <c r="AC1" s="96"/>
+      <c r="AD1" s="96"/>
+      <c r="AE1" s="96"/>
+      <c r="AF1" s="96"/>
+      <c r="AG1" s="96"/>
+      <c r="AH1" s="97"/>
+      <c r="AK1" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="AL1" s="92"/>
-      <c r="AM1" s="92"/>
-      <c r="AN1" s="92"/>
-      <c r="AO1" s="92"/>
-      <c r="AP1" s="92"/>
-      <c r="AQ1" s="92"/>
-      <c r="AR1" s="92"/>
-      <c r="AS1" s="92"/>
-      <c r="AT1" s="92"/>
-      <c r="AU1" s="92"/>
-      <c r="AV1" s="92"/>
-      <c r="AW1" s="92"/>
-      <c r="AX1" s="92"/>
-      <c r="AY1" s="92"/>
-      <c r="AZ1" s="93"/>
-      <c r="BC1" s="91" t="s">
+      <c r="AL1" s="96"/>
+      <c r="AM1" s="96"/>
+      <c r="AN1" s="96"/>
+      <c r="AO1" s="96"/>
+      <c r="AP1" s="96"/>
+      <c r="AQ1" s="96"/>
+      <c r="AR1" s="96"/>
+      <c r="AS1" s="96"/>
+      <c r="AT1" s="96"/>
+      <c r="AU1" s="96"/>
+      <c r="AV1" s="96"/>
+      <c r="AW1" s="96"/>
+      <c r="AX1" s="96"/>
+      <c r="AY1" s="96"/>
+      <c r="AZ1" s="97"/>
+      <c r="BC1" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="BD1" s="92"/>
-      <c r="BE1" s="92"/>
-      <c r="BF1" s="92"/>
-      <c r="BG1" s="92"/>
-      <c r="BH1" s="92"/>
-      <c r="BI1" s="92"/>
-      <c r="BJ1" s="92"/>
-      <c r="BK1" s="92"/>
-      <c r="BL1" s="92"/>
-      <c r="BM1" s="92"/>
-      <c r="BN1" s="92"/>
-      <c r="BO1" s="92"/>
-      <c r="BP1" s="92"/>
-      <c r="BQ1" s="92"/>
-      <c r="BR1" s="93"/>
+      <c r="BD1" s="96"/>
+      <c r="BE1" s="96"/>
+      <c r="BF1" s="96"/>
+      <c r="BG1" s="96"/>
+      <c r="BH1" s="96"/>
+      <c r="BI1" s="96"/>
+      <c r="BJ1" s="96"/>
+      <c r="BK1" s="96"/>
+      <c r="BL1" s="96"/>
+      <c r="BM1" s="96"/>
+      <c r="BN1" s="96"/>
+      <c r="BO1" s="96"/>
+      <c r="BP1" s="96"/>
+      <c r="BQ1" s="96"/>
+      <c r="BR1" s="97"/>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
@@ -34135,7 +34534,7 @@
         <v>0.03</v>
       </c>
       <c r="AI5" s="13">
-        <f t="shared" ref="AI5:AI59" si="1">AH5-Z5</f>
+        <f t="shared" ref="AI5:AI60" si="1">AH5-Z5</f>
         <v>1.8700000000000001E-2</v>
       </c>
       <c r="AK5" s="4">
@@ -34181,7 +34580,7 @@
         <v>3.44E-2</v>
       </c>
       <c r="BA5" s="13">
-        <f t="shared" ref="BA5:BA59" si="2">AZ5-AR5</f>
+        <f t="shared" ref="BA5:BA60" si="2">AZ5-AR5</f>
         <v>2.8400000000000002E-2</v>
       </c>
       <c r="BC5" s="4">
@@ -34219,7 +34618,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS59" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS60" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -44505,7 +44904,9 @@
       <c r="G60" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H60" s="9"/>
+      <c r="H60" s="9">
+        <v>8.0999999999999996E-3</v>
+      </c>
       <c r="I60" s="2">
         <v>46133</v>
       </c>
@@ -44527,10 +44928,12 @@
       <c r="O60" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P60" s="58"/>
+      <c r="P60" s="58">
+        <v>2.7400000000000001E-2</v>
+      </c>
       <c r="Q60" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.9300000000000001E-2</v>
       </c>
       <c r="S60" s="4">
         <v>46133</v>
@@ -44547,11 +44950,15 @@
       <c r="W60" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X60" s="6"/>
+      <c r="X60" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y60" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z60" s="6"/>
+      <c r="Z60" s="6">
+        <v>1.29E-2</v>
+      </c>
       <c r="AA60" s="2">
         <v>46133</v>
       </c>
@@ -44573,50 +44980,97 @@
       <c r="AG60" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH60" s="58"/>
-      <c r="AI60" s="13"/>
+      <c r="AH60" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI60" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2100000000000001E-2</v>
+      </c>
       <c r="AK60" s="4">
         <v>46133</v>
       </c>
-      <c r="AL60" s="3"/>
+      <c r="AL60" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM60" s="3"/>
       <c r="AN60" s="3"/>
       <c r="AO60" s="3"/>
-      <c r="AP60" s="3"/>
-      <c r="AQ60" s="6"/>
-      <c r="AR60" s="6"/>
+      <c r="AP60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ60" s="6">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AR60" s="6">
+        <v>7.0000000000000001E-3</v>
+      </c>
       <c r="AS60" s="2">
         <v>46133</v>
       </c>
-      <c r="AT60" s="14"/>
-      <c r="AU60" s="14"/>
-      <c r="AV60" s="14"/>
-      <c r="AW60" s="14"/>
-      <c r="AX60" s="14"/>
-      <c r="AY60" s="14"/>
-      <c r="AZ60" s="14"/>
-      <c r="BA60" s="13"/>
+      <c r="AT60" s="14">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="AU60" s="14">
+        <v>3.44E-2</v>
+      </c>
+      <c r="AV60" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AW60" s="14">
+        <v>5.5E-2</v>
+      </c>
+      <c r="AX60" s="14">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="AY60" s="14">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="AZ60" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA60" s="13">
+        <f t="shared" si="2"/>
+        <v>2.5899999999999999E-2</v>
+      </c>
       <c r="BC60" s="4">
         <v>46133</v>
       </c>
-      <c r="BD60" s="6"/>
-      <c r="BE60" s="6"/>
-      <c r="BF60" s="6"/>
+      <c r="BD60" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE60" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF60" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG60" s="3"/>
       <c r="BH60" s="3"/>
       <c r="BI60" s="3"/>
-      <c r="BJ60" s="6"/>
+      <c r="BJ60" s="6">
+        <v>8.2000000000000007E-3</v>
+      </c>
       <c r="BK60" s="2">
         <v>46133</v>
       </c>
-      <c r="BL60" s="58"/>
+      <c r="BL60" s="58">
+        <v>3.5700000000000003E-2</v>
+      </c>
       <c r="BM60" s="1"/>
-      <c r="BN60" s="58"/>
+      <c r="BN60" s="58">
+        <v>5.4800000000000001E-2</v>
+      </c>
       <c r="BO60" s="1"/>
       <c r="BP60" s="1"/>
       <c r="BQ60" s="1"/>
-      <c r="BR60" s="58"/>
-      <c r="BS60" s="13"/>
+      <c r="BR60" s="58">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="BS60" s="13">
+        <f t="shared" si="3"/>
+        <v>1.9799999999999998E-2</v>
+      </c>
     </row>
     <row r="61" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A61" s="4">
@@ -48497,7 +48951,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -48860,7 +49314,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -49221,7 +49675,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -49576,7 +50030,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94550A15-C6A9-4CF5-8DB0-87660AAD9940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF489DC1-C17B-4496-99C8-20BD82EED8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -49,6 +49,8 @@
     <sheet name="20.04.2026" sheetId="55" r:id="rId34"/>
     <sheet name="21.04.2026" sheetId="56" r:id="rId35"/>
     <sheet name="22.04.2026" sheetId="57" r:id="rId36"/>
+    <sheet name="23.04.2026" sheetId="59" r:id="rId37"/>
+    <sheet name="24.04.2026" sheetId="58" r:id="rId38"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1179,6 +1181,80 @@
 </comments>
 </file>
 
+<file path=xl/comments33.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{D583A5AD-7B82-430A-BEB7-21E1BFE7D9F9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments34.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{F93C9B86-FCB1-49C5-B91A-C7AFB7ECF84D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1402,7 +1478,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3324" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3348" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -2093,9 +2169,6 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2105,13 +2178,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="31">
+  <dxfs count="36">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2353,7 +2464,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>487484</xdr:colOff>
+      <xdr:colOff>354623</xdr:colOff>
       <xdr:row>121</xdr:row>
       <xdr:rowOff>20630</xdr:rowOff>
     </xdr:to>
@@ -5329,28 +5440,52 @@
       <c r="F113" s="23">
         <v>2.6499999999999999E-2</v>
       </c>
-      <c r="G113" s="92"/>
+      <c r="G113" s="92">
+        <v>76336</v>
+      </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="82">
         <v>46135.125</v>
       </c>
-      <c r="B114" s="82"/>
-      <c r="C114" s="10"/>
-      <c r="D114" s="10"/>
-      <c r="E114" s="10"/>
-      <c r="F114" s="10"/>
-      <c r="G114" s="90"/>
+      <c r="B114" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C114" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D114" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E114" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F114" s="23">
+        <v>3.15E-2</v>
+      </c>
+      <c r="G114" s="90">
+        <v>78179</v>
+      </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="82">
         <v>46136.125</v>
       </c>
-      <c r="B115" s="82"/>
-      <c r="C115" s="10"/>
-      <c r="D115" s="10"/>
-      <c r="E115" s="10"/>
-      <c r="F115" s="10"/>
+      <c r="B115" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C115" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D115" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E115" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F115" s="23">
+        <v>3.1600000000000003E-2</v>
+      </c>
       <c r="G115" s="90"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
@@ -6099,7 +6234,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6435,7 +6570,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6773,7 +6908,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7109,7 +7244,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7443,7 +7578,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7779,7 +7914,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8115,7 +8250,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8451,7 +8586,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8787,7 +8922,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9123,7 +9258,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9149,7 +9284,7 @@
     <col min="19" max="19" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="4.1796875" bestFit="1" customWidth="1"/>
     <col min="21" max="23" width="4.36328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="5.453125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -9182,78 +9317,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" x14ac:dyDescent="0.35">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96"/>
-      <c r="P1" s="97"/>
-      <c r="S1" s="95" t="s">
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
+      <c r="O1" s="95"/>
+      <c r="P1" s="96"/>
+      <c r="S1" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="96"/>
-      <c r="U1" s="96"/>
-      <c r="V1" s="96"/>
-      <c r="W1" s="96"/>
-      <c r="X1" s="96"/>
-      <c r="Y1" s="96"/>
-      <c r="Z1" s="96"/>
-      <c r="AA1" s="96"/>
-      <c r="AB1" s="96"/>
-      <c r="AC1" s="96"/>
-      <c r="AD1" s="96"/>
-      <c r="AE1" s="96"/>
-      <c r="AF1" s="96"/>
-      <c r="AG1" s="96"/>
-      <c r="AH1" s="97"/>
-      <c r="AK1" s="95" t="s">
+      <c r="T1" s="95"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="95"/>
+      <c r="W1" s="95"/>
+      <c r="X1" s="95"/>
+      <c r="Y1" s="95"/>
+      <c r="Z1" s="95"/>
+      <c r="AA1" s="95"/>
+      <c r="AB1" s="95"/>
+      <c r="AC1" s="95"/>
+      <c r="AD1" s="95"/>
+      <c r="AE1" s="95"/>
+      <c r="AF1" s="95"/>
+      <c r="AG1" s="95"/>
+      <c r="AH1" s="96"/>
+      <c r="AK1" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="AL1" s="96"/>
-      <c r="AM1" s="96"/>
-      <c r="AN1" s="96"/>
-      <c r="AO1" s="96"/>
-      <c r="AP1" s="96"/>
-      <c r="AQ1" s="96"/>
-      <c r="AR1" s="96"/>
-      <c r="AS1" s="96"/>
-      <c r="AT1" s="96"/>
-      <c r="AU1" s="96"/>
-      <c r="AV1" s="96"/>
-      <c r="AW1" s="96"/>
-      <c r="AX1" s="96"/>
-      <c r="AY1" s="96"/>
-      <c r="AZ1" s="97"/>
-      <c r="BC1" s="95" t="s">
+      <c r="AL1" s="95"/>
+      <c r="AM1" s="95"/>
+      <c r="AN1" s="95"/>
+      <c r="AO1" s="95"/>
+      <c r="AP1" s="95"/>
+      <c r="AQ1" s="95"/>
+      <c r="AR1" s="95"/>
+      <c r="AS1" s="95"/>
+      <c r="AT1" s="95"/>
+      <c r="AU1" s="95"/>
+      <c r="AV1" s="95"/>
+      <c r="AW1" s="95"/>
+      <c r="AX1" s="95"/>
+      <c r="AY1" s="95"/>
+      <c r="AZ1" s="96"/>
+      <c r="BC1" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="BD1" s="96"/>
-      <c r="BE1" s="96"/>
-      <c r="BF1" s="96"/>
-      <c r="BG1" s="96"/>
-      <c r="BH1" s="96"/>
-      <c r="BI1" s="96"/>
-      <c r="BJ1" s="96"/>
-      <c r="BK1" s="96"/>
-      <c r="BL1" s="96"/>
-      <c r="BM1" s="96"/>
-      <c r="BN1" s="96"/>
-      <c r="BO1" s="96"/>
-      <c r="BP1" s="96"/>
-      <c r="BQ1" s="96"/>
-      <c r="BR1" s="97"/>
+      <c r="BD1" s="95"/>
+      <c r="BE1" s="95"/>
+      <c r="BF1" s="95"/>
+      <c r="BG1" s="95"/>
+      <c r="BH1" s="95"/>
+      <c r="BI1" s="95"/>
+      <c r="BJ1" s="95"/>
+      <c r="BK1" s="95"/>
+      <c r="BL1" s="95"/>
+      <c r="BM1" s="95"/>
+      <c r="BN1" s="95"/>
+      <c r="BO1" s="95"/>
+      <c r="BP1" s="95"/>
+      <c r="BQ1" s="95"/>
+      <c r="BR1" s="96"/>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
@@ -9829,7 +9964,7 @@
         <v>0.03</v>
       </c>
       <c r="AI5" s="13">
-        <f t="shared" ref="AI5:AI61" si="1">AH5-Z5</f>
+        <f t="shared" ref="AI5:AI63" si="1">AH5-Z5</f>
         <v>1.8700000000000001E-2</v>
       </c>
       <c r="AK5" s="4">
@@ -9875,7 +10010,7 @@
         <v>3.44E-2</v>
       </c>
       <c r="BA5" s="13">
-        <f t="shared" ref="BA5:BA61" si="2">AZ5-AR5</f>
+        <f t="shared" ref="BA5:BA63" si="2">AZ5-AR5</f>
         <v>2.8400000000000002E-2</v>
       </c>
       <c r="BC5" s="4">
@@ -9913,7 +10048,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS61" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS63" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -20579,7 +20714,9 @@
       <c r="G62" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H62" s="9"/>
+      <c r="H62" s="9">
+        <v>8.5000000000000006E-3</v>
+      </c>
       <c r="I62" s="2">
         <v>46135</v>
       </c>
@@ -20601,10 +20738,12 @@
       <c r="O62" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P62" s="58"/>
+      <c r="P62" s="58">
+        <v>2.75E-2</v>
+      </c>
       <c r="Q62" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.9E-2</v>
       </c>
       <c r="S62" s="4">
         <v>46135</v>
@@ -20621,11 +20760,15 @@
       <c r="W62" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X62" s="6"/>
+      <c r="X62" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y62" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z62" s="6"/>
+      <c r="Z62" s="6">
+        <v>1.2500000000000001E-2</v>
+      </c>
       <c r="AA62" s="2">
         <v>46135</v>
       </c>
@@ -20647,50 +20790,97 @@
       <c r="AG62" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH62" s="58"/>
-      <c r="AI62" s="13"/>
+      <c r="AH62" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI62" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2500000000000001E-2</v>
+      </c>
       <c r="AK62" s="4">
         <v>46135</v>
       </c>
-      <c r="AL62" s="3"/>
+      <c r="AL62" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM62" s="3"/>
       <c r="AN62" s="3"/>
       <c r="AO62" s="3"/>
-      <c r="AP62" s="3"/>
-      <c r="AQ62" s="6"/>
-      <c r="AR62" s="6"/>
+      <c r="AP62" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ62" s="6">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AR62" s="6">
+        <v>8.0999999999999996E-3</v>
+      </c>
       <c r="AS62" s="2">
         <v>46135</v>
       </c>
-      <c r="AT62" s="14"/>
-      <c r="AU62" s="14"/>
-      <c r="AV62" s="14"/>
-      <c r="AW62" s="14"/>
-      <c r="AX62" s="14"/>
-      <c r="AY62" s="14"/>
-      <c r="AZ62" s="14"/>
-      <c r="BA62" s="13"/>
+      <c r="AT62" s="14">
+        <v>0.03</v>
+      </c>
+      <c r="AU62" s="14">
+        <v>3.09E-2</v>
+      </c>
+      <c r="AV62" s="14">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="AW62" s="14">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AX62" s="14">
+        <v>5.8700000000000002E-2</v>
+      </c>
+      <c r="AY62" s="14">
+        <v>0.06</v>
+      </c>
+      <c r="AZ62" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA62" s="13">
+        <f t="shared" si="2"/>
+        <v>2.4799999999999999E-2</v>
+      </c>
       <c r="BC62" s="4">
         <v>46135</v>
       </c>
-      <c r="BD62" s="6"/>
-      <c r="BE62" s="6"/>
-      <c r="BF62" s="6"/>
+      <c r="BD62" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE62" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF62" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG62" s="3"/>
       <c r="BH62" s="3"/>
       <c r="BI62" s="3"/>
-      <c r="BJ62" s="6"/>
+      <c r="BJ62" s="6">
+        <v>7.6E-3</v>
+      </c>
       <c r="BK62" s="2">
         <v>46135</v>
       </c>
-      <c r="BL62" s="58"/>
+      <c r="BL62" s="58">
+        <v>3.49E-2</v>
+      </c>
       <c r="BM62" s="1"/>
-      <c r="BN62" s="58"/>
+      <c r="BN62" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO62" s="1"/>
       <c r="BP62" s="1"/>
       <c r="BQ62" s="1"/>
-      <c r="BR62" s="58"/>
-      <c r="BS62" s="13"/>
+      <c r="BR62" s="58">
+        <v>2.7199999999999998E-2</v>
+      </c>
+      <c r="BS62" s="13">
+        <f t="shared" si="3"/>
+        <v>1.9599999999999999E-2</v>
+      </c>
     </row>
     <row r="63" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A63" s="4">
@@ -20714,7 +20904,9 @@
       <c r="G63" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H63" s="9"/>
+      <c r="H63" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
       <c r="I63" s="2">
         <v>46136</v>
       </c>
@@ -20736,10 +20928,12 @@
       <c r="O63" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P63" s="58"/>
+      <c r="P63" s="58">
+        <v>2.7300000000000001E-2</v>
+      </c>
       <c r="Q63" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.9300000000000001E-2</v>
       </c>
       <c r="S63" s="4">
         <v>46136</v>
@@ -20756,11 +20950,15 @@
       <c r="W63" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X63" s="6"/>
+      <c r="X63" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y63" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z63" s="6"/>
+      <c r="Z63" s="6">
+        <v>1.2500000000000001E-2</v>
+      </c>
       <c r="AA63" s="2">
         <v>46136</v>
       </c>
@@ -20782,50 +20980,97 @@
       <c r="AG63" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH63" s="58"/>
-      <c r="AI63" s="13"/>
+      <c r="AH63" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI63" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2500000000000001E-2</v>
+      </c>
       <c r="AK63" s="4">
         <v>46136</v>
       </c>
-      <c r="AL63" s="3"/>
+      <c r="AL63" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM63" s="3"/>
       <c r="AN63" s="3"/>
       <c r="AO63" s="3"/>
-      <c r="AP63" s="3"/>
-      <c r="AQ63" s="6"/>
-      <c r="AR63" s="6"/>
+      <c r="AP63" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ63" s="6">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AR63" s="6">
+        <v>7.0000000000000001E-3</v>
+      </c>
       <c r="AS63" s="2">
         <v>46136</v>
       </c>
-      <c r="AT63" s="14"/>
-      <c r="AU63" s="14"/>
-      <c r="AV63" s="14"/>
-      <c r="AW63" s="14"/>
-      <c r="AX63" s="14"/>
-      <c r="AY63" s="14"/>
-      <c r="AZ63" s="14"/>
-      <c r="BA63" s="13"/>
+      <c r="AT63" s="14">
+        <v>0.03</v>
+      </c>
+      <c r="AU63" s="14">
+        <v>3.09E-2</v>
+      </c>
+      <c r="AV63" s="14">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="AW63" s="14">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AX63" s="14">
+        <v>5.8700000000000002E-2</v>
+      </c>
+      <c r="AY63" s="14">
+        <v>0.06</v>
+      </c>
+      <c r="AZ63" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA63" s="13">
+        <f t="shared" si="2"/>
+        <v>2.5899999999999999E-2</v>
+      </c>
       <c r="BC63" s="4">
         <v>46136</v>
       </c>
-      <c r="BD63" s="6"/>
-      <c r="BE63" s="6"/>
-      <c r="BF63" s="6"/>
+      <c r="BD63" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE63" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF63" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG63" s="3"/>
       <c r="BH63" s="3"/>
       <c r="BI63" s="3"/>
-      <c r="BJ63" s="6"/>
+      <c r="BJ63" s="6">
+        <v>7.6E-3</v>
+      </c>
       <c r="BK63" s="2">
         <v>46136</v>
       </c>
-      <c r="BL63" s="58"/>
+      <c r="BL63" s="58">
+        <v>3.49E-2</v>
+      </c>
       <c r="BM63" s="1"/>
-      <c r="BN63" s="58"/>
+      <c r="BN63" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO63" s="1"/>
       <c r="BP63" s="1"/>
       <c r="BQ63" s="1"/>
-      <c r="BR63" s="58"/>
-      <c r="BS63" s="13"/>
+      <c r="BR63" s="58">
+        <v>2.7199999999999998E-2</v>
+      </c>
+      <c r="BS63" s="13">
+        <f t="shared" si="3"/>
+        <v>1.9599999999999999E-2</v>
+      </c>
     </row>
     <row r="64" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A64" s="4">
@@ -24275,7 +24520,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24611,7 +24856,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24949,7 +25194,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25287,7 +25532,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25625,7 +25870,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25993,7 +26238,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26361,7 +26606,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26729,7 +26974,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27100,7 +27345,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -27481,7 +27726,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -27502,11 +27747,11 @@
       <c r="A1" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="94" t="s">
+      <c r="B1" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="11"/>
@@ -28945,7 +29190,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -29289,7 +29534,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -29633,7 +29878,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -29977,7 +30222,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30321,7 +30566,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30653,7 +30898,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30997,11 +31242,715 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
       <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11D962B7-868E-481B-9779-BB2FE987E47A}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46135</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.03</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.09E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5.8700000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>0.06</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!H62</f>
+        <v>2.4399999999999998E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z62</f>
+        <v>1.2500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="57">
+        <v>3.49E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.721317916094455E-2</v>
+      </c>
+      <c r="D5" s="57">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.7259881528093017E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.7290397161898836E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.7382217600190828E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.7199999999999998E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>2.7572255500570853E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ63</f>
+        <v>1.9599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="55">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="55">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-K7</f>
+        <v>2.4800000000000003E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="55">
+        <v>2.07E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>1.9706912684064486E-2</v>
+      </c>
+      <c r="D7" s="55">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>1.9731398932948101E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>1.9747390079277543E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>1.9795467267421301E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>1.9894783341781519E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.08%</f>
+        <v>8.8999999999999982E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.750621653395394E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.751347152523961E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7530063944917416E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7561210701938343E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7592404443735931E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7686268375885618E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.75E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>2.7880550318131858E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H62</f>
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>2.9507153703264923E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>2.9515502614004818E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>2.953459766818926E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>2.957044530350909E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>2.9606350952279013E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>2.9714417036530872E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>2.9938207723953836E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{046A0946-F8C8-4C0E-ACA7-BA056E956E6D}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46136</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.03</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.09E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5.8700000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>0.06</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR63</f>
+        <v>2.5899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z63</f>
+        <v>1.2500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="57">
+        <v>3.49E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.721317916094455E-2</v>
+      </c>
+      <c r="D5" s="57">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.7259881528093017E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.7290397161898836E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.7382217600190828E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.7199999999999998E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>2.7572255500570853E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>'24.04.2026'!H5-'Daily Data'!BJ63</f>
+        <v>1.9599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="55">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="55">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="55">
+        <v>2.07E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>1.9706912684064486E-2</v>
+      </c>
+      <c r="D7" s="55">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>1.9731398932948101E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>1.9747390079277543E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>1.9795467267421301E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>1.9894783341781519E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.08%</f>
+        <v>8.8999999999999982E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.730612643489061E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.7313276259254522E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7329628089791263E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7360322962594403E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7391063801394545E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7483562888867545E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.7300000000000001E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>2.7675010192383942E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H63</f>
+        <v>1.9300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>2.9507153703264923E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>2.9515502614004818E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>2.953459766818926E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>2.957044530350909E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>2.9606350952279013E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>2.9714417036530872E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>2.9938207723953836E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J4 A8:J9 A5:A7 E5:J7 C5:C7">
+    <cfRule type="expression" dxfId="4" priority="7">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B7">
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>_xlfn.ISFORMULA(B5)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4">
+      <formula>_xlfn.ISFORMULA(B5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5:D7">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>_xlfn.ISFORMULA(D5)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(D5)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -49407,7 +50356,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -49770,7 +50719,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50131,7 +51080,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50486,7 +51435,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF489DC1-C17B-4496-99C8-20BD82EED8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA1F6CB-47AD-4740-BE41-CFB1D2E826AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="31" activeTab="40" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -51,6 +51,9 @@
     <sheet name="22.04.2026" sheetId="57" r:id="rId36"/>
     <sheet name="23.04.2026" sheetId="59" r:id="rId37"/>
     <sheet name="24.04.2026" sheetId="58" r:id="rId38"/>
+    <sheet name="25.04.2026" sheetId="60" r:id="rId39"/>
+    <sheet name="26.04.2026" sheetId="61" r:id="rId40"/>
+    <sheet name="27.04.2026" sheetId="62" r:id="rId41"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1255,6 +1258,117 @@
 </comments>
 </file>
 
+<file path=xl/comments35.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{818ED0A6-8E74-4AE5-81A0-6CC1140C1E13}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments36.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{BF8E6734-C4BD-4CB0-82AD-C543C992D13C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments37.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{32E69E51-05CC-439B-876E-4DFDD7446B14}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1478,7 +1592,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3348" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3387" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -2464,7 +2578,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>354623</xdr:colOff>
+      <xdr:colOff>351448</xdr:colOff>
       <xdr:row>121</xdr:row>
       <xdr:rowOff>20630</xdr:rowOff>
     </xdr:to>
@@ -5486,39 +5600,75 @@
       <c r="F115" s="23">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="G115" s="90"/>
+      <c r="G115" s="90">
+        <v>78257</v>
+      </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="82">
         <v>46137.125</v>
       </c>
-      <c r="B116" s="82"/>
-      <c r="C116" s="10"/>
-      <c r="D116" s="10"/>
-      <c r="E116" s="10"/>
-      <c r="F116" s="10"/>
-      <c r="G116" s="90"/>
+      <c r="B116" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C116" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D116" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E116" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F116" s="23">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="G116" s="90">
+        <v>77437</v>
+      </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="82">
         <v>46138.125</v>
       </c>
-      <c r="B117" s="82"/>
-      <c r="C117" s="10"/>
-      <c r="D117" s="10"/>
-      <c r="E117" s="10"/>
-      <c r="F117" s="10"/>
-      <c r="G117" s="90"/>
+      <c r="B117" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C117" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D117" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E117" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F117" s="23">
+        <v>3.2399999999999998E-2</v>
+      </c>
+      <c r="G117" s="90">
+        <v>77625</v>
+      </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="82">
         <v>46139.125</v>
       </c>
-      <c r="B118" s="82"/>
-      <c r="C118" s="10"/>
-      <c r="D118" s="10"/>
-      <c r="E118" s="10"/>
-      <c r="F118" s="10"/>
+      <c r="B118" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C118" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D118" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E118" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F118" s="23">
+        <v>3.2899999999999999E-2</v>
+      </c>
       <c r="G118" s="90"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
@@ -9964,7 +10114,7 @@
         <v>0.03</v>
       </c>
       <c r="AI5" s="13">
-        <f t="shared" ref="AI5:AI63" si="1">AH5-Z5</f>
+        <f t="shared" ref="AI5:AI66" si="1">AH5-Z5</f>
         <v>1.8700000000000001E-2</v>
       </c>
       <c r="AK5" s="4">
@@ -10010,7 +10160,7 @@
         <v>3.44E-2</v>
       </c>
       <c r="BA5" s="13">
-        <f t="shared" ref="BA5:BA63" si="2">AZ5-AR5</f>
+        <f t="shared" ref="BA5:BA66" si="2">AZ5-AR5</f>
         <v>2.8400000000000002E-2</v>
       </c>
       <c r="BC5" s="4">
@@ -10048,7 +10198,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS63" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS66" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -21094,7 +21244,9 @@
       <c r="G64" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H64" s="9"/>
+      <c r="H64" s="9">
+        <v>8.2000000000000007E-3</v>
+      </c>
       <c r="I64" s="2">
         <v>46137</v>
       </c>
@@ -21116,10 +21268,12 @@
       <c r="O64" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P64" s="58"/>
+      <c r="P64" s="58">
+        <v>2.7699999999999999E-2</v>
+      </c>
       <c r="Q64" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.9499999999999997E-2</v>
       </c>
       <c r="S64" s="4">
         <v>46137</v>
@@ -21136,11 +21290,15 @@
       <c r="W64" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X64" s="6"/>
+      <c r="X64" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y64" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z64" s="6"/>
+      <c r="Z64" s="6">
+        <v>1.23E-2</v>
+      </c>
       <c r="AA64" s="2">
         <v>46137</v>
       </c>
@@ -21162,50 +21320,97 @@
       <c r="AG64" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH64" s="58"/>
-      <c r="AI64" s="13"/>
+      <c r="AH64" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI64" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2700000000000001E-2</v>
+      </c>
       <c r="AK64" s="4">
         <v>46137</v>
       </c>
-      <c r="AL64" s="3"/>
+      <c r="AL64" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM64" s="3"/>
       <c r="AN64" s="3"/>
       <c r="AO64" s="3"/>
-      <c r="AP64" s="3"/>
-      <c r="AQ64" s="6"/>
-      <c r="AR64" s="6"/>
+      <c r="AP64" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ64" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR64" s="6">
+        <v>6.7000000000000002E-3</v>
+      </c>
       <c r="AS64" s="2">
         <v>46137</v>
       </c>
-      <c r="AT64" s="14"/>
-      <c r="AU64" s="14"/>
-      <c r="AV64" s="14"/>
-      <c r="AW64" s="14"/>
-      <c r="AX64" s="14"/>
-      <c r="AY64" s="14"/>
-      <c r="AZ64" s="14"/>
-      <c r="BA64" s="13"/>
+      <c r="AT64" s="14">
+        <v>0.03</v>
+      </c>
+      <c r="AU64" s="14">
+        <v>3.09E-2</v>
+      </c>
+      <c r="AV64" s="14">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="AW64" s="14">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AX64" s="14">
+        <v>5.8700000000000002E-2</v>
+      </c>
+      <c r="AY64" s="14">
+        <v>0.06</v>
+      </c>
+      <c r="AZ64" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA64" s="13">
+        <f t="shared" si="2"/>
+        <v>2.6199999999999998E-2</v>
+      </c>
       <c r="BC64" s="4">
         <v>46137</v>
       </c>
-      <c r="BD64" s="6"/>
-      <c r="BE64" s="6"/>
-      <c r="BF64" s="6"/>
+      <c r="BD64" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE64" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF64" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG64" s="3"/>
       <c r="BH64" s="3"/>
       <c r="BI64" s="3"/>
-      <c r="BJ64" s="6"/>
+      <c r="BJ64" s="6">
+        <v>7.7999999999999996E-3</v>
+      </c>
       <c r="BK64" s="2">
         <v>46137</v>
       </c>
-      <c r="BL64" s="58"/>
+      <c r="BL64" s="58">
+        <v>3.49E-2</v>
+      </c>
       <c r="BM64" s="1"/>
-      <c r="BN64" s="58"/>
+      <c r="BN64" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO64" s="1"/>
       <c r="BP64" s="1"/>
       <c r="BQ64" s="1"/>
-      <c r="BR64" s="58"/>
-      <c r="BS64" s="13"/>
+      <c r="BR64" s="58">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="BS64" s="13">
+        <f t="shared" si="3"/>
+        <v>2.01E-2</v>
+      </c>
     </row>
     <row r="65" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A65" s="4">
@@ -21229,7 +21434,9 @@
       <c r="G65" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H65" s="9"/>
+      <c r="H65" s="9">
+        <v>8.2000000000000007E-3</v>
+      </c>
       <c r="I65" s="2">
         <v>46138</v>
       </c>
@@ -21251,10 +21458,12 @@
       <c r="O65" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P65" s="58"/>
+      <c r="P65" s="58">
+        <v>2.7699999999999999E-2</v>
+      </c>
       <c r="Q65" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.9499999999999997E-2</v>
       </c>
       <c r="S65" s="4">
         <v>46138</v>
@@ -21271,11 +21480,15 @@
       <c r="W65" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X65" s="6"/>
+      <c r="X65" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y65" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z65" s="6"/>
+      <c r="Z65" s="6">
+        <v>1.2200000000000001E-2</v>
+      </c>
       <c r="AA65" s="2">
         <v>46138</v>
       </c>
@@ -21297,50 +21510,97 @@
       <c r="AG65" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH65" s="58"/>
-      <c r="AI65" s="13"/>
+      <c r="AH65" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI65" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2800000000000001E-2</v>
+      </c>
       <c r="AK65" s="4">
         <v>46138</v>
       </c>
-      <c r="AL65" s="3"/>
+      <c r="AL65" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM65" s="3"/>
       <c r="AN65" s="3"/>
       <c r="AO65" s="3"/>
-      <c r="AP65" s="3"/>
-      <c r="AQ65" s="6"/>
-      <c r="AR65" s="6"/>
+      <c r="AP65" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ65" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR65" s="6">
+        <v>6.7000000000000002E-3</v>
+      </c>
       <c r="AS65" s="2">
         <v>46138</v>
       </c>
-      <c r="AT65" s="14"/>
-      <c r="AU65" s="14"/>
-      <c r="AV65" s="14"/>
-      <c r="AW65" s="14"/>
-      <c r="AX65" s="14"/>
-      <c r="AY65" s="14"/>
-      <c r="AZ65" s="14"/>
-      <c r="BA65" s="13"/>
+      <c r="AT65" s="14">
+        <v>0.03</v>
+      </c>
+      <c r="AU65" s="14">
+        <v>3.09E-2</v>
+      </c>
+      <c r="AV65" s="14">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="AW65" s="14">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AX65" s="14">
+        <v>5.8700000000000002E-2</v>
+      </c>
+      <c r="AY65" s="14">
+        <v>0.06</v>
+      </c>
+      <c r="AZ65" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA65" s="13">
+        <f t="shared" si="2"/>
+        <v>2.6199999999999998E-2</v>
+      </c>
       <c r="BC65" s="4">
         <v>46138</v>
       </c>
-      <c r="BD65" s="6"/>
-      <c r="BE65" s="6"/>
-      <c r="BF65" s="6"/>
+      <c r="BD65" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE65" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF65" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG65" s="3"/>
       <c r="BH65" s="3"/>
       <c r="BI65" s="3"/>
-      <c r="BJ65" s="6"/>
+      <c r="BJ65" s="6">
+        <v>7.7999999999999996E-3</v>
+      </c>
       <c r="BK65" s="2">
         <v>46138</v>
       </c>
-      <c r="BL65" s="58"/>
+      <c r="BL65" s="58">
+        <v>3.49E-2</v>
+      </c>
       <c r="BM65" s="1"/>
-      <c r="BN65" s="58"/>
+      <c r="BN65" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO65" s="1"/>
       <c r="BP65" s="1"/>
       <c r="BQ65" s="1"/>
-      <c r="BR65" s="58"/>
-      <c r="BS65" s="13"/>
+      <c r="BR65" s="58">
+        <v>2.81E-2</v>
+      </c>
+      <c r="BS65" s="13">
+        <f t="shared" si="3"/>
+        <v>2.0299999999999999E-2</v>
+      </c>
     </row>
     <row r="66" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A66" s="4">
@@ -21364,7 +21624,9 @@
       <c r="G66" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H66" s="9"/>
+      <c r="H66" s="9">
+        <v>8.3000000000000001E-3</v>
+      </c>
       <c r="I66" s="2">
         <v>46139</v>
       </c>
@@ -21386,10 +21648,12 @@
       <c r="O66" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P66" s="58"/>
+      <c r="P66" s="58">
+        <v>2.7799999999999998E-2</v>
+      </c>
       <c r="Q66" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.9499999999999997E-2</v>
       </c>
       <c r="S66" s="4">
         <v>46139</v>
@@ -21406,11 +21670,15 @@
       <c r="W66" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X66" s="6"/>
+      <c r="X66" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y66" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z66" s="6"/>
+      <c r="Z66" s="6">
+        <v>1.2200000000000001E-2</v>
+      </c>
       <c r="AA66" s="2">
         <v>46139</v>
       </c>
@@ -21432,50 +21700,97 @@
       <c r="AG66" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH66" s="58"/>
-      <c r="AI66" s="13"/>
+      <c r="AH66" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI66" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2800000000000001E-2</v>
+      </c>
       <c r="AK66" s="4">
         <v>46139</v>
       </c>
-      <c r="AL66" s="3"/>
+      <c r="AL66" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM66" s="3"/>
       <c r="AN66" s="3"/>
       <c r="AO66" s="3"/>
-      <c r="AP66" s="3"/>
-      <c r="AQ66" s="6"/>
-      <c r="AR66" s="6"/>
+      <c r="AP66" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ66" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR66" s="6">
+        <v>7.0000000000000001E-3</v>
+      </c>
       <c r="AS66" s="2">
         <v>46139</v>
       </c>
-      <c r="AT66" s="14"/>
-      <c r="AU66" s="14"/>
-      <c r="AV66" s="14"/>
-      <c r="AW66" s="14"/>
-      <c r="AX66" s="14"/>
-      <c r="AY66" s="14"/>
-      <c r="AZ66" s="14"/>
-      <c r="BA66" s="13"/>
+      <c r="AT66" s="14">
+        <v>0.03</v>
+      </c>
+      <c r="AU66" s="14">
+        <v>3.09E-2</v>
+      </c>
+      <c r="AV66" s="14">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="AW66" s="14">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AX66" s="14">
+        <v>5.8700000000000002E-2</v>
+      </c>
+      <c r="AY66" s="14">
+        <v>0.06</v>
+      </c>
+      <c r="AZ66" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA66" s="13">
+        <f t="shared" si="2"/>
+        <v>2.5899999999999999E-2</v>
+      </c>
       <c r="BC66" s="4">
         <v>46139</v>
       </c>
-      <c r="BD66" s="6"/>
-      <c r="BE66" s="6"/>
-      <c r="BF66" s="6"/>
+      <c r="BD66" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE66" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF66" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG66" s="3"/>
       <c r="BH66" s="3"/>
       <c r="BI66" s="3"/>
-      <c r="BJ66" s="6"/>
+      <c r="BJ66" s="6">
+        <v>8.0000000000000002E-3</v>
+      </c>
       <c r="BK66" s="2">
         <v>46139</v>
       </c>
-      <c r="BL66" s="58"/>
+      <c r="BL66" s="58">
+        <v>3.49E-2</v>
+      </c>
       <c r="BM66" s="1"/>
-      <c r="BN66" s="58"/>
+      <c r="BN66" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO66" s="1"/>
       <c r="BP66" s="1"/>
       <c r="BQ66" s="1"/>
-      <c r="BR66" s="58"/>
-      <c r="BS66" s="13"/>
+      <c r="BR66" s="58">
+        <v>2.8400000000000002E-2</v>
+      </c>
+      <c r="BS66" s="13">
+        <f t="shared" si="3"/>
+        <v>2.0400000000000001E-2</v>
+      </c>
     </row>
     <row r="67" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A67" s="4">
@@ -31586,7 +31901,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31600,6 +31915,9 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{046A0946-F8C8-4C0E-ACA7-BA056E956E6D}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -31929,28 +32247,357 @@
       <c r="K9" s="69"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:J4 A8:J9 A5:A7 E5:J7 C5:C7">
-    <cfRule type="expression" dxfId="4" priority="7">
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
-    <cfRule type="expression" priority="8">
+    <cfRule type="expression" priority="2">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B7">
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>_xlfn.ISFORMULA(B5)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4">
-      <formula>_xlfn.ISFORMULA(B5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D7">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>_xlfn.ISFORMULA(D5)</formula>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="42" orientation="landscape" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB664B0-C712-43D3-A8F7-53AB834669F0}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46137</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.03</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.09E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5.8700000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>0.06</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>'Daily Data'!AR64</f>
+        <v>6.7000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z64</f>
+        <v>1.2700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="57">
+        <v>3.49E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.791386633517404E-2</v>
+      </c>
+      <c r="D5" s="57">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.7963005663145801E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.7995115183913229E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8091738995796145E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>2.8291753567093458E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ64</f>
+        <v>2.01E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="55">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="55">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="55">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.090778059017687E-2</v>
+      </c>
+      <c r="D7" s="55">
+        <v>2.3E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.0935342936297952E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.0953344478137657E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.1007473023389494E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.0899999999999998E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.1119323554426916E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-0.93%</f>
+        <v>1.1599999999999997E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.7706307290950978E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.7713668217315055E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.77305029849787E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7762104935491045E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7793754904522662E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7888993744320009E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.7699999999999999E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>2.8086131440423268E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H64</f>
+        <v>1.9499999999999997E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
-      <formula>_xlfn.ISFORMULA(D5)</formula>
+      <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -42307,6 +42954,694 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50E88AC3-95AF-4A48-BE98-C5E33EE40E11}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46138</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.03</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.09E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5.8700000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>0.06</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>((1+H3/365)^365-1)</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR65</f>
+        <v>2.6199999999999998E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">((1+H4/365)^365-1)</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!AR65</f>
+        <v>1.83E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="57">
+        <v>3.49E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.8114065879042336E-2</v>
+      </c>
+      <c r="D5" s="57">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8163912885332154E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8196485282603719E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8294504132474804E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.81E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>2.8497416706523726E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ65</f>
+        <v>2.0299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="55">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="55">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="55">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.090778059017687E-2</v>
+      </c>
+      <c r="D7" s="55">
+        <v>2.3099999999999999E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.0935342936297952E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.0953344478137657E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.1007473023389494E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.0899999999999998E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.1119323554426916E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.08%</f>
+        <v>1.0099999999999998E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.7706307290950978E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.7713668217315055E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.77305029849787E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7762104935491045E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7793754904522662E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7888993744320009E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.7699999999999999E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>2.8086131440423268E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H66</f>
+        <v>1.9400000000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B793A495-0ABB-4D50-9BD6-1C995FF8BF1D}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46139</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.03</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.09E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5.8700000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>0.06</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR66</f>
+        <v>2.5899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z66</f>
+        <v>1.2800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="57">
+        <v>3.49E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.8414367868607897E-2</v>
+      </c>
+      <c r="D5" s="57">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8465285896267883E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8498558842821323E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8598689126452321E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.8400000000000002E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>2.8805988332401222E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ66</f>
+        <v>2.0400000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="55">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="55">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="55">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.090778059017687E-2</v>
+      </c>
+      <c r="D7" s="55">
+        <v>2.3E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.0935342936297952E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.0953344478137657E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.1007473023389494E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.0899999999999998E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.1119323554426916E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-0.93%</f>
+        <v>1.1599999999999997E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.7806352915951762E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.7813767097925362E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7830723699162802E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7862554487448787E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7894433816769322E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7990363884462747E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>2.8188937377605638E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H66</f>
+        <v>1.9499999999999997E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA1F6CB-47AD-4740-BE41-CFB1D2E826AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B2BE53-CCBD-47DA-B7CE-56A15F9BF980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="31" activeTab="40" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -54,6 +54,7 @@
     <sheet name="25.04.2026" sheetId="60" r:id="rId39"/>
     <sheet name="26.04.2026" sheetId="61" r:id="rId40"/>
     <sheet name="27.04.2026" sheetId="62" r:id="rId41"/>
+    <sheet name="28.04.2026" sheetId="63" r:id="rId42"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1369,6 +1370,43 @@
 </comments>
 </file>
 
+<file path=xl/comments38.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{B2E415A0-23C0-44A4-A584-9815AAD9FDF8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1592,7 +1630,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3387" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3400" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -2301,7 +2339,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="37">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5669,17 +5714,29 @@
       <c r="F118" s="23">
         <v>3.2899999999999999E-2</v>
       </c>
-      <c r="G118" s="90"/>
+      <c r="G118" s="90">
+        <v>78657</v>
+      </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="82">
         <v>46140.125</v>
       </c>
-      <c r="B119" s="82"/>
-      <c r="C119" s="10"/>
-      <c r="D119" s="10"/>
-      <c r="E119" s="10"/>
-      <c r="F119" s="10"/>
+      <c r="B119" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C119" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D119" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E119" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F119" s="23">
+        <v>3.3399999999999999E-2</v>
+      </c>
       <c r="G119" s="90"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
@@ -6384,7 +6441,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6720,7 +6777,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7058,7 +7115,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7394,7 +7451,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7728,7 +7785,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8064,7 +8121,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8400,7 +8457,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8736,7 +8793,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9072,7 +9129,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9408,7 +9465,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10114,7 +10171,7 @@
         <v>0.03</v>
       </c>
       <c r="AI5" s="13">
-        <f t="shared" ref="AI5:AI66" si="1">AH5-Z5</f>
+        <f t="shared" ref="AI5:AI67" si="1">AH5-Z5</f>
         <v>1.8700000000000001E-2</v>
       </c>
       <c r="AK5" s="4">
@@ -10160,7 +10217,7 @@
         <v>3.44E-2</v>
       </c>
       <c r="BA5" s="13">
-        <f t="shared" ref="BA5:BA66" si="2">AZ5-AR5</f>
+        <f t="shared" ref="BA5:BA67" si="2">AZ5-AR5</f>
         <v>2.8400000000000002E-2</v>
       </c>
       <c r="BC5" s="4">
@@ -10198,7 +10255,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS66" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS67" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -21814,7 +21871,9 @@
       <c r="G67" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H67" s="9"/>
+      <c r="H67" s="9">
+        <v>8.3999999999999995E-3</v>
+      </c>
       <c r="I67" s="2">
         <v>46140</v>
       </c>
@@ -21836,10 +21895,12 @@
       <c r="O67" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P67" s="58"/>
+      <c r="P67" s="58">
+        <v>2.7900000000000001E-2</v>
+      </c>
       <c r="Q67" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.9500000000000003E-2</v>
       </c>
       <c r="S67" s="4">
         <v>46140</v>
@@ -21856,11 +21917,15 @@
       <c r="W67" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X67" s="6"/>
+      <c r="X67" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y67" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z67" s="6"/>
+      <c r="Z67" s="6">
+        <v>1.2200000000000001E-2</v>
+      </c>
       <c r="AA67" s="2">
         <v>46140</v>
       </c>
@@ -21882,50 +21947,97 @@
       <c r="AG67" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH67" s="58"/>
-      <c r="AI67" s="13"/>
+      <c r="AH67" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI67" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2800000000000001E-2</v>
+      </c>
       <c r="AK67" s="4">
         <v>46140</v>
       </c>
-      <c r="AL67" s="3"/>
+      <c r="AL67" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
-      <c r="AP67" s="3"/>
-      <c r="AQ67" s="6"/>
-      <c r="AR67" s="6"/>
+      <c r="AP67" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ67" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR67" s="6">
+        <v>6.4999999999999997E-3</v>
+      </c>
       <c r="AS67" s="2">
         <v>46140</v>
       </c>
-      <c r="AT67" s="14"/>
-      <c r="AU67" s="14"/>
-      <c r="AV67" s="14"/>
-      <c r="AW67" s="14"/>
-      <c r="AX67" s="14"/>
-      <c r="AY67" s="14"/>
-      <c r="AZ67" s="14"/>
-      <c r="BA67" s="13"/>
+      <c r="AT67" s="14">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="AU67" s="14">
+        <v>2.75E-2</v>
+      </c>
+      <c r="AV67" s="14">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="AW67" s="14">
+        <v>4.99E-2</v>
+      </c>
+      <c r="AX67" s="14">
+        <v>5.9400000000000001E-2</v>
+      </c>
+      <c r="AY67" s="14">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="AZ67" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA67" s="13">
+        <f t="shared" si="2"/>
+        <v>2.64E-2</v>
+      </c>
       <c r="BC67" s="4">
         <v>46140</v>
       </c>
-      <c r="BD67" s="6"/>
-      <c r="BE67" s="6"/>
-      <c r="BF67" s="6"/>
+      <c r="BD67" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE67" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF67" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG67" s="3"/>
       <c r="BH67" s="3"/>
       <c r="BI67" s="3"/>
-      <c r="BJ67" s="6"/>
+      <c r="BJ67" s="6">
+        <v>8.2000000000000007E-3</v>
+      </c>
       <c r="BK67" s="2">
         <v>46140</v>
       </c>
-      <c r="BL67" s="58"/>
+      <c r="BL67" s="58">
+        <v>3.49E-2</v>
+      </c>
       <c r="BM67" s="1"/>
-      <c r="BN67" s="58"/>
+      <c r="BN67" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO67" s="1"/>
       <c r="BP67" s="1"/>
       <c r="BQ67" s="1"/>
-      <c r="BR67" s="58"/>
-      <c r="BS67" s="13"/>
+      <c r="BR67" s="58">
+        <v>2.86E-2</v>
+      </c>
+      <c r="BS67" s="13">
+        <f t="shared" si="3"/>
+        <v>2.0400000000000001E-2</v>
+      </c>
     </row>
     <row r="68" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A68" s="4">
@@ -24835,7 +24947,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25171,7 +25283,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25509,7 +25621,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25847,7 +25959,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26185,7 +26297,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26553,7 +26665,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26921,7 +27033,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27289,7 +27401,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27660,7 +27772,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -28041,7 +28153,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -29505,7 +29617,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -29849,7 +29961,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30193,7 +30305,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30537,7 +30649,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30881,7 +30993,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31213,7 +31325,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31557,7 +31669,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31901,7 +32013,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32248,7 +32360,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32593,7 +32705,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -43289,7 +43401,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -43633,6 +43745,341 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49924784-A315-484D-A216-7D27408723A0}">
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46140</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>2.75E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.99E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5.9400000000000001E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR67</f>
+        <v>2.64E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I10" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z67</f>
+        <v>1.2800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="57"/>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.861457097742421E-2</v>
+      </c>
+      <c r="D5" s="57"/>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8666209355555194E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8699953491705399E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8801503984497451E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.86E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>2.9011754039298232E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ67</f>
+        <v>2.0400000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="55"/>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="55"/>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="55"/>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.1708387706840884E-2</v>
+      </c>
+      <c r="D7" s="55"/>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.1738102014333516E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.1757510124933641E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.1815873182762256E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.1936498152339556E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-0.95%</f>
+        <v>1.2200000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.7906398705557538E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.791386633517404E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7930945209710362E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7963005663145801E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.7995115183913229E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8091738995796145E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>2.8291753567093458E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H67</f>
+        <v>1.9500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+    <row r="10" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="I10" s="74"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J3 J4:J9 I4:I10 A4:H9">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
@@ -51691,7 +52138,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -52054,7 +52501,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52415,7 +52862,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52770,7 +53217,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B2BE53-CCBD-47DA-B7CE-56A15F9BF980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE707F64-AA41-4434-9496-6F80F9770F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -55,6 +55,7 @@
     <sheet name="26.04.2026" sheetId="61" r:id="rId40"/>
     <sheet name="27.04.2026" sheetId="62" r:id="rId41"/>
     <sheet name="28.04.2026" sheetId="63" r:id="rId42"/>
+    <sheet name="29.04.2026" sheetId="64" r:id="rId43"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1407,6 +1408,43 @@
 </comments>
 </file>
 
+<file path=xl/comments39.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{8B41CB9C-C305-4A0E-BF0F-AC6479A1027A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1630,7 +1668,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3400" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3413" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -2339,7 +2377,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="37">
+  <dxfs count="38">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5737,17 +5782,29 @@
       <c r="F119" s="23">
         <v>3.3399999999999999E-2</v>
       </c>
-      <c r="G119" s="90"/>
+      <c r="G119" s="90">
+        <v>77372</v>
+      </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="82">
         <v>46141.125</v>
       </c>
-      <c r="B120" s="82"/>
-      <c r="C120" s="10"/>
-      <c r="D120" s="10"/>
-      <c r="E120" s="10"/>
-      <c r="F120" s="10"/>
+      <c r="B120" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C120" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D120" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E120" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F120" s="23">
+        <v>3.3300000000000003E-2</v>
+      </c>
       <c r="G120" s="90"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
@@ -6441,7 +6498,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6777,7 +6834,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7115,7 +7172,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7451,7 +7508,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7785,7 +7842,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8121,7 +8178,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8457,7 +8514,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8793,7 +8850,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9129,7 +9186,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9465,7 +9522,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10171,7 +10228,7 @@
         <v>0.03</v>
       </c>
       <c r="AI5" s="13">
-        <f t="shared" ref="AI5:AI67" si="1">AH5-Z5</f>
+        <f t="shared" ref="AI5:AI68" si="1">AH5-Z5</f>
         <v>1.8700000000000001E-2</v>
       </c>
       <c r="AK5" s="4">
@@ -10217,7 +10274,7 @@
         <v>3.44E-2</v>
       </c>
       <c r="BA5" s="13">
-        <f t="shared" ref="BA5:BA67" si="2">AZ5-AR5</f>
+        <f t="shared" ref="BA5:BA68" si="2">AZ5-AR5</f>
         <v>2.8400000000000002E-2</v>
       </c>
       <c r="BC5" s="4">
@@ -10255,7 +10312,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS67" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS68" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -22061,7 +22118,9 @@
       <c r="G68" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H68" s="9"/>
+      <c r="H68" s="9">
+        <v>9.5999999999999992E-3</v>
+      </c>
       <c r="I68" s="2">
         <v>46141</v>
       </c>
@@ -22083,10 +22142,12 @@
       <c r="O68" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P68" s="58"/>
+      <c r="P68" s="58">
+        <v>2.9899999999999999E-2</v>
+      </c>
       <c r="Q68" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.0299999999999999E-2</v>
       </c>
       <c r="S68" s="4">
         <v>46141</v>
@@ -22103,11 +22164,15 @@
       <c r="W68" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X68" s="6"/>
+      <c r="X68" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y68" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z68" s="6"/>
+      <c r="Z68" s="6">
+        <v>1.24E-2</v>
+      </c>
       <c r="AA68" s="2">
         <v>46141</v>
       </c>
@@ -22129,50 +22194,97 @@
       <c r="AG68" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH68" s="58"/>
-      <c r="AI68" s="13"/>
+      <c r="AH68" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI68" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2600000000000002E-2</v>
+      </c>
       <c r="AK68" s="4">
         <v>46141</v>
       </c>
-      <c r="AL68" s="3"/>
+      <c r="AL68" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM68" s="3"/>
       <c r="AN68" s="3"/>
       <c r="AO68" s="3"/>
-      <c r="AP68" s="3"/>
-      <c r="AQ68" s="6"/>
-      <c r="AR68" s="6"/>
+      <c r="AP68" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ68" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR68" s="6">
+        <v>7.4999999999999997E-3</v>
+      </c>
       <c r="AS68" s="2">
         <v>46141</v>
       </c>
-      <c r="AT68" s="14"/>
-      <c r="AU68" s="14"/>
-      <c r="AV68" s="14"/>
-      <c r="AW68" s="14"/>
-      <c r="AX68" s="14"/>
-      <c r="AY68" s="14"/>
-      <c r="AZ68" s="14"/>
-      <c r="BA68" s="13"/>
+      <c r="AT68" s="14">
+        <v>2.7E-2</v>
+      </c>
+      <c r="AU68" s="14">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="AV68" s="14">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="AW68" s="14">
+        <v>4.4400000000000002E-2</v>
+      </c>
+      <c r="AX68" s="14">
+        <v>5.7799999999999997E-2</v>
+      </c>
+      <c r="AY68" s="14">
+        <v>5.5E-2</v>
+      </c>
+      <c r="AZ68" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA68" s="13">
+        <f t="shared" si="2"/>
+        <v>2.5399999999999999E-2</v>
+      </c>
       <c r="BC68" s="4">
         <v>46141</v>
       </c>
-      <c r="BD68" s="6"/>
-      <c r="BE68" s="6"/>
-      <c r="BF68" s="6"/>
+      <c r="BD68" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE68" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF68" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG68" s="3"/>
       <c r="BH68" s="3"/>
       <c r="BI68" s="3"/>
-      <c r="BJ68" s="6"/>
+      <c r="BJ68" s="6">
+        <v>8.6E-3</v>
+      </c>
       <c r="BK68" s="2">
         <v>46141</v>
       </c>
-      <c r="BL68" s="58"/>
+      <c r="BL68" s="58">
+        <v>3.61E-2</v>
+      </c>
       <c r="BM68" s="1"/>
-      <c r="BN68" s="58"/>
+      <c r="BN68" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO68" s="1"/>
       <c r="BP68" s="1"/>
       <c r="BQ68" s="1"/>
-      <c r="BR68" s="58"/>
-      <c r="BS68" s="13"/>
+      <c r="BR68" s="58">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="BS68" s="13">
+        <f t="shared" si="3"/>
+        <v>2.1600000000000001E-2</v>
+      </c>
     </row>
     <row r="69" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A69" s="4">
@@ -24947,7 +25059,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25283,7 +25395,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25621,7 +25733,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25959,7 +26071,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26297,7 +26409,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26665,7 +26777,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27033,7 +27145,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27401,7 +27513,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27772,7 +27884,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -28153,7 +28265,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -29617,7 +29729,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -29961,7 +30073,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30305,7 +30417,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30649,7 +30761,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30993,7 +31105,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31325,7 +31437,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31669,7 +31781,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32013,7 +32125,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32360,7 +32472,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32705,7 +32817,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -43401,7 +43513,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -43745,7 +43857,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -43882,7 +43994,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="I4" s="74">
-        <f t="shared" ref="I4:I10" si="1">(1+H4/365)^365-1</f>
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
         <v>2.5314242726610869E-2</v>
       </c>
       <c r="J4" s="75"/>
@@ -44079,7 +44191,339 @@
       <c r="I10" s="74"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:J3 J4:J9 I4:I10 A4:H9">
+  <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087BCCE4-974D-475D-ACEC-0E2AFFA7C214}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46141</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.7E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.4400000000000002E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5.7799999999999997E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>5.5E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR68</f>
+        <v>2.5399999999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z68</f>
+        <v>1.2600000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.0216247184851448E-2</v>
+      </c>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.0273830874697632E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.0311464275388368E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.0424739121945526E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.0659357866290149E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ68</f>
+        <v>2.1600000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-1.2%</f>
+        <v>2.1700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.4010260232618413E-2</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.4046612660404476E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.4070360298483404E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.4141790986210568E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.4E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.4289509719223279E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.05%</f>
+        <v>1.35E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.9907349030706052E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.9915925943969159E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.9935542634702439E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.9972370170845902E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.0009258115333635E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.0120285514699162E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.9899999999999999E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.0350231880070799E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H68</f>
+        <v>2.0299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
@@ -52138,7 +52582,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -52501,7 +52945,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52862,7 +53306,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53217,7 +53661,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE707F64-AA41-4434-9496-6F80F9770F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D26AF2-B37C-4B6A-A652-E4ACC8CC14AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="34" activeTab="43" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -56,6 +56,7 @@
     <sheet name="27.04.2026" sheetId="62" r:id="rId41"/>
     <sheet name="28.04.2026" sheetId="63" r:id="rId42"/>
     <sheet name="29.04.2026" sheetId="64" r:id="rId43"/>
+    <sheet name="30.04.2026" sheetId="65" r:id="rId44"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1482,6 +1483,43 @@
 </comments>
 </file>
 
+<file path=xl/comments40.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{F9FF5C6F-9A93-46BC-8B56-BF6B49EDD17C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1668,7 +1706,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3413" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3426" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -2377,7 +2415,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="38">
+  <dxfs count="39">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5805,17 +5850,29 @@
       <c r="F120" s="23">
         <v>3.3300000000000003E-2</v>
       </c>
-      <c r="G120" s="90"/>
+      <c r="G120" s="90">
+        <v>76342</v>
+      </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="82">
         <v>46142.125</v>
       </c>
-      <c r="B121" s="82"/>
-      <c r="C121" s="10"/>
-      <c r="D121" s="10"/>
-      <c r="E121" s="10"/>
-      <c r="F121" s="10"/>
+      <c r="B121" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C121" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D121" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E121" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F121" s="23">
+        <v>3.5200000000000002E-2</v>
+      </c>
       <c r="G121" s="90"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
@@ -6498,7 +6555,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6834,7 +6891,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7172,7 +7229,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7508,7 +7565,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7842,7 +7899,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8178,7 +8235,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8514,7 +8571,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8850,7 +8907,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9186,7 +9243,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9522,7 +9579,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10228,7 +10285,7 @@
         <v>0.03</v>
       </c>
       <c r="AI5" s="13">
-        <f t="shared" ref="AI5:AI68" si="1">AH5-Z5</f>
+        <f t="shared" ref="AI5:AI69" si="1">AH5-Z5</f>
         <v>1.8700000000000001E-2</v>
       </c>
       <c r="AK5" s="4">
@@ -10274,7 +10331,7 @@
         <v>3.44E-2</v>
       </c>
       <c r="BA5" s="13">
-        <f t="shared" ref="BA5:BA68" si="2">AZ5-AR5</f>
+        <f t="shared" ref="BA5:BA69" si="2">AZ5-AR5</f>
         <v>2.8400000000000002E-2</v>
       </c>
       <c r="BC5" s="4">
@@ -10312,7 +10369,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS68" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS69" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -22308,7 +22365,9 @@
       <c r="G69" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H69" s="9"/>
+      <c r="H69" s="9">
+        <v>9.1000000000000004E-3</v>
+      </c>
       <c r="I69" s="2">
         <v>46142</v>
       </c>
@@ -22330,10 +22389,12 @@
       <c r="O69" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P69" s="58"/>
+      <c r="P69" s="58">
+        <v>2.92E-2</v>
+      </c>
       <c r="Q69" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.01E-2</v>
       </c>
       <c r="S69" s="4">
         <v>46142</v>
@@ -22350,11 +22411,15 @@
       <c r="W69" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X69" s="6"/>
+      <c r="X69" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y69" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z69" s="6"/>
+      <c r="Z69" s="6">
+        <v>1.24E-2</v>
+      </c>
       <c r="AA69" s="2">
         <v>46142</v>
       </c>
@@ -22376,50 +22441,97 @@
       <c r="AG69" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH69" s="58"/>
-      <c r="AI69" s="13"/>
+      <c r="AH69" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI69" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2600000000000002E-2</v>
+      </c>
       <c r="AK69" s="4">
         <v>46142</v>
       </c>
-      <c r="AL69" s="3"/>
+      <c r="AL69" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM69" s="3"/>
       <c r="AN69" s="3"/>
       <c r="AO69" s="3"/>
-      <c r="AP69" s="3"/>
-      <c r="AQ69" s="6"/>
-      <c r="AR69" s="6"/>
+      <c r="AP69" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ69" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR69" s="6">
+        <v>7.4999999999999997E-3</v>
+      </c>
       <c r="AS69" s="2">
         <v>46142</v>
       </c>
-      <c r="AT69" s="14"/>
-      <c r="AU69" s="14"/>
-      <c r="AV69" s="14"/>
-      <c r="AW69" s="14"/>
-      <c r="AX69" s="14"/>
-      <c r="AY69" s="14"/>
-      <c r="AZ69" s="14"/>
-      <c r="BA69" s="13"/>
+      <c r="AT69" s="14">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="AU69" s="14">
+        <v>2.7E-2</v>
+      </c>
+      <c r="AV69" s="14">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="AW69" s="14">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="AX69" s="14">
+        <v>5.7599999999999998E-2</v>
+      </c>
+      <c r="AY69" s="14">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="AZ69" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA69" s="13">
+        <f t="shared" si="2"/>
+        <v>2.5399999999999999E-2</v>
+      </c>
       <c r="BC69" s="4">
         <v>46142</v>
       </c>
-      <c r="BD69" s="6"/>
-      <c r="BE69" s="6"/>
-      <c r="BF69" s="6"/>
+      <c r="BD69" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE69" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF69" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG69" s="3"/>
       <c r="BH69" s="3"/>
       <c r="BI69" s="3"/>
-      <c r="BJ69" s="6"/>
+      <c r="BJ69" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
       <c r="BK69" s="2">
         <v>46142</v>
       </c>
-      <c r="BL69" s="58"/>
+      <c r="BL69" s="58">
+        <v>3.5400000000000001E-2</v>
+      </c>
       <c r="BM69" s="1"/>
-      <c r="BN69" s="58"/>
+      <c r="BN69" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO69" s="1"/>
       <c r="BP69" s="1"/>
       <c r="BQ69" s="1"/>
-      <c r="BR69" s="58"/>
-      <c r="BS69" s="13"/>
+      <c r="BR69" s="58">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="BS69" s="13">
+        <f t="shared" si="3"/>
+        <v>2.1100000000000001E-2</v>
+      </c>
     </row>
     <row r="70" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A70" s="4">
@@ -25059,7 +25171,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25395,7 +25507,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25733,7 +25845,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26071,7 +26183,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26409,7 +26521,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26777,7 +26889,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27145,7 +27257,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27513,7 +27625,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27884,7 +27996,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -28265,7 +28377,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -29729,7 +29841,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30073,7 +30185,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30417,7 +30529,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30761,7 +30873,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31105,7 +31217,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31437,7 +31549,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31781,7 +31893,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32125,7 +32237,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32472,7 +32584,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32817,7 +32929,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -43513,7 +43625,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -43857,7 +43969,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44192,7 +44304,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44482,6 +44594,350 @@
       <c r="K8" s="68">
         <f>H8-'Daily Data'!H68</f>
         <v>2.0299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5861F84E-A3EB-4639-8D15-05F5ED0FF1A4}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46142</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>2.7E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5.7599999999999998E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR69</f>
+        <v>2.5399999999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z69</f>
+        <v>1.2600000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>3.5400000000000001E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.9515502614004818E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.957044530350909E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.9606350952279013E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.9714417036530872E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>2.9938207723953836E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ69</f>
+        <v>2.1100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>2.4299999999999999E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.3209587533257667E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.3243555094752066E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.3265743559169324E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.3332478537392582E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.3199999999999998E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.3470458733289679E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.01%</f>
+        <v>1.3099999999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.9207008934516918E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.9215188859992698E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.9233897304799861E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.9269018705551892E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.9304196365779224E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.9410067918132683E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.92E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>2.9629297440349367E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H69</f>
+        <v>2.01E-2</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
@@ -52582,7 +53038,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -52945,7 +53401,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53306,7 +53762,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53661,7 +54117,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D26AF2-B37C-4B6A-A652-E4ACC8CC14AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6A044B-7E3A-41F5-AA05-A03231B3BDF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="34" activeTab="43" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="38" activeTab="47" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -57,6 +57,10 @@
     <sheet name="28.04.2026" sheetId="63" r:id="rId42"/>
     <sheet name="29.04.2026" sheetId="64" r:id="rId43"/>
     <sheet name="30.04.2026" sheetId="65" r:id="rId44"/>
+    <sheet name="01.05.2026" sheetId="66" r:id="rId45"/>
+    <sheet name="02.05.2026" sheetId="67" r:id="rId46"/>
+    <sheet name="03.05.2026" sheetId="68" r:id="rId47"/>
+    <sheet name="04.05.2026" sheetId="69" r:id="rId48"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1520,6 +1524,154 @@
 </comments>
 </file>
 
+<file path=xl/comments41.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{83D41F6F-9298-46EC-9FD6-BC10F70FF32C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments42.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{606C2CA7-187E-4D73-876D-3420A1776794}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments43.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{0A75DC11-6F7F-4893-9F3A-4080C8C3F4AD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments44.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{DE312728-AB1D-409E-8FD7-C83D40FD7831}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1706,7 +1858,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3426" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3478" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -2415,7 +2567,84 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="39">
+  <dxfs count="50">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5873,97 +6102,220 @@
       <c r="F121" s="23">
         <v>3.5200000000000002E-2</v>
       </c>
-      <c r="G121" s="90"/>
+      <c r="G121" s="90">
+        <v>75780</v>
+      </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A122" s="80"/>
-      <c r="B122" s="80"/>
+      <c r="A122" s="82">
+        <v>46143</v>
+      </c>
+      <c r="B122" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C122" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D122" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E122" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F122" s="23">
+        <v>3.4099999999999998E-2</v>
+      </c>
+      <c r="G122" s="90">
+        <v>76347</v>
+      </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A123" s="80"/>
-      <c r="B123" s="80"/>
+      <c r="A123" s="82">
+        <v>46144</v>
+      </c>
+      <c r="B123" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C123" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D123" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E123" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F123" s="23">
+        <v>3.4299999999999997E-2</v>
+      </c>
+      <c r="G123" s="90">
+        <v>78232</v>
+      </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A124" s="80"/>
-      <c r="B124" s="80"/>
+      <c r="A124" s="82">
+        <v>46145</v>
+      </c>
+      <c r="B124" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C124" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D124" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E124" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F124" s="23">
+        <v>0.03</v>
+      </c>
+      <c r="G124" s="90">
+        <v>78687</v>
+      </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A125" s="80"/>
-      <c r="B125" s="80"/>
+      <c r="A125" s="82">
+        <v>46146</v>
+      </c>
+      <c r="B125" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C125" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D125" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E125" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F125" s="23">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G125" s="90">
+        <v>78569</v>
+      </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A126" s="80"/>
-      <c r="B126" s="80"/>
+      <c r="A126" s="82">
+        <v>46147</v>
+      </c>
+      <c r="B126" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C126" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D126" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E126" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F126" s="23">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="G126" s="90"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A127" s="80"/>
-      <c r="B127" s="80"/>
+      <c r="A127" s="82">
+        <v>46148</v>
+      </c>
+      <c r="B127" s="83"/>
+      <c r="C127" s="23"/>
+      <c r="D127" s="23"/>
+      <c r="E127" s="23"/>
+      <c r="F127" s="23"/>
+      <c r="G127" s="90"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A128" s="80"/>
-      <c r="B128" s="80"/>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A129" s="80"/>
-      <c r="B129" s="80"/>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A130" s="80"/>
-      <c r="B130" s="80"/>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A128" s="82">
+        <v>46149</v>
+      </c>
+      <c r="B128" s="83"/>
+      <c r="C128" s="23"/>
+      <c r="D128" s="23"/>
+      <c r="E128" s="23"/>
+      <c r="F128" s="23"/>
+      <c r="G128" s="90"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A129" s="82">
+        <v>46150</v>
+      </c>
+      <c r="B129" s="83"/>
+      <c r="C129" s="23"/>
+      <c r="D129" s="23"/>
+      <c r="E129" s="23"/>
+      <c r="F129" s="23"/>
+      <c r="G129" s="90"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A130" s="82">
+        <v>46151</v>
+      </c>
+      <c r="B130" s="83"/>
+      <c r="C130" s="23"/>
+      <c r="D130" s="23"/>
+      <c r="E130" s="23"/>
+      <c r="F130" s="23"/>
+      <c r="G130" s="90"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="80"/>
       <c r="B131" s="80"/>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="80"/>
       <c r="B132" s="80"/>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="80"/>
       <c r="B133" s="80"/>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="80"/>
       <c r="B134" s="80"/>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="80"/>
       <c r="B135" s="80"/>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="80"/>
       <c r="B136" s="80"/>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="80"/>
       <c r="B137" s="80"/>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="80"/>
       <c r="B138" s="80"/>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="80"/>
       <c r="B139" s="80"/>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="80"/>
       <c r="B140" s="80"/>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="80"/>
       <c r="B141" s="80"/>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="80"/>
       <c r="B142" s="80"/>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="80"/>
       <c r="B143" s="80"/>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="80"/>
       <c r="B144" s="80"/>
     </row>
@@ -6555,7 +6907,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6891,7 +7243,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7229,7 +7581,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7565,7 +7917,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7899,7 +8251,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8235,7 +8587,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8571,7 +8923,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8907,7 +9259,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9243,7 +9595,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9579,7 +9931,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10285,7 +10637,7 @@
         <v>0.03</v>
       </c>
       <c r="AI5" s="13">
-        <f t="shared" ref="AI5:AI69" si="1">AH5-Z5</f>
+        <f t="shared" ref="AI5:AI73" si="1">AH5-Z5</f>
         <v>1.8700000000000001E-2</v>
       </c>
       <c r="AK5" s="4">
@@ -10331,7 +10683,7 @@
         <v>3.44E-2</v>
       </c>
       <c r="BA5" s="13">
-        <f t="shared" ref="BA5:BA69" si="2">AZ5-AR5</f>
+        <f t="shared" ref="BA5:BA70" si="2">AZ5-AR5</f>
         <v>2.8400000000000002E-2</v>
       </c>
       <c r="BC5" s="4">
@@ -10369,7 +10721,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS69" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS73" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -22555,7 +22907,9 @@
       <c r="G70" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H70" s="9"/>
+      <c r="H70" s="9">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="I70" s="2">
         <v>46143</v>
       </c>
@@ -22577,10 +22931,12 @@
       <c r="O70" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P70" s="58"/>
+      <c r="P70" s="58">
+        <v>2.9700000000000001E-2</v>
+      </c>
       <c r="Q70" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="S70" s="4">
         <v>46143</v>
@@ -22597,11 +22953,15 @@
       <c r="W70" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X70" s="6"/>
+      <c r="X70" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y70" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z70" s="6"/>
+      <c r="Z70" s="6">
+        <v>1.24E-2</v>
+      </c>
       <c r="AA70" s="2">
         <v>46143</v>
       </c>
@@ -22623,50 +22983,97 @@
       <c r="AG70" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH70" s="58"/>
-      <c r="AI70" s="13"/>
+      <c r="AH70" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI70" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2600000000000002E-2</v>
+      </c>
       <c r="AK70" s="4">
         <v>46143</v>
       </c>
-      <c r="AL70" s="3"/>
+      <c r="AL70" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM70" s="3"/>
       <c r="AN70" s="3"/>
       <c r="AO70" s="3"/>
-      <c r="AP70" s="3"/>
-      <c r="AQ70" s="6"/>
-      <c r="AR70" s="6"/>
+      <c r="AP70" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ70" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR70" s="6">
+        <v>6.7000000000000002E-3</v>
+      </c>
       <c r="AS70" s="2">
         <v>46143</v>
       </c>
-      <c r="AT70" s="14"/>
-      <c r="AU70" s="14"/>
-      <c r="AV70" s="14"/>
-      <c r="AW70" s="14"/>
-      <c r="AX70" s="14"/>
-      <c r="AY70" s="14"/>
-      <c r="AZ70" s="14"/>
-      <c r="BA70" s="13"/>
+      <c r="AT70" s="14">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="AU70" s="14">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="AV70" s="14">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AW70" s="14">
+        <v>4.3900000000000002E-2</v>
+      </c>
+      <c r="AX70" s="14">
+        <v>5.3900000000000003E-2</v>
+      </c>
+      <c r="AY70" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="AZ70" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA70" s="13">
+        <f t="shared" si="2"/>
+        <v>2.6199999999999998E-2</v>
+      </c>
       <c r="BC70" s="4">
         <v>46143</v>
       </c>
-      <c r="BD70" s="6"/>
-      <c r="BE70" s="6"/>
-      <c r="BF70" s="6"/>
+      <c r="BD70" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE70" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF70" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG70" s="3"/>
       <c r="BH70" s="3"/>
       <c r="BI70" s="3"/>
-      <c r="BJ70" s="6"/>
+      <c r="BJ70" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
       <c r="BK70" s="2">
         <v>46143</v>
       </c>
-      <c r="BL70" s="58"/>
+      <c r="BL70" s="58">
+        <v>3.49E-2</v>
+      </c>
       <c r="BM70" s="1"/>
-      <c r="BN70" s="58"/>
+      <c r="BN70" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO70" s="1"/>
       <c r="BP70" s="1"/>
       <c r="BQ70" s="1"/>
-      <c r="BR70" s="58"/>
-      <c r="BS70" s="13"/>
+      <c r="BR70" s="58">
+        <v>2.98E-2</v>
+      </c>
+      <c r="BS70" s="13">
+        <f t="shared" si="3"/>
+        <v>2.1299999999999999E-2</v>
+      </c>
     </row>
     <row r="71" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A71" s="4">
@@ -22690,7 +23097,9 @@
       <c r="G71" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H71" s="9"/>
+      <c r="H71" s="9">
+        <v>8.0999999999999996E-3</v>
+      </c>
       <c r="I71" s="2">
         <v>46144</v>
       </c>
@@ -22712,10 +23121,12 @@
       <c r="O71" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P71" s="58"/>
+      <c r="P71" s="58">
+        <v>2.8299999999999999E-2</v>
+      </c>
       <c r="Q71" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.0199999999999999E-2</v>
       </c>
       <c r="S71" s="4">
         <v>46144</v>
@@ -22732,11 +23143,15 @@
       <c r="W71" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X71" s="6"/>
+      <c r="X71" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y71" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z71" s="6"/>
+      <c r="Z71" s="6">
+        <v>1.2500000000000001E-2</v>
+      </c>
       <c r="AA71" s="2">
         <v>46144</v>
       </c>
@@ -22758,50 +23173,97 @@
       <c r="AG71" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH71" s="58"/>
-      <c r="AI71" s="13"/>
+      <c r="AH71" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI71" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2500000000000001E-2</v>
+      </c>
       <c r="AK71" s="4">
         <v>46144</v>
       </c>
-      <c r="AL71" s="3"/>
+      <c r="AL71" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM71" s="3"/>
       <c r="AN71" s="3"/>
       <c r="AO71" s="3"/>
-      <c r="AP71" s="3"/>
-      <c r="AQ71" s="6"/>
-      <c r="AR71" s="6"/>
+      <c r="AP71" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ71" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR71" s="6">
+        <v>6.7000000000000002E-3</v>
+      </c>
       <c r="AS71" s="2">
         <v>46144</v>
       </c>
-      <c r="AT71" s="14"/>
-      <c r="AU71" s="14"/>
-      <c r="AV71" s="14"/>
-      <c r="AW71" s="14"/>
-      <c r="AX71" s="14"/>
-      <c r="AY71" s="14"/>
-      <c r="AZ71" s="14"/>
-      <c r="BA71" s="13"/>
+      <c r="AT71" s="14">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="AU71" s="14">
+        <v>2.75E-2</v>
+      </c>
+      <c r="AV71" s="14">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AW71" s="14">
+        <v>4.3900000000000002E-2</v>
+      </c>
+      <c r="AX71" s="14">
+        <v>5.3900000000000003E-2</v>
+      </c>
+      <c r="AY71" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="AZ71" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA71" s="13">
+        <f t="shared" ref="BA71:BA73" si="5">AZ71-AR71</f>
+        <v>2.6199999999999998E-2</v>
+      </c>
       <c r="BC71" s="4">
         <v>46144</v>
       </c>
-      <c r="BD71" s="6"/>
-      <c r="BE71" s="6"/>
-      <c r="BF71" s="6"/>
+      <c r="BD71" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE71" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF71" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG71" s="3"/>
       <c r="BH71" s="3"/>
       <c r="BI71" s="3"/>
-      <c r="BJ71" s="6"/>
+      <c r="BJ71" s="6">
+        <v>7.9000000000000008E-3</v>
+      </c>
       <c r="BK71" s="2">
         <v>46144</v>
       </c>
-      <c r="BL71" s="58"/>
+      <c r="BL71" s="58">
+        <v>3.49E-2</v>
+      </c>
       <c r="BM71" s="1"/>
-      <c r="BN71" s="58"/>
+      <c r="BN71" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO71" s="1"/>
       <c r="BP71" s="1"/>
       <c r="BQ71" s="1"/>
-      <c r="BR71" s="58"/>
-      <c r="BS71" s="13"/>
+      <c r="BR71" s="58">
+        <v>2.8299999999999999E-2</v>
+      </c>
+      <c r="BS71" s="13">
+        <f t="shared" si="3"/>
+        <v>2.0399999999999998E-2</v>
+      </c>
     </row>
     <row r="72" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A72" s="4">
@@ -22825,7 +23287,9 @@
       <c r="G72" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H72" s="9"/>
+      <c r="H72" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
       <c r="I72" s="2">
         <v>46145</v>
       </c>
@@ -22847,10 +23311,12 @@
       <c r="O72" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P72" s="58"/>
+      <c r="P72" s="58">
+        <v>2.81E-2</v>
+      </c>
       <c r="Q72" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.01E-2</v>
       </c>
       <c r="S72" s="4">
         <v>46145</v>
@@ -22867,11 +23333,15 @@
       <c r="W72" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X72" s="6"/>
+      <c r="X72" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y72" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z72" s="6"/>
+      <c r="Z72" s="6">
+        <v>1.24E-2</v>
+      </c>
       <c r="AA72" s="2">
         <v>46145</v>
       </c>
@@ -22893,50 +23363,97 @@
       <c r="AG72" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH72" s="58"/>
-      <c r="AI72" s="13"/>
+      <c r="AH72" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI72" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2600000000000002E-2</v>
+      </c>
       <c r="AK72" s="4">
         <v>46145</v>
       </c>
-      <c r="AL72" s="3"/>
+      <c r="AL72" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM72" s="3"/>
       <c r="AN72" s="3"/>
       <c r="AO72" s="3"/>
-      <c r="AP72" s="3"/>
-      <c r="AQ72" s="6"/>
-      <c r="AR72" s="6"/>
+      <c r="AP72" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ72" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR72" s="6">
+        <v>6.7000000000000002E-3</v>
+      </c>
       <c r="AS72" s="2">
         <v>46145</v>
       </c>
-      <c r="AT72" s="14"/>
-      <c r="AU72" s="14"/>
-      <c r="AV72" s="14"/>
-      <c r="AW72" s="14"/>
-      <c r="AX72" s="14"/>
-      <c r="AY72" s="14"/>
-      <c r="AZ72" s="14"/>
-      <c r="BA72" s="13"/>
+      <c r="AT72" s="14">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="AU72" s="14">
+        <v>2.75E-2</v>
+      </c>
+      <c r="AV72" s="14">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AW72" s="14">
+        <v>4.3900000000000002E-2</v>
+      </c>
+      <c r="AX72" s="14">
+        <v>5.3900000000000003E-2</v>
+      </c>
+      <c r="AY72" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="AZ72" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA72" s="13">
+        <f t="shared" si="5"/>
+        <v>2.6199999999999998E-2</v>
+      </c>
       <c r="BC72" s="4">
         <v>46145</v>
       </c>
-      <c r="BD72" s="6"/>
-      <c r="BE72" s="6"/>
-      <c r="BF72" s="6"/>
+      <c r="BD72" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE72" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF72" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG72" s="3"/>
       <c r="BH72" s="3"/>
       <c r="BI72" s="3"/>
-      <c r="BJ72" s="6"/>
+      <c r="BJ72" s="6">
+        <v>7.7999999999999996E-3</v>
+      </c>
       <c r="BK72" s="2">
         <v>46145</v>
       </c>
-      <c r="BL72" s="58"/>
+      <c r="BL72" s="58">
+        <v>3.49E-2</v>
+      </c>
       <c r="BM72" s="1"/>
-      <c r="BN72" s="58"/>
+      <c r="BN72" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO72" s="1"/>
       <c r="BP72" s="1"/>
       <c r="BQ72" s="1"/>
-      <c r="BR72" s="58"/>
-      <c r="BS72" s="13"/>
+      <c r="BR72" s="58">
+        <v>2.7300000000000001E-2</v>
+      </c>
+      <c r="BS72" s="13">
+        <f t="shared" si="3"/>
+        <v>1.9500000000000003E-2</v>
+      </c>
     </row>
     <row r="73" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A73" s="4">
@@ -22960,7 +23477,9 @@
       <c r="G73" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H73" s="9"/>
+      <c r="H73" s="9">
+        <v>8.8000000000000005E-3</v>
+      </c>
       <c r="I73" s="2">
         <v>46146</v>
       </c>
@@ -22982,10 +23501,12 @@
       <c r="O73" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P73" s="58"/>
+      <c r="P73" s="58">
+        <v>2.86E-2</v>
+      </c>
       <c r="Q73" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.9799999999999998E-2</v>
       </c>
       <c r="S73" s="4">
         <v>46146</v>
@@ -23002,11 +23523,15 @@
       <c r="W73" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X73" s="6"/>
+      <c r="X73" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y73" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z73" s="6"/>
+      <c r="Z73" s="6">
+        <v>1.2699999999999999E-2</v>
+      </c>
       <c r="AA73" s="2">
         <v>46146</v>
       </c>
@@ -23028,50 +23553,97 @@
       <c r="AG73" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH73" s="58"/>
-      <c r="AI73" s="13"/>
+      <c r="AH73" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI73" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2300000000000002E-2</v>
+      </c>
       <c r="AK73" s="4">
         <v>46146</v>
       </c>
-      <c r="AL73" s="3"/>
+      <c r="AL73" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM73" s="3"/>
       <c r="AN73" s="3"/>
       <c r="AO73" s="3"/>
-      <c r="AP73" s="3"/>
-      <c r="AQ73" s="6"/>
-      <c r="AR73" s="6"/>
+      <c r="AP73" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ73" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR73" s="6">
+        <v>7.3000000000000001E-3</v>
+      </c>
       <c r="AS73" s="2">
         <v>46146</v>
       </c>
-      <c r="AT73" s="14"/>
-      <c r="AU73" s="14"/>
-      <c r="AV73" s="14"/>
-      <c r="AW73" s="14"/>
-      <c r="AX73" s="14"/>
-      <c r="AY73" s="14"/>
-      <c r="AZ73" s="14"/>
-      <c r="BA73" s="13"/>
+      <c r="AT73" s="14">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="AU73" s="14">
+        <v>2.75E-2</v>
+      </c>
+      <c r="AV73" s="14">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AW73" s="14">
+        <v>4.3900000000000002E-2</v>
+      </c>
+      <c r="AX73" s="14">
+        <v>5.3900000000000003E-2</v>
+      </c>
+      <c r="AY73" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="AZ73" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA73" s="13">
+        <f t="shared" si="5"/>
+        <v>2.5599999999999998E-2</v>
+      </c>
       <c r="BC73" s="4">
         <v>46146</v>
       </c>
-      <c r="BD73" s="6"/>
-      <c r="BE73" s="6"/>
-      <c r="BF73" s="6"/>
+      <c r="BD73" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE73" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF73" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG73" s="3"/>
       <c r="BH73" s="3"/>
       <c r="BI73" s="3"/>
-      <c r="BJ73" s="6"/>
+      <c r="BJ73" s="6">
+        <v>8.0000000000000002E-3</v>
+      </c>
       <c r="BK73" s="2">
         <v>46146</v>
       </c>
-      <c r="BL73" s="58"/>
+      <c r="BL73" s="58">
+        <v>3.49E-2</v>
+      </c>
       <c r="BM73" s="1"/>
-      <c r="BN73" s="58"/>
+      <c r="BN73" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO73" s="1"/>
       <c r="BP73" s="1"/>
       <c r="BQ73" s="1"/>
-      <c r="BR73" s="58"/>
-      <c r="BS73" s="13"/>
+      <c r="BR73" s="58">
+        <v>2.81E-2</v>
+      </c>
+      <c r="BS73" s="13">
+        <f t="shared" si="3"/>
+        <v>2.01E-2</v>
+      </c>
     </row>
     <row r="74" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A74" s="4">
@@ -25171,7 +25743,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25507,7 +26079,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25845,7 +26417,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26183,7 +26755,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26521,7 +27093,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26889,7 +27461,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27257,7 +27829,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27625,7 +28197,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27996,7 +28568,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -28377,7 +28949,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -29841,7 +30413,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30185,7 +30757,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30529,7 +31101,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30873,7 +31445,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31217,7 +31789,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31549,7 +32121,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31893,7 +32465,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32237,7 +32809,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32584,7 +33156,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32929,7 +33501,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -43625,7 +44197,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -43969,7 +44541,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44304,7 +44876,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44636,7 +45208,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44980,11 +45552,1419 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
       <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1318DD74-AF09-4FA7-915C-A92EC7B9A56C}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46143</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.3900000000000002E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5.3900000000000003E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>0.05</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR70</f>
+        <v>2.6199999999999998E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z70</f>
+        <v>1.2600000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="57">
+        <v>3.49E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.9815819576702873E-2</v>
+      </c>
+      <c r="D5" s="57">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.9871886517863155E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.9908527640715526E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.0018810931547121E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.98E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.0247210433201888E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ70</f>
+        <v>2.1299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="57">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="56">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="57">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="56">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="56">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="56">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="57">
+        <v>2.63E-2</v>
+      </c>
+      <c r="C7" s="56">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.4510692254110272E-2</v>
+      </c>
+      <c r="D7" s="57">
+        <v>2.75E-2</v>
+      </c>
+      <c r="E7" s="56">
+        <f t="shared" si="4"/>
+        <v>2.4548576373024433E-2</v>
+      </c>
+      <c r="F7" s="56">
+        <f t="shared" si="4"/>
+        <v>2.457332546501876E-2</v>
+      </c>
+      <c r="G7" s="56">
+        <f t="shared" si="4"/>
+        <v>2.4647772518713307E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.4500000000000001E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.4801748490785425E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-0.94%</f>
+        <v>1.5100000000000002E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="56">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.9707251038128626E-2</v>
+      </c>
+      <c r="C8" s="56">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.97157135659997E-2</v>
+      </c>
+      <c r="D8" s="56">
+        <f t="shared" si="5"/>
+        <v>2.9735068558820243E-2</v>
+      </c>
+      <c r="E8" s="56">
+        <f t="shared" si="5"/>
+        <v>2.9771404489047876E-2</v>
+      </c>
+      <c r="F8" s="56">
+        <f t="shared" si="5"/>
+        <v>2.9807799622090583E-2</v>
+      </c>
+      <c r="G8" s="56">
+        <f t="shared" si="5"/>
+        <v>2.991734132434765E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.9700000000000001E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.0144199258958837E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H70</f>
+        <v>2.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="11" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7FC2505-CC41-4CA2-9D7A-DD2D1DABD304}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46144</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>2.75E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.3900000000000002E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5.3900000000000003E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>0.05</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR71</f>
+        <v>2.6199999999999998E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z71</f>
+        <v>1.2500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="57">
+        <v>3.49E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.8314266848908365E-2</v>
+      </c>
+      <c r="D5" s="57">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8364826602223003E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8397865201035391E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8497289156265086E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.8299999999999999E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>2.8703120866840903E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ71</f>
+        <v>2.0399999999999998E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="55">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="55">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="55">
+        <v>2.63E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.5611674069389738E-2</v>
+      </c>
+      <c r="D7" s="55">
+        <v>2.75E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.5653039346812418E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.5680064688384588E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.576136868155746E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.5600000000000001E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.5929573201264544E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-0.94%</f>
+        <v>1.6200000000000003E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.8306583508236022E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.8314266848908365E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8331839214008798E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8364826602223003E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8397865201035391E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8497289156265086E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.8299999999999999E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>2.8703120866840903E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H71</f>
+        <v>2.0199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="7" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1605D5E-D928-4AD2-B15A-9912B7DC07B2}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46145</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>2.75E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.3900000000000002E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5.3900000000000003E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>0.05</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR72</f>
+        <v>2.6199999999999998E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z72</f>
+        <v>1.2600000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="57">
+        <v>3.49E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.7313276259254522E-2</v>
+      </c>
+      <c r="D5" s="57">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.7360322962594403E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.7391063801394545E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.7483562888867545E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.7300000000000001E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>2.7675010192383942E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ72</f>
+        <v>1.9500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="55">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="55">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="55">
+        <v>2.63E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.5611674069389738E-2</v>
+      </c>
+      <c r="D7" s="55">
+        <v>2.75E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.5653039346812418E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.5680064688384588E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.576136868155746E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.5600000000000001E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.5929573201264544E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-0.98%</f>
+        <v>1.5800000000000002E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.8106490777993605E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.8114065879042336E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8131390619379859E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8163912885332154E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8196485282603719E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8294504132474804E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.81E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>2.8497416706523726E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H72</f>
+        <v>2.01E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J4 A8:J9 A5:A7 C5:C7 E5:J7">
+    <cfRule type="expression" dxfId="6" priority="5">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B7">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>_xlfn.ISFORMULA(B5)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4">
+      <formula>_xlfn.ISFORMULA(B5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5:D7">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>_xlfn.ISFORMULA(D5)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(D5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{213ECE2A-375A-45BB-837C-D28481160CEB}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46146</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>2.75E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.3900000000000002E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5.3900000000000003E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>0.05</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR73</f>
+        <v>2.5599999999999998E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z73</f>
+        <v>1.2300000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="57">
+        <v>3.49E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.8114065879042336E-2</v>
+      </c>
+      <c r="D5" s="57">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8163912885332154E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8196485282603719E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8294504132474804E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.81E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>2.8497416706523726E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ73</f>
+        <v>2.01E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="55">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="55">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="55">
+        <v>2.63E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D7" s="55">
+        <v>2.75E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-0.98%</f>
+        <v>1.5200000000000002E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.8606723836956154E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.861457097742421E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8632518077824447E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8666209355555194E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8699953491705399E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8801503984497451E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.86E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>2.9011754039298232E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H73</f>
+        <v>1.9799999999999998E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J4 A8:J9 A5:A7 E5:J7 C5:C7">
+    <cfRule type="expression" dxfId="5" priority="5">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5:D7">
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>_xlfn.ISFORMULA(D5)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4">
+      <formula>_xlfn.ISFORMULA(D5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B7">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>_xlfn.ISFORMULA(B5)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -53038,7 +55018,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -53401,7 +55381,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="48" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53762,7 +55742,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54117,7 +56097,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6A044B-7E3A-41F5-AA05-A03231B3BDF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DDA91F-E788-4EA3-ABF5-F2A2354D9FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="38" activeTab="47" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -2567,56 +2567,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="50">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="43">
     <dxf>
       <fill>
         <patternFill>
@@ -6192,7 +6143,7 @@
         <v>3.1099999999999999E-2</v>
       </c>
       <c r="F125" s="23">
-        <v>0.28000000000000003</v>
+        <v>3.2800000000000003E-2</v>
       </c>
       <c r="G125" s="90">
         <v>78569</v>
@@ -6202,21 +6153,11 @@
       <c r="A126" s="82">
         <v>46147</v>
       </c>
-      <c r="B126" s="83">
-        <v>2.9499999999999998E-2</v>
-      </c>
-      <c r="C126" s="23">
-        <v>2.47E-2</v>
-      </c>
-      <c r="D126" s="23">
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="E126" s="23">
-        <v>3.1099999999999999E-2</v>
-      </c>
-      <c r="F126" s="23">
-        <v>3.2199999999999999E-2</v>
-      </c>
+      <c r="B126" s="83"/>
+      <c r="C126" s="23"/>
+      <c r="D126" s="23"/>
+      <c r="E126" s="23"/>
+      <c r="F126" s="23"/>
       <c r="G126" s="90"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
@@ -6907,7 +6848,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7243,7 +7184,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="44" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7581,7 +7522,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7917,7 +7858,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8251,7 +8192,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8587,7 +8528,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8923,7 +8864,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9259,7 +9200,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9595,7 +9536,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9931,7 +9872,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25743,7 +25684,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26079,7 +26020,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26417,7 +26358,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26755,7 +26696,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27093,7 +27034,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27461,7 +27402,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27829,7 +27770,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28197,7 +28138,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28568,7 +28509,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -28949,7 +28890,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30413,7 +30354,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30757,7 +30698,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31101,7 +31042,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31445,7 +31386,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31789,7 +31730,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32121,7 +32062,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32465,7 +32406,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32809,7 +32750,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33156,7 +33097,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33501,7 +33442,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44197,7 +44138,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44541,7 +44482,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44876,7 +44817,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45208,7 +45149,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45896,7 +45837,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46240,7 +46181,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46583,28 +46524,12 @@
       <c r="K9" s="69"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:J4 A8:J9 A5:A7 C5:C7 E5:J7">
-    <cfRule type="expression" dxfId="6" priority="5">
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
-    <cfRule type="expression" priority="6">
+    <cfRule type="expression" priority="2">
       <formula>_xlfn.ISFORMULA(A1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B7">
-    <cfRule type="expression" dxfId="3" priority="3">
-      <formula>_xlfn.ISFORMULA(B5)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4">
-      <formula>_xlfn.ISFORMULA(B5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D7">
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>_xlfn.ISFORMULA(D5)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2">
-      <formula>_xlfn.ISFORMULA(D5)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -46943,28 +46868,12 @@
       <c r="K9" s="69"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:J4 A8:J9 A5:A7 E5:J7 C5:C7">
-    <cfRule type="expression" dxfId="5" priority="5">
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
-    <cfRule type="expression" priority="6">
+    <cfRule type="expression" priority="2">
       <formula>_xlfn.ISFORMULA(A1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D7">
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>_xlfn.ISFORMULA(D5)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4">
-      <formula>_xlfn.ISFORMULA(D5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B7">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>_xlfn.ISFORMULA(B5)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2">
-      <formula>_xlfn.ISFORMULA(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55018,7 +54927,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="49" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -55381,7 +55290,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -55742,7 +55651,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56097,7 +56006,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="46" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DDA91F-E788-4EA3-ABF5-F2A2354D9FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B1E5202-75E5-407C-8880-C0B4D979DE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="39" activeTab="48" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -61,6 +61,7 @@
     <sheet name="02.05.2026" sheetId="67" r:id="rId46"/>
     <sheet name="03.05.2026" sheetId="68" r:id="rId47"/>
     <sheet name="04.05.2026" sheetId="69" r:id="rId48"/>
+    <sheet name="05.05.2026" sheetId="70" r:id="rId49"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1672,6 +1673,43 @@
 </comments>
 </file>
 
+<file path=xl/comments45.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{A44D2B25-B8D7-46A8-BB09-259EBF75EAA9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1858,7 +1896,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3478" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3491" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -2567,7 +2605,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="43">
+  <dxfs count="44">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2893,7 +2938,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>351448</xdr:colOff>
+      <xdr:colOff>354623</xdr:colOff>
       <xdr:row>121</xdr:row>
       <xdr:rowOff>20630</xdr:rowOff>
     </xdr:to>
@@ -6143,7 +6188,7 @@
         <v>3.1099999999999999E-2</v>
       </c>
       <c r="F125" s="23">
-        <v>3.2800000000000003E-2</v>
+        <v>3.2199999999999999E-2</v>
       </c>
       <c r="G125" s="90">
         <v>78569</v>
@@ -6153,11 +6198,21 @@
       <c r="A126" s="82">
         <v>46147</v>
       </c>
-      <c r="B126" s="83"/>
-      <c r="C126" s="23"/>
-      <c r="D126" s="23"/>
-      <c r="E126" s="23"/>
-      <c r="F126" s="23"/>
+      <c r="B126" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C126" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D126" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E126" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F126" s="23">
+        <v>3.27E-2</v>
+      </c>
       <c r="G126" s="90"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
@@ -6848,7 +6903,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7184,7 +7239,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7522,7 +7577,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7858,7 +7913,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8192,7 +8247,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8528,7 +8583,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8864,7 +8919,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9200,7 +9255,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9536,7 +9591,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9872,7 +9927,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9914,7 +9969,8 @@
     <col min="45" max="45" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="6.1796875" bestFit="1" customWidth="1"/>
     <col min="47" max="48" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="49" max="51" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="50" max="51" width="6.1796875" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="7.08984375" bestFit="1" customWidth="1"/>
     <col min="55" max="55" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="56" max="58" width="6.1796875" bestFit="1" customWidth="1"/>
@@ -10578,7 +10634,7 @@
         <v>0.03</v>
       </c>
       <c r="AI5" s="13">
-        <f t="shared" ref="AI5:AI73" si="1">AH5-Z5</f>
+        <f t="shared" ref="AI5:AI74" si="1">AH5-Z5</f>
         <v>1.8700000000000001E-2</v>
       </c>
       <c r="AK5" s="4">
@@ -10662,7 +10718,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS73" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS74" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -23164,7 +23220,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="BA71" s="13">
-        <f t="shared" ref="BA71:BA73" si="5">AZ71-AR71</f>
+        <f t="shared" ref="BA71:BA74" si="5">AZ71-AR71</f>
         <v>2.6199999999999998E-2</v>
       </c>
       <c r="BC71" s="4">
@@ -23608,7 +23664,9 @@
       <c r="G74" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H74" s="9"/>
+      <c r="H74" s="9">
+        <v>8.5000000000000006E-3</v>
+      </c>
       <c r="I74" s="2">
         <v>46147</v>
       </c>
@@ -23630,10 +23688,12 @@
       <c r="O74" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P74" s="58"/>
+      <c r="P74" s="58">
+        <v>2.81E-2</v>
+      </c>
       <c r="Q74" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="S74" s="4">
         <v>46147</v>
@@ -23650,11 +23710,15 @@
       <c r="W74" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X74" s="6"/>
+      <c r="X74" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y74" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z74" s="6"/>
+      <c r="Z74" s="6">
+        <v>1.23E-2</v>
+      </c>
       <c r="AA74" s="2">
         <v>46147</v>
       </c>
@@ -23676,50 +23740,97 @@
       <c r="AG74" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH74" s="58"/>
-      <c r="AI74" s="13"/>
+      <c r="AH74" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI74" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2700000000000001E-2</v>
+      </c>
       <c r="AK74" s="4">
         <v>46147</v>
       </c>
-      <c r="AL74" s="3"/>
+      <c r="AL74" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM74" s="3"/>
       <c r="AN74" s="3"/>
       <c r="AO74" s="3"/>
-      <c r="AP74" s="3"/>
-      <c r="AQ74" s="6"/>
-      <c r="AR74" s="6"/>
+      <c r="AP74" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ74" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR74" s="6">
+        <v>6.8999999999999999E-3</v>
+      </c>
       <c r="AS74" s="2">
         <v>46147</v>
       </c>
-      <c r="AT74" s="14"/>
-      <c r="AU74" s="14"/>
-      <c r="AV74" s="14"/>
-      <c r="AW74" s="14"/>
-      <c r="AX74" s="14"/>
-      <c r="AY74" s="14"/>
-      <c r="AZ74" s="14"/>
-      <c r="BA74" s="13"/>
+      <c r="AT74" s="14">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AU74" s="14">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="AV74" s="14">
+        <v>2.75E-2</v>
+      </c>
+      <c r="AW74" s="14">
+        <v>4.3900000000000002E-2</v>
+      </c>
+      <c r="AX74" s="14">
+        <v>5.3699999999999998E-2</v>
+      </c>
+      <c r="AY74" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="AZ74" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA74" s="13">
+        <f t="shared" si="5"/>
+        <v>2.5999999999999999E-2</v>
+      </c>
       <c r="BC74" s="4">
         <v>46147</v>
       </c>
-      <c r="BD74" s="6"/>
-      <c r="BE74" s="6"/>
-      <c r="BF74" s="6"/>
+      <c r="BD74" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE74" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF74" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG74" s="3"/>
       <c r="BH74" s="3"/>
       <c r="BI74" s="3"/>
-      <c r="BJ74" s="6"/>
+      <c r="BJ74" s="6">
+        <v>8.2000000000000007E-3</v>
+      </c>
       <c r="BK74" s="2">
         <v>46147</v>
       </c>
-      <c r="BL74" s="58"/>
+      <c r="BL74" s="58">
+        <v>3.49E-2</v>
+      </c>
       <c r="BM74" s="1"/>
-      <c r="BN74" s="58"/>
+      <c r="BN74" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO74" s="1"/>
       <c r="BP74" s="1"/>
       <c r="BQ74" s="1"/>
-      <c r="BR74" s="58"/>
-      <c r="BS74" s="13"/>
+      <c r="BR74" s="58">
+        <v>2.8799999999999999E-2</v>
+      </c>
+      <c r="BS74" s="13">
+        <f t="shared" si="3"/>
+        <v>2.06E-2</v>
+      </c>
     </row>
     <row r="75" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A75" s="4">
@@ -25684,7 +25795,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26020,7 +26131,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26358,7 +26469,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26696,7 +26807,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27034,7 +27145,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27402,7 +27513,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27770,7 +27881,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28138,7 +28249,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28509,7 +28620,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -28890,7 +29001,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30354,7 +30465,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30698,7 +30809,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31042,7 +31153,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31386,7 +31497,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31730,7 +31841,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32062,7 +32173,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32406,7 +32517,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32750,7 +32861,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33097,7 +33208,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33442,7 +33553,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44138,7 +44249,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44482,7 +44593,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44817,7 +44928,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45149,7 +45260,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45493,7 +45604,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45837,7 +45948,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46181,7 +46292,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46525,7 +46636,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46827,6 +46938,350 @@
       <c r="K8" s="68">
         <f>H8-'Daily Data'!H73</f>
         <v>1.9799999999999998E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66F05DCD-47C0-4B80-89EE-6F899D8ADF4D}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46147</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>2.75E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.3900000000000002E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5.3699999999999998E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>0.05</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR74</f>
+        <v>2.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z74</f>
+        <v>1.2700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="57">
+        <v>3.49E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.8814775512232469E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8867139310035983E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8901357961484207E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.9004338734472852E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.8799999999999999E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>2.9217560787452745E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ74</f>
+        <v>2.06E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>2.58E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.4610779727792322E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>2.7099999999999999E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.4648973983705396E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.4673925856523601E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.4748983713435448E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.46E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.4904226896770965E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-0.95%</f>
+        <v>1.5100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.8106490777993605E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.8114065879042336E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8131390619379859E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8163912885332154E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8196485282603719E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8294504132474804E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.81E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>2.8497416706523726E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H74</f>
+        <v>1.9599999999999999E-2</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
@@ -54927,7 +55382,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -55290,7 +55745,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -55651,7 +56106,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56006,7 +56461,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B1E5202-75E5-407C-8880-C0B4D979DE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FBDA7D-7664-46DE-9316-41808516C9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="39" activeTab="48" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" firstSheet="44" activeTab="49" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -62,6 +62,7 @@
     <sheet name="03.05.2026" sheetId="68" r:id="rId47"/>
     <sheet name="04.05.2026" sheetId="69" r:id="rId48"/>
     <sheet name="05.05.2026" sheetId="70" r:id="rId49"/>
+    <sheet name="06.05.2026" sheetId="71" r:id="rId50"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1710,6 +1711,43 @@
 </comments>
 </file>
 
+<file path=xl/comments46.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{FEAB58A6-783E-41E2-8009-C7CA6DFA7B1A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1896,7 +1934,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3491" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3504" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -2605,7 +2643,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="44">
+  <dxfs count="45">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -6213,17 +6258,29 @@
       <c r="F126" s="23">
         <v>3.27E-2</v>
       </c>
-      <c r="G126" s="90"/>
+      <c r="G126" s="90">
+        <v>80905</v>
+      </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="82">
         <v>46148</v>
       </c>
-      <c r="B127" s="83"/>
-      <c r="C127" s="23"/>
-      <c r="D127" s="23"/>
-      <c r="E127" s="23"/>
-      <c r="F127" s="23"/>
+      <c r="B127" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C127" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D127" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E127" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F127" s="23">
+        <v>3.3500000000000002E-2</v>
+      </c>
       <c r="G127" s="90"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
@@ -6903,7 +6960,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7239,7 +7296,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7577,7 +7634,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7913,7 +7970,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8247,7 +8304,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8583,7 +8640,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8919,7 +8976,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9255,7 +9312,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9591,7 +9648,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9927,7 +9984,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10634,7 +10691,7 @@
         <v>0.03</v>
       </c>
       <c r="AI5" s="13">
-        <f t="shared" ref="AI5:AI74" si="1">AH5-Z5</f>
+        <f t="shared" ref="AI5:AI75" si="1">AH5-Z5</f>
         <v>1.8700000000000001E-2</v>
       </c>
       <c r="AK5" s="4">
@@ -10718,7 +10775,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS74" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS75" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -23220,7 +23277,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="BA71" s="13">
-        <f t="shared" ref="BA71:BA74" si="5">AZ71-AR71</f>
+        <f t="shared" ref="BA71:BA75" si="5">AZ71-AR71</f>
         <v>2.6199999999999998E-2</v>
       </c>
       <c r="BC71" s="4">
@@ -23854,7 +23911,9 @@
       <c r="G75" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H75" s="9"/>
+      <c r="H75" s="9">
+        <v>8.8000000000000005E-3</v>
+      </c>
       <c r="I75" s="2">
         <v>46148</v>
       </c>
@@ -23876,10 +23935,12 @@
       <c r="O75" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P75" s="58"/>
+      <c r="P75" s="58">
+        <v>2.86E-2</v>
+      </c>
       <c r="Q75" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.9799999999999998E-2</v>
       </c>
       <c r="S75" s="4">
         <v>46148</v>
@@ -23896,11 +23957,15 @@
       <c r="W75" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X75" s="6"/>
+      <c r="X75" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y75" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z75" s="6"/>
+      <c r="Z75" s="6">
+        <v>1.26E-2</v>
+      </c>
       <c r="AA75" s="2">
         <v>46148</v>
       </c>
@@ -23922,50 +23987,97 @@
       <c r="AG75" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH75" s="58"/>
-      <c r="AI75" s="13"/>
+      <c r="AH75" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI75" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2400000000000001E-2</v>
+      </c>
       <c r="AK75" s="4">
         <v>46148</v>
       </c>
-      <c r="AL75" s="3"/>
+      <c r="AL75" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM75" s="3"/>
       <c r="AN75" s="3"/>
       <c r="AO75" s="3"/>
-      <c r="AP75" s="3"/>
-      <c r="AQ75" s="6"/>
-      <c r="AR75" s="6"/>
+      <c r="AP75" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ75" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR75" s="6">
+        <v>7.1000000000000004E-3</v>
+      </c>
       <c r="AS75" s="2">
         <v>46148</v>
       </c>
-      <c r="AT75" s="14"/>
-      <c r="AU75" s="14"/>
-      <c r="AV75" s="14"/>
-      <c r="AW75" s="14"/>
-      <c r="AX75" s="14"/>
-      <c r="AY75" s="14"/>
-      <c r="AZ75" s="14"/>
-      <c r="BA75" s="13"/>
+      <c r="AT75" s="14">
+        <v>2.7E-2</v>
+      </c>
+      <c r="AU75" s="14">
+        <v>2.75E-2</v>
+      </c>
+      <c r="AV75" s="14">
+        <v>2.75E-2</v>
+      </c>
+      <c r="AW75" s="14">
+        <v>4.3900000000000002E-2</v>
+      </c>
+      <c r="AX75" s="14">
+        <v>5.1900000000000002E-2</v>
+      </c>
+      <c r="AY75" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="AZ75" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA75" s="13">
+        <f t="shared" si="5"/>
+        <v>2.5799999999999997E-2</v>
+      </c>
       <c r="BC75" s="4">
         <v>46148</v>
       </c>
-      <c r="BD75" s="6"/>
-      <c r="BE75" s="6"/>
-      <c r="BF75" s="6"/>
+      <c r="BD75" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE75" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF75" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG75" s="3"/>
       <c r="BH75" s="3"/>
       <c r="BI75" s="3"/>
-      <c r="BJ75" s="6"/>
+      <c r="BJ75" s="6">
+        <v>8.2000000000000007E-3</v>
+      </c>
       <c r="BK75" s="2">
         <v>46148</v>
       </c>
-      <c r="BL75" s="58"/>
+      <c r="BL75" s="58">
+        <v>3.49E-2</v>
+      </c>
       <c r="BM75" s="1"/>
-      <c r="BN75" s="58"/>
+      <c r="BN75" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO75" s="1"/>
       <c r="BP75" s="1"/>
       <c r="BQ75" s="1"/>
-      <c r="BR75" s="58"/>
-      <c r="BS75" s="13"/>
+      <c r="BR75" s="58">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="BS75" s="13">
+        <f t="shared" si="3"/>
+        <v>2.0699999999999996E-2</v>
+      </c>
     </row>
     <row r="76" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A76" s="4">
@@ -25795,7 +25907,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26131,7 +26243,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26469,7 +26581,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26807,7 +26919,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27145,7 +27257,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27513,7 +27625,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27881,7 +27993,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28249,7 +28361,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28620,7 +28732,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -29001,7 +29113,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30465,7 +30577,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30809,7 +30921,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31153,7 +31265,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31497,7 +31609,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31841,7 +31953,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32173,7 +32285,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32517,7 +32629,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32861,7 +32973,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33208,7 +33320,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33553,7 +33665,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44249,7 +44361,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44593,7 +44705,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44928,7 +45040,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45260,7 +45372,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45604,7 +45716,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45948,7 +46060,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46292,7 +46404,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46636,7 +46748,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46980,7 +47092,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47324,7 +47436,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -55029,6 +55141,350 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{465B481D-2271-4BCC-B6A1-E5C87AE1A90C}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46148</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.7E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>2.75E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>2.75E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.3900000000000002E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5.1900000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>0.05</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR75</f>
+        <v>2.5799999999999997E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z75</f>
+        <v>1.2400000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>3.49E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.8914878314429165E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.8967606723085199E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.9002063879406133E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.9105763569589695E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>2.9320479554602263E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ75</f>
+        <v>2.0699999999999996E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>2.5600000000000001E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.4410605136875558E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.4448180385079121E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.4472727526308455E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.4546566287036671E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.4400000000000002E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.4699280303361215E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-0.98%</f>
+        <v>1.4600000000000002E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.8606723836956154E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.861457097742421E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8632518077824447E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8666209355555194E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8699953491705399E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.8801503984497451E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.86E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>2.9011754039298232E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H75</f>
+        <v>1.9799999999999998E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D18876AE-A1D0-4504-93FB-F23D7E286EC6}">
   <sheetPr>
@@ -55382,7 +55838,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -55745,7 +56201,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56106,7 +56562,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56461,7 +56917,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FBDA7D-7664-46DE-9316-41808516C9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92B108F-2D2A-4C5C-BB2D-350287A027C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" firstSheet="44" activeTab="49" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="41" activeTab="50" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -63,6 +63,7 @@
     <sheet name="04.05.2026" sheetId="69" r:id="rId48"/>
     <sheet name="05.05.2026" sheetId="70" r:id="rId49"/>
     <sheet name="06.05.2026" sheetId="71" r:id="rId50"/>
+    <sheet name="07.05.2026" sheetId="72" r:id="rId51"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -95,7 +96,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="162"/>
           </rPr>
           <t>Batuhan Helvaci:</t>
         </r>
@@ -104,7 +106,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="162"/>
           </rPr>
           <t xml:space="preserve">
 VIP Only
@@ -122,7 +125,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="162"/>
           </rPr>
           <t>Batuhan Helvaci:</t>
         </r>
@@ -131,7 +135,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="162"/>
           </rPr>
           <t xml:space="preserve">
 ≤ 200 USDT 5.61%</t>
@@ -146,6 +151,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
             <charset val="162"/>
           </rPr>
           <t>Batuhan Helvaci:</t>
@@ -155,6 +161,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
             <charset val="162"/>
           </rPr>
           <t xml:space="preserve">
@@ -172,7 +179,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="162"/>
           </rPr>
           <t>Batuhan Helvaci:</t>
         </r>
@@ -181,7 +189,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="162"/>
           </rPr>
           <t xml:space="preserve">
 VIP Only
@@ -197,7 +206,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="162"/>
           </rPr>
           <t>Batuhan Helvaci:</t>
         </r>
@@ -206,7 +216,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="162"/>
           </rPr>
           <t xml:space="preserve">
 &lt;500 USDT 10%
@@ -222,7 +233,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="162"/>
           </rPr>
           <t>Batuhan Helvaci:</t>
         </r>
@@ -231,7 +243,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="162"/>
           </rPr>
           <t xml:space="preserve">
 VIP Only
@@ -247,7 +260,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="162"/>
           </rPr>
           <t>Batuhan Helvaci:</t>
         </r>
@@ -256,7 +270,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="162"/>
           </rPr>
           <t xml:space="preserve">
 &lt;500 USDT 10%
@@ -1748,6 +1763,43 @@
 </comments>
 </file>
 
+<file path=xl/comments47.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{05EB89FC-ADF4-40BC-A954-A51A6D5CF66E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1934,7 +1986,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3504" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3517" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -2154,7 +2206,7 @@
     <numFmt numFmtId="166" formatCode="0.00000%"/>
     <numFmt numFmtId="167" formatCode="0.000000%"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2174,6 +2226,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
+      <family val="2"/>
       <charset val="162"/>
     </font>
     <font>
@@ -2181,20 +2234,8 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
+      <family val="2"/>
       <charset val="162"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -2211,21 +2252,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="162"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="162"/>
     </font>
     <font>
       <b/>
@@ -2379,8 +2405,8 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2412,13 +2438,13 @@
     <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2429,7 +2455,7 @@
     <xf numFmtId="10" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -2438,16 +2464,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2474,7 +2500,7 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -2483,54 +2509,54 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -2538,45 +2564,45 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -2588,7 +2614,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2603,10 +2629,10 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -2620,7 +2646,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -2643,7 +2669,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="45">
+  <dxfs count="46">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2983,7 +3016,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>354623</xdr:colOff>
+      <xdr:colOff>351448</xdr:colOff>
       <xdr:row>121</xdr:row>
       <xdr:rowOff>20630</xdr:rowOff>
     </xdr:to>
@@ -6281,17 +6314,29 @@
       <c r="F127" s="23">
         <v>3.3500000000000002E-2</v>
       </c>
-      <c r="G127" s="90"/>
+      <c r="G127" s="90">
+        <v>81200</v>
+      </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="82">
         <v>46149</v>
       </c>
-      <c r="B128" s="83"/>
-      <c r="C128" s="23"/>
-      <c r="D128" s="23"/>
-      <c r="E128" s="23"/>
-      <c r="F128" s="23"/>
+      <c r="B128" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C128" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D128" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E128" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F128" s="23">
+        <v>3.3599999999999998E-2</v>
+      </c>
       <c r="G128" s="90"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
@@ -6960,7 +7005,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7296,7 +7341,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7634,7 +7679,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7970,7 +8015,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8304,7 +8349,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8640,7 +8685,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8976,7 +9021,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9312,7 +9357,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9648,7 +9693,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9984,7 +10029,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10691,7 +10736,7 @@
         <v>0.03</v>
       </c>
       <c r="AI5" s="13">
-        <f t="shared" ref="AI5:AI75" si="1">AH5-Z5</f>
+        <f t="shared" ref="AI5:AI76" si="1">AH5-Z5</f>
         <v>1.8700000000000001E-2</v>
       </c>
       <c r="AK5" s="4">
@@ -10775,7 +10820,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS75" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS76" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -23277,7 +23322,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="BA71" s="13">
-        <f t="shared" ref="BA71:BA75" si="5">AZ71-AR71</f>
+        <f t="shared" ref="BA71:BA76" si="5">AZ71-AR71</f>
         <v>2.6199999999999998E-2</v>
       </c>
       <c r="BC71" s="4">
@@ -24101,7 +24146,9 @@
       <c r="G76" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H76" s="9"/>
+      <c r="H76" s="9">
+        <v>9.2999999999999992E-3</v>
+      </c>
       <c r="I76" s="2">
         <v>46149</v>
       </c>
@@ -24123,10 +24170,12 @@
       <c r="O76" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P76" s="58"/>
+      <c r="P76" s="58">
+        <v>2.93E-2</v>
+      </c>
       <c r="Q76" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S76" s="4">
         <v>46149</v>
@@ -24143,11 +24192,15 @@
       <c r="W76" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X76" s="6"/>
+      <c r="X76" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y76" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z76" s="6"/>
+      <c r="Z76" s="6">
+        <v>1.2999999999999999E-2</v>
+      </c>
       <c r="AA76" s="2">
         <v>46149</v>
       </c>
@@ -24169,50 +24222,97 @@
       <c r="AG76" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH76" s="58"/>
-      <c r="AI76" s="13"/>
+      <c r="AH76" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI76" s="13">
+        <f t="shared" si="1"/>
+        <v>1.2000000000000002E-2</v>
+      </c>
       <c r="AK76" s="4">
         <v>46149</v>
       </c>
-      <c r="AL76" s="3"/>
+      <c r="AL76" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM76" s="3"/>
       <c r="AN76" s="3"/>
       <c r="AO76" s="3"/>
-      <c r="AP76" s="3"/>
-      <c r="AQ76" s="6"/>
-      <c r="AR76" s="6"/>
+      <c r="AP76" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ76" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR76" s="6">
+        <v>8.9999999999999993E-3</v>
+      </c>
       <c r="AS76" s="2">
         <v>46149</v>
       </c>
-      <c r="AT76" s="14"/>
-      <c r="AU76" s="14"/>
-      <c r="AV76" s="14"/>
-      <c r="AW76" s="14"/>
-      <c r="AX76" s="14"/>
-      <c r="AY76" s="14"/>
-      <c r="AZ76" s="14"/>
-      <c r="BA76" s="13"/>
+      <c r="AT76" s="14">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AU76" s="14">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="AV76" s="14">
+        <v>2.75E-2</v>
+      </c>
+      <c r="AW76" s="14">
+        <v>4.3900000000000002E-2</v>
+      </c>
+      <c r="AX76" s="14">
+        <v>5.1700000000000003E-2</v>
+      </c>
+      <c r="AY76" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="AZ76" s="14">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA76" s="13">
+        <f t="shared" si="5"/>
+        <v>2.3899999999999998E-2</v>
+      </c>
       <c r="BC76" s="4">
         <v>46149</v>
       </c>
-      <c r="BD76" s="6"/>
-      <c r="BE76" s="6"/>
-      <c r="BF76" s="6"/>
+      <c r="BD76" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE76" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF76" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG76" s="3"/>
       <c r="BH76" s="3"/>
       <c r="BI76" s="3"/>
-      <c r="BJ76" s="6"/>
+      <c r="BJ76" s="6">
+        <v>8.6E-3</v>
+      </c>
       <c r="BK76" s="2">
         <v>46149</v>
       </c>
-      <c r="BL76" s="58"/>
+      <c r="BL76" s="58">
+        <v>3.56E-2</v>
+      </c>
       <c r="BM76" s="1"/>
-      <c r="BN76" s="58"/>
+      <c r="BN76" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO76" s="1"/>
       <c r="BP76" s="1"/>
       <c r="BQ76" s="1"/>
-      <c r="BR76" s="58"/>
-      <c r="BS76" s="13"/>
+      <c r="BR76" s="58">
+        <v>2.9700000000000001E-2</v>
+      </c>
+      <c r="BS76" s="13">
+        <f t="shared" si="3"/>
+        <v>2.1100000000000001E-2</v>
+      </c>
     </row>
     <row r="77" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A77" s="4">
@@ -25907,7 +26007,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26243,7 +26343,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26581,7 +26681,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26919,7 +27019,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27257,7 +27357,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27625,7 +27725,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27993,7 +28093,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28361,7 +28461,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28732,7 +28832,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -29113,7 +29213,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30577,7 +30677,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30921,7 +31021,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31265,7 +31365,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31609,7 +31709,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31953,7 +32053,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32285,7 +32385,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32629,7 +32729,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32973,7 +33073,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33320,7 +33420,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33665,7 +33765,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44361,7 +44461,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44705,7 +44805,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45040,7 +45140,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45372,7 +45472,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45716,7 +45816,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46060,7 +46160,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46404,7 +46504,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46748,7 +46848,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47092,7 +47192,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47436,7 +47536,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -55473,6 +55573,350 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF20F1AC-8134-488C-BF6A-ABCBB682B323}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46149</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>2.75E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.3900000000000002E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5.1700000000000003E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>0.05</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR76</f>
+        <v>2.3899999999999998E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z76</f>
+        <v>1.2000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>3.56E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.97157135659997E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.9771404489047876E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.9807799622090583E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.991734132434765E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.9700000000000001E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.0144199258958837E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ76</f>
+        <v>2.1100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.6512509454446293E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>2.92E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.6556836941645196E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.6585799405461893E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.6672939714643285E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.6853259490220882E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.01%</f>
+        <v>1.6399999999999998E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>2.9307057026300192E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>2.9315293088140817E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.9334129962939159E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.9369492614198467E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.940491210560266E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>2.9511512649485608E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2.93E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>2.9732257267065743E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H76</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
@@ -55838,7 +56282,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="44" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -56201,7 +56645,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56562,7 +57006,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56917,7 +57361,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92B108F-2D2A-4C5C-BB2D-350287A027C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1036A130-A93B-4650-A375-CFC1DD9AC813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="41" activeTab="50" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -64,6 +64,10 @@
     <sheet name="05.05.2026" sheetId="70" r:id="rId49"/>
     <sheet name="06.05.2026" sheetId="71" r:id="rId50"/>
     <sheet name="07.05.2026" sheetId="72" r:id="rId51"/>
+    <sheet name="08.05.2026" sheetId="73" r:id="rId52"/>
+    <sheet name="09.05.2026" sheetId="74" r:id="rId53"/>
+    <sheet name="10.05.2026" sheetId="75" r:id="rId54"/>
+    <sheet name="11.05.2026" sheetId="77" r:id="rId55"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1800,6 +1804,80 @@
 </comments>
 </file>
 
+<file path=xl/comments48.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{47DDAE83-F1B0-4EEA-A046-FF4868BC909C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments49.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{9B9F1AF3-6F14-4770-B62B-7C2DE04E6EA1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1807,6 +1885,80 @@
   </authors>
   <commentList>
     <comment ref="H9" authorId="0" shapeId="0" xr:uid="{FD113D3C-C9FD-4FEC-9899-C2944144B19D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments50.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{AAA1CA66-FE3D-4611-A02B-D87804B67358}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments51.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{1CBA9BA3-8516-4B5A-942B-BC95057F0A1E}">
       <text>
         <r>
           <rPr>
@@ -1986,7 +2138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3517" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3569" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -2669,7 +2821,49 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="46">
+  <dxfs count="52">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3016,7 +3210,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>351448</xdr:colOff>
+      <xdr:colOff>354623</xdr:colOff>
       <xdr:row>121</xdr:row>
       <xdr:rowOff>20630</xdr:rowOff>
     </xdr:to>
@@ -6337,61 +6531,165 @@
       <c r="F128" s="23">
         <v>3.3599999999999998E-2</v>
       </c>
-      <c r="G128" s="90"/>
+      <c r="G128" s="90">
+        <v>81448</v>
+      </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="82">
         <v>46150</v>
       </c>
-      <c r="B129" s="83"/>
-      <c r="C129" s="23"/>
-      <c r="D129" s="23"/>
-      <c r="E129" s="23"/>
-      <c r="F129" s="23"/>
-      <c r="G129" s="90"/>
+      <c r="B129" s="83">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="C129" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D129" s="23">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E129" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F129" s="23">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="G129" s="90">
+        <v>80007</v>
+      </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="82">
         <v>46151</v>
       </c>
-      <c r="B130" s="83"/>
-      <c r="C130" s="23"/>
-      <c r="D130" s="23"/>
-      <c r="E130" s="23"/>
-      <c r="F130" s="23"/>
-      <c r="G130" s="90"/>
+      <c r="B130" s="83">
+        <v>3.04E-2</v>
+      </c>
+      <c r="C130" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D130" s="23">
+        <v>3.3399999999999999E-2</v>
+      </c>
+      <c r="E130" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F130" s="23">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="G130" s="90">
+        <v>82215</v>
+      </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A131" s="80"/>
-      <c r="B131" s="80"/>
+      <c r="A131" s="82">
+        <v>46152</v>
+      </c>
+      <c r="B131" s="83">
+        <v>3.1399999999999997E-2</v>
+      </c>
+      <c r="C131" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D131" s="23">
+        <v>3.39E-2</v>
+      </c>
+      <c r="E131" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F131" s="23">
+        <v>3.61E-2</v>
+      </c>
+      <c r="G131" s="90">
+        <v>80678</v>
+      </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A132" s="80"/>
-      <c r="B132" s="80"/>
+      <c r="A132" s="82">
+        <v>46153</v>
+      </c>
+      <c r="B132" s="83">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="C132" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D132" s="23">
+        <v>3.6200000000000003E-2</v>
+      </c>
+      <c r="E132" s="23">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F132" s="23">
+        <v>3.6499999999999998E-2</v>
+      </c>
+      <c r="G132" s="90"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A133" s="80"/>
-      <c r="B133" s="80"/>
+      <c r="A133" s="82">
+        <v>46154</v>
+      </c>
+      <c r="B133" s="83"/>
+      <c r="C133" s="23"/>
+      <c r="D133" s="23"/>
+      <c r="E133" s="23"/>
+      <c r="F133" s="23"/>
+      <c r="G133" s="90"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A134" s="80"/>
-      <c r="B134" s="80"/>
+      <c r="A134" s="82">
+        <v>46155</v>
+      </c>
+      <c r="B134" s="83"/>
+      <c r="C134" s="23"/>
+      <c r="D134" s="23"/>
+      <c r="E134" s="23"/>
+      <c r="F134" s="23"/>
+      <c r="G134" s="90"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A135" s="80"/>
-      <c r="B135" s="80"/>
+      <c r="A135" s="82">
+        <v>46156</v>
+      </c>
+      <c r="B135" s="83"/>
+      <c r="C135" s="23"/>
+      <c r="D135" s="23"/>
+      <c r="E135" s="23"/>
+      <c r="F135" s="23"/>
+      <c r="G135" s="90"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A136" s="80"/>
-      <c r="B136" s="80"/>
+      <c r="A136" s="82">
+        <v>46157</v>
+      </c>
+      <c r="B136" s="83"/>
+      <c r="C136" s="23"/>
+      <c r="D136" s="23"/>
+      <c r="E136" s="23"/>
+      <c r="F136" s="23"/>
+      <c r="G136" s="90"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A137" s="80"/>
-      <c r="B137" s="80"/>
+      <c r="A137" s="82">
+        <v>46158</v>
+      </c>
+      <c r="B137" s="83"/>
+      <c r="C137" s="23"/>
+      <c r="D137" s="23"/>
+      <c r="E137" s="23"/>
+      <c r="F137" s="23"/>
+      <c r="G137" s="90"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A138" s="80"/>
-      <c r="B138" s="80"/>
+      <c r="A138" s="82">
+        <v>46159</v>
+      </c>
+      <c r="B138" s="83"/>
+      <c r="C138" s="23"/>
+      <c r="D138" s="23"/>
+      <c r="E138" s="23"/>
+      <c r="F138" s="23"/>
+      <c r="G138" s="90"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="80"/>
@@ -7005,7 +7303,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7341,7 +7639,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7679,7 +7977,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8015,7 +8313,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8349,7 +8647,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8685,7 +8983,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9021,7 +9319,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9357,7 +9655,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9693,7 +9991,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10029,7 +10327,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10736,7 +11034,7 @@
         <v>0.03</v>
       </c>
       <c r="AI5" s="13">
-        <f t="shared" ref="AI5:AI76" si="1">AH5-Z5</f>
+        <f t="shared" ref="AI5:AI77" si="1">AH5-Z5</f>
         <v>1.8700000000000001E-2</v>
       </c>
       <c r="AK5" s="4">
@@ -10820,7 +11118,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS76" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS80" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -23322,7 +23620,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="BA71" s="13">
-        <f t="shared" ref="BA71:BA76" si="5">AZ71-AR71</f>
+        <f t="shared" ref="BA71:BA80" si="5">AZ71-AR71</f>
         <v>2.6199999999999998E-2</v>
       </c>
       <c r="BC71" s="4">
@@ -24336,7 +24634,9 @@
       <c r="G77" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H77" s="9"/>
+      <c r="H77" s="9">
+        <v>9.5999999999999992E-3</v>
+      </c>
       <c r="I77" s="2">
         <v>46150</v>
       </c>
@@ -24358,10 +24658,12 @@
       <c r="O77" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P77" s="58"/>
+      <c r="P77" s="58">
+        <v>3.1E-2</v>
+      </c>
       <c r="Q77" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.1400000000000002E-2</v>
       </c>
       <c r="S77" s="4">
         <v>46150</v>
@@ -24378,11 +24680,15 @@
       <c r="W77" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X77" s="6"/>
+      <c r="X77" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y77" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z77" s="6"/>
+      <c r="Z77" s="6">
+        <v>1.34E-2</v>
+      </c>
       <c r="AA77" s="2">
         <v>46150</v>
       </c>
@@ -24404,50 +24710,97 @@
       <c r="AG77" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH77" s="58"/>
-      <c r="AI77" s="13"/>
+      <c r="AH77" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI77" s="13">
+        <f t="shared" si="1"/>
+        <v>1.1600000000000001E-2</v>
+      </c>
       <c r="AK77" s="4">
         <v>46150</v>
       </c>
-      <c r="AL77" s="3"/>
+      <c r="AL77" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM77" s="3"/>
       <c r="AN77" s="3"/>
       <c r="AO77" s="3"/>
-      <c r="AP77" s="3"/>
-      <c r="AQ77" s="6"/>
-      <c r="AR77" s="6"/>
+      <c r="AP77" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ77" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR77" s="6">
+        <v>8.6E-3</v>
+      </c>
       <c r="AS77" s="2">
         <v>46150</v>
       </c>
-      <c r="AT77" s="14"/>
-      <c r="AU77" s="14"/>
-      <c r="AV77" s="14"/>
-      <c r="AW77" s="14"/>
-      <c r="AX77" s="14"/>
-      <c r="AY77" s="14"/>
-      <c r="AZ77" s="14"/>
-      <c r="BA77" s="13"/>
+      <c r="AT77" s="14">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="AU77" s="14">
+        <v>2.76E-2</v>
+      </c>
+      <c r="AV77" s="14">
+        <v>0.03</v>
+      </c>
+      <c r="AW77" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AX77" s="14">
+        <v>4.7800000000000002E-2</v>
+      </c>
+      <c r="AY77" s="14">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="AZ77" s="14">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="BA77" s="13">
+        <f t="shared" si="5"/>
+        <v>2.4900000000000002E-2</v>
+      </c>
       <c r="BC77" s="4">
         <v>46150</v>
       </c>
-      <c r="BD77" s="6"/>
-      <c r="BE77" s="6"/>
-      <c r="BF77" s="6"/>
+      <c r="BD77" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE77" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF77" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG77" s="3"/>
       <c r="BH77" s="3"/>
       <c r="BI77" s="3"/>
-      <c r="BJ77" s="6"/>
+      <c r="BJ77" s="6">
+        <v>9.1000000000000004E-3</v>
+      </c>
       <c r="BK77" s="2">
         <v>46150</v>
       </c>
-      <c r="BL77" s="58"/>
+      <c r="BL77" s="58">
+        <v>4.07E-2</v>
+      </c>
       <c r="BM77" s="1"/>
-      <c r="BN77" s="58"/>
+      <c r="BN77" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO77" s="1"/>
       <c r="BP77" s="1"/>
       <c r="BQ77" s="1"/>
-      <c r="BR77" s="58"/>
-      <c r="BS77" s="13"/>
+      <c r="BR77" s="58">
+        <v>2.98E-2</v>
+      </c>
+      <c r="BS77" s="13">
+        <f t="shared" si="3"/>
+        <v>2.07E-2</v>
+      </c>
     </row>
     <row r="78" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A78" s="4">
@@ -24471,7 +24824,9 @@
       <c r="G78" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H78" s="9"/>
+      <c r="H78" s="9">
+        <v>0.01</v>
+      </c>
       <c r="I78" s="2">
         <v>46151</v>
       </c>
@@ -24493,10 +24848,12 @@
       <c r="O78" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P78" s="58"/>
+      <c r="P78" s="58">
+        <v>3.32E-2</v>
+      </c>
       <c r="Q78" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.3199999999999998E-2</v>
       </c>
       <c r="S78" s="4">
         <v>46151</v>
@@ -24513,11 +24870,15 @@
       <c r="W78" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X78" s="6"/>
+      <c r="X78" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y78" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z78" s="6"/>
+      <c r="Z78" s="6">
+        <v>1.35E-2</v>
+      </c>
       <c r="AA78" s="2">
         <v>46151</v>
       </c>
@@ -24539,50 +24900,97 @@
       <c r="AG78" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH78" s="58"/>
-      <c r="AI78" s="13"/>
+      <c r="AH78" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI78" s="13">
+        <f t="shared" ref="AI78:AI80" si="6">AH78-Z78</f>
+        <v>1.1500000000000002E-2</v>
+      </c>
       <c r="AK78" s="4">
         <v>46151</v>
       </c>
-      <c r="AL78" s="3"/>
+      <c r="AL78" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM78" s="3"/>
       <c r="AN78" s="3"/>
       <c r="AO78" s="3"/>
-      <c r="AP78" s="3"/>
-      <c r="AQ78" s="6"/>
-      <c r="AR78" s="6"/>
+      <c r="AP78" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ78" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR78" s="6">
+        <v>8.9999999999999993E-3</v>
+      </c>
       <c r="AS78" s="2">
         <v>46151</v>
       </c>
-      <c r="AT78" s="14"/>
-      <c r="AU78" s="14"/>
-      <c r="AV78" s="14"/>
-      <c r="AW78" s="14"/>
-      <c r="AX78" s="14"/>
-      <c r="AY78" s="14"/>
-      <c r="AZ78" s="14"/>
-      <c r="BA78" s="13"/>
+      <c r="AT78" s="14">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="AU78" s="14">
+        <v>2.76E-2</v>
+      </c>
+      <c r="AV78" s="14">
+        <v>0.03</v>
+      </c>
+      <c r="AW78" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AX78" s="14">
+        <v>4.7800000000000002E-2</v>
+      </c>
+      <c r="AY78" s="14">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="AZ78" s="14">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="BA78" s="13">
+        <f t="shared" si="5"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="BC78" s="4">
         <v>46151</v>
       </c>
-      <c r="BD78" s="6"/>
-      <c r="BE78" s="6"/>
-      <c r="BF78" s="6"/>
+      <c r="BD78" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE78" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF78" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG78" s="3"/>
       <c r="BH78" s="3"/>
       <c r="BI78" s="3"/>
-      <c r="BJ78" s="6"/>
+      <c r="BJ78" s="6">
+        <v>9.7000000000000003E-3</v>
+      </c>
       <c r="BK78" s="2">
         <v>46151</v>
       </c>
-      <c r="BL78" s="58"/>
+      <c r="BL78" s="58">
+        <v>4.07E-2</v>
+      </c>
       <c r="BM78" s="1"/>
-      <c r="BN78" s="58"/>
+      <c r="BN78" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO78" s="1"/>
       <c r="BP78" s="1"/>
       <c r="BQ78" s="1"/>
-      <c r="BR78" s="58"/>
-      <c r="BS78" s="13"/>
+      <c r="BR78" s="58">
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="BS78" s="13">
+        <f t="shared" si="3"/>
+        <v>2.1100000000000001E-2</v>
+      </c>
     </row>
     <row r="79" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A79" s="4">
@@ -24606,7 +25014,9 @@
       <c r="G79" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H79" s="9"/>
+      <c r="H79" s="9">
+        <v>1.0200000000000001E-2</v>
+      </c>
       <c r="I79" s="2">
         <v>46152</v>
       </c>
@@ -24628,10 +25038,12 @@
       <c r="O79" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P79" s="58"/>
+      <c r="P79" s="58">
+        <v>3.3500000000000002E-2</v>
+      </c>
       <c r="Q79" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.3300000000000001E-2</v>
       </c>
       <c r="S79" s="4">
         <v>46152</v>
@@ -24648,11 +25060,15 @@
       <c r="W79" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X79" s="6"/>
+      <c r="X79" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y79" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z79" s="6"/>
+      <c r="Z79" s="6">
+        <v>1.41E-2</v>
+      </c>
       <c r="AA79" s="2">
         <v>46152</v>
       </c>
@@ -24674,50 +25090,97 @@
       <c r="AG79" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH79" s="58"/>
-      <c r="AI79" s="13"/>
+      <c r="AH79" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI79" s="13">
+        <f t="shared" si="6"/>
+        <v>1.0900000000000002E-2</v>
+      </c>
       <c r="AK79" s="4">
         <v>46152</v>
       </c>
-      <c r="AL79" s="3"/>
+      <c r="AL79" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM79" s="3"/>
       <c r="AN79" s="3"/>
       <c r="AO79" s="3"/>
-      <c r="AP79" s="3"/>
-      <c r="AQ79" s="6"/>
-      <c r="AR79" s="6"/>
+      <c r="AP79" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ79" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR79" s="6">
+        <v>9.1999999999999998E-3</v>
+      </c>
       <c r="AS79" s="2">
         <v>46152</v>
       </c>
-      <c r="AT79" s="14"/>
-      <c r="AU79" s="14"/>
-      <c r="AV79" s="14"/>
-      <c r="AW79" s="14"/>
-      <c r="AX79" s="14"/>
-      <c r="AY79" s="14"/>
-      <c r="AZ79" s="14"/>
-      <c r="BA79" s="13"/>
+      <c r="AT79" s="14">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="AU79" s="14">
+        <v>2.76E-2</v>
+      </c>
+      <c r="AV79" s="14">
+        <v>0.03</v>
+      </c>
+      <c r="AW79" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AX79" s="14">
+        <v>4.7800000000000002E-2</v>
+      </c>
+      <c r="AY79" s="14">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="AZ79" s="14">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="BA79" s="13">
+        <f t="shared" si="5"/>
+        <v>2.5300000000000003E-2</v>
+      </c>
       <c r="BC79" s="4">
         <v>46152</v>
       </c>
-      <c r="BD79" s="6"/>
-      <c r="BE79" s="6"/>
-      <c r="BF79" s="6"/>
+      <c r="BD79" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE79" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF79" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG79" s="3"/>
       <c r="BH79" s="3"/>
       <c r="BI79" s="3"/>
-      <c r="BJ79" s="6"/>
+      <c r="BJ79" s="6">
+        <v>1.0200000000000001E-2</v>
+      </c>
       <c r="BK79" s="2">
         <v>46152</v>
       </c>
-      <c r="BL79" s="58"/>
+      <c r="BL79" s="58">
+        <v>4.07E-2</v>
+      </c>
       <c r="BM79" s="1"/>
-      <c r="BN79" s="58"/>
+      <c r="BN79" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO79" s="1"/>
       <c r="BP79" s="1"/>
       <c r="BQ79" s="1"/>
-      <c r="BR79" s="58"/>
-      <c r="BS79" s="13"/>
+      <c r="BR79" s="58">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="BS79" s="13">
+        <f t="shared" si="3"/>
+        <v>2.0899999999999998E-2</v>
+      </c>
     </row>
     <row r="80" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A80" s="4">
@@ -24741,7 +25204,9 @@
       <c r="G80" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H80" s="9"/>
+      <c r="H80" s="9">
+        <v>1.0200000000000001E-2</v>
+      </c>
       <c r="I80" s="2">
         <v>46153</v>
       </c>
@@ -24763,10 +25228,12 @@
       <c r="O80" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P80" s="58"/>
+      <c r="P80" s="58">
+        <v>3.3500000000000002E-2</v>
+      </c>
       <c r="Q80" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.3300000000000001E-2</v>
       </c>
       <c r="S80" s="4">
         <v>46153</v>
@@ -24783,11 +25250,15 @@
       <c r="W80" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X80" s="6"/>
+      <c r="X80" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y80" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z80" s="6"/>
+      <c r="Z80" s="6">
+        <v>1.41E-2</v>
+      </c>
       <c r="AA80" s="2">
         <v>46153</v>
       </c>
@@ -24809,50 +25280,97 @@
       <c r="AG80" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH80" s="58"/>
-      <c r="AI80" s="13"/>
+      <c r="AH80" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI80" s="13">
+        <f t="shared" si="6"/>
+        <v>1.0900000000000002E-2</v>
+      </c>
       <c r="AK80" s="4">
         <v>46153</v>
       </c>
-      <c r="AL80" s="3"/>
+      <c r="AL80" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM80" s="3"/>
       <c r="AN80" s="3"/>
       <c r="AO80" s="3"/>
-      <c r="AP80" s="3"/>
-      <c r="AQ80" s="6"/>
-      <c r="AR80" s="6"/>
+      <c r="AP80" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ80" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR80" s="6">
+        <v>1.11E-2</v>
+      </c>
       <c r="AS80" s="2">
         <v>46153</v>
       </c>
-      <c r="AT80" s="14"/>
-      <c r="AU80" s="14"/>
-      <c r="AV80" s="14"/>
-      <c r="AW80" s="14"/>
-      <c r="AX80" s="14"/>
-      <c r="AY80" s="14"/>
-      <c r="AZ80" s="14"/>
-      <c r="BA80" s="13"/>
+      <c r="AT80" s="14">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="AU80" s="14">
+        <v>2.76E-2</v>
+      </c>
+      <c r="AV80" s="14">
+        <v>0.03</v>
+      </c>
+      <c r="AW80" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AX80" s="14">
+        <v>4.7800000000000002E-2</v>
+      </c>
+      <c r="AY80" s="14">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="AZ80" s="14">
+        <v>3.6900000000000002E-2</v>
+      </c>
+      <c r="BA80" s="13">
+        <f t="shared" si="5"/>
+        <v>2.5800000000000003E-2</v>
+      </c>
       <c r="BC80" s="4">
         <v>46153</v>
       </c>
-      <c r="BD80" s="6"/>
-      <c r="BE80" s="6"/>
-      <c r="BF80" s="6"/>
+      <c r="BD80" s="6">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="BE80" s="6">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="BF80" s="6">
+        <v>8.6999999999999994E-3</v>
+      </c>
       <c r="BG80" s="3"/>
       <c r="BH80" s="3"/>
       <c r="BI80" s="3"/>
-      <c r="BJ80" s="6"/>
+      <c r="BJ80" s="6">
+        <v>1.11E-2</v>
+      </c>
       <c r="BK80" s="2">
         <v>46153</v>
       </c>
-      <c r="BL80" s="58"/>
+      <c r="BL80" s="58">
+        <v>4.07E-2</v>
+      </c>
       <c r="BM80" s="1"/>
-      <c r="BN80" s="58"/>
+      <c r="BN80" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO80" s="1"/>
       <c r="BP80" s="1"/>
       <c r="BQ80" s="1"/>
-      <c r="BR80" s="58"/>
-      <c r="BS80" s="13"/>
+      <c r="BR80" s="58">
+        <v>3.39E-2</v>
+      </c>
+      <c r="BS80" s="13">
+        <f t="shared" si="3"/>
+        <v>2.2800000000000001E-2</v>
+      </c>
     </row>
     <row r="81" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A81" s="4">
@@ -24949,12 +25467,12 @@
       <c r="AK81" s="4">
         <v>46154</v>
       </c>
-      <c r="AL81" s="3"/>
+      <c r="AL81" s="6"/>
       <c r="AM81" s="3"/>
       <c r="AN81" s="3"/>
       <c r="AO81" s="3"/>
       <c r="AP81" s="3"/>
-      <c r="AQ81" s="6"/>
+      <c r="AQ81" s="3"/>
       <c r="AR81" s="6"/>
       <c r="AS81" s="2">
         <v>46154</v>
@@ -25084,7 +25602,7 @@
       <c r="AK82" s="4">
         <v>46155</v>
       </c>
-      <c r="AL82" s="3"/>
+      <c r="AL82" s="6"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
@@ -26007,7 +26525,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26343,7 +26861,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26681,7 +27199,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27019,7 +27537,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27357,7 +27875,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27725,7 +28243,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28093,7 +28611,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28461,7 +28979,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28832,7 +29350,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -29213,7 +29731,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30677,7 +31195,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31021,7 +31539,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31365,7 +31883,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31709,7 +32227,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32053,7 +32571,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32385,7 +32903,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32729,7 +33247,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33073,7 +33591,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33420,7 +33938,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33765,7 +34283,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44461,7 +44979,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44805,7 +45323,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45140,7 +45658,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45472,7 +45990,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45816,7 +46334,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46160,7 +46678,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46504,7 +47022,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46848,7 +47366,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47192,7 +47710,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47536,7 +48054,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -55573,7 +56091,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -55875,6 +56393,1382 @@
       <c r="K8" s="68">
         <f>H8-'Daily Data'!H76</f>
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECB8D11-FB06-49BE-B0E0-DD74C87BDA7B}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46150</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>2.76E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>0.03</v>
+      </c>
+      <c r="E3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.7800000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.4065854123153105E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR77</f>
+        <v>2.4900000000000002E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z77</f>
+        <v>1.1600000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.07E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>2.9815819576702873E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.9871886517863155E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.9908527640715526E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.0018810931547121E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>2.98E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.0247210433201888E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ77</f>
+        <v>2.07E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.32E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.1617788734936939E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.4799999999999998E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.1680840785172228E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.172205199932869E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.1846114975320451E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.2103169169868329E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.1000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.1007899748336825E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.1017119513989746E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.103820699217404E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.1077797552172309E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.1117455444773193E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.1236834407789606E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.1E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1484146077251696E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H77</f>
+        <v>2.1400000000000002E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF4880A7-BF72-405C-AB40-BFAB88E5DFC8}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46151</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>2.76E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>0.03</v>
+      </c>
+      <c r="E3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.7800000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.4582968502674616E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR78</f>
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z78</f>
+        <v>1.1500000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.07E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.0816899292500168E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.087679613673544E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.0915942913661267E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.1033780718266069E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.127788733589032E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ78</f>
+        <v>2.1100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.32E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.1617788734936939E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.4799999999999998E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.1680840785172228E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.172205199932869E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.1846114975320451E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.2103169169868329E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.1000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.320906088040159E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.3219636075024761E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3243824812786905E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3289242013672393E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3334741945595443E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3471739824844977E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.32E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.3755709228882935E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H78</f>
+        <v>2.3199999999999998E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$H9)^(B2/365)-1)*365/B2</f>
+        <v>3.0635189475697006E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$H9)^(C2/365)-1)*365/C2</f>
+        <v>3.0644188933007483E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.06647723601375E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.0703415987420896E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.0742124546103724E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.0858641039178882E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B52757C-9E20-4F21-B787-51AC5F13ABDD}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46152</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>2.76E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>0.03</v>
+      </c>
+      <c r="E3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.7800000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.5100340771234473E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR79</f>
+        <v>2.5300000000000003E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z79</f>
+        <v>1.0900000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.07E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ79</f>
+        <v>2.0899999999999998E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.7725321103891055E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.7815101107635661E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.7873806743672578E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.8050653690731094E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.8417638613382321E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.4699999999999998E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.32E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.1617788734936939E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.4799999999999998E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.1680840785172228E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.172205199932869E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.1846114975320451E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.2103169169868329E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.1000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.3509225383722141E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.3519992612899605E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3544620748271248E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3590863552975504E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3637191354794753E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3776686502467984E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4065854123153105E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H79</f>
+        <v>2.3300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.1107950800242885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.1117230159457634E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1138453984796127E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1178300696434385E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1218215395197819E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.1338368720569248E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9788B82-8AEB-4A99-9D29-2FB9B67D884B}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46153</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>2.76E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>0.03</v>
+      </c>
+      <c r="E3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.7800000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.6900000000000002E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.7587321525166306E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR80</f>
+        <v>2.5800000000000003E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>'11.05.2026'!H4-'Daily Data'!Z80</f>
+        <v>1.0900000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.07E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.3920472988498589E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.3993048356382727E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.4040491647770316E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.4183351862080429E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.39E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4479524999688094E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ80</f>
+        <v>2.2800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.32E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.1617788734936939E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.4799999999999998E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.1680840785172228E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.172205199932869E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.1846114975320451E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.2103169169868329E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.1000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.3509225383722141E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.3519992612899605E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3544620748271248E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3590863552975504E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3637191354794753E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3776686502467984E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4065854123153105E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H80</f>
+        <v>2.3300000000000001E-2</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
@@ -56282,7 +58176,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -56645,7 +58539,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="44" priority="1">
+    <cfRule type="expression" dxfId="50" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -57006,7 +58900,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -57361,7 +59255,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="48" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1036A130-A93B-4650-A375-CFC1DD9AC813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C44FFAA-3957-404B-B969-C76D11ABD79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="1830" windowWidth="29040" windowHeight="15720" firstSheet="46" activeTab="55" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -68,6 +68,7 @@
     <sheet name="09.05.2026" sheetId="74" r:id="rId53"/>
     <sheet name="10.05.2026" sheetId="75" r:id="rId54"/>
     <sheet name="11.05.2026" sheetId="77" r:id="rId55"/>
+    <sheet name="12.05.2026" sheetId="78" r:id="rId56"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1989,6 +1990,43 @@
 </comments>
 </file>
 
+<file path=xl/comments52.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{17A5D5ED-927A-440C-A0FA-B87EAAFC197C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -2138,7 +2176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3569" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3582" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -2821,14 +2859,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="52">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="51">
     <dxf>
       <fill>
         <patternFill>
@@ -3210,7 +3241,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>354623</xdr:colOff>
+      <xdr:colOff>351448</xdr:colOff>
       <xdr:row>121</xdr:row>
       <xdr:rowOff>20630</xdr:rowOff>
     </xdr:to>
@@ -6623,17 +6654,29 @@
       <c r="F132" s="23">
         <v>3.6499999999999998E-2</v>
       </c>
-      <c r="G132" s="90"/>
+      <c r="G132" s="90">
+        <v>82210</v>
+      </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="82">
         <v>46154</v>
       </c>
-      <c r="B133" s="83"/>
-      <c r="C133" s="23"/>
-      <c r="D133" s="23"/>
-      <c r="E133" s="23"/>
-      <c r="F133" s="23"/>
+      <c r="B133" s="83">
+        <v>3.27E-2</v>
+      </c>
+      <c r="C133" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D133" s="23">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="E133" s="23">
+        <v>4.19E-2</v>
+      </c>
+      <c r="F133" s="23">
+        <v>3.9899999999999998E-2</v>
+      </c>
       <c r="G133" s="90"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
@@ -7303,7 +7346,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7639,7 +7682,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="46" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7977,7 +8020,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8313,7 +8356,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="44" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8647,7 +8690,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8983,7 +9026,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9319,7 +9362,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9655,7 +9698,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9991,7 +10034,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10327,7 +10370,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10363,7 +10406,9 @@
     <col min="34" max="34" width="7.08984375" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="39" max="41" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="42" max="43" width="6.1796875" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="7.08984375" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -11118,7 +11163,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS80" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS81" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -23620,7 +23665,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="BA71" s="13">
-        <f t="shared" ref="BA71:BA80" si="5">AZ71-AR71</f>
+        <f t="shared" ref="BA71:BA81" si="5">AZ71-AR71</f>
         <v>2.6199999999999998E-2</v>
       </c>
       <c r="BC71" s="4">
@@ -24904,7 +24949,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="AI78" s="13">
-        <f t="shared" ref="AI78:AI80" si="6">AH78-Z78</f>
+        <f t="shared" ref="AI78:AI81" si="6">AH78-Z78</f>
         <v>1.1500000000000002E-2</v>
       </c>
       <c r="AK78" s="4">
@@ -25394,7 +25439,9 @@
       <c r="G81" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H81" s="9"/>
+      <c r="H81" s="9">
+        <v>1.18E-2</v>
+      </c>
       <c r="I81" s="2">
         <v>46154</v>
       </c>
@@ -25416,10 +25463,12 @@
       <c r="O81" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P81" s="58"/>
+      <c r="P81" s="58">
+        <v>3.32E-2</v>
+      </c>
       <c r="Q81" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.1400000000000002E-2</v>
       </c>
       <c r="S81" s="4">
         <v>46154</v>
@@ -25436,11 +25485,15 @@
       <c r="W81" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X81" s="6"/>
+      <c r="X81" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y81" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z81" s="6"/>
+      <c r="Z81" s="6">
+        <v>1.41E-2</v>
+      </c>
       <c r="AA81" s="2">
         <v>46154</v>
       </c>
@@ -25462,50 +25515,99 @@
       <c r="AG81" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH81" s="58"/>
-      <c r="AI81" s="13"/>
+      <c r="AH81" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI81" s="13">
+        <f t="shared" si="6"/>
+        <v>1.0900000000000002E-2</v>
+      </c>
       <c r="AK81" s="4">
         <v>46154</v>
       </c>
-      <c r="AL81" s="6"/>
+      <c r="AL81" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM81" s="3"/>
-      <c r="AN81" s="3"/>
+      <c r="AN81" s="6">
+        <v>2.5999999999999999E-2</v>
+      </c>
       <c r="AO81" s="3"/>
-      <c r="AP81" s="3"/>
-      <c r="AQ81" s="3"/>
-      <c r="AR81" s="6"/>
+      <c r="AP81" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ81" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR81" s="6">
+        <v>1.03E-2</v>
+      </c>
       <c r="AS81" s="2">
         <v>46154</v>
       </c>
-      <c r="AT81" s="14"/>
-      <c r="AU81" s="14"/>
-      <c r="AV81" s="14"/>
-      <c r="AW81" s="14"/>
-      <c r="AX81" s="14"/>
-      <c r="AY81" s="14"/>
-      <c r="AZ81" s="14"/>
-      <c r="BA81" s="13"/>
+      <c r="AT81" s="14">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="AU81" s="14">
+        <v>3.1E-2</v>
+      </c>
+      <c r="AV81" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AW81" s="14">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="AX81" s="14">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="AY81" s="14">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="AZ81" s="14">
+        <v>3.61E-2</v>
+      </c>
+      <c r="BA81" s="13">
+        <f t="shared" si="5"/>
+        <v>2.58E-2</v>
+      </c>
       <c r="BC81" s="4">
         <v>46154</v>
       </c>
-      <c r="BD81" s="6"/>
-      <c r="BE81" s="6"/>
-      <c r="BF81" s="6"/>
+      <c r="BD81" s="6">
+        <v>1.1299999999999999E-2</v>
+      </c>
+      <c r="BE81" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BF81" s="6">
+        <v>1.15E-2</v>
+      </c>
       <c r="BG81" s="3"/>
       <c r="BH81" s="3"/>
       <c r="BI81" s="3"/>
-      <c r="BJ81" s="6"/>
+      <c r="BJ81" s="6">
+        <v>1.12E-2</v>
+      </c>
       <c r="BK81" s="2">
         <v>46154</v>
       </c>
-      <c r="BL81" s="58"/>
+      <c r="BL81" s="58">
+        <v>4.0399999999999998E-2</v>
+      </c>
       <c r="BM81" s="1"/>
-      <c r="BN81" s="58"/>
+      <c r="BN81" s="58">
+        <v>5.5100000000000003E-2</v>
+      </c>
       <c r="BO81" s="1"/>
       <c r="BP81" s="1"/>
       <c r="BQ81" s="1"/>
-      <c r="BR81" s="58"/>
-      <c r="BS81" s="13"/>
+      <c r="BR81" s="58">
+        <v>3.32E-2</v>
+      </c>
+      <c r="BS81" s="13">
+        <f t="shared" si="3"/>
+        <v>2.1999999999999999E-2</v>
+      </c>
     </row>
     <row r="82" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A82" s="4">
@@ -26525,7 +26627,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26861,7 +26963,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27199,7 +27301,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27537,7 +27639,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27875,7 +27977,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28243,7 +28345,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28611,7 +28713,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28979,7 +29081,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29350,7 +29452,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -29731,7 +29833,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31195,7 +31297,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31539,7 +31641,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31883,7 +31985,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32227,7 +32329,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32571,7 +32673,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32903,7 +33005,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33247,7 +33349,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33591,7 +33693,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33938,7 +34040,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -34283,7 +34385,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -44979,7 +45081,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45323,7 +45425,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45658,7 +45760,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45990,7 +46092,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46334,7 +46436,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46678,7 +46780,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47022,7 +47124,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47366,7 +47468,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47710,7 +47812,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -48054,7 +48156,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -56091,7 +56193,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -56435,7 +56537,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -56779,7 +56881,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -57123,7 +57225,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -57805,6 +57907,350 @@
       <c r="I9" s="74">
         <f t="shared" si="1"/>
         <v>3.1587290874597329E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABD966B-F40F-4576-98E1-42700F331F18}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46154</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.1E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.61E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.6757666539783518E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR81</f>
+        <v>2.58E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z81</f>
+        <v>1.0900000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.3219636075024761E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.3289242013672393E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.3334741945595443E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.3471739824844977E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.32E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.3755709228882935E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ81</f>
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>'12.05.2026'!H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.0616680497176203E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.0675801218832937E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.071444020872649E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.0830746942096931E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.0599999999999999E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1071669725747597E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>1.9999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.320906088040159E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.3219636075024761E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3243824812786905E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3289242013672393E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3334741945595443E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3471739824844977E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.32E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.3755709228882935E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H81</f>
+        <v>2.1400000000000002E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>4.1914432432310952E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>4.1931278648089418E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.1969818193079732E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.2042207191949066E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.2114762664961662E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.2333432241796282E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>4.19E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>4.2787686858843488E-2</v>
       </c>
       <c r="J9" s="75"/>
       <c r="K9" s="69"/>
@@ -58176,7 +58622,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="51" priority="1">
+    <cfRule type="expression" dxfId="50" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58539,7 +58985,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="50" priority="1">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -58900,7 +59346,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="49" priority="1">
+    <cfRule type="expression" dxfId="48" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -59255,7 +59701,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C44FFAA-3957-404B-B969-C76D11ABD79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35736C7-815B-48E5-A154-5BB4CFF11ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="1830" windowWidth="29040" windowHeight="15720" firstSheet="46" activeTab="55" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="47" activeTab="56" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -69,6 +69,8 @@
     <sheet name="10.05.2026" sheetId="75" r:id="rId54"/>
     <sheet name="11.05.2026" sheetId="77" r:id="rId55"/>
     <sheet name="12.05.2026" sheetId="78" r:id="rId56"/>
+    <sheet name="13.05.2026" sheetId="79" r:id="rId57"/>
+    <sheet name="Sheet2" sheetId="80" r:id="rId58"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2027,6 +2029,43 @@
 </comments>
 </file>
 
+<file path=xl/comments53.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{EF361E1B-7D51-41B7-9ACF-EE2F1B913DAD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -2176,7 +2215,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3582" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3595" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -2859,7 +2898,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="51">
+  <dxfs count="52">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3241,7 +3287,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>351448</xdr:colOff>
+      <xdr:colOff>354623</xdr:colOff>
       <xdr:row>121</xdr:row>
       <xdr:rowOff>20630</xdr:rowOff>
     </xdr:to>
@@ -6677,17 +6723,29 @@
       <c r="F133" s="23">
         <v>3.9899999999999998E-2</v>
       </c>
-      <c r="G133" s="90"/>
+      <c r="G133" s="90">
+        <v>81745</v>
+      </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="82">
         <v>46155</v>
       </c>
-      <c r="B134" s="83"/>
-      <c r="C134" s="23"/>
-      <c r="D134" s="23"/>
-      <c r="E134" s="23"/>
-      <c r="F134" s="23"/>
+      <c r="B134" s="83">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="C134" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D134" s="23">
+        <v>3.6799999999999999E-2</v>
+      </c>
+      <c r="E134" s="23">
+        <v>4.2799999999999998E-2</v>
+      </c>
+      <c r="F134" s="23">
+        <v>3.8600000000000002E-2</v>
+      </c>
       <c r="G134" s="90"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
@@ -7346,7 +7404,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="46" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7682,7 +7740,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8020,7 +8078,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="44" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8356,7 +8414,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8690,7 +8748,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9026,7 +9084,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9362,7 +9420,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9698,7 +9756,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10034,7 +10092,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10370,7 +10428,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10418,10 +10476,12 @@
     <col min="50" max="51" width="6.1796875" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="7.08984375" bestFit="1" customWidth="1"/>
     <col min="55" max="55" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="56" max="58" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="6.1796875" bestFit="1" customWidth="1"/>
     <col min="59" max="60" width="4.36328125" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="8.26953125" bestFit="1" customWidth="1"/>
     <col min="63" max="63" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="64" max="64" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="65" max="65" width="4.36328125" bestFit="1" customWidth="1"/>
@@ -11163,7 +11223,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS81" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS82" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -23665,7 +23725,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="BA71" s="13">
-        <f t="shared" ref="BA71:BA81" si="5">AZ71-AR71</f>
+        <f t="shared" ref="BA71:BA82" si="5">AZ71-AR71</f>
         <v>2.6199999999999998E-2</v>
       </c>
       <c r="BC71" s="4">
@@ -24949,7 +25009,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="AI78" s="13">
-        <f t="shared" ref="AI78:AI81" si="6">AH78-Z78</f>
+        <f t="shared" ref="AI78:AI82" si="6">AH78-Z78</f>
         <v>1.1500000000000002E-2</v>
       </c>
       <c r="AK78" s="4">
@@ -25631,7 +25691,9 @@
       <c r="G82" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H82" s="9"/>
+      <c r="H82" s="9">
+        <v>1.2500000000000001E-2</v>
+      </c>
       <c r="I82" s="2">
         <v>46155</v>
       </c>
@@ -25653,10 +25715,12 @@
       <c r="O82" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P82" s="58"/>
+      <c r="P82" s="58">
+        <v>3.4200000000000001E-2</v>
+      </c>
       <c r="Q82" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.1700000000000001E-2</v>
       </c>
       <c r="S82" s="4">
         <v>46155</v>
@@ -25673,11 +25737,15 @@
       <c r="W82" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X82" s="6"/>
+      <c r="X82" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y82" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z82" s="6"/>
+      <c r="Z82" s="6">
+        <v>1.4200000000000001E-2</v>
+      </c>
       <c r="AA82" s="2">
         <v>46155</v>
       </c>
@@ -25699,50 +25767,97 @@
       <c r="AG82" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH82" s="58"/>
-      <c r="AI82" s="13"/>
+      <c r="AH82" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI82" s="13">
+        <f t="shared" si="6"/>
+        <v>1.0800000000000001E-2</v>
+      </c>
       <c r="AK82" s="4">
         <v>46155</v>
       </c>
-      <c r="AL82" s="6"/>
+      <c r="AL82" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
-      <c r="AP82" s="3"/>
-      <c r="AQ82" s="6"/>
-      <c r="AR82" s="6"/>
+      <c r="AP82" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ82" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR82" s="6">
+        <v>1.01E-2</v>
+      </c>
       <c r="AS82" s="2">
         <v>46155</v>
       </c>
-      <c r="AT82" s="14"/>
-      <c r="AU82" s="14"/>
-      <c r="AV82" s="14"/>
-      <c r="AW82" s="14"/>
-      <c r="AX82" s="14"/>
-      <c r="AY82" s="14"/>
-      <c r="AZ82" s="14"/>
-      <c r="BA82" s="13"/>
+      <c r="AT82" s="14">
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="AU82" s="14">
+        <v>2.75E-2</v>
+      </c>
+      <c r="AV82" s="14">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AW82" s="14">
+        <v>3.95E-2</v>
+      </c>
+      <c r="AX82" s="14">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="AY82" s="14">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="AZ82" s="14">
+        <v>3.73E-2</v>
+      </c>
+      <c r="BA82" s="13">
+        <f t="shared" si="5"/>
+        <v>2.7200000000000002E-2</v>
+      </c>
       <c r="BC82" s="4">
         <v>46155</v>
       </c>
-      <c r="BD82" s="6"/>
-      <c r="BE82" s="6"/>
-      <c r="BF82" s="6"/>
+      <c r="BD82" s="6">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="BE82" s="6">
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="BF82" s="6">
+        <v>9.2999999999999992E-3</v>
+      </c>
       <c r="BG82" s="3"/>
       <c r="BH82" s="3"/>
       <c r="BI82" s="3"/>
-      <c r="BJ82" s="6"/>
+      <c r="BJ82" s="6">
+        <v>1.17E-2</v>
+      </c>
       <c r="BK82" s="2">
         <v>46155</v>
       </c>
-      <c r="BL82" s="58"/>
+      <c r="BL82" s="58">
+        <v>4.1399999999999999E-2</v>
+      </c>
       <c r="BM82" s="1"/>
-      <c r="BN82" s="58"/>
+      <c r="BN82" s="58">
+        <v>4.9599999999999998E-2</v>
+      </c>
       <c r="BO82" s="1"/>
       <c r="BP82" s="1"/>
       <c r="BQ82" s="1"/>
-      <c r="BR82" s="58"/>
-      <c r="BS82" s="13"/>
+      <c r="BR82" s="58">
+        <v>3.44E-2</v>
+      </c>
+      <c r="BS82" s="13">
+        <f t="shared" si="3"/>
+        <v>2.2699999999999998E-2</v>
+      </c>
     </row>
     <row r="83" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A83" s="4">
@@ -26627,7 +26742,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26963,7 +27078,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27301,7 +27416,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27639,7 +27754,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27977,7 +28092,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28345,7 +28460,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28713,7 +28828,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29081,7 +29196,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29452,7 +29567,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -29833,7 +29948,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31297,7 +31412,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31641,7 +31756,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31985,7 +32100,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32329,7 +32444,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32673,7 +32788,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33005,7 +33120,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33349,7 +33464,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33693,7 +33808,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -34040,7 +34155,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -34385,7 +34500,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45081,7 +45196,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45425,7 +45540,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45760,7 +45875,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46092,7 +46207,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46436,7 +46551,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46780,7 +46895,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47124,7 +47239,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47468,7 +47583,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47812,7 +47927,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -48156,7 +48271,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -56193,7 +56308,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -56537,7 +56652,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -56881,7 +56996,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -57225,7 +57340,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -57569,7 +57684,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -57913,7 +58028,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58257,6 +58372,350 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A741243F-B5F4-4BE0-B5EE-B3D199C0E724}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46155</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>2.75E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>3.95E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.73E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.8002397273573685E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR82</f>
+        <v>2.7200000000000002E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z82</f>
+        <v>1.0800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.442108148072958E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>4.9599999999999998E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.449581592722497E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.4544672327758312E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.4691795745238868E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.44E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4996845680234534E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ82</f>
+        <v>2.2699999999999998E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-1.5%</f>
+        <v>1.8700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.2800000000000003E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.121734116151758E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.4299999999999997E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.1278805465217829E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.1318977802404467E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.1439908012476682E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1690445957877067E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.06E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.4209614980849228E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.4220837014135107E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.4246505811097595E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.4294704023164348E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.4342992680180727E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.4488403232455951E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4789886456186414E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H82</f>
+        <v>2.1700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>4.2815059161980883E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>4.2832637114085803E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.287285143257006E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.2948389023937085E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.3024104068013491E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.3252318612913926E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>4.2799999999999998E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>4.3726509254560675E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
@@ -58266,6 +58725,15 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B49AEEAE-C199-40A3-A457-875D909AD397}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -58622,7 +59090,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="50" priority="1">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58985,7 +59453,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="49" priority="1">
+    <cfRule type="expression" dxfId="50" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -59346,7 +59814,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -59701,7 +60169,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="48" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35736C7-815B-48E5-A154-5BB4CFF11ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8364CE26-E74A-44B2-AEE8-A2FCCABE0183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="47" activeTab="56" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="1830" windowWidth="29040" windowHeight="15720" firstSheet="48" activeTab="57" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -70,7 +70,7 @@
     <sheet name="11.05.2026" sheetId="77" r:id="rId55"/>
     <sheet name="12.05.2026" sheetId="78" r:id="rId56"/>
     <sheet name="13.05.2026" sheetId="79" r:id="rId57"/>
-    <sheet name="Sheet2" sheetId="80" r:id="rId58"/>
+    <sheet name="14.05.2026" sheetId="80" r:id="rId58"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2066,6 +2066,43 @@
 </comments>
 </file>
 
+<file path=xl/comments54.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{C4D953EA-87B4-484F-BE58-398561D13019}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -2215,7 +2252,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3595" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -2898,7 +2935,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="52">
+  <dxfs count="53">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -6741,22 +6785,34 @@
         <v>3.6799999999999999E-2</v>
       </c>
       <c r="E134" s="23">
-        <v>4.2799999999999998E-2</v>
+        <v>4.3499999999999997E-2</v>
       </c>
       <c r="F134" s="23">
         <v>3.8600000000000002E-2</v>
       </c>
-      <c r="G134" s="90"/>
+      <c r="G134" s="90">
+        <v>80505</v>
+      </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="82">
         <v>46156</v>
       </c>
-      <c r="B135" s="83"/>
-      <c r="C135" s="23"/>
-      <c r="D135" s="23"/>
-      <c r="E135" s="23"/>
-      <c r="F135" s="23"/>
+      <c r="B135" s="83">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="C135" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D135" s="23">
+        <v>3.6900000000000002E-2</v>
+      </c>
+      <c r="E135" s="23">
+        <v>3.7199999999999997E-2</v>
+      </c>
+      <c r="F135" s="23">
+        <v>4.0300000000000002E-2</v>
+      </c>
       <c r="G135" s="90"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
@@ -7404,7 +7460,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="48" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7740,7 +7796,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="46" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8078,7 +8134,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8414,7 +8470,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="44" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8748,7 +8804,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9084,7 +9140,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9420,7 +9476,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9756,7 +9812,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10092,7 +10148,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10428,7 +10484,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10463,9 +10519,7 @@
     <col min="33" max="33" width="5.453125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="7.08984375" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="38" max="40" width="6.08984375" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="42" max="43" width="6.1796875" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="7.08984375" bestFit="1" customWidth="1"/>
@@ -11223,7 +11277,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS82" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS83" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -23725,7 +23779,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="BA71" s="13">
-        <f t="shared" ref="BA71:BA82" si="5">AZ71-AR71</f>
+        <f t="shared" ref="BA71:BA83" si="5">AZ71-AR71</f>
         <v>2.6199999999999998E-2</v>
       </c>
       <c r="BC71" s="4">
@@ -25009,7 +25063,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="AI78" s="13">
-        <f t="shared" ref="AI78:AI82" si="6">AH78-Z78</f>
+        <f t="shared" ref="AI78:AI83" si="6">AH78-Z78</f>
         <v>1.1500000000000002E-2</v>
       </c>
       <c r="AK78" s="4">
@@ -25881,7 +25935,9 @@
       <c r="G83" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H83" s="9"/>
+      <c r="H83" s="9">
+        <v>1.21E-2</v>
+      </c>
       <c r="I83" s="2">
         <v>46156</v>
       </c>
@@ -25903,10 +25959,12 @@
       <c r="O83" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P83" s="58"/>
+      <c r="P83" s="58">
+        <v>3.3599999999999998E-2</v>
+      </c>
       <c r="Q83" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.1499999999999998E-2</v>
       </c>
       <c r="S83" s="4">
         <v>46156</v>
@@ -25923,11 +25981,15 @@
       <c r="W83" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X83" s="6"/>
+      <c r="X83" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y83" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z83" s="6"/>
+      <c r="Z83" s="6">
+        <v>1.4200000000000001E-2</v>
+      </c>
       <c r="AA83" s="2">
         <v>46156</v>
       </c>
@@ -25949,50 +26011,99 @@
       <c r="AG83" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH83" s="58"/>
-      <c r="AI83" s="13"/>
+      <c r="AH83" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI83" s="13">
+        <f t="shared" si="6"/>
+        <v>1.0800000000000001E-2</v>
+      </c>
       <c r="AK83" s="4">
         <v>46156</v>
       </c>
-      <c r="AL83" s="3"/>
-      <c r="AM83" s="3"/>
+      <c r="AL83" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="AM83" s="6">
+        <v>2.6800000000000001E-2</v>
+      </c>
       <c r="AN83" s="3"/>
       <c r="AO83" s="3"/>
-      <c r="AP83" s="3"/>
-      <c r="AQ83" s="6"/>
-      <c r="AR83" s="6"/>
+      <c r="AP83" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ83" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR83" s="6">
+        <v>9.5999999999999992E-3</v>
+      </c>
       <c r="AS83" s="2">
         <v>46156</v>
       </c>
-      <c r="AT83" s="14"/>
-      <c r="AU83" s="14"/>
-      <c r="AV83" s="14"/>
-      <c r="AW83" s="14"/>
-      <c r="AX83" s="14"/>
-      <c r="AY83" s="14"/>
-      <c r="AZ83" s="14"/>
-      <c r="BA83" s="13"/>
+      <c r="AT83" s="14">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AU83" s="14">
+        <v>2.75E-2</v>
+      </c>
+      <c r="AV83" s="14">
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="AW83" s="14">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="AX83" s="14">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="AY83" s="14">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="AZ83" s="14">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="BA83" s="13">
+        <f t="shared" si="5"/>
+        <v>2.7400000000000001E-2</v>
+      </c>
       <c r="BC83" s="4">
         <v>46156</v>
       </c>
-      <c r="BD83" s="6"/>
-      <c r="BE83" s="6"/>
-      <c r="BF83" s="6"/>
+      <c r="BD83" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BE83" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BF83" s="6">
+        <v>1.17E-2</v>
+      </c>
       <c r="BG83" s="3"/>
       <c r="BH83" s="3"/>
       <c r="BI83" s="3"/>
-      <c r="BJ83" s="6"/>
+      <c r="BJ83" s="6">
+        <v>1.1599999999999999E-2</v>
+      </c>
       <c r="BK83" s="2">
         <v>46156</v>
       </c>
-      <c r="BL83" s="58"/>
+      <c r="BL83" s="58">
+        <v>4.1000000000000002E-2</v>
+      </c>
       <c r="BM83" s="1"/>
-      <c r="BN83" s="58"/>
+      <c r="BN83" s="58">
+        <v>4.9099999999999998E-2</v>
+      </c>
       <c r="BO83" s="1"/>
       <c r="BP83" s="1"/>
       <c r="BQ83" s="1"/>
-      <c r="BR83" s="58"/>
-      <c r="BS83" s="13"/>
+      <c r="BR83" s="58">
+        <v>3.4099999999999998E-2</v>
+      </c>
+      <c r="BS83" s="13">
+        <f t="shared" si="3"/>
+        <v>2.2499999999999999E-2</v>
+      </c>
     </row>
     <row r="84" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A84" s="4">
@@ -26742,7 +26853,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27078,7 +27189,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27416,7 +27527,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27754,7 +27865,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28092,7 +28203,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28460,7 +28571,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28828,7 +28939,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29196,7 +29307,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29567,7 +29678,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -29948,7 +30059,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31412,7 +31523,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31756,7 +31867,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32100,7 +32211,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32444,7 +32555,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32788,7 +32899,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33120,7 +33231,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33464,7 +33575,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33808,7 +33919,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -34155,7 +34266,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -34500,7 +34611,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45196,7 +45307,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45540,7 +45651,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45875,7 +45986,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46207,7 +46318,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46551,7 +46662,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46895,7 +47006,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47239,7 +47350,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47583,7 +47694,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47927,7 +48038,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -48271,7 +48382,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -56308,7 +56419,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -56652,7 +56763,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -56996,7 +57107,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -57340,7 +57451,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -57684,7 +57795,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58028,7 +58139,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58372,7 +58483,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58716,7 +58827,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58729,11 +58840,346 @@
 </file>
 
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B49AEEAE-C199-40A3-A457-875D909AD397}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B49AEEAE-C199-40A3-A457-875D909AD397}">
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46156</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>2.75E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.7691074941686109E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR83</f>
+        <v>2.7400000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z83</f>
+        <v>1.0800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.4120715315691226E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.4194150509021019E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.4242156544242203E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.4386714456067322E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.4099999999999998E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4686422321102972E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ83</f>
+        <v>2.2499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-1.5%</f>
+        <v>1.8700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.49E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.3219636075024761E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.3289242013672393E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.3334741945595443E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.3471739824844977E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.32E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.3755709228882935E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.2600000000000002E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.3609280547048134E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.3620112171935869E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3644887653183776E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3691407316138212E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3738012740671279E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3878345364413684E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4169256374043444E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H83</f>
+        <v>2.1499999999999998E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.7211375959605046E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.7224653775365733E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.7255026795251799E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.7312065302985954E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.7369220247494755E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.7541386378962212E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.7199999999999997E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.7898612814819987E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -59090,7 +59536,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="51" priority="1">
+    <cfRule type="expression" dxfId="52" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -59453,7 +59899,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="50" priority="1">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -59814,7 +60260,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="49" priority="1">
+    <cfRule type="expression" dxfId="50" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -60169,7 +60615,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8364CE26-E74A-44B2-AEE8-A2FCCABE0183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EECDA49-19C0-4CFD-9EE0-3164432CDF4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="1830" windowWidth="29040" windowHeight="15720" firstSheet="48" activeTab="57" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="1830" windowWidth="29040" windowHeight="15720" firstSheet="49" activeTab="58" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -71,6 +71,7 @@
     <sheet name="12.05.2026" sheetId="78" r:id="rId56"/>
     <sheet name="13.05.2026" sheetId="79" r:id="rId57"/>
     <sheet name="14.05.2026" sheetId="80" r:id="rId58"/>
+    <sheet name="15.05.2026" sheetId="81" r:id="rId59"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2103,6 +2104,43 @@
 </comments>
 </file>
 
+<file path=xl/comments55.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{9F575ED3-68DE-4FB9-A322-9E3415C71C12}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -2252,7 +2290,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3621" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -2935,7 +2973,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="53">
+  <dxfs count="54">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -6813,17 +6858,29 @@
       <c r="F135" s="23">
         <v>4.0300000000000002E-2</v>
       </c>
-      <c r="G135" s="90"/>
+      <c r="G135" s="90">
+        <v>79315</v>
+      </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="82">
         <v>46157</v>
       </c>
-      <c r="B136" s="83"/>
-      <c r="C136" s="23"/>
-      <c r="D136" s="23"/>
-      <c r="E136" s="23"/>
-      <c r="F136" s="23"/>
+      <c r="B136" s="83">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="C136" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D136" s="23">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="E136" s="23">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="F136" s="23">
+        <v>3.9899999999999998E-2</v>
+      </c>
       <c r="G136" s="90"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
@@ -7460,7 +7517,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7796,7 +7853,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="48" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8134,7 +8191,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="46" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8470,7 +8527,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8804,7 +8861,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="44" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9140,7 +9197,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9476,7 +9533,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9812,7 +9869,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10148,7 +10205,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10484,7 +10541,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11277,7 +11334,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS83" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS84" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -23779,7 +23836,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="BA71" s="13">
-        <f t="shared" ref="BA71:BA83" si="5">AZ71-AR71</f>
+        <f t="shared" ref="BA71:BA84" si="5">AZ71-AR71</f>
         <v>2.6199999999999998E-2</v>
       </c>
       <c r="BC71" s="4">
@@ -25063,7 +25120,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="AI78" s="13">
-        <f t="shared" ref="AI78:AI83" si="6">AH78-Z78</f>
+        <f t="shared" ref="AI78:AI86" si="6">AH78-Z78</f>
         <v>1.1500000000000002E-2</v>
       </c>
       <c r="AK78" s="4">
@@ -26127,7 +26184,9 @@
       <c r="G84" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H84" s="9"/>
+      <c r="H84" s="9">
+        <v>1.12E-2</v>
+      </c>
       <c r="I84" s="2">
         <v>46157</v>
       </c>
@@ -26149,10 +26208,12 @@
       <c r="O84" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P84" s="58"/>
+      <c r="P84" s="58">
+        <v>3.2300000000000002E-2</v>
+      </c>
       <c r="Q84" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.1100000000000001E-2</v>
       </c>
       <c r="S84" s="4">
         <v>46157</v>
@@ -26169,11 +26230,15 @@
       <c r="W84" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X84" s="6"/>
+      <c r="X84" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y84" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z84" s="6"/>
+      <c r="Z84" s="6">
+        <v>1.46E-2</v>
+      </c>
       <c r="AA84" s="2">
         <v>46157</v>
       </c>
@@ -26195,50 +26260,97 @@
       <c r="AG84" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH84" s="58"/>
-      <c r="AI84" s="13"/>
+      <c r="AH84" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI84" s="13">
+        <f t="shared" si="6"/>
+        <v>1.0400000000000001E-2</v>
+      </c>
       <c r="AK84" s="4">
         <v>46157</v>
       </c>
-      <c r="AL84" s="3"/>
+      <c r="AL84" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM84" s="3"/>
       <c r="AN84" s="3"/>
       <c r="AO84" s="3"/>
-      <c r="AP84" s="3"/>
-      <c r="AQ84" s="6"/>
-      <c r="AR84" s="6"/>
+      <c r="AP84" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ84" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR84" s="6">
+        <v>1.09E-2</v>
+      </c>
       <c r="AS84" s="2">
         <v>46157</v>
       </c>
-      <c r="AT84" s="14"/>
-      <c r="AU84" s="14"/>
-      <c r="AV84" s="14"/>
-      <c r="AW84" s="14"/>
-      <c r="AX84" s="14"/>
-      <c r="AY84" s="14"/>
-      <c r="AZ84" s="14"/>
-      <c r="BA84" s="13"/>
+      <c r="AT84" s="14">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AU84" s="14">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="AV84" s="14">
+        <v>0.03</v>
+      </c>
+      <c r="AW84" s="14">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="AX84" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="AY84" s="14">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="AZ84" s="14">
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="BA84" s="13">
+        <f t="shared" si="5"/>
+        <v>2.4899999999999999E-2</v>
+      </c>
       <c r="BC84" s="4">
         <v>46157</v>
       </c>
-      <c r="BD84" s="6"/>
-      <c r="BE84" s="6"/>
-      <c r="BF84" s="6"/>
+      <c r="BD84" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BE84" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BF84" s="6">
+        <v>1.17E-2</v>
+      </c>
       <c r="BG84" s="3"/>
       <c r="BH84" s="3"/>
       <c r="BI84" s="3"/>
-      <c r="BJ84" s="6"/>
+      <c r="BJ84" s="6">
+        <v>1.2E-2</v>
+      </c>
       <c r="BK84" s="2">
         <v>46157</v>
       </c>
-      <c r="BL84" s="58"/>
+      <c r="BL84" s="58">
+        <v>4.1599999999999998E-2</v>
+      </c>
       <c r="BM84" s="1"/>
-      <c r="BN84" s="58"/>
+      <c r="BN84" s="58">
+        <v>4.99E-2</v>
+      </c>
       <c r="BO84" s="1"/>
       <c r="BP84" s="1"/>
       <c r="BQ84" s="1"/>
-      <c r="BR84" s="58"/>
-      <c r="BS84" s="13"/>
+      <c r="BR84" s="58">
+        <v>3.4700000000000002E-2</v>
+      </c>
+      <c r="BS84" s="13">
+        <f t="shared" si="3"/>
+        <v>2.2700000000000001E-2</v>
+      </c>
     </row>
     <row r="85" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A85" s="4">
@@ -26853,7 +26965,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27189,7 +27301,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27527,7 +27639,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27865,7 +27977,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28203,7 +28315,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28571,7 +28683,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28939,7 +29051,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29307,7 +29419,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29678,7 +29790,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30059,7 +30171,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31523,7 +31635,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31867,7 +31979,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32211,7 +32323,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32555,7 +32667,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32899,7 +33011,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33231,7 +33343,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33575,7 +33687,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33919,7 +34031,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -34266,7 +34378,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -34611,7 +34723,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45307,7 +45419,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45651,7 +45763,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45986,7 +46098,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46318,7 +46430,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46662,7 +46774,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47006,7 +47118,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47350,7 +47462,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47694,7 +47806,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -48038,7 +48150,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -48382,7 +48494,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -56419,7 +56531,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -56763,7 +56875,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -57107,7 +57219,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -57451,7 +57563,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -57795,7 +57907,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58139,7 +58251,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58483,7 +58595,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58827,7 +58939,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -59165,6 +59277,350 @@
       <c r="I9" s="74">
         <f t="shared" si="1"/>
         <v>3.7898612814819987E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8BDB68E-1E8A-4CCA-8789-465577234C5F}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46157</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>0.03</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>0.05</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.6446716511065569E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR84</f>
+        <v>2.4899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z84</f>
+        <v>1.0400000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.4721450854841733E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>4.99E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.4797495973070948E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.4847210239193682E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.4996921918003271E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.4700000000000002E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.5307361916328883E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ84</f>
+        <v>2.2700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.39E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.2318585715067308E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2384465142249297E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2427526440872788E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.255716890990918E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.2825831032744723E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1</f>
+        <v>-0.9677</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.2308576251097731E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.2318585715067308E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.2341480019105272E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.2384465142249297E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.2427526440872788E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.255716890990918E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.2825831032744723E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-1.06%</f>
+        <v>2.1700000000000004E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.4509784417989478E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.4521204248868585E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.4547325644198969E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.4596374317178734E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.4645515839499125E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.479349948210321E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.5100340771234473E-2</v>
       </c>
       <c r="J9" s="75"/>
       <c r="K9" s="69"/>
@@ -59536,7 +59992,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="52" priority="1">
+    <cfRule type="expression" dxfId="53" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -59899,7 +60355,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="51" priority="1">
+    <cfRule type="expression" dxfId="52" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -60260,7 +60716,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="50" priority="1">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -60615,7 +61071,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="49" priority="1">
+    <cfRule type="expression" dxfId="50" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EECDA49-19C0-4CFD-9EE0-3164432CDF4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D7F26C-0EB4-462A-B735-BC29FF1CAD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="1830" windowWidth="29040" windowHeight="15720" firstSheet="49" activeTab="58" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="1830" windowWidth="29040" windowHeight="15720" firstSheet="54" activeTab="63" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -72,6 +72,11 @@
     <sheet name="13.05.2026" sheetId="79" r:id="rId57"/>
     <sheet name="14.05.2026" sheetId="80" r:id="rId58"/>
     <sheet name="15.05.2026" sheetId="81" r:id="rId59"/>
+    <sheet name="16.05.2026" sheetId="82" r:id="rId60"/>
+    <sheet name="17.05.2026" sheetId="83" r:id="rId61"/>
+    <sheet name="18.05.2026" sheetId="84" r:id="rId62"/>
+    <sheet name="19.05.2026" sheetId="85" r:id="rId63"/>
+    <sheet name="20.05.2026" sheetId="86" r:id="rId64"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2141,6 +2146,154 @@
 </comments>
 </file>
 
+<file path=xl/comments56.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{C09DBBD8-CFA6-4F17-85AD-B8F2D4058A33}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments57.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{24F4450E-8C7E-45C8-AB0C-B01489138898}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments58.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{DC750809-EDD2-4482-9AC4-EA27D1F0C457}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments59.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{CDEBCE68-5772-450C-8AE9-1457A22298EF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -2148,6 +2301,43 @@
   </authors>
   <commentList>
     <comment ref="H9" authorId="0" shapeId="0" xr:uid="{45C0A957-29C3-40B8-89A2-6C7253E6208E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments60.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{96403D67-1E08-4ED8-9DCA-7ABF5D8139F5}">
       <text>
         <r>
           <rPr>
@@ -2290,7 +2480,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3621" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3847" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -2973,7 +3163,42 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="54">
+  <dxfs count="59">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3370,15 +3595,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>8362</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>167312</xdr:rowOff>
+      <xdr:colOff>61233</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>73029</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>354623</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>20630</xdr:rowOff>
+      <xdr:colOff>407494</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>111739</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3401,8 +3626,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7496477" y="15920197"/>
-          <a:ext cx="6444215" cy="6264375"/>
+          <a:off x="7540429" y="17748116"/>
+          <a:ext cx="6463933" cy="6234101"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6881,115 +7106,224 @@
       <c r="F136" s="23">
         <v>3.9899999999999998E-2</v>
       </c>
-      <c r="G136" s="90"/>
+      <c r="G136" s="90">
+        <v>81090</v>
+      </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="82">
         <v>46158</v>
       </c>
-      <c r="B137" s="83"/>
-      <c r="C137" s="23"/>
-      <c r="D137" s="23"/>
-      <c r="E137" s="23"/>
-      <c r="F137" s="23"/>
-      <c r="G137" s="90"/>
+      <c r="B137" s="83">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="C137" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D137" s="23">
+        <v>3.4799999999999998E-2</v>
+      </c>
+      <c r="E137" s="23">
+        <v>3.3300000000000003E-2</v>
+      </c>
+      <c r="F137" s="23">
+        <v>4.0899999999999999E-2</v>
+      </c>
+      <c r="G137" s="90">
+        <v>79114</v>
+      </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="82">
         <v>46159</v>
       </c>
-      <c r="B138" s="83"/>
-      <c r="C138" s="23"/>
-      <c r="D138" s="23"/>
-      <c r="E138" s="23"/>
-      <c r="F138" s="23"/>
-      <c r="G138" s="90"/>
+      <c r="B138" s="83">
+        <v>3.0700000000000002E-2</v>
+      </c>
+      <c r="C138" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D138" s="23">
+        <v>3.3799999999999997E-2</v>
+      </c>
+      <c r="E138" s="23">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="F138" s="23">
+        <v>3.7600000000000001E-2</v>
+      </c>
+      <c r="G138" s="90">
+        <v>78149</v>
+      </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A139" s="80"/>
-      <c r="B139" s="80"/>
+      <c r="A139" s="82">
+        <v>46160</v>
+      </c>
+      <c r="B139" s="83">
+        <v>2.9899999999999999E-2</v>
+      </c>
+      <c r="C139" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D139" s="23">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="E139" s="23">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="F139" s="23">
+        <v>3.6900000000000002E-2</v>
+      </c>
+      <c r="G139" s="90">
+        <v>76751</v>
+      </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A140" s="80"/>
-      <c r="B140" s="80"/>
+      <c r="A140" s="82">
+        <v>46161</v>
+      </c>
+      <c r="B140" s="83">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="C140" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D140" s="23">
+        <v>3.4700000000000002E-2</v>
+      </c>
+      <c r="E140" s="23">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="F140" s="23">
+        <v>3.5400000000000001E-2</v>
+      </c>
+      <c r="G140" s="90">
+        <v>77002</v>
+      </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A141" s="80"/>
-      <c r="B141" s="80"/>
+      <c r="A141" s="82">
+        <v>46162</v>
+      </c>
+      <c r="B141" s="83">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="C141" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D141" s="23">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="E141" s="23">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="F141" s="23">
+        <v>3.85E-2</v>
+      </c>
+      <c r="G141" s="90"/>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A142" s="80"/>
-      <c r="B142" s="80"/>
+      <c r="A142" s="82">
+        <v>46163</v>
+      </c>
+      <c r="B142" s="83"/>
+      <c r="C142" s="23"/>
+      <c r="D142" s="23"/>
+      <c r="E142" s="23"/>
+      <c r="F142" s="23"/>
+      <c r="G142" s="90"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A143" s="80"/>
-      <c r="B143" s="80"/>
+      <c r="A143" s="82">
+        <v>46164</v>
+      </c>
+      <c r="B143" s="83"/>
+      <c r="C143" s="23"/>
+      <c r="D143" s="23"/>
+      <c r="E143" s="23"/>
+      <c r="F143" s="23"/>
+      <c r="G143" s="90"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A144" s="80"/>
-      <c r="B144" s="80"/>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A145" s="80"/>
-      <c r="B145" s="80"/>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A144" s="82">
+        <v>46165</v>
+      </c>
+      <c r="B144" s="83"/>
+      <c r="C144" s="23"/>
+      <c r="D144" s="23"/>
+      <c r="E144" s="23"/>
+      <c r="F144" s="23"/>
+      <c r="G144" s="90"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A145" s="82">
+        <v>46166</v>
+      </c>
+      <c r="B145" s="83"/>
+      <c r="C145" s="23"/>
+      <c r="D145" s="23"/>
+      <c r="E145" s="23"/>
+      <c r="F145" s="23"/>
+      <c r="G145" s="90"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="80"/>
       <c r="B146" s="80"/>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="80"/>
       <c r="B147" s="80"/>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="80"/>
       <c r="B148" s="80"/>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="80"/>
       <c r="B149" s="80"/>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="80"/>
       <c r="B150" s="80"/>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="80"/>
       <c r="B151" s="80"/>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="80"/>
       <c r="B152" s="80"/>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="80"/>
       <c r="B153" s="80"/>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="80"/>
       <c r="B154" s="80"/>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="80"/>
       <c r="B155" s="80"/>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="80"/>
       <c r="B156" s="80"/>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="80"/>
       <c r="B157" s="80"/>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="80"/>
       <c r="B158" s="80"/>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="80"/>
       <c r="B159" s="80"/>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="80"/>
       <c r="B160" s="80"/>
     </row>
@@ -7517,7 +7851,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="49" priority="1">
+    <cfRule type="expression" dxfId="54" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7853,7 +8187,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="53" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8191,7 +8525,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="52" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8527,7 +8861,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="46" priority="1">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8861,7 +9195,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="50" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9197,7 +9531,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="44" priority="1">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9533,7 +9867,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="48" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9869,7 +10203,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10205,7 +10539,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10541,7 +10875,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10585,7 +10919,7 @@
     <col min="47" max="48" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="8.26953125" bestFit="1" customWidth="1"/>
     <col min="50" max="51" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="8.26953125" bestFit="1" customWidth="1"/>
     <col min="55" max="55" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="56" max="56" width="6.1796875" bestFit="1" customWidth="1"/>
     <col min="57" max="57" width="7.1796875" bestFit="1" customWidth="1"/>
@@ -11334,7 +11668,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS84" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS89" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -23836,7 +24170,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="BA71" s="13">
-        <f t="shared" ref="BA71:BA84" si="5">AZ71-AR71</f>
+        <f t="shared" ref="BA71:BA89" si="5">AZ71-AR71</f>
         <v>2.6199999999999998E-2</v>
       </c>
       <c r="BC71" s="4">
@@ -25120,7 +25454,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="AI78" s="13">
-        <f t="shared" ref="AI78:AI86" si="6">AH78-Z78</f>
+        <f t="shared" ref="AI78:AI89" si="6">AH78-Z78</f>
         <v>1.1500000000000002E-2</v>
       </c>
       <c r="AK78" s="4">
@@ -26374,7 +26708,9 @@
       <c r="G85" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H85" s="9"/>
+      <c r="H85" s="9">
+        <v>0.01</v>
+      </c>
       <c r="I85" s="2">
         <v>46158</v>
       </c>
@@ -26396,10 +26732,12 @@
       <c r="O85" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P85" s="58"/>
+      <c r="P85" s="58">
+        <v>3.2300000000000002E-2</v>
+      </c>
       <c r="Q85" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.23E-2</v>
       </c>
       <c r="S85" s="4">
         <v>46158</v>
@@ -26416,11 +26754,15 @@
       <c r="W85" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X85" s="6"/>
+      <c r="X85" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y85" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z85" s="6"/>
+      <c r="Z85" s="6">
+        <v>1.41E-2</v>
+      </c>
       <c r="AA85" s="2">
         <v>46158</v>
       </c>
@@ -26442,50 +26784,97 @@
       <c r="AG85" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH85" s="58"/>
-      <c r="AI85" s="13"/>
+      <c r="AH85" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI85" s="13">
+        <f t="shared" si="6"/>
+        <v>1.0900000000000002E-2</v>
+      </c>
       <c r="AK85" s="4">
         <v>46158</v>
       </c>
-      <c r="AL85" s="3"/>
+      <c r="AL85" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM85" s="3"/>
       <c r="AN85" s="3"/>
       <c r="AO85" s="3"/>
-      <c r="AP85" s="3"/>
-      <c r="AQ85" s="6"/>
-      <c r="AR85" s="6"/>
+      <c r="AP85" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ85" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR85" s="6">
+        <v>8.8000000000000005E-3</v>
+      </c>
       <c r="AS85" s="2">
         <v>46158</v>
       </c>
-      <c r="AT85" s="14"/>
-      <c r="AU85" s="14"/>
-      <c r="AV85" s="14"/>
-      <c r="AW85" s="14"/>
-      <c r="AX85" s="14"/>
-      <c r="AY85" s="14"/>
-      <c r="AZ85" s="14"/>
-      <c r="BA85" s="13"/>
+      <c r="AT85" s="14">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AU85" s="14">
+        <v>2.8199999999999999E-2</v>
+      </c>
+      <c r="AV85" s="14">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="AW85" s="14">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="AX85" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="AY85" s="14">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="AZ85" s="14">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="BA85" s="13">
+        <f t="shared" si="5"/>
+        <v>2.7199999999999995E-2</v>
+      </c>
       <c r="BC85" s="4">
         <v>46158</v>
       </c>
-      <c r="BD85" s="6"/>
-      <c r="BE85" s="6"/>
-      <c r="BF85" s="6"/>
+      <c r="BD85" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BE85" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BF85" s="6">
+        <v>1.17E-2</v>
+      </c>
       <c r="BG85" s="3"/>
       <c r="BH85" s="3"/>
       <c r="BI85" s="3"/>
-      <c r="BJ85" s="6"/>
+      <c r="BJ85" s="6">
+        <v>1.14E-2</v>
+      </c>
       <c r="BK85" s="2">
         <v>46158</v>
       </c>
-      <c r="BL85" s="58"/>
+      <c r="BL85" s="58">
+        <v>4.1599999999999998E-2</v>
+      </c>
       <c r="BM85" s="1"/>
-      <c r="BN85" s="58"/>
+      <c r="BN85" s="58">
+        <v>4.99E-2</v>
+      </c>
       <c r="BO85" s="1"/>
       <c r="BP85" s="1"/>
       <c r="BQ85" s="1"/>
-      <c r="BR85" s="58"/>
-      <c r="BS85" s="13"/>
+      <c r="BR85" s="58">
+        <v>3.2599999999999997E-2</v>
+      </c>
+      <c r="BS85" s="13">
+        <f t="shared" si="3"/>
+        <v>2.1199999999999997E-2</v>
+      </c>
     </row>
     <row r="86" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A86" s="4">
@@ -26509,7 +26898,9 @@
       <c r="G86" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H86" s="9"/>
+      <c r="H86" s="9">
+        <v>9.7000000000000003E-3</v>
+      </c>
       <c r="I86" s="2">
         <v>46159</v>
       </c>
@@ -26531,10 +26922,12 @@
       <c r="O86" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P86" s="58"/>
+      <c r="P86" s="58">
+        <v>3.2300000000000002E-2</v>
+      </c>
       <c r="Q86" s="86">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.2600000000000002E-2</v>
       </c>
       <c r="S86" s="4">
         <v>46159</v>
@@ -26551,11 +26944,15 @@
       <c r="W86" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X86" s="6"/>
+      <c r="X86" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y86" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z86" s="6"/>
+      <c r="Z86" s="6">
+        <v>1.3899999999999999E-2</v>
+      </c>
       <c r="AA86" s="2">
         <v>46159</v>
       </c>
@@ -26577,50 +26974,1207 @@
       <c r="AG86" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH86" s="58"/>
-      <c r="AI86" s="13"/>
+      <c r="AH86" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI86" s="13">
+        <f t="shared" si="6"/>
+        <v>1.1100000000000002E-2</v>
+      </c>
       <c r="AK86" s="4">
         <v>46159</v>
       </c>
-      <c r="AL86" s="3"/>
+      <c r="AL86" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM86" s="3"/>
       <c r="AN86" s="3"/>
       <c r="AO86" s="3"/>
-      <c r="AP86" s="3"/>
-      <c r="AQ86" s="6"/>
-      <c r="AR86" s="6"/>
+      <c r="AP86" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ86" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR86" s="6">
+        <v>8.6E-3</v>
+      </c>
       <c r="AS86" s="2">
         <v>46159</v>
       </c>
-      <c r="AT86" s="14"/>
-      <c r="AU86" s="14"/>
-      <c r="AV86" s="14"/>
-      <c r="AW86" s="14"/>
-      <c r="AX86" s="14"/>
-      <c r="AY86" s="14"/>
-      <c r="AZ86" s="14"/>
-      <c r="BA86" s="13"/>
+      <c r="AT86" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AU86" s="14">
+        <v>3.15E-2</v>
+      </c>
+      <c r="AV86" s="14">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="AW86" s="14">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="AX86" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="AY86" s="14">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="AZ86" s="14">
+        <v>3.6499999999999998E-2</v>
+      </c>
+      <c r="BA86" s="13">
+        <f t="shared" si="5"/>
+        <v>2.7899999999999998E-2</v>
+      </c>
       <c r="BC86" s="4">
         <v>46159</v>
       </c>
-      <c r="BD86" s="6"/>
-      <c r="BE86" s="6"/>
-      <c r="BF86" s="6"/>
+      <c r="BD86" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BE86" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BF86" s="6">
+        <v>1.17E-2</v>
+      </c>
       <c r="BG86" s="3"/>
       <c r="BH86" s="3"/>
       <c r="BI86" s="3"/>
-      <c r="BJ86" s="6"/>
+      <c r="BJ86" s="6">
+        <v>1.11E-2</v>
+      </c>
       <c r="BK86" s="2">
         <v>46159</v>
       </c>
-      <c r="BL86" s="58"/>
+      <c r="BL86" s="58">
+        <v>4.1000000000000002E-2</v>
+      </c>
       <c r="BM86" s="1"/>
-      <c r="BN86" s="58"/>
+      <c r="BN86" s="58">
+        <v>4.9099999999999998E-2</v>
+      </c>
       <c r="BO86" s="1"/>
       <c r="BP86" s="1"/>
       <c r="BQ86" s="1"/>
-      <c r="BR86" s="58"/>
-      <c r="BS86" s="13"/>
+      <c r="BR86" s="58">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="BS86" s="13">
+        <f t="shared" si="3"/>
+        <v>2.0500000000000004E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A87" s="4">
+        <v>46160</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H87" s="9">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="I87" s="2">
+        <v>46160</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N87" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O87" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P87" s="58">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="Q87" s="86">
+        <f t="shared" ref="Q87:Q93" si="7">P87-H87</f>
+        <v>2.2400000000000003E-2</v>
+      </c>
+      <c r="S87" s="4">
+        <v>46160</v>
+      </c>
+      <c r="T87" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U87" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V87" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W87" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X87" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Y87" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z87" s="6">
+        <v>1.4E-2</v>
+      </c>
+      <c r="AA87" s="2">
+        <v>46160</v>
+      </c>
+      <c r="AB87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH87" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI87" s="13">
+        <f t="shared" si="6"/>
+        <v>1.1000000000000001E-2</v>
+      </c>
+      <c r="AK87" s="4">
+        <v>46160</v>
+      </c>
+      <c r="AL87" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="AM87" s="3"/>
+      <c r="AN87" s="3"/>
+      <c r="AO87" s="3"/>
+      <c r="AP87" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ87" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR87" s="6">
+        <v>8.8999999999999999E-3</v>
+      </c>
+      <c r="AS87" s="2">
+        <v>46160</v>
+      </c>
+      <c r="AT87" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AU87" s="14">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="AV87" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AW87" s="14">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="AX87" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="AY87" s="14">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="AZ87" s="14">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="BA87" s="13">
+        <f t="shared" si="5"/>
+        <v>2.5300000000000003E-2</v>
+      </c>
+      <c r="BC87" s="4">
+        <v>46160</v>
+      </c>
+      <c r="BD87" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE87" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF87" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BG87" s="3"/>
+      <c r="BH87" s="3"/>
+      <c r="BI87" s="3"/>
+      <c r="BJ87" s="6">
+        <v>9.5999999999999992E-3</v>
+      </c>
+      <c r="BK87" s="2">
+        <v>46160</v>
+      </c>
+      <c r="BL87" s="58">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="BM87" s="1"/>
+      <c r="BN87" s="58">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="BO87" s="1"/>
+      <c r="BP87" s="1"/>
+      <c r="BQ87" s="1"/>
+      <c r="BR87" s="58">
+        <v>3.04E-2</v>
+      </c>
+      <c r="BS87" s="13">
+        <f t="shared" si="3"/>
+        <v>2.0799999999999999E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A88" s="4">
+        <v>46161</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H88" s="9">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="I88" s="2">
+        <v>46161</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N88" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O88" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P88" s="58">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="Q88" s="86">
+        <f t="shared" si="7"/>
+        <v>2.2000000000000002E-2</v>
+      </c>
+      <c r="S88" s="4">
+        <v>46161</v>
+      </c>
+      <c r="T88" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U88" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V88" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W88" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X88" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Y88" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z88" s="6">
+        <v>1.4E-2</v>
+      </c>
+      <c r="AA88" s="2">
+        <v>46161</v>
+      </c>
+      <c r="AB88" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC88" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD88" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE88" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF88" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG88" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH88" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI88" s="13">
+        <f t="shared" si="6"/>
+        <v>1.1000000000000001E-2</v>
+      </c>
+      <c r="AK88" s="4">
+        <v>46161</v>
+      </c>
+      <c r="AL88" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="AM88" s="3"/>
+      <c r="AN88" s="3"/>
+      <c r="AO88" s="3"/>
+      <c r="AP88" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ88" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR88" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="AS88" s="2">
+        <v>46161</v>
+      </c>
+      <c r="AT88" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AU88" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AV88" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AW88" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AX88" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="AY88" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="AZ88" s="14">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="BA88" s="13">
+        <f t="shared" si="5"/>
+        <v>2.5499999999999995E-2</v>
+      </c>
+      <c r="BC88" s="4">
+        <v>46161</v>
+      </c>
+      <c r="BD88" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE88" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF88" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BG88" s="3"/>
+      <c r="BH88" s="3"/>
+      <c r="BI88" s="3"/>
+      <c r="BJ88" s="6">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="BK88" s="2">
+        <v>46161</v>
+      </c>
+      <c r="BL88" s="58">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BM88" s="1"/>
+      <c r="BN88" s="58">
+        <v>4.7399999999999998E-2</v>
+      </c>
+      <c r="BO88" s="1"/>
+      <c r="BP88" s="1"/>
+      <c r="BQ88" s="1"/>
+      <c r="BR88" s="58">
+        <v>3.2599999999999997E-2</v>
+      </c>
+      <c r="BS88" s="13">
+        <f t="shared" si="3"/>
+        <v>2.1799999999999996E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A89" s="4">
+        <v>46162</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H89" s="9">
+        <v>1.18E-2</v>
+      </c>
+      <c r="I89" s="2">
+        <v>46162</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N89" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O89" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P89" s="58">
+        <v>3.32E-2</v>
+      </c>
+      <c r="Q89" s="86">
+        <f t="shared" si="7"/>
+        <v>2.1400000000000002E-2</v>
+      </c>
+      <c r="S89" s="4">
+        <v>46162</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X89" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="AA89" s="2">
+        <v>46162</v>
+      </c>
+      <c r="AB89" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC89" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD89" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE89" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF89" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG89" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH89" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI89" s="13">
+        <f t="shared" si="6"/>
+        <v>1.2000000000000002E-2</v>
+      </c>
+      <c r="AK89" s="4">
+        <v>46162</v>
+      </c>
+      <c r="AL89" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="AM89" s="3"/>
+      <c r="AN89" s="3"/>
+      <c r="AO89" s="3"/>
+      <c r="AP89" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ89" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR89" s="6">
+        <v>1.15E-2</v>
+      </c>
+      <c r="AS89" s="2">
+        <v>46162</v>
+      </c>
+      <c r="AT89" s="14">
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="AU89" s="14">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="AV89" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AW89" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AX89" s="14">
+        <v>4.9500000000000002E-2</v>
+      </c>
+      <c r="AY89" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="AZ89" s="14">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="BA89" s="13">
+        <f t="shared" si="5"/>
+        <v>2.5100000000000001E-2</v>
+      </c>
+      <c r="BC89" s="4">
+        <v>46162</v>
+      </c>
+      <c r="BD89" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE89" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF89" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BG89" s="3"/>
+      <c r="BH89" s="3"/>
+      <c r="BI89" s="3"/>
+      <c r="BJ89" s="6">
+        <v>1.11E-2</v>
+      </c>
+      <c r="BK89" s="2">
+        <v>46162</v>
+      </c>
+      <c r="BL89" s="58">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BM89" s="1"/>
+      <c r="BN89" s="58">
+        <v>4.7399999999999998E-2</v>
+      </c>
+      <c r="BO89" s="1"/>
+      <c r="BP89" s="1"/>
+      <c r="BQ89" s="1"/>
+      <c r="BR89" s="58">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BS89" s="13">
+        <f t="shared" si="3"/>
+        <v>2.18E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A90" s="4">
+        <v>46163</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H90" s="9"/>
+      <c r="I90" s="2">
+        <v>46163</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M90" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N90" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O90" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P90" s="58"/>
+      <c r="Q90" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S90" s="4">
+        <v>46163</v>
+      </c>
+      <c r="T90" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U90" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V90" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W90" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X90" s="6"/>
+      <c r="Y90" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z90" s="6"/>
+      <c r="AA90" s="2">
+        <v>46163</v>
+      </c>
+      <c r="AB90" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC90" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD90" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE90" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF90" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG90" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH90" s="58"/>
+      <c r="AI90" s="13"/>
+      <c r="AK90" s="4">
+        <v>46163</v>
+      </c>
+      <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
+      <c r="AR90" s="6"/>
+      <c r="AS90" s="2">
+        <v>46163</v>
+      </c>
+      <c r="AT90" s="14"/>
+      <c r="AU90" s="14"/>
+      <c r="AV90" s="14"/>
+      <c r="AW90" s="14"/>
+      <c r="AX90" s="14"/>
+      <c r="AY90" s="14"/>
+      <c r="AZ90" s="14"/>
+      <c r="BA90" s="13"/>
+      <c r="BC90" s="4">
+        <v>46163</v>
+      </c>
+      <c r="BD90" s="6"/>
+      <c r="BE90" s="6"/>
+      <c r="BF90" s="6"/>
+      <c r="BG90" s="3"/>
+      <c r="BH90" s="3"/>
+      <c r="BI90" s="3"/>
+      <c r="BJ90" s="6"/>
+      <c r="BK90" s="2">
+        <v>46163</v>
+      </c>
+      <c r="BL90" s="58"/>
+      <c r="BM90" s="1"/>
+      <c r="BN90" s="58"/>
+      <c r="BO90" s="1"/>
+      <c r="BP90" s="1"/>
+      <c r="BQ90" s="1"/>
+      <c r="BR90" s="58"/>
+      <c r="BS90" s="13"/>
+    </row>
+    <row r="91" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A91" s="4">
+        <v>46164</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H91" s="9"/>
+      <c r="I91" s="2">
+        <v>46164</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M91" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N91" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O91" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P91" s="58"/>
+      <c r="Q91" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S91" s="4">
+        <v>46164</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X91" s="6"/>
+      <c r="Y91" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z91" s="6"/>
+      <c r="AA91" s="2">
+        <v>46164</v>
+      </c>
+      <c r="AB91" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC91" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD91" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE91" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF91" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG91" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH91" s="58"/>
+      <c r="AI91" s="13"/>
+      <c r="AK91" s="4">
+        <v>46164</v>
+      </c>
+      <c r="AL91" s="3"/>
+      <c r="AM91" s="3"/>
+      <c r="AN91" s="3"/>
+      <c r="AO91" s="3"/>
+      <c r="AP91" s="3"/>
+      <c r="AQ91" s="6"/>
+      <c r="AR91" s="6"/>
+      <c r="AS91" s="2">
+        <v>46164</v>
+      </c>
+      <c r="AT91" s="14"/>
+      <c r="AU91" s="14"/>
+      <c r="AV91" s="14"/>
+      <c r="AW91" s="14"/>
+      <c r="AX91" s="14"/>
+      <c r="AY91" s="14"/>
+      <c r="AZ91" s="14"/>
+      <c r="BA91" s="13"/>
+      <c r="BC91" s="4">
+        <v>46164</v>
+      </c>
+      <c r="BD91" s="6"/>
+      <c r="BE91" s="6"/>
+      <c r="BF91" s="6"/>
+      <c r="BG91" s="3"/>
+      <c r="BH91" s="3"/>
+      <c r="BI91" s="3"/>
+      <c r="BJ91" s="6"/>
+      <c r="BK91" s="2">
+        <v>46164</v>
+      </c>
+      <c r="BL91" s="58"/>
+      <c r="BM91" s="1"/>
+      <c r="BN91" s="58"/>
+      <c r="BO91" s="1"/>
+      <c r="BP91" s="1"/>
+      <c r="BQ91" s="1"/>
+      <c r="BR91" s="58"/>
+      <c r="BS91" s="13"/>
+    </row>
+    <row r="92" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A92" s="4">
+        <v>46165</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H92" s="9"/>
+      <c r="I92" s="2">
+        <v>46165</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N92" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O92" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P92" s="58"/>
+      <c r="Q92" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S92" s="4">
+        <v>46165</v>
+      </c>
+      <c r="T92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X92" s="6"/>
+      <c r="Y92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z92" s="6"/>
+      <c r="AA92" s="2">
+        <v>46165</v>
+      </c>
+      <c r="AB92" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC92" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD92" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE92" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF92" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG92" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH92" s="58"/>
+      <c r="AI92" s="13"/>
+      <c r="AK92" s="4">
+        <v>46165</v>
+      </c>
+      <c r="AL92" s="3"/>
+      <c r="AM92" s="3"/>
+      <c r="AN92" s="3"/>
+      <c r="AO92" s="3"/>
+      <c r="AP92" s="3"/>
+      <c r="AQ92" s="6"/>
+      <c r="AR92" s="6"/>
+      <c r="AS92" s="2">
+        <v>46165</v>
+      </c>
+      <c r="AT92" s="14"/>
+      <c r="AU92" s="14"/>
+      <c r="AV92" s="14"/>
+      <c r="AW92" s="14"/>
+      <c r="AX92" s="14"/>
+      <c r="AY92" s="14"/>
+      <c r="AZ92" s="14"/>
+      <c r="BA92" s="13"/>
+      <c r="BC92" s="4">
+        <v>46165</v>
+      </c>
+      <c r="BD92" s="6"/>
+      <c r="BE92" s="6"/>
+      <c r="BF92" s="6"/>
+      <c r="BG92" s="3"/>
+      <c r="BH92" s="3"/>
+      <c r="BI92" s="3"/>
+      <c r="BJ92" s="6"/>
+      <c r="BK92" s="2">
+        <v>46165</v>
+      </c>
+      <c r="BL92" s="58"/>
+      <c r="BM92" s="1"/>
+      <c r="BN92" s="58"/>
+      <c r="BO92" s="1"/>
+      <c r="BP92" s="1"/>
+      <c r="BQ92" s="1"/>
+      <c r="BR92" s="58"/>
+      <c r="BS92" s="13"/>
+    </row>
+    <row r="93" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A93" s="4">
+        <v>46166</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H93" s="9"/>
+      <c r="I93" s="2">
+        <v>46166</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O93" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P93" s="58"/>
+      <c r="Q93" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S93" s="4">
+        <v>46166</v>
+      </c>
+      <c r="T93" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U93" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V93" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W93" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X93" s="6"/>
+      <c r="Y93" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z93" s="6"/>
+      <c r="AA93" s="2">
+        <v>46166</v>
+      </c>
+      <c r="AB93" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC93" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD93" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE93" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF93" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG93" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH93" s="58"/>
+      <c r="AI93" s="13"/>
+      <c r="AK93" s="4">
+        <v>46166</v>
+      </c>
+      <c r="AL93" s="3"/>
+      <c r="AM93" s="3"/>
+      <c r="AN93" s="3"/>
+      <c r="AO93" s="3"/>
+      <c r="AP93" s="3"/>
+      <c r="AQ93" s="6"/>
+      <c r="AR93" s="6"/>
+      <c r="AS93" s="2">
+        <v>46166</v>
+      </c>
+      <c r="AT93" s="14"/>
+      <c r="AU93" s="14"/>
+      <c r="AV93" s="14"/>
+      <c r="AW93" s="14"/>
+      <c r="AX93" s="14"/>
+      <c r="AY93" s="14"/>
+      <c r="AZ93" s="14"/>
+      <c r="BA93" s="13"/>
+      <c r="BC93" s="4">
+        <v>46166</v>
+      </c>
+      <c r="BD93" s="6"/>
+      <c r="BE93" s="6"/>
+      <c r="BF93" s="6"/>
+      <c r="BG93" s="3"/>
+      <c r="BH93" s="3"/>
+      <c r="BI93" s="3"/>
+      <c r="BJ93" s="6"/>
+      <c r="BK93" s="2">
+        <v>46166</v>
+      </c>
+      <c r="BL93" s="58"/>
+      <c r="BM93" s="1"/>
+      <c r="BN93" s="58"/>
+      <c r="BO93" s="1"/>
+      <c r="BP93" s="1"/>
+      <c r="BQ93" s="1"/>
+      <c r="BR93" s="58"/>
+      <c r="BS93" s="13"/>
     </row>
     <row r="1048576" spans="42:42" x14ac:dyDescent="0.35">
       <c r="AP1048576" s="18"/>
@@ -26965,7 +28519,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27301,7 +28855,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27639,7 +29193,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27977,7 +29531,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28315,7 +29869,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28683,7 +30237,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29051,7 +30605,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29419,7 +30973,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29790,7 +31344,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -30171,7 +31725,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31635,7 +33189,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31979,7 +33533,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32323,7 +33877,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -32667,7 +34221,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33011,7 +34565,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33343,7 +34897,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33687,7 +35241,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -34031,7 +35585,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -34378,7 +35932,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -34723,7 +36277,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45419,7 +46973,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -45763,7 +47317,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46098,7 +47652,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46430,7 +47984,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46774,7 +48328,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47118,7 +48672,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47462,7 +49016,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47806,7 +49360,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -48150,7 +49704,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -48494,7 +50048,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -56531,7 +58085,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -56875,7 +58429,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -57219,7 +58773,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -57563,7 +59117,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -57907,7 +59461,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58251,7 +59805,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58595,7 +60149,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58939,7 +60493,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -59283,7 +60837,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -59627,7 +61181,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -59992,7 +61546,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="53" priority="1">
+    <cfRule type="expression" dxfId="58" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -60002,6 +61556,1726 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="56" orientation="landscape" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F4918FB-FFA9-4212-83BA-1FE4F8ABF171}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46158</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>2.8199999999999999E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>0.05</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.6654006194406952E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR85</f>
+        <v>2.7199999999999995E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+ $I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+ $I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z89</f>
+        <v>1.2000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f>((1+I5)^(C2/365)-1)*365/C2</f>
+        <v>3.2618932626085458E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>4.99E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f>((1+I5)^(E2/365)-1)*365/E2</f>
+        <v>3.2686042808954284E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" ref="F5:G5" si="2">((1+J5)^(F2/365)-1)*365/F2</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>2.1087297787769743E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.2599999999999997E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.3135697711292433E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ85</f>
+        <v>2.1199999999999997E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f>((1+I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f>((1+I6)^(E2/365)-1)*365/E2</f>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" ref="F6:G6" si="3">((1+J6)^(F2/365)-1)*365/F2</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>1.0671140309914364E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f>((1+I7)^(C2/365)-1)*365/C2</f>
+        <v>3.2018242012937716E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f>((1+$I7)^(E2/365)-1)*365/E2</f>
+        <v>3.2082902098360046E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" ref="F7:G7" si="4">((1+$I7)^(F2/365)-1)*365/F2</f>
+        <v>3.2125165508335836E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2252401622451465E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.2516057037460744E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.3%</f>
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.2308576251097731E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.2318585715067308E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.2341480019105272E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.2384465142249297E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.2427526440872788E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.255716890990918E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.2825831032744723E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H85</f>
+        <v>2.23E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>4.0913751691330012E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>4.0929803123583457E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.0966523649155873E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.1035493076274597E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.1104617321895423E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.1312922884725982E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>4.0899999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>4.1745538538283444E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30EC5F3E-EB0C-4CDB-BA8A-3D1278AF132B}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46159</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.15E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>0.05</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.6499999999999998E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.7172411302539565E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR86</f>
+        <v>2.7899999999999998E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z86</f>
+        <v>1.1100000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.1617788734936939E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.1680840785172228E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.172205199932869E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.1846114975320451E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.2103169169868329E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ86</f>
+        <v>2.0500000000000004E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.2118356223753065E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.5299999999999998E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2183421488258611E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2225950028510517E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2353985736690669E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.2619304739437416E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.1499999999999998E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.2308576251097731E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.2318585715067308E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.2341480019105272E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.2384465142249297E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.2427526440872788E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.255716890990918E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.2825831032744723E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H86</f>
+        <v>2.2600000000000002E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.3509225383722141E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.3519992612899605E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.3544620748271248E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.3590863552975504E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.3637191354794753E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.3776686502467984E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4065854123153105E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA2CDAD0-0812-415D-93E3-C1FEB5BC5A59}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46160</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>0.05</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.4789886456186414E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>'18.05.2026'!H3-'Daily Data'!AR87</f>
+        <v>2.5300000000000003E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z87</f>
+        <v>1.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.0416463127971544E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.0474812798236512E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.0512947329474491E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.0627733077317729E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.04E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.0865493238620978E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ87</f>
+        <v>2.0799999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.2118356223753065E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.5299999999999998E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2183421488258611E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2225950028510517E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2353985736690669E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.2619304739437416E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.1499999999999998E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.2308576251097731E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.2318585715067308E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.2341480019105272E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.2384465142249297E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.2427526440872788E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.255716890990918E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.2825831032744723E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H87</f>
+        <v>2.2400000000000003E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.5210185527416567E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.5222073609817203E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5249266470243436E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5300328557368831E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5351489269211729E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5505565298553574E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.582509544513357E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84FB4A0B-4394-40A3-A6A1-1A40387CFBB3}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46161</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="C3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="F3" s="55">
+        <v>0.05</v>
+      </c>
+      <c r="G3" s="55">
+        <v>0.05</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.6135859488784616E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR88</f>
+        <v>2.5499999999999995E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z88</f>
+        <v>1.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f>((1+I5)^(C2/365)-1)*365/C2</f>
+        <v>3.2618932626085458E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>4.7399999999999998E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f>((1+$I5)^(E2/365)-1)*365/E2</f>
+        <v>3.2686042808954284E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" ref="F5:G5" si="2">((1+$I5)^(F2/365)-1)*365/F2</f>
+        <v>3.2729909490182445E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.286198103507449E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.2599999999999997E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.3135697711292433E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ88</f>
+        <v>2.1799999999999996E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.2118356223753065E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.5299999999999998E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2183421488258611E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2225950028510517E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2353985736690669E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.2619304739437416E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.1499999999999998E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.3008952033828365E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.3019400165881306E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3043298171878198E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3088169112457676E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3133121295987555E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3268466960937645E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.3548997504548206E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H88</f>
+        <v>2.2000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.4509784417989478E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.4521204248868585E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.4547325644198969E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.4596374317178734E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.4645515839499125E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.479349948210321E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.5100340771234473E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{713A6C45-DF38-4D03-AB47-7E2F5FA3D817}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46162</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.9500000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>0.05</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.727612334382413E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR89</f>
+        <v>2.5100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z89</f>
+        <v>1.2000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.2919282746055836E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>4.7399999999999998E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.2987635099189561E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.3032314657883019E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.3166838004525655E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.3445657100777071E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ89</f>
+        <v>2.18E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.2118356223753065E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.5299999999999998E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2183421488258611E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2225950028510517E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2353985736690669E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.2619304739437416E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.1499999999999998E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.320906088040159E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.3219636075024761E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3243824812786905E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3289242013672393E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3334741945595443E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3471739824844977E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.32E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.3755709228882935E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H89</f>
+        <v>2.1400000000000002E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.3709335874898071E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.3745155354740729E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -60355,7 +63629,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="52" priority="1">
+    <cfRule type="expression" dxfId="57" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -60716,7 +63990,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="51" priority="1">
+    <cfRule type="expression" dxfId="56" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -61071,7 +64345,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="50" priority="1">
+    <cfRule type="expression" dxfId="55" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D7F26C-0EB4-462A-B735-BC29FF1CAD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2536A8B3-8969-429C-8C26-A1599B9CDE41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="1830" windowWidth="29040" windowHeight="15720" firstSheet="54" activeTab="63" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="55" activeTab="64" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -77,6 +77,7 @@
     <sheet name="18.05.2026" sheetId="84" r:id="rId62"/>
     <sheet name="19.05.2026" sheetId="85" r:id="rId63"/>
     <sheet name="20.05.2026" sheetId="86" r:id="rId64"/>
+    <sheet name="21.05.2026" sheetId="87" r:id="rId65"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2368,6 +2369,43 @@
 </comments>
 </file>
 
+<file path=xl/comments61.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{B1D74FCD-0782-4E0D-8138-0FA57C3065B9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -2480,7 +2518,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3847" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3860" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -3163,7 +3201,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="59">
+  <dxfs count="60">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3601,7 +3646,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>407494</xdr:colOff>
+      <xdr:colOff>410669</xdr:colOff>
       <xdr:row>131</xdr:row>
       <xdr:rowOff>111739</xdr:rowOff>
     </xdr:to>
@@ -7221,17 +7266,29 @@
       <c r="F141" s="23">
         <v>3.85E-2</v>
       </c>
-      <c r="G141" s="90"/>
+      <c r="G141" s="90">
+        <v>76835</v>
+      </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="82">
         <v>46163</v>
       </c>
-      <c r="B142" s="83"/>
-      <c r="C142" s="23"/>
-      <c r="D142" s="23"/>
-      <c r="E142" s="23"/>
-      <c r="F142" s="23"/>
+      <c r="B142" s="83">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="C142" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D142" s="23">
+        <v>3.7100000000000001E-2</v>
+      </c>
+      <c r="E142" s="23">
+        <v>3.5400000000000001E-2</v>
+      </c>
+      <c r="F142" s="23">
+        <v>3.8199999999999998E-2</v>
+      </c>
       <c r="G142" s="90"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
@@ -7851,7 +7908,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="54" priority="1">
+    <cfRule type="expression" dxfId="55" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8187,7 +8244,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="53" priority="1">
+    <cfRule type="expression" dxfId="54" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8525,7 +8582,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="52" priority="1">
+    <cfRule type="expression" dxfId="53" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8861,7 +8918,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="51" priority="1">
+    <cfRule type="expression" dxfId="52" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9195,7 +9252,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="50" priority="1">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9531,7 +9588,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="49" priority="1">
+    <cfRule type="expression" dxfId="50" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9867,7 +9924,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10203,7 +10260,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="48" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10539,7 +10596,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="46" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10875,7 +10932,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11668,7 +11725,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS89" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS90" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -24170,7 +24227,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="BA71" s="13">
-        <f t="shared" ref="BA71:BA89" si="5">AZ71-AR71</f>
+        <f t="shared" ref="BA71:BA90" si="5">AZ71-AR71</f>
         <v>2.6199999999999998E-2</v>
       </c>
       <c r="BC71" s="4">
@@ -25454,7 +25511,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="AI78" s="13">
-        <f t="shared" ref="AI78:AI89" si="6">AH78-Z78</f>
+        <f t="shared" ref="AI78:AI90" si="6">AH78-Z78</f>
         <v>1.1500000000000002E-2</v>
       </c>
       <c r="AK78" s="4">
@@ -27658,7 +27715,9 @@
       <c r="G90" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H90" s="9"/>
+      <c r="H90" s="9">
+        <v>1.1900000000000001E-2</v>
+      </c>
       <c r="I90" s="2">
         <v>46163</v>
       </c>
@@ -27680,10 +27739,12 @@
       <c r="O90" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P90" s="58"/>
+      <c r="P90" s="58">
+        <v>3.3399999999999999E-2</v>
+      </c>
       <c r="Q90" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.1499999999999998E-2</v>
       </c>
       <c r="S90" s="4">
         <v>46163</v>
@@ -27700,11 +27761,15 @@
       <c r="W90" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X90" s="6"/>
+      <c r="X90" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y90" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z90" s="6"/>
+      <c r="Z90" s="6">
+        <v>1.3899999999999999E-2</v>
+      </c>
       <c r="AA90" s="2">
         <v>46163</v>
       </c>
@@ -27726,50 +27791,97 @@
       <c r="AG90" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH90" s="58"/>
-      <c r="AI90" s="13"/>
+      <c r="AH90" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI90" s="13">
+        <f t="shared" si="6"/>
+        <v>1.1100000000000002E-2</v>
+      </c>
       <c r="AK90" s="4">
         <v>46163</v>
       </c>
-      <c r="AL90" s="3"/>
+      <c r="AL90" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
-      <c r="AP90" s="3"/>
-      <c r="AQ90" s="3"/>
-      <c r="AR90" s="6"/>
+      <c r="AP90" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ90" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR90" s="6">
+        <v>1.2200000000000001E-2</v>
+      </c>
       <c r="AS90" s="2">
         <v>46163</v>
       </c>
-      <c r="AT90" s="14"/>
-      <c r="AU90" s="14"/>
-      <c r="AV90" s="14"/>
-      <c r="AW90" s="14"/>
-      <c r="AX90" s="14"/>
-      <c r="AY90" s="14"/>
-      <c r="AZ90" s="14"/>
-      <c r="BA90" s="13"/>
+      <c r="AT90" s="14">
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="AU90" s="14">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="AV90" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AW90" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AX90" s="14">
+        <v>4.9500000000000002E-2</v>
+      </c>
+      <c r="AY90" s="14">
+        <v>4.7399999999999998E-2</v>
+      </c>
+      <c r="AZ90" s="14">
+        <v>3.7100000000000001E-2</v>
+      </c>
+      <c r="BA90" s="13">
+        <f t="shared" si="5"/>
+        <v>2.4899999999999999E-2</v>
+      </c>
       <c r="BC90" s="4">
         <v>46163</v>
       </c>
-      <c r="BD90" s="6"/>
-      <c r="BE90" s="6"/>
-      <c r="BF90" s="6"/>
+      <c r="BD90" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE90" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF90" s="6">
+        <v>1.14E-2</v>
+      </c>
       <c r="BG90" s="3"/>
       <c r="BH90" s="3"/>
       <c r="BI90" s="3"/>
-      <c r="BJ90" s="6"/>
+      <c r="BJ90" s="6">
+        <v>1.14E-2</v>
+      </c>
       <c r="BK90" s="2">
         <v>46163</v>
       </c>
-      <c r="BL90" s="58"/>
+      <c r="BL90" s="58">
+        <v>4.1099999999999998E-2</v>
+      </c>
       <c r="BM90" s="1"/>
-      <c r="BN90" s="58"/>
+      <c r="BN90" s="58">
+        <v>4.9399999999999999E-2</v>
+      </c>
       <c r="BO90" s="1"/>
       <c r="BP90" s="1"/>
       <c r="BQ90" s="1"/>
-      <c r="BR90" s="58"/>
-      <c r="BS90" s="13"/>
+      <c r="BR90" s="58">
+        <v>3.4299999999999997E-2</v>
+      </c>
+      <c r="BS90" s="13">
+        <f t="shared" si="3"/>
+        <v>2.2899999999999997E-2</v>
+      </c>
     </row>
     <row r="91" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A91" s="4">
@@ -28519,7 +28631,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="44" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28855,7 +28967,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29193,7 +29305,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29531,7 +29643,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29869,7 +29981,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30237,7 +30349,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30605,7 +30717,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30973,7 +31085,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31344,7 +31456,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31725,7 +31837,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33189,7 +33301,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33533,7 +33645,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33877,7 +33989,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -34221,7 +34333,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -34565,7 +34677,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -34897,7 +35009,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -35241,7 +35353,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -35585,7 +35697,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -35932,7 +36044,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -36277,7 +36389,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -46973,7 +47085,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47317,7 +47429,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47652,7 +47764,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47984,7 +48096,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -48328,7 +48440,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -48672,7 +48784,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -49016,7 +49128,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -49360,7 +49472,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -49704,7 +49816,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -50048,7 +50160,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58085,7 +58197,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58429,7 +58541,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58773,7 +58885,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -59117,7 +59229,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -59461,7 +59573,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -59805,7 +59917,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -60149,7 +60261,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -60493,7 +60605,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -60837,7 +60949,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -61181,7 +61293,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -61546,7 +61658,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="58" priority="1">
+    <cfRule type="expression" dxfId="59" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -61891,7 +62003,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -62235,7 +62347,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -62579,7 +62691,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -62923,7 +63035,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63261,6 +63373,350 @@
       <c r="I9" s="74">
         <f t="shared" si="1"/>
         <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D939304D-33CE-4C33-BA85-BFB19A64C1AD}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46163</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.9500000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.7399999999999998E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.7100000000000001E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.7794838704558797E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR90</f>
+        <v>2.4899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z90</f>
+        <v>1.1100000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.1099999999999998E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f>((1+I5)^(C2/365)-1)*365/C2</f>
+        <v>3.4320959069194204E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>4.9399999999999999E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f>((1+$I5)^(E2/365)-1)*365/E2</f>
+        <v>3.4395259162604379E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" ref="F5:G5" si="2">((1+$I5)^(F2/365)-1)*365/F2</f>
+        <v>3.4443831274714017E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.459009699547997E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.4299999999999997E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4893360908936799E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ90</f>
+        <v>2.2899999999999997E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f>((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f>((1+$I6)^(E2/365)-1)*365/E2</f>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" ref="F6:G6" si="3">((1+$I6)^(F2/365)-1)*365/F2</f>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f>((1+I7)^(C2/365)-1)*365/C2</f>
+        <v>3.6223345863170948E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f>((1+$I7)^(E2/365)-1)*365/E2</f>
+        <v>3.6306115642032878E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" ref="F7:G7" si="4">((1+$I7)^(F2/365)-1)*365/F2</f>
+        <v>3.6360231771886457E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.6523226266277575E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.6200000000000003E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.6861337222164892E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.5600000000000005E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.340917038478116E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.3419873410345406E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3444354639846442E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3490321414801537E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3536372426970877E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3675032625327374E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.3399999999999999E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.3962462182619113E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H90</f>
+        <v>2.1499999999999998E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.5410301610253284E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.5422325207818642E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5449828161880172E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5501472969416858E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5553218094735967E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5709057572161224E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.5400000000000001E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.6032261144603783E-2</v>
       </c>
       <c r="J9" s="75"/>
       <c r="K9" s="69"/>
@@ -63629,7 +64085,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="57" priority="1">
+    <cfRule type="expression" dxfId="58" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63990,7 +64446,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="56" priority="1">
+    <cfRule type="expression" dxfId="57" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64345,7 +64801,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="55" priority="1">
+    <cfRule type="expression" dxfId="56" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2536A8B3-8969-429C-8C26-A1599B9CDE41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAFB924-9722-4369-80C4-733D3017C554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="55" activeTab="64" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="56" activeTab="65" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -78,6 +78,7 @@
     <sheet name="19.05.2026" sheetId="85" r:id="rId63"/>
     <sheet name="20.05.2026" sheetId="86" r:id="rId64"/>
     <sheet name="21.05.2026" sheetId="87" r:id="rId65"/>
+    <sheet name="22.05.2026" sheetId="88" r:id="rId66"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2406,6 +2407,43 @@
 </comments>
 </file>
 
+<file path=xl/comments62.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{E97ECFA0-F68A-4087-8131-8E8101AD01E1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -2518,7 +2556,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3860" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3873" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -3201,7 +3239,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="60">
+  <dxfs count="61">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -7289,17 +7334,29 @@
       <c r="F142" s="23">
         <v>3.8199999999999998E-2</v>
       </c>
-      <c r="G142" s="90"/>
+      <c r="G142" s="90">
+        <v>77553</v>
+      </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="82">
         <v>46164</v>
       </c>
-      <c r="B143" s="83"/>
-      <c r="C143" s="23"/>
-      <c r="D143" s="23"/>
-      <c r="E143" s="23"/>
-      <c r="F143" s="23"/>
+      <c r="B143" s="83">
+        <v>3.3300000000000003E-2</v>
+      </c>
+      <c r="C143" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D143" s="23">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="E143" s="23">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="F143" s="23">
+        <v>4.0399999999999998E-2</v>
+      </c>
       <c r="G143" s="90"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
@@ -7908,7 +7965,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="55" priority="1">
+    <cfRule type="expression" dxfId="56" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8244,7 +8301,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="54" priority="1">
+    <cfRule type="expression" dxfId="55" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8582,7 +8639,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="53" priority="1">
+    <cfRule type="expression" dxfId="54" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8918,7 +8975,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="52" priority="1">
+    <cfRule type="expression" dxfId="53" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9252,7 +9309,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="51" priority="1">
+    <cfRule type="expression" dxfId="52" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9588,7 +9645,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="50" priority="1">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9924,7 +9981,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="49" priority="1">
+    <cfRule type="expression" dxfId="50" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10260,7 +10317,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10596,7 +10653,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="48" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10932,7 +10989,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="46" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11725,7 +11782,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS90" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS91" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -24227,7 +24284,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="BA71" s="13">
-        <f t="shared" ref="BA71:BA90" si="5">AZ71-AR71</f>
+        <f t="shared" ref="BA71:BA91" si="5">AZ71-AR71</f>
         <v>2.6199999999999998E-2</v>
       </c>
       <c r="BC71" s="4">
@@ -25511,7 +25568,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="AI78" s="13">
-        <f t="shared" ref="AI78:AI90" si="6">AH78-Z78</f>
+        <f t="shared" ref="AI78:AI91" si="6">AH78-Z78</f>
         <v>1.1500000000000002E-2</v>
       </c>
       <c r="AK78" s="4">
@@ -27905,7 +27962,9 @@
       <c r="G91" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H91" s="9"/>
+      <c r="H91" s="9">
+        <v>1.18E-2</v>
+      </c>
       <c r="I91" s="2">
         <v>46164</v>
       </c>
@@ -27927,10 +27986,12 @@
       <c r="O91" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P91" s="58"/>
+      <c r="P91" s="58">
+        <v>3.32E-2</v>
+      </c>
       <c r="Q91" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.1400000000000002E-2</v>
       </c>
       <c r="S91" s="4">
         <v>46164</v>
@@ -27947,11 +28008,15 @@
       <c r="W91" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X91" s="6"/>
+      <c r="X91" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y91" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z91" s="6"/>
+      <c r="Z91" s="6">
+        <v>1.3899999999999999E-2</v>
+      </c>
       <c r="AA91" s="2">
         <v>46164</v>
       </c>
@@ -27973,50 +28038,97 @@
       <c r="AG91" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH91" s="58"/>
-      <c r="AI91" s="13"/>
+      <c r="AH91" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI91" s="13">
+        <f t="shared" si="6"/>
+        <v>1.1100000000000002E-2</v>
+      </c>
       <c r="AK91" s="4">
         <v>46164</v>
       </c>
-      <c r="AL91" s="3"/>
+      <c r="AL91" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM91" s="3"/>
       <c r="AN91" s="3"/>
       <c r="AO91" s="3"/>
-      <c r="AP91" s="3"/>
-      <c r="AQ91" s="6"/>
-      <c r="AR91" s="6"/>
+      <c r="AP91" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ91" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR91" s="6">
+        <v>1.29E-2</v>
+      </c>
       <c r="AS91" s="2">
         <v>46164</v>
       </c>
-      <c r="AT91" s="14"/>
-      <c r="AU91" s="14"/>
-      <c r="AV91" s="14"/>
-      <c r="AW91" s="14"/>
-      <c r="AX91" s="14"/>
-      <c r="AY91" s="14"/>
-      <c r="AZ91" s="14"/>
-      <c r="BA91" s="13"/>
+      <c r="AT91" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AU91" s="14">
+        <v>3.49E-2</v>
+      </c>
+      <c r="AV91" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AW91" s="14">
+        <v>4.99E-2</v>
+      </c>
+      <c r="AX91" s="14">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="AY91" s="14">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="AZ91" s="14">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="BA91" s="13">
+        <f t="shared" si="5"/>
+        <v>2.4099999999999996E-2</v>
+      </c>
       <c r="BC91" s="4">
         <v>46164</v>
       </c>
-      <c r="BD91" s="6"/>
-      <c r="BE91" s="6"/>
-      <c r="BF91" s="6"/>
+      <c r="BD91" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE91" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF91" s="6">
+        <v>1.14E-2</v>
+      </c>
       <c r="BG91" s="3"/>
       <c r="BH91" s="3"/>
       <c r="BI91" s="3"/>
-      <c r="BJ91" s="6"/>
+      <c r="BJ91" s="6">
+        <v>1.1599999999999999E-2</v>
+      </c>
       <c r="BK91" s="2">
         <v>46164</v>
       </c>
-      <c r="BL91" s="58"/>
+      <c r="BL91" s="58">
+        <v>4.1000000000000002E-2</v>
+      </c>
       <c r="BM91" s="1"/>
-      <c r="BN91" s="58"/>
+      <c r="BN91" s="58">
+        <v>4.9299999999999997E-2</v>
+      </c>
       <c r="BO91" s="1"/>
       <c r="BP91" s="1"/>
       <c r="BQ91" s="1"/>
-      <c r="BR91" s="58"/>
-      <c r="BS91" s="13"/>
+      <c r="BR91" s="58">
+        <v>3.4299999999999997E-2</v>
+      </c>
+      <c r="BS91" s="13">
+        <f t="shared" si="3"/>
+        <v>2.2699999999999998E-2</v>
+      </c>
     </row>
     <row r="92" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A92" s="4">
@@ -28631,7 +28743,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28967,7 +29079,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="44" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29305,7 +29417,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29643,7 +29755,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29981,7 +30093,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30349,7 +30461,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30717,7 +30829,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31085,7 +31197,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31456,7 +31568,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31837,7 +31949,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33301,7 +33413,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33645,7 +33757,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33989,7 +34101,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -34333,7 +34445,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -34677,7 +34789,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -35009,7 +35121,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -35353,7 +35465,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -35697,7 +35809,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -36044,7 +36156,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -36389,7 +36501,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47085,7 +47197,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47429,7 +47541,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47764,7 +47876,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -48096,7 +48208,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -48440,7 +48552,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -48784,7 +48896,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -49128,7 +49240,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -49472,7 +49584,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -49816,7 +49928,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -50160,7 +50272,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58197,7 +58309,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58541,7 +58653,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58885,7 +58997,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -59229,7 +59341,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -59573,7 +59685,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -59917,7 +60029,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -60261,7 +60373,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -60605,7 +60717,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -60949,7 +61061,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -61293,7 +61405,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -61658,7 +61770,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="59" priority="1">
+    <cfRule type="expression" dxfId="60" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -62003,7 +62115,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -62347,7 +62459,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -62691,7 +62803,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63035,7 +63147,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63379,7 +63491,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63717,6 +63829,350 @@
       <c r="I9" s="74">
         <f t="shared" si="1"/>
         <v>3.6032261144603783E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFF8F308-069A-40C7-BB3D-50A3552189B5}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46164</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.49E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.99E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.7691074941686109E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR91</f>
+        <v>2.4099999999999996E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I5)^(B2/365)-1)*365/B2</f>
+        <v>3.430967129548395E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.4320959069194204E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>3.4346778292231983E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>3.4395259162604379E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>3.4443831274714017E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>3.459009699547997E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z91</f>
+        <v>1.1100000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.4320959069194204E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>4.9299999999999997E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.4395259162604379E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.4443831274714017E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.459009699547997E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.4299999999999997E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4893360908936799E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ91</f>
+        <v>2.2699999999999998E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.7900000000000003E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.6123217033267992E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.9699999999999999E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.6205529618120479E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.6259346453876025E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.6421437712058899E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.61E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.6757666539783518E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.5500000000000002E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.320906088040159E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.3219636075024761E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3243824812786905E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3289242013672393E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3334741945595443E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3471739824844977E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.32E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.3755709228882935E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H91</f>
+        <v>2.1400000000000002E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.5110127732749401E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.5121948345736405E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5148986819484897E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5199758789666746E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5250628545236418E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5403826645448506E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.5721528087785392E-2</v>
       </c>
       <c r="J9" s="75"/>
       <c r="K9" s="69"/>
@@ -64085,7 +64541,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="58" priority="1">
+    <cfRule type="expression" dxfId="59" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64446,7 +64902,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="57" priority="1">
+    <cfRule type="expression" dxfId="58" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64801,7 +65257,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="56" priority="1">
+    <cfRule type="expression" dxfId="57" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAFB924-9722-4369-80C4-733D3017C554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA0C05B-9C03-40F2-9667-6769D7060D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="56" activeTab="65" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="68" activeTab="73" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -79,6 +79,18 @@
     <sheet name="20.05.2026" sheetId="86" r:id="rId64"/>
     <sheet name="21.05.2026" sheetId="87" r:id="rId65"/>
     <sheet name="22.05.2026" sheetId="88" r:id="rId66"/>
+    <sheet name="23.05.2026" sheetId="89" r:id="rId67"/>
+    <sheet name="24.05.2026" sheetId="90" r:id="rId68"/>
+    <sheet name="25.05.2026" sheetId="91" r:id="rId69"/>
+    <sheet name="26.05.2026" sheetId="92" r:id="rId70"/>
+    <sheet name="27.05.2026" sheetId="93" r:id="rId71"/>
+    <sheet name="28.05.2026" sheetId="94" r:id="rId72"/>
+    <sheet name="29.05.2026" sheetId="95" r:id="rId73"/>
+    <sheet name="30.05.2026" sheetId="96" r:id="rId74"/>
+    <sheet name="31.05.2026" sheetId="97" r:id="rId75"/>
+    <sheet name="01.06.2026" sheetId="98" r:id="rId76"/>
+    <sheet name="02.06.2026" sheetId="99" r:id="rId77"/>
+    <sheet name="03.06.2026" sheetId="100" r:id="rId78"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2444,6 +2456,265 @@
 </comments>
 </file>
 
+<file path=xl/comments63.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{C2EB9C2D-CCC8-42D2-A39A-981E83F63D4C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments64.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{975CEF52-044F-40E2-B269-D40A9F10A65D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments65.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{DC0E4A19-B037-492D-B427-ACE8174A2E3B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments66.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{E027B512-8445-4ABB-8940-7D742A1ECE33}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments67.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{14A5AFB6-7A60-4069-8F1E-81795FD774AE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments68.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{5BE5D6C4-A43B-4CDD-BEB5-5A2392E34F85}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments69.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{0EB3BDFC-865B-4D5C-AB61-67550A5024AA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -2451,6 +2722,191 @@
   </authors>
   <commentList>
     <comment ref="H9" authorId="0" shapeId="0" xr:uid="{16266662-255E-4650-9378-14AA30C962F6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments70.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{9F2D48B7-3557-48A6-8E01-09BBB7070A21}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments71.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{B4B4053A-6D81-4F87-9E1A-D9AAC5B78E06}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments72.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{F214FF3E-E3F8-4F33-B095-DA5A38A7BC2F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments73.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{C2C54052-3090-4B8B-8007-262D8901D621}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments74.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{8CCC9706-FC32-48A1-8669-65DB093E7A65}">
       <text>
         <r>
           <rPr>
@@ -2556,7 +3012,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3873" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4581" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -3239,7 +3695,91 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="61">
+  <dxfs count="73">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3685,15 +4225,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>61233</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>73029</xdr:rowOff>
+      <xdr:colOff>172082</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>28441</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>410669</xdr:colOff>
-      <xdr:row>131</xdr:row>
-      <xdr:rowOff>111739</xdr:rowOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>27736</xdr:colOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>67150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3716,8 +4256,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7540429" y="17748116"/>
-          <a:ext cx="6463933" cy="6234101"/>
+          <a:off x="7651278" y="22076745"/>
+          <a:ext cx="6470283" cy="6230926"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7357,77 +7897,295 @@
       <c r="F143" s="23">
         <v>4.0399999999999998E-2</v>
       </c>
-      <c r="G143" s="90"/>
+      <c r="G143" s="90">
+        <v>77616</v>
+      </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="82">
         <v>46165</v>
       </c>
-      <c r="B144" s="83"/>
-      <c r="C144" s="23"/>
-      <c r="D144" s="23"/>
-      <c r="E144" s="23"/>
-      <c r="F144" s="23"/>
-      <c r="G144" s="90"/>
+      <c r="B144" s="83">
+        <v>3.2800000000000003E-2</v>
+      </c>
+      <c r="C144" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D144" s="23">
+        <v>3.61E-2</v>
+      </c>
+      <c r="E144" s="23">
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="F144" s="23">
+        <v>4.0599999999999997E-2</v>
+      </c>
+      <c r="G144" s="90">
+        <v>75540</v>
+      </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="82">
         <v>46166</v>
       </c>
-      <c r="B145" s="83"/>
-      <c r="C145" s="23"/>
-      <c r="D145" s="23"/>
-      <c r="E145" s="23"/>
-      <c r="F145" s="23"/>
-      <c r="G145" s="90"/>
+      <c r="B145" s="83">
+        <v>3.32E-2</v>
+      </c>
+      <c r="C145" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D145" s="23">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="E145" s="23">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="F145" s="23">
+        <v>3.9600000000000003E-2</v>
+      </c>
+      <c r="G145" s="90">
+        <v>76752</v>
+      </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A146" s="80"/>
-      <c r="B146" s="80"/>
+      <c r="A146" s="82">
+        <v>46167</v>
+      </c>
+      <c r="B146" s="83">
+        <v>3.32E-2</v>
+      </c>
+      <c r="C146" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D146" s="23">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="E146" s="23">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="F146" s="23">
+        <v>3.9600000000000003E-2</v>
+      </c>
+      <c r="G146" s="90">
+        <v>77065</v>
+      </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A147" s="80"/>
-      <c r="B147" s="80"/>
+      <c r="A147" s="82">
+        <v>46168</v>
+      </c>
+      <c r="B147" s="83">
+        <v>3.4599999999999999E-2</v>
+      </c>
+      <c r="C147" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D147" s="23">
+        <v>3.7600000000000001E-2</v>
+      </c>
+      <c r="E147" s="23">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="F147" s="23">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="G147" s="90">
+        <v>77323</v>
+      </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A148" s="80"/>
-      <c r="B148" s="80"/>
+      <c r="A148" s="82">
+        <v>46169</v>
+      </c>
+      <c r="B148" s="83">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="C148" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D148" s="23">
+        <v>3.9E-2</v>
+      </c>
+      <c r="E148" s="23">
+        <v>3.7199999999999997E-2</v>
+      </c>
+      <c r="F148" s="23">
+        <v>4.2799999999999998E-2</v>
+      </c>
+      <c r="G148" s="90">
+        <v>75931</v>
+      </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A149" s="80"/>
-      <c r="B149" s="80"/>
+      <c r="A149" s="82">
+        <v>46170</v>
+      </c>
+      <c r="B149" s="83">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="C149" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D149" s="23">
+        <v>4.02E-2</v>
+      </c>
+      <c r="E149" s="23">
+        <v>3.8399999999999997E-2</v>
+      </c>
+      <c r="F149" s="23">
+        <v>4.4200000000000003E-2</v>
+      </c>
+      <c r="G149" s="90">
+        <v>74450</v>
+      </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A150" s="80"/>
-      <c r="B150" s="80"/>
+      <c r="A150" s="82">
+        <v>46171</v>
+      </c>
+      <c r="B150" s="83">
+        <v>3.7400000000000003E-2</v>
+      </c>
+      <c r="C150" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D150" s="23">
+        <v>4.1099999999999998E-2</v>
+      </c>
+      <c r="E150" s="23">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="F150" s="23">
+        <v>4.5400000000000003E-2</v>
+      </c>
+      <c r="G150" s="90">
+        <v>73618</v>
+      </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A151" s="80"/>
-      <c r="B151" s="80"/>
+      <c r="A151" s="82">
+        <v>46172</v>
+      </c>
+      <c r="B151" s="83">
+        <v>3.73E-2</v>
+      </c>
+      <c r="C151" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D151" s="23">
+        <v>4.0599999999999997E-2</v>
+      </c>
+      <c r="E151" s="23">
+        <v>3.8800000000000001E-2</v>
+      </c>
+      <c r="F151" s="23">
+        <v>4.5499999999999999E-2</v>
+      </c>
+      <c r="G151" s="90">
+        <v>73461</v>
+      </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A152" s="80"/>
-      <c r="B152" s="80"/>
+      <c r="A152" s="82">
+        <v>46173</v>
+      </c>
+      <c r="B152" s="83">
+        <v>3.73E-2</v>
+      </c>
+      <c r="C152" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D152" s="23">
+        <v>4.1099999999999998E-2</v>
+      </c>
+      <c r="E152" s="23">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="F152" s="23">
+        <v>0.04</v>
+      </c>
+      <c r="G152" s="90">
+        <v>73885</v>
+      </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A153" s="80"/>
-      <c r="B153" s="80"/>
+      <c r="A153" s="82">
+        <v>46174</v>
+      </c>
+      <c r="B153" s="83">
+        <v>3.73E-2</v>
+      </c>
+      <c r="C153" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D153" s="23">
+        <v>4.1099999999999998E-2</v>
+      </c>
+      <c r="E153" s="23">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="F153" s="23">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="G153" s="90">
+        <v>73675</v>
+      </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A154" s="80"/>
-      <c r="B154" s="80"/>
+      <c r="A154" s="82">
+        <v>46175</v>
+      </c>
+      <c r="B154" s="83">
+        <v>4.1799999999999997E-2</v>
+      </c>
+      <c r="C154" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D154" s="23">
+        <v>4.5400000000000003E-2</v>
+      </c>
+      <c r="E154" s="23">
+        <v>4.2900000000000001E-2</v>
+      </c>
+      <c r="F154" s="23">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="G154" s="90">
+        <v>71408</v>
+      </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A155" s="80"/>
-      <c r="B155" s="80"/>
+      <c r="A155" s="82">
+        <v>46176</v>
+      </c>
+      <c r="B155" s="83"/>
+      <c r="C155" s="23"/>
+      <c r="D155" s="23"/>
+      <c r="E155" s="23"/>
+      <c r="F155" s="23"/>
+      <c r="G155" s="90"/>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A156" s="80"/>
-      <c r="B156" s="80"/>
+      <c r="A156" s="82">
+        <v>46177</v>
+      </c>
+      <c r="B156" s="83"/>
+      <c r="C156" s="23"/>
+      <c r="D156" s="23"/>
+      <c r="E156" s="23"/>
+      <c r="F156" s="23"/>
+      <c r="G156" s="90"/>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A157" s="80"/>
-      <c r="B157" s="80"/>
+      <c r="A157" s="82">
+        <v>46178</v>
+      </c>
+      <c r="B157" s="83"/>
+      <c r="C157" s="23"/>
+      <c r="D157" s="23"/>
+      <c r="E157" s="23"/>
+      <c r="F157" s="23"/>
+      <c r="G157" s="90"/>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="80"/>
@@ -7965,7 +8723,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="56" priority="1">
+    <cfRule type="expression" dxfId="68" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8301,7 +9059,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="55" priority="1">
+    <cfRule type="expression" dxfId="67" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8639,7 +9397,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="54" priority="1">
+    <cfRule type="expression" dxfId="66" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8975,7 +9733,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="53" priority="1">
+    <cfRule type="expression" dxfId="65" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9309,7 +10067,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="52" priority="1">
+    <cfRule type="expression" dxfId="64" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9645,7 +10403,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="51" priority="1">
+    <cfRule type="expression" dxfId="63" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9981,7 +10739,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="50" priority="1">
+    <cfRule type="expression" dxfId="62" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10317,7 +11075,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="49" priority="1">
+    <cfRule type="expression" dxfId="61" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10653,7 +11411,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="60" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10989,7 +11747,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="59" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11782,7 +12540,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS91" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS103" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -24284,7 +25042,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="BA71" s="13">
-        <f t="shared" ref="BA71:BA91" si="5">AZ71-AR71</f>
+        <f t="shared" ref="BA71:BA103" si="5">AZ71-AR71</f>
         <v>2.6199999999999998E-2</v>
       </c>
       <c r="BC71" s="4">
@@ -25568,7 +26326,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="AI78" s="13">
-        <f t="shared" ref="AI78:AI91" si="6">AH78-Z78</f>
+        <f t="shared" ref="AI78:AI103" si="6">AH78-Z78</f>
         <v>1.1500000000000002E-2</v>
       </c>
       <c r="AK78" s="4">
@@ -28152,7 +28910,9 @@
       <c r="G92" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H92" s="9"/>
+      <c r="H92" s="9">
+        <v>1.12E-2</v>
+      </c>
       <c r="I92" s="2">
         <v>46165</v>
       </c>
@@ -28174,10 +28934,12 @@
       <c r="O92" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P92" s="58"/>
+      <c r="P92" s="58">
+        <v>3.3799999999999997E-2</v>
+      </c>
       <c r="Q92" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.2599999999999995E-2</v>
       </c>
       <c r="S92" s="4">
         <v>46165</v>
@@ -28194,11 +28956,15 @@
       <c r="W92" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X92" s="6"/>
+      <c r="X92" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y92" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z92" s="6"/>
+      <c r="Z92" s="6">
+        <v>1.35E-2</v>
+      </c>
       <c r="AA92" s="2">
         <v>46165</v>
       </c>
@@ -28220,50 +28986,97 @@
       <c r="AG92" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH92" s="58"/>
-      <c r="AI92" s="13"/>
+      <c r="AH92" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI92" s="13">
+        <f t="shared" si="6"/>
+        <v>1.1500000000000002E-2</v>
+      </c>
       <c r="AK92" s="4">
         <v>46165</v>
       </c>
-      <c r="AL92" s="3"/>
+      <c r="AL92" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM92" s="3"/>
       <c r="AN92" s="3"/>
       <c r="AO92" s="3"/>
-      <c r="AP92" s="3"/>
-      <c r="AQ92" s="6"/>
-      <c r="AR92" s="6"/>
+      <c r="AP92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR92" s="6">
+        <v>1.15E-2</v>
+      </c>
       <c r="AS92" s="2">
         <v>46165</v>
       </c>
-      <c r="AT92" s="14"/>
-      <c r="AU92" s="14"/>
-      <c r="AV92" s="14"/>
-      <c r="AW92" s="14"/>
-      <c r="AX92" s="14"/>
-      <c r="AY92" s="14"/>
-      <c r="AZ92" s="14"/>
-      <c r="BA92" s="13"/>
+      <c r="AT92" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AU92" s="14">
+        <v>3.49E-2</v>
+      </c>
+      <c r="AV92" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AW92" s="14">
+        <v>4.99E-2</v>
+      </c>
+      <c r="AX92" s="14">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="AY92" s="14">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="AZ92" s="14">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="BA92" s="13">
+        <f t="shared" si="5"/>
+        <v>2.5499999999999998E-2</v>
+      </c>
       <c r="BC92" s="4">
         <v>46165</v>
       </c>
-      <c r="BD92" s="6"/>
-      <c r="BE92" s="6"/>
-      <c r="BF92" s="6"/>
+      <c r="BD92" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE92" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF92" s="6">
+        <v>1.14E-2</v>
+      </c>
       <c r="BG92" s="3"/>
       <c r="BH92" s="3"/>
       <c r="BI92" s="3"/>
-      <c r="BJ92" s="6"/>
+      <c r="BJ92" s="6">
+        <v>1.15E-2</v>
+      </c>
       <c r="BK92" s="2">
         <v>46165</v>
       </c>
-      <c r="BL92" s="58"/>
+      <c r="BL92" s="58">
+        <v>4.1000000000000002E-2</v>
+      </c>
       <c r="BM92" s="1"/>
-      <c r="BN92" s="58"/>
+      <c r="BN92" s="58">
+        <v>4.9299999999999997E-2</v>
+      </c>
       <c r="BO92" s="1"/>
       <c r="BP92" s="1"/>
       <c r="BQ92" s="1"/>
-      <c r="BR92" s="58"/>
-      <c r="BS92" s="13"/>
+      <c r="BR92" s="58">
+        <v>3.39E-2</v>
+      </c>
+      <c r="BS92" s="13">
+        <f t="shared" si="3"/>
+        <v>2.24E-2</v>
+      </c>
     </row>
     <row r="93" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A93" s="4">
@@ -28287,7 +29100,9 @@
       <c r="G93" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H93" s="9"/>
+      <c r="H93" s="9">
+        <v>1.1900000000000001E-2</v>
+      </c>
       <c r="I93" s="2">
         <v>46166</v>
       </c>
@@ -28309,10 +29124,12 @@
       <c r="O93" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P93" s="58"/>
+      <c r="P93" s="58">
+        <v>3.4200000000000001E-2</v>
+      </c>
       <c r="Q93" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.23E-2</v>
       </c>
       <c r="S93" s="4">
         <v>46166</v>
@@ -28329,11 +29146,15 @@
       <c r="W93" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X93" s="6"/>
+      <c r="X93" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y93" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z93" s="6"/>
+      <c r="Z93" s="6">
+        <v>1.35E-2</v>
+      </c>
       <c r="AA93" s="2">
         <v>46166</v>
       </c>
@@ -28355,50 +29176,3887 @@
       <c r="AG93" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH93" s="58"/>
-      <c r="AI93" s="13"/>
+      <c r="AH93" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI93" s="13">
+        <f t="shared" si="6"/>
+        <v>1.1500000000000002E-2</v>
+      </c>
       <c r="AK93" s="4">
         <v>46166</v>
       </c>
-      <c r="AL93" s="3"/>
+      <c r="AL93" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM93" s="3"/>
       <c r="AN93" s="3"/>
       <c r="AO93" s="3"/>
-      <c r="AP93" s="3"/>
-      <c r="AQ93" s="6"/>
-      <c r="AR93" s="6"/>
+      <c r="AP93" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ93" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR93" s="6">
+        <v>1.17E-2</v>
+      </c>
       <c r="AS93" s="2">
         <v>46166</v>
       </c>
-      <c r="AT93" s="14"/>
-      <c r="AU93" s="14"/>
-      <c r="AV93" s="14"/>
-      <c r="AW93" s="14"/>
-      <c r="AX93" s="14"/>
-      <c r="AY93" s="14"/>
-      <c r="AZ93" s="14"/>
-      <c r="BA93" s="13"/>
+      <c r="AT93" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AU93" s="14">
+        <v>3.49E-2</v>
+      </c>
+      <c r="AV93" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AW93" s="14">
+        <v>4.99E-2</v>
+      </c>
+      <c r="AX93" s="14">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="AY93" s="14">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="AZ93" s="14">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="BA93" s="13">
+        <f t="shared" si="5"/>
+        <v>2.5299999999999996E-2</v>
+      </c>
       <c r="BC93" s="4">
         <v>46166</v>
       </c>
-      <c r="BD93" s="6"/>
-      <c r="BE93" s="6"/>
-      <c r="BF93" s="6"/>
+      <c r="BD93" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE93" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF93" s="6">
+        <v>1.14E-2</v>
+      </c>
       <c r="BG93" s="3"/>
       <c r="BH93" s="3"/>
       <c r="BI93" s="3"/>
-      <c r="BJ93" s="6"/>
+      <c r="BJ93" s="6">
+        <v>1.14E-2</v>
+      </c>
       <c r="BK93" s="2">
         <v>46166</v>
       </c>
-      <c r="BL93" s="58"/>
+      <c r="BL93" s="58">
+        <v>4.1000000000000002E-2</v>
+      </c>
       <c r="BM93" s="1"/>
-      <c r="BN93" s="58"/>
+      <c r="BN93" s="58">
+        <v>4.9299999999999997E-2</v>
+      </c>
       <c r="BO93" s="1"/>
       <c r="BP93" s="1"/>
       <c r="BQ93" s="1"/>
-      <c r="BR93" s="58"/>
-      <c r="BS93" s="13"/>
+      <c r="BR93" s="58">
+        <v>3.3799999999999997E-2</v>
+      </c>
+      <c r="BS93" s="13">
+        <f t="shared" si="3"/>
+        <v>2.2399999999999996E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A94" s="4">
+        <v>46167</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H94" s="9">
+        <v>1.23E-2</v>
+      </c>
+      <c r="I94" s="2">
+        <v>46167</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O94" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P94" s="58">
+        <v>3.44E-2</v>
+      </c>
+      <c r="Q94" s="86">
+        <f t="shared" ref="Q94:Q117" si="8">P94-H94</f>
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="S94" s="4">
+        <v>46167</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X94" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z94" s="6">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="AA94" s="2">
+        <v>46167</v>
+      </c>
+      <c r="AB94" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC94" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD94" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE94" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF94" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG94" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH94" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI94" s="13">
+        <f t="shared" si="6"/>
+        <v>1.1400000000000002E-2</v>
+      </c>
+      <c r="AK94" s="4">
+        <v>46167</v>
+      </c>
+      <c r="AL94" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="AM94" s="3"/>
+      <c r="AN94" s="3"/>
+      <c r="AO94" s="3"/>
+      <c r="AP94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR94" s="6">
+        <v>1.2200000000000001E-2</v>
+      </c>
+      <c r="AS94" s="2">
+        <v>46167</v>
+      </c>
+      <c r="AT94" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AU94" s="14">
+        <v>3.49E-2</v>
+      </c>
+      <c r="AV94" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AW94" s="14">
+        <v>4.99E-2</v>
+      </c>
+      <c r="AX94" s="14">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="AY94" s="14">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="AZ94" s="14">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="BA94" s="13">
+        <f t="shared" si="5"/>
+        <v>2.4799999999999996E-2</v>
+      </c>
+      <c r="BC94" s="4">
+        <v>46167</v>
+      </c>
+      <c r="BD94" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE94" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF94" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BG94" s="3"/>
+      <c r="BH94" s="3"/>
+      <c r="BI94" s="3"/>
+      <c r="BJ94" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BK94" s="2">
+        <v>46167</v>
+      </c>
+      <c r="BL94" s="58">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="BM94" s="1"/>
+      <c r="BN94" s="58">
+        <v>4.99E-2</v>
+      </c>
+      <c r="BO94" s="1"/>
+      <c r="BP94" s="1"/>
+      <c r="BQ94" s="1"/>
+      <c r="BR94" s="58">
+        <v>3.4099999999999998E-2</v>
+      </c>
+      <c r="BS94" s="13">
+        <f t="shared" si="3"/>
+        <v>2.2699999999999998E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A95" s="4">
+        <v>46168</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H95" s="9">
+        <v>1.3100000000000001E-2</v>
+      </c>
+      <c r="I95" s="2">
+        <v>46168</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M95" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N95" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O95" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P95" s="58">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="Q95" s="86">
+        <f t="shared" si="8"/>
+        <v>2.2399999999999996E-2</v>
+      </c>
+      <c r="S95" s="4">
+        <v>46168</v>
+      </c>
+      <c r="T95" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U95" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V95" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W95" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X95" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Y95" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z95" s="6">
+        <v>1.37E-2</v>
+      </c>
+      <c r="AA95" s="2">
+        <v>46168</v>
+      </c>
+      <c r="AB95" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC95" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD95" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE95" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF95" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG95" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH95" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI95" s="13">
+        <f t="shared" si="6"/>
+        <v>1.1300000000000001E-2</v>
+      </c>
+      <c r="AK95" s="4">
+        <v>46168</v>
+      </c>
+      <c r="AL95" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ95" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR95" s="6">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="AS95" s="2">
+        <v>46168</v>
+      </c>
+      <c r="AT95" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AU95" s="14">
+        <v>3.49E-2</v>
+      </c>
+      <c r="AV95" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AW95" s="14">
+        <v>4.99E-2</v>
+      </c>
+      <c r="AX95" s="14">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="AY95" s="14">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="AZ95" s="14">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="BA95" s="13">
+        <f t="shared" si="5"/>
+        <v>2.4E-2</v>
+      </c>
+      <c r="BC95" s="4">
+        <v>46168</v>
+      </c>
+      <c r="BD95" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE95" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF95" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BG95" s="3"/>
+      <c r="BH95" s="3"/>
+      <c r="BI95" s="3"/>
+      <c r="BJ95" s="6">
+        <v>1.21E-2</v>
+      </c>
+      <c r="BK95" s="2">
+        <v>46168</v>
+      </c>
+      <c r="BL95" s="58">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="BM95" s="1"/>
+      <c r="BN95" s="58">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="BO95" s="1"/>
+      <c r="BP95" s="1"/>
+      <c r="BQ95" s="1"/>
+      <c r="BR95" s="58">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="BS95" s="13">
+        <f t="shared" si="3"/>
+        <v>2.3800000000000002E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A96" s="4">
+        <v>46169</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H96" s="9">
+        <v>1.41E-2</v>
+      </c>
+      <c r="I96" s="2">
+        <v>46169</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M96" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N96" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O96" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P96" s="58">
+        <v>3.6799999999999999E-2</v>
+      </c>
+      <c r="Q96" s="86">
+        <f t="shared" si="8"/>
+        <v>2.2699999999999998E-2</v>
+      </c>
+      <c r="S96" s="4">
+        <v>46169</v>
+      </c>
+      <c r="T96" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U96" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V96" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W96" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X96" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Y96" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z96" s="6">
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="AA96" s="2">
+        <v>46169</v>
+      </c>
+      <c r="AB96" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC96" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD96" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE96" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF96" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG96" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH96" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI96" s="13">
+        <f t="shared" si="6"/>
+        <v>1.1100000000000002E-2</v>
+      </c>
+      <c r="AK96" s="4">
+        <v>46169</v>
+      </c>
+      <c r="AL96" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="AM96" s="3"/>
+      <c r="AN96" s="3"/>
+      <c r="AO96" s="3"/>
+      <c r="AP96" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ96" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR96" s="6">
+        <v>1.34E-2</v>
+      </c>
+      <c r="AS96" s="2">
+        <v>46169</v>
+      </c>
+      <c r="AT96" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AU96" s="14">
+        <v>3.49E-2</v>
+      </c>
+      <c r="AV96" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AW96" s="14">
+        <v>4.99E-2</v>
+      </c>
+      <c r="AX96" s="14">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="AY96" s="14">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="AZ96" s="14">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="BA96" s="13">
+        <f t="shared" si="5"/>
+        <v>2.3599999999999996E-2</v>
+      </c>
+      <c r="BC96" s="4">
+        <v>46169</v>
+      </c>
+      <c r="BD96" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE96" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF96" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BG96" s="3"/>
+      <c r="BH96" s="3"/>
+      <c r="BI96" s="3"/>
+      <c r="BJ96" s="6">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="BK96" s="2">
+        <v>46169</v>
+      </c>
+      <c r="BL96" s="58">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="BM96" s="1"/>
+      <c r="BN96" s="58">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="BO96" s="1"/>
+      <c r="BP96" s="1"/>
+      <c r="BQ96" s="1"/>
+      <c r="BR96" s="58">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="BS96" s="13">
+        <f t="shared" si="3"/>
+        <v>2.4299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A97" s="4">
+        <v>46170</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H97" s="9">
+        <v>1.47E-2</v>
+      </c>
+      <c r="I97" s="2">
+        <v>46170</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M97" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O97" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P97" s="58">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="Q97" s="86">
+        <f t="shared" si="8"/>
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="S97" s="4">
+        <v>46170</v>
+      </c>
+      <c r="T97" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U97" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V97" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W97" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X97" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Y97" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z97" s="6">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="AA97" s="2">
+        <v>46170</v>
+      </c>
+      <c r="AB97" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC97" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD97" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE97" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF97" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG97" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH97" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI97" s="13">
+        <f t="shared" si="6"/>
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="AK97" s="4">
+        <v>46170</v>
+      </c>
+      <c r="AL97" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="AM97" s="3"/>
+      <c r="AN97" s="3"/>
+      <c r="AO97" s="3"/>
+      <c r="AP97" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ97" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR97" s="6">
+        <v>1.4E-2</v>
+      </c>
+      <c r="AS97" s="2">
+        <v>46170</v>
+      </c>
+      <c r="AT97" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AU97" s="14">
+        <v>3.49E-2</v>
+      </c>
+      <c r="AV97" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AW97" s="14">
+        <v>4.99E-2</v>
+      </c>
+      <c r="AX97" s="14">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="AY97" s="14">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="AZ97" s="14">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="BA97" s="13">
+        <f t="shared" si="5"/>
+        <v>2.3E-2</v>
+      </c>
+      <c r="BC97" s="4">
+        <v>46170</v>
+      </c>
+      <c r="BD97" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE97" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF97" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BG97" s="3"/>
+      <c r="BH97" s="3"/>
+      <c r="BI97" s="3"/>
+      <c r="BJ97" s="6">
+        <v>1.35E-2</v>
+      </c>
+      <c r="BK97" s="2">
+        <v>46170</v>
+      </c>
+      <c r="BL97" s="58">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="BM97" s="1"/>
+      <c r="BN97" s="58">
+        <v>5.5E-2</v>
+      </c>
+      <c r="BO97" s="1"/>
+      <c r="BP97" s="1"/>
+      <c r="BQ97" s="1"/>
+      <c r="BR97" s="58">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="BS97" s="13">
+        <f t="shared" si="3"/>
+        <v>2.4500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A98" s="4">
+        <v>46171</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H98" s="9">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="I98" s="2">
+        <v>46171</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M98" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O98" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P98" s="58">
+        <v>3.85E-2</v>
+      </c>
+      <c r="Q98" s="86">
+        <f t="shared" si="8"/>
+        <v>2.3399999999999997E-2</v>
+      </c>
+      <c r="S98" s="4">
+        <v>46171</v>
+      </c>
+      <c r="T98" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U98" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V98" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W98" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X98" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Y98" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z98" s="6">
+        <v>1.44E-2</v>
+      </c>
+      <c r="AA98" s="2">
+        <v>46171</v>
+      </c>
+      <c r="AB98" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC98" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD98" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE98" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF98" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG98" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH98" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI98" s="13">
+        <f t="shared" si="6"/>
+        <v>1.0600000000000002E-2</v>
+      </c>
+      <c r="AK98" s="4">
+        <v>46171</v>
+      </c>
+      <c r="AL98" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="AM98" s="3"/>
+      <c r="AN98" s="3"/>
+      <c r="AO98" s="3"/>
+      <c r="AP98" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ98" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR98" s="6">
+        <v>1.54E-2</v>
+      </c>
+      <c r="AS98" s="2">
+        <v>46171</v>
+      </c>
+      <c r="AT98" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AU98" s="14">
+        <v>3.49E-2</v>
+      </c>
+      <c r="AV98" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AW98" s="14">
+        <v>4.99E-2</v>
+      </c>
+      <c r="AX98" s="14">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="AY98" s="14">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="AZ98" s="14">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="BA98" s="13">
+        <f t="shared" si="5"/>
+        <v>2.1599999999999998E-2</v>
+      </c>
+      <c r="BC98" s="4">
+        <v>46171</v>
+      </c>
+      <c r="BD98" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE98" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF98" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BG98" s="3"/>
+      <c r="BH98" s="3"/>
+      <c r="BI98" s="3"/>
+      <c r="BJ98" s="6">
+        <v>1.4E-2</v>
+      </c>
+      <c r="BK98" s="2">
+        <v>46171</v>
+      </c>
+      <c r="BL98" s="58">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="BM98" s="1"/>
+      <c r="BN98" s="58">
+        <v>5.5E-2</v>
+      </c>
+      <c r="BO98" s="1"/>
+      <c r="BP98" s="1"/>
+      <c r="BQ98" s="1"/>
+      <c r="BR98" s="58">
+        <v>3.8600000000000002E-2</v>
+      </c>
+      <c r="BS98" s="13">
+        <f t="shared" si="3"/>
+        <v>2.4600000000000004E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A99" s="4">
+        <v>46172</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H99" s="9">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I99" s="2">
+        <v>46172</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M99" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N99" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O99" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P99" s="58">
+        <v>3.8300000000000001E-2</v>
+      </c>
+      <c r="Q99" s="86">
+        <f t="shared" si="8"/>
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="S99" s="4">
+        <v>46172</v>
+      </c>
+      <c r="T99" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U99" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V99" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W99" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X99" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Y99" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z99" s="6">
+        <v>1.43E-2</v>
+      </c>
+      <c r="AA99" s="2">
+        <v>46172</v>
+      </c>
+      <c r="AB99" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC99" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD99" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE99" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF99" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG99" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH99" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI99" s="13">
+        <f t="shared" si="6"/>
+        <v>1.0700000000000001E-2</v>
+      </c>
+      <c r="AK99" s="4">
+        <v>46172</v>
+      </c>
+      <c r="AL99" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="AM99" s="3"/>
+      <c r="AN99" s="3"/>
+      <c r="AO99" s="3"/>
+      <c r="AP99" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ99" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR99" s="6">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="AS99" s="2">
+        <v>46172</v>
+      </c>
+      <c r="AT99" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AU99" s="14">
+        <v>3.49E-2</v>
+      </c>
+      <c r="AV99" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AW99" s="14">
+        <v>4.99E-2</v>
+      </c>
+      <c r="AX99" s="14">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="AY99" s="14">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="AZ99" s="14">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="BA99" s="13">
+        <f t="shared" si="5"/>
+        <v>2.1399999999999999E-2</v>
+      </c>
+      <c r="BC99" s="4">
+        <v>46172</v>
+      </c>
+      <c r="BD99" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE99" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF99" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BG99" s="3"/>
+      <c r="BH99" s="3"/>
+      <c r="BI99" s="3"/>
+      <c r="BJ99" s="6">
+        <v>1.38E-2</v>
+      </c>
+      <c r="BK99" s="2">
+        <v>46172</v>
+      </c>
+      <c r="BL99" s="58">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="BM99" s="1"/>
+      <c r="BN99" s="58">
+        <v>5.5E-2</v>
+      </c>
+      <c r="BO99" s="1"/>
+      <c r="BP99" s="1"/>
+      <c r="BQ99" s="1"/>
+      <c r="BR99" s="58">
+        <v>3.8199999999999998E-2</v>
+      </c>
+      <c r="BS99" s="13">
+        <f t="shared" si="3"/>
+        <v>2.4399999999999998E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A100" s="4">
+        <v>46173</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H100" s="9">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I100" s="2">
+        <v>46173</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M100" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N100" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O100" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P100" s="58">
+        <v>3.85E-2</v>
+      </c>
+      <c r="Q100" s="86">
+        <f t="shared" si="8"/>
+        <v>2.35E-2</v>
+      </c>
+      <c r="S100" s="4">
+        <v>46173</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X100" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z100" s="6">
+        <v>1.35E-2</v>
+      </c>
+      <c r="AA100" s="2">
+        <v>46173</v>
+      </c>
+      <c r="AB100" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC100" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD100" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE100" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF100" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG100" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH100" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI100" s="13">
+        <f t="shared" si="6"/>
+        <v>1.1500000000000002E-2</v>
+      </c>
+      <c r="AK100" s="4">
+        <v>46173</v>
+      </c>
+      <c r="AL100" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="AM100" s="3"/>
+      <c r="AN100" s="3"/>
+      <c r="AO100" s="3"/>
+      <c r="AP100" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ100" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR100" s="6">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="AS100" s="2">
+        <v>46173</v>
+      </c>
+      <c r="AT100" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AU100" s="14">
+        <v>3.49E-2</v>
+      </c>
+      <c r="AV100" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AW100" s="14">
+        <v>4.99E-2</v>
+      </c>
+      <c r="AX100" s="14">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="AY100" s="14">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="AZ100" s="14">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="BA100" s="13">
+        <f t="shared" si="5"/>
+        <v>2.1099999999999997E-2</v>
+      </c>
+      <c r="BC100" s="4">
+        <v>46173</v>
+      </c>
+      <c r="BD100" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE100" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF100" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BG100" s="3"/>
+      <c r="BH100" s="3"/>
+      <c r="BI100" s="3"/>
+      <c r="BJ100" s="6">
+        <v>1.38E-2</v>
+      </c>
+      <c r="BK100" s="2">
+        <v>46173</v>
+      </c>
+      <c r="BL100" s="58">
+        <v>4.7300000000000002E-2</v>
+      </c>
+      <c r="BM100" s="1"/>
+      <c r="BN100" s="58">
+        <v>5.67E-2</v>
+      </c>
+      <c r="BO100" s="1"/>
+      <c r="BP100" s="1"/>
+      <c r="BQ100" s="1"/>
+      <c r="BR100" s="58">
+        <v>3.8300000000000001E-2</v>
+      </c>
+      <c r="BS100" s="13">
+        <f t="shared" si="3"/>
+        <v>2.4500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A101" s="4">
+        <v>46174</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H101" s="9">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="I101" s="2">
+        <v>46174</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M101" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N101" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O101" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P101" s="58">
+        <v>3.8600000000000002E-2</v>
+      </c>
+      <c r="Q101" s="86">
+        <f t="shared" si="8"/>
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="S101" s="4">
+        <v>46174</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X101" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z101" s="6">
+        <v>1.35E-2</v>
+      </c>
+      <c r="AA101" s="2">
+        <v>46174</v>
+      </c>
+      <c r="AB101" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC101" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD101" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE101" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF101" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG101" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH101" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI101" s="13">
+        <f t="shared" si="6"/>
+        <v>1.1500000000000002E-2</v>
+      </c>
+      <c r="AK101" s="4">
+        <v>46174</v>
+      </c>
+      <c r="AL101" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="AM101" s="3"/>
+      <c r="AN101" s="3"/>
+      <c r="AO101" s="3"/>
+      <c r="AP101" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ101" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR101" s="6">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="AS101" s="2">
+        <v>46174</v>
+      </c>
+      <c r="AT101" s="14">
+        <v>3.4599999999999999E-2</v>
+      </c>
+      <c r="AU101" s="14">
+        <v>3.49E-2</v>
+      </c>
+      <c r="AV101" s="14">
+        <v>4.99E-2</v>
+      </c>
+      <c r="AW101" s="14">
+        <v>4.8899999999999999E-2</v>
+      </c>
+      <c r="AX101" s="14">
+        <v>4.8899999999999999E-2</v>
+      </c>
+      <c r="AY101" s="14">
+        <v>5.4399999999999997E-2</v>
+      </c>
+      <c r="AZ101" s="14">
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="BA101" s="13">
+        <f t="shared" si="5"/>
+        <v>2.4599999999999997E-2</v>
+      </c>
+      <c r="BC101" s="4">
+        <v>46174</v>
+      </c>
+      <c r="BD101" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE101" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF101" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BG101" s="3"/>
+      <c r="BH101" s="3"/>
+      <c r="BI101" s="3"/>
+      <c r="BJ101" s="6">
+        <v>1.38E-2</v>
+      </c>
+      <c r="BK101" s="2">
+        <v>46174</v>
+      </c>
+      <c r="BL101" s="58">
+        <v>4.7300000000000002E-2</v>
+      </c>
+      <c r="BM101" s="1"/>
+      <c r="BN101" s="58">
+        <v>5.67E-2</v>
+      </c>
+      <c r="BO101" s="1"/>
+      <c r="BP101" s="1"/>
+      <c r="BQ101" s="1"/>
+      <c r="BR101" s="58">
+        <v>3.95E-2</v>
+      </c>
+      <c r="BS101" s="13">
+        <f t="shared" si="3"/>
+        <v>2.5700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A102" s="4">
+        <v>46175</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H102" s="9">
+        <v>1.9199999999999998E-2</v>
+      </c>
+      <c r="I102" s="2">
+        <v>46175</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M102" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N102" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O102" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P102" s="58">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="Q102" s="86">
+        <f t="shared" si="8"/>
+        <v>2.3300000000000005E-2</v>
+      </c>
+      <c r="S102" s="4">
+        <v>46175</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X102" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>1.54E-2</v>
+      </c>
+      <c r="AA102" s="2">
+        <v>46175</v>
+      </c>
+      <c r="AB102" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC102" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD102" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE102" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF102" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG102" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH102" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI102" s="13">
+        <f t="shared" si="6"/>
+        <v>9.6000000000000009E-3</v>
+      </c>
+      <c r="AK102" s="4">
+        <v>46175</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="AM102" s="3"/>
+      <c r="AN102" s="3"/>
+      <c r="AO102" s="3"/>
+      <c r="AP102" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ102" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR102" s="6">
+        <v>2.07E-2</v>
+      </c>
+      <c r="AS102" s="2">
+        <v>46175</v>
+      </c>
+      <c r="AT102" s="14">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="AU102" s="14">
+        <v>3.4799999999999998E-2</v>
+      </c>
+      <c r="AV102" s="14">
+        <v>4.8899999999999999E-2</v>
+      </c>
+      <c r="AW102" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AX102" s="14">
+        <v>4.8800000000000003E-2</v>
+      </c>
+      <c r="AY102" s="14">
+        <v>5.5E-2</v>
+      </c>
+      <c r="AZ102" s="14">
+        <v>4.65E-2</v>
+      </c>
+      <c r="BA102" s="13">
+        <f t="shared" si="5"/>
+        <v>2.58E-2</v>
+      </c>
+      <c r="BC102" s="4">
+        <v>46175</v>
+      </c>
+      <c r="BD102" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE102" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF102" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BG102" s="3"/>
+      <c r="BH102" s="3"/>
+      <c r="BI102" s="3"/>
+      <c r="BJ102" s="6">
+        <v>1.61E-2</v>
+      </c>
+      <c r="BK102" s="2">
+        <v>46175</v>
+      </c>
+      <c r="BL102" s="58">
+        <v>5.1200000000000002E-2</v>
+      </c>
+      <c r="BM102" s="1"/>
+      <c r="BN102" s="58">
+        <v>6.1499999999999999E-2</v>
+      </c>
+      <c r="BO102" s="1"/>
+      <c r="BP102" s="1"/>
+      <c r="BQ102" s="1"/>
+      <c r="BR102" s="58">
+        <v>4.2700000000000002E-2</v>
+      </c>
+      <c r="BS102" s="13">
+        <f t="shared" si="3"/>
+        <v>2.6600000000000002E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A103" s="4">
+        <v>46176</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H103" s="9">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="I103" s="2">
+        <v>46176</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M103" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N103" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O103" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P103" s="58">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="Q103" s="86">
+        <f t="shared" si="8"/>
+        <v>2.3299999999999998E-2</v>
+      </c>
+      <c r="S103" s="4">
+        <v>46176</v>
+      </c>
+      <c r="T103" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U103" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V103" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W103" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X103" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Y103" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z103" s="6">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="AA103" s="2">
+        <v>46176</v>
+      </c>
+      <c r="AB103" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC103" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD103" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE103" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF103" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG103" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH103" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI103" s="13">
+        <f t="shared" si="6"/>
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="AK103" s="4">
+        <v>46176</v>
+      </c>
+      <c r="AL103" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="AM103" s="3"/>
+      <c r="AN103" s="3"/>
+      <c r="AO103" s="3"/>
+      <c r="AP103" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ103" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR103" s="6">
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="AS103" s="2">
+        <v>46176</v>
+      </c>
+      <c r="AT103" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AU103" s="14">
+        <v>3.49E-2</v>
+      </c>
+      <c r="AV103" s="14">
+        <v>4.8800000000000003E-2</v>
+      </c>
+      <c r="AW103" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AX103" s="14">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="AY103" s="14">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="AZ103" s="14">
+        <v>4.6899999999999997E-2</v>
+      </c>
+      <c r="BA103" s="13">
+        <f t="shared" si="5"/>
+        <v>2.6699999999999998E-2</v>
+      </c>
+      <c r="BC103" s="4">
+        <v>46176</v>
+      </c>
+      <c r="BD103" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE103" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF103" s="6">
+        <v>1.14E-2</v>
+      </c>
+      <c r="BG103" s="3"/>
+      <c r="BH103" s="3"/>
+      <c r="BI103" s="3"/>
+      <c r="BJ103" s="6">
+        <v>1.78E-2</v>
+      </c>
+      <c r="BK103" s="2">
+        <v>46176</v>
+      </c>
+      <c r="BL103" s="58">
+        <v>5.28E-2</v>
+      </c>
+      <c r="BM103" s="1"/>
+      <c r="BN103" s="58">
+        <v>6.3299999999999995E-2</v>
+      </c>
+      <c r="BO103" s="1"/>
+      <c r="BP103" s="1"/>
+      <c r="BQ103" s="1"/>
+      <c r="BR103" s="58">
+        <v>4.41E-2</v>
+      </c>
+      <c r="BS103" s="13">
+        <f t="shared" si="3"/>
+        <v>2.63E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A104" s="4">
+        <v>46177</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H104" s="9"/>
+      <c r="I104" s="2">
+        <v>46177</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M104" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N104" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O104" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P104" s="58"/>
+      <c r="Q104" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S104" s="4">
+        <v>46177</v>
+      </c>
+      <c r="T104" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U104" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V104" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W104" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X104" s="6"/>
+      <c r="Y104" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z104" s="6"/>
+      <c r="AA104" s="2">
+        <v>46177</v>
+      </c>
+      <c r="AB104" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC104" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD104" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE104" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF104" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG104" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH104" s="58"/>
+      <c r="AI104" s="13"/>
+      <c r="AK104" s="4">
+        <v>46177</v>
+      </c>
+      <c r="AL104" s="3"/>
+      <c r="AM104" s="3"/>
+      <c r="AN104" s="3"/>
+      <c r="AO104" s="3"/>
+      <c r="AP104" s="3"/>
+      <c r="AQ104" s="6"/>
+      <c r="AR104" s="6"/>
+      <c r="AS104" s="2">
+        <v>46177</v>
+      </c>
+      <c r="AT104" s="14"/>
+      <c r="AU104" s="14"/>
+      <c r="AV104" s="14"/>
+      <c r="AW104" s="14"/>
+      <c r="AX104" s="14"/>
+      <c r="AY104" s="14"/>
+      <c r="AZ104" s="14"/>
+      <c r="BA104" s="13"/>
+      <c r="BC104" s="4">
+        <v>46177</v>
+      </c>
+      <c r="BD104" s="6"/>
+      <c r="BE104" s="6"/>
+      <c r="BF104" s="6"/>
+      <c r="BG104" s="3"/>
+      <c r="BH104" s="3"/>
+      <c r="BI104" s="3"/>
+      <c r="BJ104" s="6"/>
+      <c r="BK104" s="2">
+        <v>46177</v>
+      </c>
+      <c r="BL104" s="58"/>
+      <c r="BM104" s="1"/>
+      <c r="BN104" s="58"/>
+      <c r="BO104" s="1"/>
+      <c r="BP104" s="1"/>
+      <c r="BQ104" s="1"/>
+      <c r="BR104" s="58"/>
+      <c r="BS104" s="13"/>
+    </row>
+    <row r="105" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A105" s="4">
+        <v>46178</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H105" s="9"/>
+      <c r="I105" s="2">
+        <v>46178</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L105" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M105" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N105" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O105" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P105" s="58"/>
+      <c r="Q105" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S105" s="4">
+        <v>46178</v>
+      </c>
+      <c r="T105" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U105" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V105" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W105" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X105" s="6"/>
+      <c r="Y105" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z105" s="6"/>
+      <c r="AA105" s="2">
+        <v>46178</v>
+      </c>
+      <c r="AB105" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC105" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD105" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE105" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF105" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG105" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH105" s="58"/>
+      <c r="AI105" s="13"/>
+      <c r="AK105" s="4">
+        <v>46178</v>
+      </c>
+      <c r="AL105" s="3"/>
+      <c r="AM105" s="3"/>
+      <c r="AN105" s="3"/>
+      <c r="AO105" s="3"/>
+      <c r="AP105" s="3"/>
+      <c r="AQ105" s="6"/>
+      <c r="AR105" s="6"/>
+      <c r="AS105" s="2">
+        <v>46178</v>
+      </c>
+      <c r="AT105" s="14"/>
+      <c r="AU105" s="14"/>
+      <c r="AV105" s="14"/>
+      <c r="AW105" s="14"/>
+      <c r="AX105" s="14"/>
+      <c r="AY105" s="14"/>
+      <c r="AZ105" s="14"/>
+      <c r="BA105" s="13"/>
+      <c r="BC105" s="4">
+        <v>46178</v>
+      </c>
+      <c r="BD105" s="6"/>
+      <c r="BE105" s="6"/>
+      <c r="BF105" s="6"/>
+      <c r="BG105" s="3"/>
+      <c r="BH105" s="3"/>
+      <c r="BI105" s="3"/>
+      <c r="BJ105" s="6"/>
+      <c r="BK105" s="2">
+        <v>46178</v>
+      </c>
+      <c r="BL105" s="58"/>
+      <c r="BM105" s="1"/>
+      <c r="BN105" s="58"/>
+      <c r="BO105" s="1"/>
+      <c r="BP105" s="1"/>
+      <c r="BQ105" s="1"/>
+      <c r="BR105" s="58"/>
+      <c r="BS105" s="13"/>
+    </row>
+    <row r="106" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A106" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H106" s="9"/>
+      <c r="I106" s="2">
+        <v>46179</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M106" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N106" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O106" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P106" s="58"/>
+      <c r="Q106" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S106" s="4">
+        <v>46179</v>
+      </c>
+      <c r="T106" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U106" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V106" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W106" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X106" s="6"/>
+      <c r="Y106" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z106" s="6"/>
+      <c r="AA106" s="2">
+        <v>46179</v>
+      </c>
+      <c r="AB106" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC106" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD106" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE106" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF106" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG106" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH106" s="58"/>
+      <c r="AI106" s="13"/>
+      <c r="AK106" s="4">
+        <v>46179</v>
+      </c>
+      <c r="AL106" s="3"/>
+      <c r="AM106" s="3"/>
+      <c r="AN106" s="3"/>
+      <c r="AO106" s="3"/>
+      <c r="AP106" s="3"/>
+      <c r="AQ106" s="6"/>
+      <c r="AR106" s="6"/>
+      <c r="AS106" s="2">
+        <v>46179</v>
+      </c>
+      <c r="AT106" s="14"/>
+      <c r="AU106" s="14"/>
+      <c r="AV106" s="14"/>
+      <c r="AW106" s="14"/>
+      <c r="AX106" s="14"/>
+      <c r="AY106" s="14"/>
+      <c r="AZ106" s="14"/>
+      <c r="BA106" s="13"/>
+      <c r="BC106" s="4">
+        <v>46179</v>
+      </c>
+      <c r="BD106" s="6"/>
+      <c r="BE106" s="6"/>
+      <c r="BF106" s="6"/>
+      <c r="BG106" s="3"/>
+      <c r="BH106" s="3"/>
+      <c r="BI106" s="3"/>
+      <c r="BJ106" s="6"/>
+      <c r="BK106" s="2">
+        <v>46179</v>
+      </c>
+      <c r="BL106" s="58"/>
+      <c r="BM106" s="1"/>
+      <c r="BN106" s="58"/>
+      <c r="BO106" s="1"/>
+      <c r="BP106" s="1"/>
+      <c r="BQ106" s="1"/>
+      <c r="BR106" s="58"/>
+      <c r="BS106" s="13"/>
+    </row>
+    <row r="107" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A107" s="4">
+        <v>46180</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H107" s="9"/>
+      <c r="I107" s="2">
+        <v>46180</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M107" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N107" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O107" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P107" s="58"/>
+      <c r="Q107" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S107" s="4">
+        <v>46180</v>
+      </c>
+      <c r="T107" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U107" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V107" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W107" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X107" s="6"/>
+      <c r="Y107" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z107" s="6"/>
+      <c r="AA107" s="2">
+        <v>46180</v>
+      </c>
+      <c r="AB107" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC107" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD107" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE107" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF107" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG107" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH107" s="58"/>
+      <c r="AI107" s="13"/>
+      <c r="AK107" s="4">
+        <v>46180</v>
+      </c>
+      <c r="AL107" s="3"/>
+      <c r="AM107" s="3"/>
+      <c r="AN107" s="3"/>
+      <c r="AO107" s="3"/>
+      <c r="AP107" s="3"/>
+      <c r="AQ107" s="6"/>
+      <c r="AR107" s="6"/>
+      <c r="AS107" s="2">
+        <v>46180</v>
+      </c>
+      <c r="AT107" s="14"/>
+      <c r="AU107" s="14"/>
+      <c r="AV107" s="14"/>
+      <c r="AW107" s="14"/>
+      <c r="AX107" s="14"/>
+      <c r="AY107" s="14"/>
+      <c r="AZ107" s="14"/>
+      <c r="BA107" s="13"/>
+      <c r="BC107" s="4">
+        <v>46180</v>
+      </c>
+      <c r="BD107" s="6"/>
+      <c r="BE107" s="6"/>
+      <c r="BF107" s="6"/>
+      <c r="BG107" s="3"/>
+      <c r="BH107" s="3"/>
+      <c r="BI107" s="3"/>
+      <c r="BJ107" s="6"/>
+      <c r="BK107" s="2">
+        <v>46180</v>
+      </c>
+      <c r="BL107" s="58"/>
+      <c r="BM107" s="1"/>
+      <c r="BN107" s="58"/>
+      <c r="BO107" s="1"/>
+      <c r="BP107" s="1"/>
+      <c r="BQ107" s="1"/>
+      <c r="BR107" s="58"/>
+      <c r="BS107" s="13"/>
+    </row>
+    <row r="108" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A108" s="4">
+        <v>46181</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H108" s="9"/>
+      <c r="I108" s="2">
+        <v>46181</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L108" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M108" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N108" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O108" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P108" s="58"/>
+      <c r="Q108" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S108" s="4">
+        <v>46181</v>
+      </c>
+      <c r="T108" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U108" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V108" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W108" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X108" s="6"/>
+      <c r="Y108" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z108" s="6"/>
+      <c r="AA108" s="2">
+        <v>46181</v>
+      </c>
+      <c r="AB108" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC108" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD108" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE108" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF108" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG108" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH108" s="58"/>
+      <c r="AI108" s="13"/>
+      <c r="AK108" s="4">
+        <v>46181</v>
+      </c>
+      <c r="AL108" s="3"/>
+      <c r="AM108" s="3"/>
+      <c r="AN108" s="3"/>
+      <c r="AO108" s="3"/>
+      <c r="AP108" s="3"/>
+      <c r="AQ108" s="6"/>
+      <c r="AR108" s="6"/>
+      <c r="AS108" s="2">
+        <v>46181</v>
+      </c>
+      <c r="AT108" s="14"/>
+      <c r="AU108" s="14"/>
+      <c r="AV108" s="14"/>
+      <c r="AW108" s="14"/>
+      <c r="AX108" s="14"/>
+      <c r="AY108" s="14"/>
+      <c r="AZ108" s="14"/>
+      <c r="BA108" s="13"/>
+      <c r="BC108" s="4">
+        <v>46181</v>
+      </c>
+      <c r="BD108" s="6"/>
+      <c r="BE108" s="6"/>
+      <c r="BF108" s="6"/>
+      <c r="BG108" s="3"/>
+      <c r="BH108" s="3"/>
+      <c r="BI108" s="3"/>
+      <c r="BJ108" s="6"/>
+      <c r="BK108" s="2">
+        <v>46181</v>
+      </c>
+      <c r="BL108" s="58"/>
+      <c r="BM108" s="1"/>
+      <c r="BN108" s="58"/>
+      <c r="BO108" s="1"/>
+      <c r="BP108" s="1"/>
+      <c r="BQ108" s="1"/>
+      <c r="BR108" s="58"/>
+      <c r="BS108" s="13"/>
+    </row>
+    <row r="109" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A109" s="4">
+        <v>46182</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H109" s="9"/>
+      <c r="I109" s="2">
+        <v>46182</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L109" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M109" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N109" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O109" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P109" s="58"/>
+      <c r="Q109" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S109" s="4">
+        <v>46182</v>
+      </c>
+      <c r="T109" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U109" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V109" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W109" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X109" s="6"/>
+      <c r="Y109" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z109" s="6"/>
+      <c r="AA109" s="2">
+        <v>46182</v>
+      </c>
+      <c r="AB109" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC109" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD109" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE109" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF109" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG109" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH109" s="58"/>
+      <c r="AI109" s="13"/>
+      <c r="AK109" s="4">
+        <v>46182</v>
+      </c>
+      <c r="AL109" s="3"/>
+      <c r="AM109" s="3"/>
+      <c r="AN109" s="3"/>
+      <c r="AO109" s="3"/>
+      <c r="AP109" s="3"/>
+      <c r="AQ109" s="6"/>
+      <c r="AR109" s="6"/>
+      <c r="AS109" s="2">
+        <v>46182</v>
+      </c>
+      <c r="AT109" s="14"/>
+      <c r="AU109" s="14"/>
+      <c r="AV109" s="14"/>
+      <c r="AW109" s="14"/>
+      <c r="AX109" s="14"/>
+      <c r="AY109" s="14"/>
+      <c r="AZ109" s="14"/>
+      <c r="BA109" s="13"/>
+      <c r="BC109" s="4">
+        <v>46182</v>
+      </c>
+      <c r="BD109" s="6"/>
+      <c r="BE109" s="6"/>
+      <c r="BF109" s="6"/>
+      <c r="BG109" s="3"/>
+      <c r="BH109" s="3"/>
+      <c r="BI109" s="3"/>
+      <c r="BJ109" s="6"/>
+      <c r="BK109" s="2">
+        <v>46182</v>
+      </c>
+      <c r="BL109" s="58"/>
+      <c r="BM109" s="1"/>
+      <c r="BN109" s="58"/>
+      <c r="BO109" s="1"/>
+      <c r="BP109" s="1"/>
+      <c r="BQ109" s="1"/>
+      <c r="BR109" s="58"/>
+      <c r="BS109" s="13"/>
+    </row>
+    <row r="110" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A110" s="4">
+        <v>46183</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H110" s="9"/>
+      <c r="I110" s="2">
+        <v>46183</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L110" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M110" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N110" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O110" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P110" s="58"/>
+      <c r="Q110" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S110" s="4">
+        <v>46183</v>
+      </c>
+      <c r="T110" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U110" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V110" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W110" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X110" s="6"/>
+      <c r="Y110" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z110" s="6"/>
+      <c r="AA110" s="2">
+        <v>46183</v>
+      </c>
+      <c r="AB110" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC110" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD110" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE110" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF110" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG110" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH110" s="58"/>
+      <c r="AI110" s="13"/>
+      <c r="AK110" s="4">
+        <v>46183</v>
+      </c>
+      <c r="AL110" s="3"/>
+      <c r="AM110" s="3"/>
+      <c r="AN110" s="3"/>
+      <c r="AO110" s="3"/>
+      <c r="AP110" s="3"/>
+      <c r="AQ110" s="6"/>
+      <c r="AR110" s="6"/>
+      <c r="AS110" s="2">
+        <v>46183</v>
+      </c>
+      <c r="AT110" s="14"/>
+      <c r="AU110" s="14"/>
+      <c r="AV110" s="14"/>
+      <c r="AW110" s="14"/>
+      <c r="AX110" s="14"/>
+      <c r="AY110" s="14"/>
+      <c r="AZ110" s="14"/>
+      <c r="BA110" s="13"/>
+      <c r="BC110" s="4">
+        <v>46183</v>
+      </c>
+      <c r="BD110" s="6"/>
+      <c r="BE110" s="6"/>
+      <c r="BF110" s="6"/>
+      <c r="BG110" s="3"/>
+      <c r="BH110" s="3"/>
+      <c r="BI110" s="3"/>
+      <c r="BJ110" s="6"/>
+      <c r="BK110" s="2">
+        <v>46183</v>
+      </c>
+      <c r="BL110" s="58"/>
+      <c r="BM110" s="1"/>
+      <c r="BN110" s="58"/>
+      <c r="BO110" s="1"/>
+      <c r="BP110" s="1"/>
+      <c r="BQ110" s="1"/>
+      <c r="BR110" s="58"/>
+      <c r="BS110" s="13"/>
+    </row>
+    <row r="111" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A111" s="4">
+        <v>46184</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H111" s="9"/>
+      <c r="I111" s="2">
+        <v>46184</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L111" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M111" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N111" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O111" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P111" s="58"/>
+      <c r="Q111" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S111" s="4">
+        <v>46184</v>
+      </c>
+      <c r="T111" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U111" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V111" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W111" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X111" s="6"/>
+      <c r="Y111" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z111" s="6"/>
+      <c r="AA111" s="2">
+        <v>46184</v>
+      </c>
+      <c r="AB111" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC111" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD111" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE111" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF111" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG111" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH111" s="58"/>
+      <c r="AI111" s="13"/>
+      <c r="AK111" s="4">
+        <v>46184</v>
+      </c>
+      <c r="AL111" s="3"/>
+      <c r="AM111" s="3"/>
+      <c r="AN111" s="3"/>
+      <c r="AO111" s="3"/>
+      <c r="AP111" s="3"/>
+      <c r="AQ111" s="6"/>
+      <c r="AR111" s="6"/>
+      <c r="AS111" s="2">
+        <v>46184</v>
+      </c>
+      <c r="AT111" s="14"/>
+      <c r="AU111" s="14"/>
+      <c r="AV111" s="14"/>
+      <c r="AW111" s="14"/>
+      <c r="AX111" s="14"/>
+      <c r="AY111" s="14"/>
+      <c r="AZ111" s="14"/>
+      <c r="BA111" s="13"/>
+      <c r="BC111" s="4">
+        <v>46184</v>
+      </c>
+      <c r="BD111" s="6"/>
+      <c r="BE111" s="6"/>
+      <c r="BF111" s="6"/>
+      <c r="BG111" s="3"/>
+      <c r="BH111" s="3"/>
+      <c r="BI111" s="3"/>
+      <c r="BJ111" s="6"/>
+      <c r="BK111" s="2">
+        <v>46184</v>
+      </c>
+      <c r="BL111" s="58"/>
+      <c r="BM111" s="1"/>
+      <c r="BN111" s="58"/>
+      <c r="BO111" s="1"/>
+      <c r="BP111" s="1"/>
+      <c r="BQ111" s="1"/>
+      <c r="BR111" s="58"/>
+      <c r="BS111" s="13"/>
+    </row>
+    <row r="112" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A112" s="4">
+        <v>46185</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H112" s="9"/>
+      <c r="I112" s="2">
+        <v>46185</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M112" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N112" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O112" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P112" s="58"/>
+      <c r="Q112" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S112" s="4">
+        <v>46185</v>
+      </c>
+      <c r="T112" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U112" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V112" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W112" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X112" s="6"/>
+      <c r="Y112" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z112" s="6"/>
+      <c r="AA112" s="2">
+        <v>46185</v>
+      </c>
+      <c r="AB112" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC112" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD112" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE112" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF112" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG112" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH112" s="58"/>
+      <c r="AI112" s="13"/>
+      <c r="AK112" s="4">
+        <v>46185</v>
+      </c>
+      <c r="AL112" s="3"/>
+      <c r="AM112" s="3"/>
+      <c r="AN112" s="3"/>
+      <c r="AO112" s="3"/>
+      <c r="AP112" s="3"/>
+      <c r="AQ112" s="6"/>
+      <c r="AR112" s="6"/>
+      <c r="AS112" s="2">
+        <v>46185</v>
+      </c>
+      <c r="AT112" s="14"/>
+      <c r="AU112" s="14"/>
+      <c r="AV112" s="14"/>
+      <c r="AW112" s="14"/>
+      <c r="AX112" s="14"/>
+      <c r="AY112" s="14"/>
+      <c r="AZ112" s="14"/>
+      <c r="BA112" s="13"/>
+      <c r="BC112" s="4">
+        <v>46185</v>
+      </c>
+      <c r="BD112" s="6"/>
+      <c r="BE112" s="6"/>
+      <c r="BF112" s="6"/>
+      <c r="BG112" s="3"/>
+      <c r="BH112" s="3"/>
+      <c r="BI112" s="3"/>
+      <c r="BJ112" s="6"/>
+      <c r="BK112" s="2">
+        <v>46185</v>
+      </c>
+      <c r="BL112" s="58"/>
+      <c r="BM112" s="1"/>
+      <c r="BN112" s="58"/>
+      <c r="BO112" s="1"/>
+      <c r="BP112" s="1"/>
+      <c r="BQ112" s="1"/>
+      <c r="BR112" s="58"/>
+      <c r="BS112" s="13"/>
+    </row>
+    <row r="113" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A113" s="4">
+        <v>46186</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H113" s="9"/>
+      <c r="I113" s="2">
+        <v>46186</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L113" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M113" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N113" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O113" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P113" s="58"/>
+      <c r="Q113" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S113" s="4">
+        <v>46186</v>
+      </c>
+      <c r="T113" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U113" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V113" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W113" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X113" s="6"/>
+      <c r="Y113" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z113" s="6"/>
+      <c r="AA113" s="2">
+        <v>46186</v>
+      </c>
+      <c r="AB113" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC113" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD113" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE113" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF113" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG113" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH113" s="58"/>
+      <c r="AI113" s="13"/>
+      <c r="AK113" s="4">
+        <v>46186</v>
+      </c>
+      <c r="AL113" s="3"/>
+      <c r="AM113" s="3"/>
+      <c r="AN113" s="3"/>
+      <c r="AO113" s="3"/>
+      <c r="AP113" s="3"/>
+      <c r="AQ113" s="6"/>
+      <c r="AR113" s="6"/>
+      <c r="AS113" s="2">
+        <v>46186</v>
+      </c>
+      <c r="AT113" s="14"/>
+      <c r="AU113" s="14"/>
+      <c r="AV113" s="14"/>
+      <c r="AW113" s="14"/>
+      <c r="AX113" s="14"/>
+      <c r="AY113" s="14"/>
+      <c r="AZ113" s="14"/>
+      <c r="BA113" s="13"/>
+      <c r="BC113" s="4">
+        <v>46186</v>
+      </c>
+      <c r="BD113" s="6"/>
+      <c r="BE113" s="6"/>
+      <c r="BF113" s="6"/>
+      <c r="BG113" s="3"/>
+      <c r="BH113" s="3"/>
+      <c r="BI113" s="3"/>
+      <c r="BJ113" s="6"/>
+      <c r="BK113" s="2">
+        <v>46186</v>
+      </c>
+      <c r="BL113" s="58"/>
+      <c r="BM113" s="1"/>
+      <c r="BN113" s="58"/>
+      <c r="BO113" s="1"/>
+      <c r="BP113" s="1"/>
+      <c r="BQ113" s="1"/>
+      <c r="BR113" s="58"/>
+      <c r="BS113" s="13"/>
+    </row>
+    <row r="114" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A114" s="4">
+        <v>46187</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H114" s="9"/>
+      <c r="I114" s="2">
+        <v>46187</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M114" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N114" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O114" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P114" s="58"/>
+      <c r="Q114" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S114" s="4">
+        <v>46187</v>
+      </c>
+      <c r="T114" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U114" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V114" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W114" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X114" s="6"/>
+      <c r="Y114" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z114" s="6"/>
+      <c r="AA114" s="2">
+        <v>46187</v>
+      </c>
+      <c r="AB114" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC114" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD114" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE114" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF114" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG114" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH114" s="58"/>
+      <c r="AI114" s="13"/>
+      <c r="AK114" s="4">
+        <v>46187</v>
+      </c>
+      <c r="AL114" s="3"/>
+      <c r="AM114" s="3"/>
+      <c r="AN114" s="3"/>
+      <c r="AO114" s="3"/>
+      <c r="AP114" s="3"/>
+      <c r="AQ114" s="6"/>
+      <c r="AR114" s="6"/>
+      <c r="AS114" s="2">
+        <v>46187</v>
+      </c>
+      <c r="AT114" s="14"/>
+      <c r="AU114" s="14"/>
+      <c r="AV114" s="14"/>
+      <c r="AW114" s="14"/>
+      <c r="AX114" s="14"/>
+      <c r="AY114" s="14"/>
+      <c r="AZ114" s="14"/>
+      <c r="BA114" s="13"/>
+      <c r="BC114" s="4">
+        <v>46187</v>
+      </c>
+      <c r="BD114" s="6"/>
+      <c r="BE114" s="6"/>
+      <c r="BF114" s="6"/>
+      <c r="BG114" s="3"/>
+      <c r="BH114" s="3"/>
+      <c r="BI114" s="3"/>
+      <c r="BJ114" s="6"/>
+      <c r="BK114" s="2">
+        <v>46187</v>
+      </c>
+      <c r="BL114" s="58"/>
+      <c r="BM114" s="1"/>
+      <c r="BN114" s="58"/>
+      <c r="BO114" s="1"/>
+      <c r="BP114" s="1"/>
+      <c r="BQ114" s="1"/>
+      <c r="BR114" s="58"/>
+      <c r="BS114" s="13"/>
+    </row>
+    <row r="115" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A115" s="4">
+        <v>46188</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H115" s="9"/>
+      <c r="I115" s="2">
+        <v>46188</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M115" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N115" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O115" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P115" s="58"/>
+      <c r="Q115" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S115" s="4">
+        <v>46188</v>
+      </c>
+      <c r="T115" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U115" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V115" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W115" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X115" s="6"/>
+      <c r="Y115" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z115" s="6"/>
+      <c r="AA115" s="2">
+        <v>46188</v>
+      </c>
+      <c r="AB115" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC115" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD115" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE115" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF115" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG115" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH115" s="58"/>
+      <c r="AI115" s="13"/>
+      <c r="AK115" s="4">
+        <v>46188</v>
+      </c>
+      <c r="AL115" s="3"/>
+      <c r="AM115" s="3"/>
+      <c r="AN115" s="3"/>
+      <c r="AO115" s="3"/>
+      <c r="AP115" s="3"/>
+      <c r="AQ115" s="6"/>
+      <c r="AR115" s="6"/>
+      <c r="AS115" s="2">
+        <v>46188</v>
+      </c>
+      <c r="AT115" s="14"/>
+      <c r="AU115" s="14"/>
+      <c r="AV115" s="14"/>
+      <c r="AW115" s="14"/>
+      <c r="AX115" s="14"/>
+      <c r="AY115" s="14"/>
+      <c r="AZ115" s="14"/>
+      <c r="BA115" s="13"/>
+      <c r="BC115" s="4">
+        <v>46188</v>
+      </c>
+      <c r="BD115" s="6"/>
+      <c r="BE115" s="6"/>
+      <c r="BF115" s="6"/>
+      <c r="BG115" s="3"/>
+      <c r="BH115" s="3"/>
+      <c r="BI115" s="3"/>
+      <c r="BJ115" s="6"/>
+      <c r="BK115" s="2">
+        <v>46188</v>
+      </c>
+      <c r="BL115" s="58"/>
+      <c r="BM115" s="1"/>
+      <c r="BN115" s="58"/>
+      <c r="BO115" s="1"/>
+      <c r="BP115" s="1"/>
+      <c r="BQ115" s="1"/>
+      <c r="BR115" s="58"/>
+      <c r="BS115" s="13"/>
+    </row>
+    <row r="116" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A116" s="4">
+        <v>46189</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H116" s="9"/>
+      <c r="I116" s="2">
+        <v>46189</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M116" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N116" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O116" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P116" s="58"/>
+      <c r="Q116" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S116" s="4">
+        <v>46189</v>
+      </c>
+      <c r="T116" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U116" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V116" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W116" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X116" s="6"/>
+      <c r="Y116" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z116" s="6"/>
+      <c r="AA116" s="2">
+        <v>46189</v>
+      </c>
+      <c r="AB116" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC116" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD116" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE116" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF116" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG116" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH116" s="58"/>
+      <c r="AI116" s="13"/>
+      <c r="AK116" s="4">
+        <v>46189</v>
+      </c>
+      <c r="AL116" s="3"/>
+      <c r="AM116" s="3"/>
+      <c r="AN116" s="3"/>
+      <c r="AO116" s="3"/>
+      <c r="AP116" s="3"/>
+      <c r="AQ116" s="6"/>
+      <c r="AR116" s="6"/>
+      <c r="AS116" s="2">
+        <v>46189</v>
+      </c>
+      <c r="AT116" s="14"/>
+      <c r="AU116" s="14"/>
+      <c r="AV116" s="14"/>
+      <c r="AW116" s="14"/>
+      <c r="AX116" s="14"/>
+      <c r="AY116" s="14"/>
+      <c r="AZ116" s="14"/>
+      <c r="BA116" s="13"/>
+      <c r="BC116" s="4">
+        <v>46189</v>
+      </c>
+      <c r="BD116" s="6"/>
+      <c r="BE116" s="6"/>
+      <c r="BF116" s="6"/>
+      <c r="BG116" s="3"/>
+      <c r="BH116" s="3"/>
+      <c r="BI116" s="3"/>
+      <c r="BJ116" s="6"/>
+      <c r="BK116" s="2">
+        <v>46189</v>
+      </c>
+      <c r="BL116" s="58"/>
+      <c r="BM116" s="1"/>
+      <c r="BN116" s="58"/>
+      <c r="BO116" s="1"/>
+      <c r="BP116" s="1"/>
+      <c r="BQ116" s="1"/>
+      <c r="BR116" s="58"/>
+      <c r="BS116" s="13"/>
+    </row>
+    <row r="117" spans="1:71" x14ac:dyDescent="0.35">
+      <c r="A117" s="4">
+        <v>46190</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H117" s="9"/>
+      <c r="I117" s="2">
+        <v>46190</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L117" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M117" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N117" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O117" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P117" s="58"/>
+      <c r="Q117" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S117" s="4">
+        <v>46190</v>
+      </c>
+      <c r="T117" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U117" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V117" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W117" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X117" s="6"/>
+      <c r="Y117" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z117" s="6"/>
+      <c r="AA117" s="2">
+        <v>46190</v>
+      </c>
+      <c r="AB117" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC117" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD117" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE117" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF117" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG117" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH117" s="58"/>
+      <c r="AI117" s="13"/>
+      <c r="AK117" s="4">
+        <v>46190</v>
+      </c>
+      <c r="AL117" s="3"/>
+      <c r="AM117" s="3"/>
+      <c r="AN117" s="3"/>
+      <c r="AO117" s="3"/>
+      <c r="AP117" s="3"/>
+      <c r="AQ117" s="6"/>
+      <c r="AR117" s="6"/>
+      <c r="AS117" s="2">
+        <v>46190</v>
+      </c>
+      <c r="AT117" s="14"/>
+      <c r="AU117" s="14"/>
+      <c r="AV117" s="14"/>
+      <c r="AW117" s="14"/>
+      <c r="AX117" s="14"/>
+      <c r="AY117" s="14"/>
+      <c r="AZ117" s="14"/>
+      <c r="BA117" s="13"/>
+      <c r="BC117" s="4">
+        <v>46190</v>
+      </c>
+      <c r="BD117" s="6"/>
+      <c r="BE117" s="6"/>
+      <c r="BF117" s="6"/>
+      <c r="BG117" s="3"/>
+      <c r="BH117" s="3"/>
+      <c r="BI117" s="3"/>
+      <c r="BJ117" s="6"/>
+      <c r="BK117" s="2">
+        <v>46190</v>
+      </c>
+      <c r="BL117" s="58"/>
+      <c r="BM117" s="1"/>
+      <c r="BN117" s="58"/>
+      <c r="BO117" s="1"/>
+      <c r="BP117" s="1"/>
+      <c r="BQ117" s="1"/>
+      <c r="BR117" s="58"/>
+      <c r="BS117" s="13"/>
     </row>
     <row r="1048576" spans="42:42" x14ac:dyDescent="0.35">
       <c r="AP1048576" s="18"/>
@@ -28743,7 +33401,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="46" priority="1">
+    <cfRule type="expression" dxfId="58" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29079,7 +33737,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="57" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29417,7 +34075,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="44" priority="1">
+    <cfRule type="expression" dxfId="56" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29755,7 +34413,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="55" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30093,7 +34751,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="54" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30461,7 +35119,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="53" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30829,7 +35487,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="52" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31197,7 +35855,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31568,7 +36226,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="50" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -31949,7 +36607,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33413,7 +38071,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="48" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -33757,7 +38415,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -34101,7 +38759,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -34445,7 +39103,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -34789,7 +39447,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -35121,7 +39779,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -35465,7 +40123,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -35809,7 +40467,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -36156,7 +40814,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -36501,7 +41159,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47197,7 +51855,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47541,7 +52199,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -47876,7 +52534,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -48208,7 +52866,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -48552,7 +53210,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -48896,7 +53554,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -49240,7 +53898,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -49584,7 +54242,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -49928,7 +54586,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -50272,7 +54930,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58309,7 +62967,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58653,7 +63311,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -58997,7 +63655,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -59341,7 +63999,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -59685,7 +64343,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -60029,7 +64687,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -60373,7 +65031,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -60717,7 +65375,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -61061,7 +65719,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -61405,7 +66063,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -61770,7 +66428,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="60" priority="1">
+    <cfRule type="expression" dxfId="72" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -62115,7 +66773,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -62459,7 +67117,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -62803,7 +67461,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63147,7 +67805,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63491,7 +68149,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63835,7 +68493,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -64179,7 +68837,888 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88CDD9CF-1EBA-4737-A0B3-0E492C5A0DD6}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46165</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.49E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.99E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.7691074941686109E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>(H3-'Daily Data'!AR92)</f>
+        <v>2.5499999999999998E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z92</f>
+        <v>1.1500000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f>((1+I5)^(C2/365)-1)*365/C2</f>
+        <v>3.3920472988498589E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>4.9299999999999997E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f>((1+$I5)^(E2/365)-1)*365/E2</f>
+        <v>3.3993048356382727E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" ref="F5:G5" si="2">((1+$I5)^(F2/365)-1)*365/F2</f>
+        <v>3.4040491647770316E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.4183351862080429E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.39E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4479524999688094E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!AR92</f>
+        <v>2.24E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f>((1+I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f>((1+$I6)^(E2/365)-1)*365/E2</f>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" ref="F6:G6" si="3">((1+$I6)^(F2/365)-1)*365/F2</f>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.1699999999999999E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f>((1+I7)^(C2/365)-1)*365/C2</f>
+        <v>3.0216247184851448E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.32E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f>((1+$I7)^(E2/365)-1)*365/E2</f>
+        <v>3.0273830874697632E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" ref="F7:G7" si="4">((1+$I7)^(F2/365)-1)*365/F2</f>
+        <v>3.0311464275388368E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.0424739121945526E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.0659357866290149E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>1.9599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.3809391367190918E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.382035235981351E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3845423852858346E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3892499717891801E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.3939662887175724E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.4081678044053536E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.3799999999999997E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4376091811363807E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H92</f>
+        <v>2.2599999999999995E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.5710476968021175E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.5722705279200455E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5750676674493942E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5803201779262009E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5855829777621806E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.6014333404489757E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.6343087170924049E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="11" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCCD9838-4A8D-4B71-A6AD-2D5D39E8C515}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46166</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.49E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.99E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.7691074941686109E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR63</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z63</f>
+        <v>1.2500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.382035235981351E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>4.9299999999999997E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.3892499717891801E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.3939662887175724E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.4081678044053536E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.3799999999999997E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4376091811363807E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ63</f>
+        <v>2.6199999999999998E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.2800000000000003E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.121734116151758E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.4299999999999997E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.1278805465217829E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.1318977802404467E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.1439908012476682E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1690445957877067E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.36%</f>
+        <v>1.7599999999999998E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.4209614980849228E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.4220837014135107E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.4246505811097595E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.4294704023164348E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.4342992680180727E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.4488403232455951E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4789886456186414E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H63</f>
+        <v>2.6200000000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.5110127732749401E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.5121948345736405E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5148986819484897E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5199758789666746E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5250628545236418E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5403826645448506E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.5721528087785392E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="10" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72890A40-AABF-4DEB-8CC4-8A6516F0DAC9}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46167</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.49E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.99E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="I3" s="74"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68"/>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68"/>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68"/>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68"/>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68"/>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="74"/>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68"/>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="74"/>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -64541,13 +70080,3124 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="59" priority="1">
+    <cfRule type="expression" dxfId="71" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="56" orientation="landscape" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC2D2994-5492-4ABB-8F86-3F9AA9D7C4CD}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46168</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.49E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.99E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.7691074941686109E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR95</f>
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z95</f>
+        <v>1.1300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f>((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.5922960443012478E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f>((1+$I5)^(E2/365)-1)*365/E2</f>
+        <v>3.6004362447270476E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" ref="F5:G5" si="2">((1+$I5)^(F2/365)-1)*365/F2</f>
+        <v>3.6057583196594925E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.6217875576784582E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.6550356185158339E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ95</f>
+        <v>2.3800000000000002E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f>((1+I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f>((1+$I6)^(E2/365)-1)*365/E2</f>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" ref="F6:G6" si="3">((1+$I6)^(F2/365)-1)*365/F2</f>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.2800000000000003E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f>((1+I7)^(C2/365)-1)*365/C2</f>
+        <v>3.121734116151758E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.4299999999999997E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f>((1+$I7)^(E2/365)-1)*365/E2</f>
+        <v>3.1278805465217829E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" ref="F7:G7" si="4">((1+$I7)^(F2/365)-1)*365/F2</f>
+        <v>3.1318977802404467E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.1439908012476682E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.1690445957877067E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.06E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.5510359898422834E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.5522451541739289E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.5550110202771878E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.5602047613818195E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.5654086196407357E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.581081119315413E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.6135859488784616E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H95</f>
+        <v>2.2399999999999996E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.5910594695506913E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.5922960443012478E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.5951246333042218E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.6004362447270476E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.6057583196594925E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.6217875576784582E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.6550356185158339E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="8" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79EAD8A0-C05A-4043-B2C4-23349B2ED06F}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46169</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.49E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.99E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.7691074941686109E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR96</f>
+        <v>2.3599999999999996E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z96</f>
+        <v>1.1100000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f>((1+I5)^(C2/365)-1)*365/C2</f>
+        <v>3.7024389340166004E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f>((1+$I5)^(E2/365)-1)*365/E2</f>
+        <v>3.7110862363455399E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f>((1+$I5)^(F2/365)-1)*365/F2</f>
+        <v>3.7167402871694732E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f>((1+$I5)^(G2/365)-1)*365/G2</f>
+        <v>3.7337714413147337E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.7691074941686109E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ96</f>
+        <v>2.4299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f>((1+I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f>((1+$I6)^(E2/365)-1)*365/E2</f>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" ref="F6:G6" si="2">((1+$I6)^(F2/365)-1)*365/F2</f>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="2"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="3">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.4220837014135107E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.7600000000000001E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="3"/>
+        <v>3.4294704023164348E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="3"/>
+        <v>3.4342992680180727E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="3"/>
+        <v>3.4488403232455951E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4789886456186414E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-2%</f>
+        <v>1.4200000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.6811132610262698E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="4">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.6824126331346081E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="4"/>
+        <v>3.6853849234498227E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="4"/>
+        <v>3.6909665927788916E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="4"/>
+        <v>3.6965595336695314E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="4"/>
+        <v>3.7134062420906062E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.6799999999999999E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.7483578454069244E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H96</f>
+        <v>2.2699999999999998E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>4.2815059161980883E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="5">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>4.2832637114085803E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="5"/>
+        <v>4.287285143257006E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="5"/>
+        <v>4.2948389023937085E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="5"/>
+        <v>4.3024104068013491E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="5"/>
+        <v>4.3252318612913926E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>4.2799999999999998E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>4.3726509254560675E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="7" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5528CAE-D8CC-482E-9792-790664C75C8E}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46170</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.49E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.99E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.7691074941686109E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR97</f>
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z97</f>
+        <v>1.0800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f>((1+I5)^(C2/365)-1)*365/C2</f>
+        <v>3.8025725780286922E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.5E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f>((1+$I5)^(E2/365)-1)*365/E2</f>
+        <v>3.8116942104048458E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" ref="F5:G5" si="2">((1+$I5)^(F2/365)-1)*365/F2</f>
+        <v>3.8176588168356236E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.8356274017090804E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.8729178327362002E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ97</f>
+        <v>2.4500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f>((1+I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f>((1+$I6)^(E2/365)-1)*365/E2</f>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" ref="F6:G6" si="3">((1+$I6)^(F2/365)-1)*365/F2</f>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f>((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.4220837014135107E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.7600000000000001E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f>((1+$I7)^(E2/365)-1)*365/E2</f>
+        <v>3.4294704023164348E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" ref="F7:G7" si="4">((1+$I7)^(F2/365)-1)*365/F2</f>
+        <v>3.4342992680180727E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.4488403232455951E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4789886456186414E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.3600000000000003E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.751156019854017E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.7525053102707075E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.7555918332129311E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.7613881907545298E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.7671964763798499E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.7846931782462699E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.8209997240440829E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H98</f>
+        <v>2.2399999999999996E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.9212632178726885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.9227376581002268E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.9261105836655874E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.932445245712831E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.9387935354773279E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.9579205013178513E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.9976269562287836E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D58D361F-0357-46CD-874E-40265DB778C8}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46171</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.49E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.99E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>((1+H3/365)^365-1)</f>
+        <v>3.7691074941686109E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR98</f>
+        <v>2.1599999999999998E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">((1+H4/365)^365-1)</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z98</f>
+        <v>1.0600000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f>((1+I5)^(C2/365)-1)*365/C2</f>
+        <v>3.8626544761562069E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.5E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f>((1+$I5)^(E2/365)-1)*365/E2</f>
+        <v>3.8720668005707982E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" ref="F5:G5" si="2">((1+$I5)^(F2/365)-1)*365/F2</f>
+        <v>3.8782217460826149E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.8967649563848281E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.8600000000000002E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.9352537413389843E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ98</f>
+        <v>2.4600000000000004E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.2018242012937716E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2082902098360046E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2125165508335836E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2252401622451465E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.2516057037460744E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.1400000000000002E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.851218501867569E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.8526407373154492E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.8558941915132906E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.862004295629589E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.8681273092882745E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.8865741147578438E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.85E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.9248618331255036E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H98</f>
+        <v>2.3399999999999997E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.9212632178726885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.9227376581002268E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.9261105836655874E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.932445245712831E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.9387935354773279E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.9579205013178513E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.9976269562287836E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E8A9522-A862-4FBC-B887-C8EF252EF836}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46172</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.49E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.99E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.7691074941686109E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR99</f>
+        <v>2.1399999999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z99</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.8225997347559368E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.5E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.8318177566042645E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.837845475532109E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.8560045880042144E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.8199999999999998E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.8936923251637001E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ99</f>
+        <v>2.4399999999999998E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.2018242012937716E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2082902098360046E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2125165508335836E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2252401622451465E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.2516057037460744E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.1400000000000002E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.8312058738885373E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.8326133666167612E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.8358330823753763E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.8418797736503744E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.8479391740204962E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.8661939305934263E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.8300000000000001E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.9040811251424667E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H99</f>
+        <v>2.3300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.8812375671868189E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.8826820608222859E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.8859864528720513E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.8921922983701972E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.8984113580225445E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.9171481388509101E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.8800000000000001E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.9560406667257908E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB632294-5F49-4A2A-9A71-90C63ACB4DE4}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46173</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.49E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.99E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>3.7691074941686109E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR100</f>
+        <v>2.1099999999999997E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z100</f>
+        <v>1.1500000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.7300000000000002E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.8326133666167612E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.67E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.8418797736503744E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.8479391740204962E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.8661939305934263E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.8300000000000001E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.9040811251424667E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ100</f>
+        <v>2.4500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.2018242012937716E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2082902098360046E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2125165508335836E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2252401622451465E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.2516057037460744E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.1400000000000002E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.851218501867569E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.8526407373154492E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.8558941915132906E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.862004295629589E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.8681273092882745E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.8865741147578438E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.85E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.9248618331255036E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H100</f>
+        <v>2.35E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.9212632178726885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.9227376581002268E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.9261105836655874E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.932445245712831E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.9387935354773279E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.9579205013178513E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.9976269562287836E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2127FDC4-508C-44F0-A0D4-C3FD37436318}">
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46174</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>3.4599999999999999E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.49E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>4.99E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>4.8899999999999999E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.8899999999999999E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>5.4399999999999997E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>4.2996241252897249E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR101</f>
+        <v>2.4599999999999997E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z101</f>
+        <v>1.1500000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.7300000000000002E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.9527797305134844E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.67E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.9626366640761357E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.969082753132306E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.9885050217776455E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>3.95E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>4.0288275604905666E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ101</f>
+        <v>2.5700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.3620112171935869E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.6900000000000002E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.3691407316138212E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.3738012740671279E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.3878345364413684E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4169256374043444E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.8612248405269937E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.8626544761562069E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.8659248656118694E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.8720668005707982E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.8782217460826149E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.8967649563848281E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.8600000000000002E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.9352537413389843E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H101</f>
+        <v>2.2800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.9212632178726885E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.9227376581002268E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.9261105836655874E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.932445245712831E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.9387935354773279E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.9579205013178513E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.9976269562287836E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G16" s="19"/>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G17" s="19"/>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G18" s="60"/>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G19" s="60"/>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G20" s="19"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC40608F-00C6-41B4-8B26-1E71F4136743}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46175</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.4799999999999998E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>4.8899999999999999E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.8800000000000003E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>5.5E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>4.65E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>4.7594976365493258E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR102</f>
+        <v>2.58E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!H102</f>
+        <v>5.8000000000000031E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>5.1200000000000002E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>4.2732484746831965E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>6.1499999999999999E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>4.2847695644248965E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>4.2923056280611376E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>4.315020010039558E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>4.2700000000000002E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>4.3622154043978734E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ102</f>
+        <v>2.6600000000000002E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>3.3620112171935869E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.6900000000000002E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.3691407316138212E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.3738012740671279E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.3878345364413684E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4169256374043444E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>4.2514848771842341E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>4.2532181082204676E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>4.2571833178827546E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>4.2646313767056111E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>4.2720968096388673E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>4.2945978096879549E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>4.3413474837240562E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-1.92%</f>
+        <v>2.3300000000000005E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>4.2915129621032513E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>4.2932789838088001E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.2973192444788845E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.3049084031183106E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.3125154319151399E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.3354442133061333E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>4.2900000000000001E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>4.3830874871463754E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D979A206-CD6A-4297-8F66-6D11A37D5E8C}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46176</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.49E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>4.8800000000000003E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>4.6899999999999997E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>4.8014044546304424E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR103</f>
+        <v>2.6699999999999998E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z103</f>
+        <v>9.1000000000000004E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>5.28E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f>((1+I5)^(C2/365)-1)*365/C2</f>
+        <v>4.4134650346251733E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>6.3799999999999996E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f>((1+$I5)^(E2/365)-1)*365/E2</f>
+        <v>4.4257551069836011E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" ref="F5:G5" si="2">((1+$I5)^(F2/365)-1)*365/F2</f>
+        <v>4.4337949518542676E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>4.4580315051523496E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>4.41E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>4.5084074336688928E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ103</f>
+        <v>2.63E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f>((1+I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f>((1+$I6)^(E2/365)-1)*365/E2</f>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" ref="F6:G6" si="3">((1+$I6)^(F2/365)-1)*365/F2</f>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>3.4099999999999998E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f>((1+I7)^(C2/365)-1)*365/C2</f>
+        <v>3.2518816632587697E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f>((1+$I7)^(E2/365)-1)*365/E2</f>
+        <v>3.2585515295304769E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" ref="F7:G7" si="4">((1+$I7)^(F2/365)-1)*365/F2</f>
+        <v>3.2629112682946743E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>3.2760372011032608E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>3.303239851864892E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>2.1900000000000003E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>4.3015200244608094E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>4.3032942918809609E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>4.3073534254197764E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>4.3149780665970826E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>4.3226207034042216E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>4.3456570661041326E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>4.3935250895680733E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H103</f>
+        <v>2.3299999999999998E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>4.4916573342820607E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>4.4935919219425809E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.4980180096211742E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.5063325983943532E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.5146676798634426E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.5397964494985968E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>4.4900000000000002E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>4.5920374111655837E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -64902,7 +73552,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="58" priority="1">
+    <cfRule type="expression" dxfId="70" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65257,7 +73907,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="57" priority="1">
+    <cfRule type="expression" dxfId="69" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA0C05B-9C03-40F2-9667-6769D7060D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEF734F-45B3-4F28-849A-C8718FA3EBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="68" activeTab="73" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="58" activeTab="58" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -65978,8 +65978,8 @@
       </c>
       <c r="J7" s="75"/>
       <c r="K7" s="68">
-        <f>H7-1</f>
-        <v>-0.9677</v>
+        <f>H7-1.06%</f>
+        <v>2.1700000000000004E-2</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEF734F-45B3-4F28-849A-C8718FA3EBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3406F1-C593-49EF-968A-260D69CB0354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="58" activeTab="58" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="69" activeTab="78" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -91,6 +91,7 @@
     <sheet name="01.06.2026" sheetId="98" r:id="rId76"/>
     <sheet name="02.06.2026" sheetId="99" r:id="rId77"/>
     <sheet name="03.06.2026" sheetId="100" r:id="rId78"/>
+    <sheet name="04.06.2026" sheetId="101" r:id="rId79"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2937,6 +2938,43 @@
 </comments>
 </file>
 
+<file path=xl/comments75.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{FEB91884-879D-49E5-BF6A-63FC882D9E5D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -3012,7 +3050,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4581" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4594" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -3695,7 +3733,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="73">
+  <dxfs count="74">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -8158,12 +8203,24 @@
       <c r="A155" s="82">
         <v>46176</v>
       </c>
-      <c r="B155" s="83"/>
-      <c r="C155" s="23"/>
-      <c r="D155" s="23"/>
-      <c r="E155" s="23"/>
-      <c r="F155" s="23"/>
-      <c r="G155" s="90"/>
+      <c r="B155" s="83">
+        <v>4.2799999999999998E-2</v>
+      </c>
+      <c r="C155" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D155" s="23">
+        <v>4.7E-2</v>
+      </c>
+      <c r="E155" s="23">
+        <v>4.4900000000000002E-2</v>
+      </c>
+      <c r="F155" s="23">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="G155" s="90">
+        <v>66761</v>
+      </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="82">
@@ -8723,7 +8780,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="68" priority="1">
+    <cfRule type="expression" dxfId="69" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9059,7 +9116,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="67" priority="1">
+    <cfRule type="expression" dxfId="68" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9397,7 +9454,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="66" priority="1">
+    <cfRule type="expression" dxfId="67" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9733,7 +9790,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="65" priority="1">
+    <cfRule type="expression" dxfId="66" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10067,7 +10124,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="64" priority="1">
+    <cfRule type="expression" dxfId="65" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10403,7 +10460,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="63" priority="1">
+    <cfRule type="expression" dxfId="64" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10739,7 +10796,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="62" priority="1">
+    <cfRule type="expression" dxfId="63" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11075,7 +11132,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="61" priority="1">
+    <cfRule type="expression" dxfId="62" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11411,7 +11468,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="60" priority="1">
+    <cfRule type="expression" dxfId="61" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11747,7 +11804,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="59" priority="1">
+    <cfRule type="expression" dxfId="60" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12540,7 +12597,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS103" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS104" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -25042,7 +25099,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="BA71" s="13">
-        <f t="shared" ref="BA71:BA103" si="5">AZ71-AR71</f>
+        <f t="shared" ref="BA71:BA104" si="5">AZ71-AR71</f>
         <v>2.6199999999999998E-2</v>
       </c>
       <c r="BC71" s="4">
@@ -31190,7 +31247,9 @@
       <c r="G104" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H104" s="9"/>
+      <c r="H104" s="9">
+        <v>2.0199999999999999E-2</v>
+      </c>
       <c r="I104" s="2">
         <v>46177</v>
       </c>
@@ -31212,10 +31271,12 @@
       <c r="O104" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P104" s="58"/>
+      <c r="P104" s="58">
+        <v>4.36E-2</v>
+      </c>
       <c r="Q104" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.3400000000000001E-2</v>
       </c>
       <c r="S104" s="4">
         <v>46177</v>
@@ -31263,45 +31324,87 @@
       <c r="AK104" s="4">
         <v>46177</v>
       </c>
-      <c r="AL104" s="3"/>
+      <c r="AL104" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM104" s="3"/>
       <c r="AN104" s="3"/>
       <c r="AO104" s="3"/>
-      <c r="AP104" s="3"/>
-      <c r="AQ104" s="6"/>
-      <c r="AR104" s="6"/>
+      <c r="AP104" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ104" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR104" s="6">
+        <v>2.0799999999999999E-2</v>
+      </c>
       <c r="AS104" s="2">
         <v>46177</v>
       </c>
-      <c r="AT104" s="14"/>
-      <c r="AU104" s="14"/>
-      <c r="AV104" s="14"/>
-      <c r="AW104" s="14"/>
-      <c r="AX104" s="14"/>
-      <c r="AY104" s="14"/>
-      <c r="AZ104" s="14"/>
-      <c r="BA104" s="13"/>
+      <c r="AT104" s="14">
+        <v>3.95E-2</v>
+      </c>
+      <c r="AU104" s="14">
+        <v>3.49E-2</v>
+      </c>
+      <c r="AV104" s="14">
+        <v>4.87E-2</v>
+      </c>
+      <c r="AW104" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AX104" s="14">
+        <v>4.7E-2</v>
+      </c>
+      <c r="AY104" s="14">
+        <v>5.9200000000000003E-2</v>
+      </c>
+      <c r="AZ104" s="14">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="BA104" s="13">
+        <f t="shared" si="5"/>
+        <v>2.8299999999999999E-2</v>
+      </c>
       <c r="BC104" s="4">
         <v>46177</v>
       </c>
-      <c r="BD104" s="6"/>
-      <c r="BE104" s="6"/>
-      <c r="BF104" s="6"/>
+      <c r="BD104" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE104" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF104" s="6">
+        <v>1.14E-2</v>
+      </c>
       <c r="BG104" s="3"/>
       <c r="BH104" s="3"/>
       <c r="BI104" s="3"/>
-      <c r="BJ104" s="6"/>
+      <c r="BJ104" s="6">
+        <v>1.9E-2</v>
+      </c>
       <c r="BK104" s="2">
         <v>46177</v>
       </c>
-      <c r="BL104" s="58"/>
+      <c r="BL104" s="58">
+        <v>5.5800000000000002E-2</v>
+      </c>
       <c r="BM104" s="1"/>
-      <c r="BN104" s="58"/>
+      <c r="BN104" s="58">
+        <v>6.6900000000000001E-2</v>
+      </c>
       <c r="BO104" s="1"/>
       <c r="BP104" s="1"/>
       <c r="BQ104" s="1"/>
-      <c r="BR104" s="58"/>
-      <c r="BS104" s="13"/>
+      <c r="BR104" s="58">
+        <v>4.65E-2</v>
+      </c>
+      <c r="BS104" s="13">
+        <f t="shared" si="3"/>
+        <v>2.75E-2</v>
+      </c>
     </row>
     <row r="105" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A105" s="4">
@@ -33401,7 +33504,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="58" priority="1">
+    <cfRule type="expression" dxfId="59" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -33737,7 +33840,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="57" priority="1">
+    <cfRule type="expression" dxfId="58" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34075,7 +34178,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="56" priority="1">
+    <cfRule type="expression" dxfId="57" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34413,7 +34516,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="55" priority="1">
+    <cfRule type="expression" dxfId="56" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34751,7 +34854,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="54" priority="1">
+    <cfRule type="expression" dxfId="55" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35119,7 +35222,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="53" priority="1">
+    <cfRule type="expression" dxfId="54" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35487,7 +35590,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="52" priority="1">
+    <cfRule type="expression" dxfId="53" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35855,7 +35958,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="51" priority="1">
+    <cfRule type="expression" dxfId="52" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36226,7 +36329,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="50" priority="1">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -36607,7 +36710,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="49" priority="1">
+    <cfRule type="expression" dxfId="50" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -38071,7 +38174,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -38415,7 +38518,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="48" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -38759,7 +38862,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="46" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -39103,7 +39206,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -39447,7 +39550,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="44" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -39779,7 +39882,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -40123,7 +40226,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -40467,7 +40570,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -40814,7 +40917,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -41159,7 +41262,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -51855,7 +51958,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -52199,7 +52302,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -52534,7 +52637,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -52866,7 +52969,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -53210,7 +53313,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -53554,7 +53657,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -53898,7 +54001,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -54242,7 +54345,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -54586,7 +54689,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -54930,7 +55033,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -62967,7 +63070,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63311,7 +63414,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63655,7 +63758,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63999,7 +64102,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -64343,7 +64446,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -64687,7 +64790,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -65031,7 +65134,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -65375,7 +65478,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -65719,7 +65822,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -66063,7 +66166,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -66428,7 +66531,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="72" priority="1">
+    <cfRule type="expression" dxfId="73" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -66773,7 +66876,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -67117,7 +67220,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -67461,7 +67564,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -67805,7 +67908,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -68149,7 +68252,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -68493,7 +68596,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -68837,7 +68940,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -69181,7 +69284,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -69525,7 +69628,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -69718,7 +69821,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -70080,7 +70183,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="71" priority="1">
+    <cfRule type="expression" dxfId="72" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70422,7 +70525,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -70766,7 +70869,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -71110,7 +71213,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -71454,7 +71557,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -71798,7 +71901,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -72142,7 +72245,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -72501,7 +72604,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -72845,7 +72948,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -73147,6 +73250,350 @@
       <c r="K8" s="68">
         <f>H8-'Daily Data'!H103</f>
         <v>2.3299999999999998E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>4.4916573342820607E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>4.4935919219425809E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.4980180096211742E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.5063325983943532E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.5146676798634426E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.5397964494985968E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>4.4900000000000002E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>4.5920374111655837E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E1E89E5-6B17-460D-A8FA-2408FE61DFE5}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46177</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>3.95E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.49E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>4.87E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.7E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>5.9200000000000003E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>5.0321909665185904E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR104</f>
+        <v>2.8299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z103</f>
+        <v>9.1000000000000004E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>5.5800000000000002E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>4.6538525450946423E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>6.6900000000000001E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>4.6675188403669354E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>4.6764604648815496E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>4.7034225939659821E-2</v>
+      </c>
+      <c r="H5" s="53">
+        <v>4.65E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>4.7594976365493258E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ104</f>
+        <v>2.75E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.7613569693030509E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.7661657006941637E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.7693078446810349E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.7787628574820866E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.76E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.7983335754216743E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>4.3615627439733053E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>4.363386889274766E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>4.3675601850457969E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>4.3753994653074044E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>4.3832575064065793E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>4.4069447005582213E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>4.36E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>4.4561725651013573E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H104</f>
+        <v>2.3400000000000001E-2</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
@@ -73552,7 +73999,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="70" priority="1">
+    <cfRule type="expression" dxfId="71" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -73907,7 +74354,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="69" priority="1">
+    <cfRule type="expression" dxfId="70" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3406F1-C593-49EF-968A-260D69CB0354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1035FAEF-D814-4B27-ADDF-5374AA0C2C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="69" activeTab="78" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="74" activeTab="79" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -92,6 +92,7 @@
     <sheet name="02.06.2026" sheetId="99" r:id="rId77"/>
     <sheet name="03.06.2026" sheetId="100" r:id="rId78"/>
     <sheet name="04.06.2026" sheetId="101" r:id="rId79"/>
+    <sheet name="05.06.2026" sheetId="102" r:id="rId80"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2975,6 +2976,43 @@
 </comments>
 </file>
 
+<file path=xl/comments76.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{7EC125C5-B50A-451B-B76C-80983FC70EA7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -3050,7 +3088,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4594" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4606" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -3733,7 +3771,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="74">
+  <dxfs count="75">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -8226,12 +8271,24 @@
       <c r="A156" s="82">
         <v>46177</v>
       </c>
-      <c r="B156" s="83"/>
-      <c r="C156" s="23"/>
-      <c r="D156" s="23"/>
-      <c r="E156" s="23"/>
-      <c r="F156" s="23"/>
-      <c r="G156" s="90"/>
+      <c r="B156" s="83">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="C156" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D156" s="23">
+        <v>5.0200000000000002E-2</v>
+      </c>
+      <c r="E156" s="23">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="F156" s="23">
+        <v>5.28E-2</v>
+      </c>
+      <c r="G156" s="90">
+        <v>64143</v>
+      </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="82">
@@ -8780,7 +8837,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="69" priority="1">
+    <cfRule type="expression" dxfId="70" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9116,7 +9173,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="68" priority="1">
+    <cfRule type="expression" dxfId="69" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9454,7 +9511,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="67" priority="1">
+    <cfRule type="expression" dxfId="68" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9790,7 +9847,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="66" priority="1">
+    <cfRule type="expression" dxfId="67" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10124,7 +10181,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="65" priority="1">
+    <cfRule type="expression" dxfId="66" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10460,7 +10517,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="64" priority="1">
+    <cfRule type="expression" dxfId="65" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10796,7 +10853,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="63" priority="1">
+    <cfRule type="expression" dxfId="64" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11132,7 +11189,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="62" priority="1">
+    <cfRule type="expression" dxfId="63" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11468,7 +11525,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="61" priority="1">
+    <cfRule type="expression" dxfId="62" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11804,7 +11861,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="60" priority="1">
+    <cfRule type="expression" dxfId="61" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12597,7 +12654,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS104" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS105" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -25099,7 +25156,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="BA71" s="13">
-        <f t="shared" ref="BA71:BA104" si="5">AZ71-AR71</f>
+        <f t="shared" ref="BA71:BA105" si="5">AZ71-AR71</f>
         <v>2.6199999999999998E-2</v>
       </c>
       <c r="BC71" s="4">
@@ -26383,7 +26440,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="AI78" s="13">
-        <f t="shared" ref="AI78:AI103" si="6">AH78-Z78</f>
+        <f t="shared" ref="AI78:AI105" si="6">AH78-Z78</f>
         <v>1.1500000000000002E-2</v>
       </c>
       <c r="AK78" s="4">
@@ -31293,11 +31350,15 @@
       <c r="W104" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X104" s="6"/>
+      <c r="X104" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y104" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z104" s="6"/>
+      <c r="Z104" s="6">
+        <v>1.5900000000000001E-2</v>
+      </c>
       <c r="AA104" s="2">
         <v>46177</v>
       </c>
@@ -31319,8 +31380,13 @@
       <c r="AG104" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH104" s="58"/>
-      <c r="AI104" s="13"/>
+      <c r="AH104" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI104" s="13">
+        <f t="shared" si="6"/>
+        <v>9.1000000000000004E-3</v>
+      </c>
       <c r="AK104" s="4">
         <v>46177</v>
       </c>
@@ -31428,7 +31494,9 @@
       <c r="G105" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H105" s="9"/>
+      <c r="H105" s="9">
+        <v>1.5900000000000001E-2</v>
+      </c>
       <c r="I105" s="2">
         <v>46178</v>
       </c>
@@ -31450,10 +31518,12 @@
       <c r="O105" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P105" s="58"/>
+      <c r="P105" s="58">
+        <v>3.8699999999999998E-2</v>
+      </c>
       <c r="Q105" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.2799999999999997E-2</v>
       </c>
       <c r="S105" s="4">
         <v>46178</v>
@@ -31470,11 +31540,15 @@
       <c r="W105" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X105" s="6"/>
+      <c r="X105" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="Y105" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z105" s="6"/>
+      <c r="Z105" s="6">
+        <v>1.5299999999999999E-2</v>
+      </c>
       <c r="AA105" s="2">
         <v>46178</v>
       </c>
@@ -31496,50 +31570,97 @@
       <c r="AG105" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH105" s="58"/>
-      <c r="AI105" s="13"/>
+      <c r="AH105" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI105" s="13">
+        <f t="shared" si="6"/>
+        <v>9.700000000000002E-3</v>
+      </c>
       <c r="AK105" s="4">
         <v>46178</v>
       </c>
-      <c r="AL105" s="3"/>
+      <c r="AL105" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM105" s="3"/>
       <c r="AN105" s="3"/>
       <c r="AO105" s="3"/>
-      <c r="AP105" s="3"/>
-      <c r="AQ105" s="6"/>
-      <c r="AR105" s="6"/>
+      <c r="AP105" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ105" s="6">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="AR105" s="6">
+        <v>1.66E-2</v>
+      </c>
       <c r="AS105" s="2">
         <v>46178</v>
       </c>
-      <c r="AT105" s="14"/>
-      <c r="AU105" s="14"/>
-      <c r="AV105" s="14"/>
-      <c r="AW105" s="14"/>
-      <c r="AX105" s="14"/>
-      <c r="AY105" s="14"/>
-      <c r="AZ105" s="14"/>
-      <c r="BA105" s="13"/>
+      <c r="AT105" s="14">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="AU105" s="14">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="AV105" s="14">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="AW105" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AX105" s="14">
+        <v>4.7E-2</v>
+      </c>
+      <c r="AY105" s="14">
+        <v>5.9900000000000002E-2</v>
+      </c>
+      <c r="AZ105" s="14">
+        <v>4.41E-2</v>
+      </c>
+      <c r="BA105" s="13">
+        <f t="shared" si="5"/>
+        <v>2.75E-2</v>
+      </c>
       <c r="BC105" s="4">
         <v>46178</v>
       </c>
-      <c r="BD105" s="6"/>
-      <c r="BE105" s="6"/>
-      <c r="BF105" s="6"/>
+      <c r="BD105" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE105" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF105" s="6">
+        <v>1.14E-2</v>
+      </c>
       <c r="BG105" s="3"/>
       <c r="BH105" s="3"/>
       <c r="BI105" s="3"/>
-      <c r="BJ105" s="6"/>
+      <c r="BJ105" s="6">
+        <v>1.52E-2</v>
+      </c>
       <c r="BK105" s="2">
         <v>46178</v>
       </c>
-      <c r="BL105" s="58"/>
+      <c r="BL105" s="58">
+        <v>4.8599999999999997E-2</v>
+      </c>
       <c r="BM105" s="1"/>
-      <c r="BN105" s="58"/>
+      <c r="BN105" s="58">
+        <v>5.8299999999999998E-2</v>
+      </c>
       <c r="BO105" s="1"/>
       <c r="BP105" s="1"/>
       <c r="BQ105" s="1"/>
-      <c r="BR105" s="58"/>
-      <c r="BS105" s="13"/>
+      <c r="BR105" s="58">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="BS105" s="13">
+        <f t="shared" si="3"/>
+        <v>2.5300000000000003E-2</v>
+      </c>
     </row>
     <row r="106" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A106" s="4">
@@ -33504,7 +33625,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="59" priority="1">
+    <cfRule type="expression" dxfId="60" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -33840,7 +33961,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="58" priority="1">
+    <cfRule type="expression" dxfId="59" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34178,7 +34299,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="57" priority="1">
+    <cfRule type="expression" dxfId="58" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34516,7 +34637,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="56" priority="1">
+    <cfRule type="expression" dxfId="57" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34854,7 +34975,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="55" priority="1">
+    <cfRule type="expression" dxfId="56" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35222,7 +35343,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="54" priority="1">
+    <cfRule type="expression" dxfId="55" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35590,7 +35711,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="53" priority="1">
+    <cfRule type="expression" dxfId="54" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35958,7 +36079,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="52" priority="1">
+    <cfRule type="expression" dxfId="53" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36329,7 +36450,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="51" priority="1">
+    <cfRule type="expression" dxfId="52" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -36710,7 +36831,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="50" priority="1">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -38174,7 +38295,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="49" priority="1">
+    <cfRule type="expression" dxfId="50" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -38518,7 +38639,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -38862,7 +38983,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="48" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -39206,7 +39327,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="46" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -39550,7 +39671,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -39882,7 +40003,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="44" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -40226,7 +40347,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -40570,7 +40691,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -40917,7 +41038,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -41262,7 +41383,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -51958,7 +52079,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -52302,7 +52423,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -52637,7 +52758,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -52969,7 +53090,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -53313,7 +53434,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -53657,7 +53778,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -54001,7 +54122,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -54345,7 +54466,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -54689,7 +54810,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -55033,7 +55154,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63070,7 +63191,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63414,7 +63535,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63758,7 +63879,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -64102,7 +64223,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -64446,7 +64567,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -64790,7 +64911,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -65134,7 +65255,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -65478,7 +65599,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -65822,7 +65943,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -66166,7 +66287,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -66531,7 +66652,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="73" priority="1">
+    <cfRule type="expression" dxfId="74" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -66876,7 +66997,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -67220,7 +67341,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -67564,7 +67685,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -67908,7 +68029,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -68252,7 +68373,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -68596,7 +68717,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -68940,7 +69061,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -69284,7 +69405,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -69628,7 +69749,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -69821,7 +69942,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -70183,7 +70304,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="72" priority="1">
+    <cfRule type="expression" dxfId="73" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70525,7 +70646,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -70869,7 +70990,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -71213,7 +71334,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -71557,7 +71678,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -71901,7 +72022,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -72245,7 +72366,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -72604,7 +72725,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -72948,7 +73069,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -73292,7 +73413,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -73636,7 +73757,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -73999,7 +74120,351 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="71" priority="1">
+    <cfRule type="expression" dxfId="72" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FC88A17-34D7-46C7-A02C-753C2B364658}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46177</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.7E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>5.9900000000000002E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>4.41E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>4.5084074336688928E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR105</f>
+        <v>2.75E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="57">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z105</f>
+        <v>9.700000000000002E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.8599999999999997E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>4.052922289982909E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.8299999999999998E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>4.0632852986788683E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>4.0700628138462452E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>4.0904859236788139E-2</v>
+      </c>
+      <c r="H5" s="57">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>4.1328970092306072E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ105</f>
+        <v>2.5300000000000003E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.75</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>2.5700000000000001E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.4510692254110272E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>2.69E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.4548576373024433E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.457332546501876E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.4647772518713307E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.4500000000000001E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.4801748490785425E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>1.3900000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.8712311956318669E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.8726682506561701E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.8759556193956914E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.8821294681477138E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.8883164289896549E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.9069562977386327E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.8699999999999998E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.9456466858355688E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H105</f>
+        <v>2.2799999999999997E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>4.2614918737380006E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>4.263233273613546E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.2672171799586711E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.2747003891891823E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.2822010956684808E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.3048086595060091E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>4.3517809238476701E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -74354,7 +74819,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="70" priority="1">
+    <cfRule type="expression" dxfId="71" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1035FAEF-D814-4B27-ADDF-5374AA0C2C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0228067C-BC59-4514-A9AF-2283201D13D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="74" activeTab="79" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74307,7 +74307,7 @@
         <v>60</v>
       </c>
       <c r="B6" s="52">
-        <v>3.75</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="C6" s="52">
         <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0228067C-BC59-4514-A9AF-2283201D13D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E403CB86-6FAB-42B7-8176-5E9C84ED939A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="74" activeTab="79" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28965" yWindow="810" windowWidth="29130" windowHeight="17610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -93,6 +93,9 @@
     <sheet name="03.06.2026" sheetId="100" r:id="rId78"/>
     <sheet name="04.06.2026" sheetId="101" r:id="rId79"/>
     <sheet name="05.06.2026" sheetId="102" r:id="rId80"/>
+    <sheet name="06.06.2026" sheetId="103" r:id="rId81"/>
+    <sheet name="07.06.2026" sheetId="104" r:id="rId82"/>
+    <sheet name="08.06.2026" sheetId="105" r:id="rId83"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3013,6 +3016,117 @@
 </comments>
 </file>
 
+<file path=xl/comments77.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{298129DF-0202-4166-9919-C5376728132B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments78.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{A909F44B-9D91-45CC-BCB6-C00E794FEE52}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments79.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{162F99BF-B2CF-4760-B56C-F27B9467FC75}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -3088,7 +3202,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4606" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4645" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -3771,7 +3885,42 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="75">
+  <dxfs count="80">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4321,9 +4470,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>27736</xdr:colOff>
+      <xdr:colOff>30911</xdr:colOff>
       <xdr:row>155</xdr:row>
-      <xdr:rowOff>67150</xdr:rowOff>
+      <xdr:rowOff>63975</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -8294,86 +8443,169 @@
       <c r="A157" s="82">
         <v>46178</v>
       </c>
-      <c r="B157" s="83"/>
-      <c r="C157" s="23"/>
-      <c r="D157" s="23"/>
-      <c r="E157" s="23"/>
-      <c r="F157" s="23"/>
-      <c r="G157" s="90"/>
+      <c r="B157" s="83">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="C157" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D157" s="23">
+        <v>4.4600000000000001E-2</v>
+      </c>
+      <c r="E157" s="23">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="F157" s="23">
+        <v>5.4800000000000001E-2</v>
+      </c>
+      <c r="G157" s="90">
+        <v>63885</v>
+      </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A158" s="80"/>
-      <c r="B158" s="80"/>
+      <c r="A158" s="82">
+        <v>46179</v>
+      </c>
+      <c r="B158" s="83">
+        <v>3.7900000000000003E-2</v>
+      </c>
+      <c r="C158" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D158" s="23">
+        <v>4.24E-2</v>
+      </c>
+      <c r="E158" s="23">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="F158" s="23">
+        <v>4.7E-2</v>
+      </c>
+      <c r="G158" s="90">
+        <v>61057</v>
+      </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A159" s="80"/>
-      <c r="B159" s="80"/>
+      <c r="A159" s="82">
+        <v>46180</v>
+      </c>
+      <c r="B159" s="83">
+        <v>3.6799999999999999E-2</v>
+      </c>
+      <c r="C159" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D159" s="23">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="E159" s="23">
+        <v>3.8699999999999998E-2</v>
+      </c>
+      <c r="F159" s="23">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="G159" s="90">
+        <v>60885</v>
+      </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A160" s="80"/>
-      <c r="B160" s="80"/>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A161" s="80"/>
-      <c r="B161" s="80"/>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A162" s="80"/>
-      <c r="B162" s="80"/>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A160" s="82">
+        <v>46181</v>
+      </c>
+      <c r="B160" s="83">
+        <v>3.6299999999999999E-2</v>
+      </c>
+      <c r="C160" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D160" s="23">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="E160" s="23">
+        <v>3.8100000000000002E-2</v>
+      </c>
+      <c r="F160" s="23">
+        <v>4.3700000000000003E-2</v>
+      </c>
+      <c r="G160" s="90">
+        <v>63332</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A161" s="82">
+        <v>46182</v>
+      </c>
+      <c r="B161" s="83"/>
+      <c r="C161" s="23"/>
+      <c r="D161" s="23"/>
+      <c r="E161" s="23"/>
+      <c r="F161" s="23"/>
+      <c r="G161" s="90"/>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A162" s="82">
+        <v>46183</v>
+      </c>
+      <c r="B162" s="83"/>
+      <c r="C162" s="23"/>
+      <c r="D162" s="23"/>
+      <c r="E162" s="23"/>
+      <c r="F162" s="23"/>
+      <c r="G162" s="90"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="80"/>
       <c r="B163" s="80"/>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="80"/>
       <c r="B164" s="80"/>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="80"/>
       <c r="B165" s="80"/>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="80"/>
       <c r="B166" s="80"/>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="80"/>
       <c r="B167" s="80"/>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="80"/>
       <c r="B168" s="80"/>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="80"/>
       <c r="B169" s="80"/>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="80"/>
       <c r="B170" s="80"/>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="80"/>
       <c r="B171" s="80"/>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="80"/>
       <c r="B172" s="80"/>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="80"/>
       <c r="B173" s="80"/>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="80"/>
       <c r="B174" s="80"/>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="80"/>
       <c r="B175" s="80"/>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="80"/>
       <c r="B176" s="80"/>
     </row>
@@ -8837,7 +9069,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="70" priority="1">
+    <cfRule type="expression" dxfId="75" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9173,7 +9405,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="69" priority="1">
+    <cfRule type="expression" dxfId="74" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9511,7 +9743,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="68" priority="1">
+    <cfRule type="expression" dxfId="73" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9847,7 +10079,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="67" priority="1">
+    <cfRule type="expression" dxfId="72" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10181,7 +10413,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="66" priority="1">
+    <cfRule type="expression" dxfId="71" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10517,7 +10749,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="65" priority="1">
+    <cfRule type="expression" dxfId="70" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10853,7 +11085,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="64" priority="1">
+    <cfRule type="expression" dxfId="69" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11189,7 +11421,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="63" priority="1">
+    <cfRule type="expression" dxfId="68" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11525,7 +11757,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="62" priority="1">
+    <cfRule type="expression" dxfId="67" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11861,7 +12093,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="61" priority="1">
+    <cfRule type="expression" dxfId="66" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12654,7 +12886,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS105" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS108" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -25156,7 +25388,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="BA71" s="13">
-        <f t="shared" ref="BA71:BA105" si="5">AZ71-AR71</f>
+        <f t="shared" ref="BA71:BA108" si="5">AZ71-AR71</f>
         <v>2.6199999999999998E-2</v>
       </c>
       <c r="BC71" s="4">
@@ -26440,7 +26672,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="AI78" s="13">
-        <f t="shared" ref="AI78:AI105" si="6">AH78-Z78</f>
+        <f t="shared" ref="AI78:AI108" si="6">AH78-Z78</f>
         <v>1.1500000000000002E-2</v>
       </c>
       <c r="AK78" s="4">
@@ -31495,7 +31727,7 @@
         <v>33</v>
       </c>
       <c r="H105" s="9">
-        <v>1.5900000000000001E-2</v>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="I105" s="2">
         <v>46178</v>
@@ -31523,7 +31755,7 @@
       </c>
       <c r="Q105" s="86">
         <f t="shared" si="8"/>
-        <v>2.2799999999999997E-2</v>
+        <v>2.24E-2</v>
       </c>
       <c r="S105" s="4">
         <v>46178</v>
@@ -31684,7 +31916,9 @@
       <c r="G106" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H106" s="9"/>
+      <c r="H106" s="9">
+        <v>1.4500000000000001E-2</v>
+      </c>
       <c r="I106" s="2">
         <v>46179</v>
       </c>
@@ -31706,10 +31940,12 @@
       <c r="O106" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P106" s="58"/>
+      <c r="P106" s="58">
+        <v>3.6400000000000002E-2</v>
+      </c>
       <c r="Q106" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.1900000000000003E-2</v>
       </c>
       <c r="S106" s="4">
         <v>46179</v>
@@ -31726,11 +31962,15 @@
       <c r="W106" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X106" s="6"/>
+      <c r="X106" s="6">
+        <v>0.03</v>
+      </c>
       <c r="Y106" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z106" s="6"/>
+      <c r="Z106" s="6">
+        <v>1.49E-2</v>
+      </c>
       <c r="AA106" s="2">
         <v>46179</v>
       </c>
@@ -31752,50 +31992,97 @@
       <c r="AG106" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH106" s="58"/>
-      <c r="AI106" s="13"/>
+      <c r="AH106" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI106" s="13">
+        <f t="shared" si="6"/>
+        <v>1.0100000000000001E-2</v>
+      </c>
       <c r="AK106" s="4">
         <v>46179</v>
       </c>
-      <c r="AL106" s="3"/>
+      <c r="AL106" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM106" s="3"/>
       <c r="AN106" s="3"/>
       <c r="AO106" s="3"/>
-      <c r="AP106" s="3"/>
-      <c r="AQ106" s="6"/>
-      <c r="AR106" s="6"/>
+      <c r="AP106" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ106" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR106" s="6">
+        <v>1.4500000000000001E-2</v>
+      </c>
       <c r="AS106" s="2">
         <v>46179</v>
       </c>
-      <c r="AT106" s="14"/>
-      <c r="AU106" s="14"/>
-      <c r="AV106" s="14"/>
-      <c r="AW106" s="14"/>
-      <c r="AX106" s="14"/>
-      <c r="AY106" s="14"/>
-      <c r="AZ106" s="14"/>
-      <c r="BA106" s="13"/>
+      <c r="AT106" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AU106" s="14">
+        <v>3.9E-2</v>
+      </c>
+      <c r="AV106" s="14">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="AW106" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AX106" s="14">
+        <v>4.4900000000000002E-2</v>
+      </c>
+      <c r="AY106" s="14">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="AZ106" s="14">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="BA106" s="13">
+        <f t="shared" si="5"/>
+        <v>2.5899999999999999E-2</v>
+      </c>
       <c r="BC106" s="4">
         <v>46179</v>
       </c>
-      <c r="BD106" s="6"/>
-      <c r="BE106" s="6"/>
-      <c r="BF106" s="6"/>
+      <c r="BD106" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE106" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF106" s="6">
+        <v>1.14E-2</v>
+      </c>
       <c r="BG106" s="3"/>
       <c r="BH106" s="3"/>
       <c r="BI106" s="3"/>
-      <c r="BJ106" s="6"/>
+      <c r="BJ106" s="6">
+        <v>1.3899999999999999E-2</v>
+      </c>
       <c r="BK106" s="2">
         <v>46179</v>
       </c>
-      <c r="BL106" s="58"/>
+      <c r="BL106" s="58">
+        <v>4.4200000000000003E-2</v>
+      </c>
       <c r="BM106" s="1"/>
-      <c r="BN106" s="58"/>
+      <c r="BN106" s="58">
+        <v>5.2999999999999999E-2</v>
+      </c>
       <c r="BO106" s="1"/>
       <c r="BP106" s="1"/>
       <c r="BQ106" s="1"/>
-      <c r="BR106" s="58"/>
-      <c r="BS106" s="13"/>
+      <c r="BR106" s="58">
+        <v>3.8199999999999998E-2</v>
+      </c>
+      <c r="BS106" s="13">
+        <f t="shared" si="3"/>
+        <v>2.4299999999999999E-2</v>
+      </c>
     </row>
     <row r="107" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A107" s="4">
@@ -31819,7 +32106,9 @@
       <c r="G107" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H107" s="9"/>
+      <c r="H107" s="9">
+        <v>1.4E-2</v>
+      </c>
       <c r="I107" s="2">
         <v>46180</v>
       </c>
@@ -31841,10 +32130,12 @@
       <c r="O107" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P107" s="58"/>
+      <c r="P107" s="58">
+        <v>3.6299999999999999E-2</v>
+      </c>
       <c r="Q107" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.23E-2</v>
       </c>
       <c r="S107" s="4">
         <v>46180</v>
@@ -31861,11 +32152,15 @@
       <c r="W107" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X107" s="6"/>
+      <c r="X107" s="6">
+        <v>0.03</v>
+      </c>
       <c r="Y107" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z107" s="6"/>
+      <c r="Z107" s="6">
+        <v>1.4999999999999999E-2</v>
+      </c>
       <c r="AA107" s="2">
         <v>46180</v>
       </c>
@@ -31887,50 +32182,97 @@
       <c r="AG107" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH107" s="58"/>
-      <c r="AI107" s="13"/>
+      <c r="AH107" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI107" s="13">
+        <f t="shared" si="6"/>
+        <v>1.0000000000000002E-2</v>
+      </c>
       <c r="AK107" s="4">
         <v>46180</v>
       </c>
-      <c r="AL107" s="3"/>
+      <c r="AL107" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM107" s="3"/>
       <c r="AN107" s="3"/>
       <c r="AO107" s="3"/>
-      <c r="AP107" s="3"/>
-      <c r="AQ107" s="6"/>
-      <c r="AR107" s="6"/>
+      <c r="AP107" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ107" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR107" s="6">
+        <v>1.47E-2</v>
+      </c>
       <c r="AS107" s="2">
         <v>46180</v>
       </c>
-      <c r="AT107" s="14"/>
-      <c r="AU107" s="14"/>
-      <c r="AV107" s="14"/>
-      <c r="AW107" s="14"/>
-      <c r="AX107" s="14"/>
-      <c r="AY107" s="14"/>
-      <c r="AZ107" s="14"/>
-      <c r="BA107" s="13"/>
+      <c r="AT107" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AU107" s="14">
+        <v>3.9E-2</v>
+      </c>
+      <c r="AV107" s="14">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="AW107" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AX107" s="14">
+        <v>4.4900000000000002E-2</v>
+      </c>
+      <c r="AY107" s="14">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="AZ107" s="14">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="BA107" s="13">
+        <f t="shared" si="5"/>
+        <v>2.5700000000000001E-2</v>
+      </c>
       <c r="BC107" s="4">
         <v>46180</v>
       </c>
-      <c r="BD107" s="6"/>
-      <c r="BE107" s="6"/>
-      <c r="BF107" s="6"/>
+      <c r="BD107" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE107" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF107" s="6">
+        <v>1.14E-2</v>
+      </c>
       <c r="BG107" s="3"/>
       <c r="BH107" s="3"/>
       <c r="BI107" s="3"/>
-      <c r="BJ107" s="6"/>
+      <c r="BJ107" s="6">
+        <v>1.5599999999999999E-2</v>
+      </c>
       <c r="BK107" s="2">
         <v>46180</v>
       </c>
-      <c r="BL107" s="58"/>
+      <c r="BL107" s="58">
+        <v>4.4200000000000003E-2</v>
+      </c>
       <c r="BM107" s="1"/>
-      <c r="BN107" s="58"/>
+      <c r="BN107" s="58">
+        <v>5.2999999999999999E-2</v>
+      </c>
       <c r="BO107" s="1"/>
       <c r="BP107" s="1"/>
       <c r="BQ107" s="1"/>
-      <c r="BR107" s="58"/>
-      <c r="BS107" s="13"/>
+      <c r="BR107" s="58">
+        <v>3.7199999999999997E-2</v>
+      </c>
+      <c r="BS107" s="13">
+        <f t="shared" si="3"/>
+        <v>2.1599999999999998E-2</v>
+      </c>
     </row>
     <row r="108" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A108" s="4">
@@ -31954,7 +32296,9 @@
       <c r="G108" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H108" s="9"/>
+      <c r="H108" s="9">
+        <v>1.41E-2</v>
+      </c>
       <c r="I108" s="2">
         <v>46181</v>
       </c>
@@ -31976,10 +32320,12 @@
       <c r="O108" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P108" s="58"/>
+      <c r="P108" s="58">
+        <v>3.6400000000000002E-2</v>
+      </c>
       <c r="Q108" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.23E-2</v>
       </c>
       <c r="S108" s="4">
         <v>46181</v>
@@ -31996,11 +32342,15 @@
       <c r="W108" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X108" s="6"/>
+      <c r="X108" s="6">
+        <v>0.03</v>
+      </c>
       <c r="Y108" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z108" s="6"/>
+      <c r="Z108" s="6">
+        <v>1.4200000000000001E-2</v>
+      </c>
       <c r="AA108" s="2">
         <v>46181</v>
       </c>
@@ -32022,50 +32372,97 @@
       <c r="AG108" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH108" s="58"/>
-      <c r="AI108" s="13"/>
+      <c r="AH108" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI108" s="13">
+        <f t="shared" si="6"/>
+        <v>1.0800000000000001E-2</v>
+      </c>
       <c r="AK108" s="4">
         <v>46181</v>
       </c>
-      <c r="AL108" s="3"/>
+      <c r="AL108" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM108" s="3"/>
       <c r="AN108" s="3"/>
       <c r="AO108" s="3"/>
-      <c r="AP108" s="3"/>
-      <c r="AQ108" s="6"/>
-      <c r="AR108" s="6"/>
+      <c r="AP108" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ108" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR108" s="6">
+        <v>1.4E-2</v>
+      </c>
       <c r="AS108" s="2">
         <v>46181</v>
       </c>
-      <c r="AT108" s="14"/>
-      <c r="AU108" s="14"/>
-      <c r="AV108" s="14"/>
-      <c r="AW108" s="14"/>
-      <c r="AX108" s="14"/>
-      <c r="AY108" s="14"/>
-      <c r="AZ108" s="14"/>
-      <c r="BA108" s="13"/>
+      <c r="AT108" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AU108" s="14">
+        <v>3.9E-2</v>
+      </c>
+      <c r="AV108" s="14">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="AW108" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AX108" s="14">
+        <v>4.4900000000000002E-2</v>
+      </c>
+      <c r="AY108" s="14">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="AZ108" s="14">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="BA108" s="13">
+        <f t="shared" si="5"/>
+        <v>2.64E-2</v>
+      </c>
       <c r="BC108" s="4">
         <v>46181</v>
       </c>
-      <c r="BD108" s="6"/>
-      <c r="BE108" s="6"/>
-      <c r="BF108" s="6"/>
+      <c r="BD108" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE108" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF108" s="6">
+        <v>1.14E-2</v>
+      </c>
       <c r="BG108" s="3"/>
       <c r="BH108" s="3"/>
       <c r="BI108" s="3"/>
-      <c r="BJ108" s="6"/>
+      <c r="BJ108" s="6">
+        <v>1.3100000000000001E-2</v>
+      </c>
       <c r="BK108" s="2">
         <v>46181</v>
       </c>
-      <c r="BL108" s="58"/>
+      <c r="BL108" s="58">
+        <v>4.4200000000000003E-2</v>
+      </c>
       <c r="BM108" s="1"/>
-      <c r="BN108" s="58"/>
+      <c r="BN108" s="58">
+        <v>5.2999999999999999E-2</v>
+      </c>
       <c r="BO108" s="1"/>
       <c r="BP108" s="1"/>
       <c r="BQ108" s="1"/>
-      <c r="BR108" s="58"/>
-      <c r="BS108" s="13"/>
+      <c r="BR108" s="58">
+        <v>3.6799999999999999E-2</v>
+      </c>
+      <c r="BS108" s="13">
+        <f t="shared" si="3"/>
+        <v>2.3699999999999999E-2</v>
+      </c>
     </row>
     <row r="109" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A109" s="4">
@@ -33625,7 +34022,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="60" priority="1">
+    <cfRule type="expression" dxfId="65" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -33961,7 +34358,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="59" priority="1">
+    <cfRule type="expression" dxfId="64" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34299,7 +34696,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="58" priority="1">
+    <cfRule type="expression" dxfId="63" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34637,7 +35034,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="57" priority="1">
+    <cfRule type="expression" dxfId="62" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34975,7 +35372,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="56" priority="1">
+    <cfRule type="expression" dxfId="61" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35343,7 +35740,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="55" priority="1">
+    <cfRule type="expression" dxfId="60" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35711,7 +36108,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="54" priority="1">
+    <cfRule type="expression" dxfId="59" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36079,7 +36476,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="53" priority="1">
+    <cfRule type="expression" dxfId="58" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36450,7 +36847,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="52" priority="1">
+    <cfRule type="expression" dxfId="57" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -36831,7 +37228,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="51" priority="1">
+    <cfRule type="expression" dxfId="56" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -38295,7 +38692,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="50" priority="1">
+    <cfRule type="expression" dxfId="55" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -38639,7 +39036,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="49" priority="1">
+    <cfRule type="expression" dxfId="54" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -38983,7 +39380,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="53" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -39327,7 +39724,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="52" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -39671,7 +40068,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="46" priority="1">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -40003,7 +40400,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="50" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -40347,7 +40744,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="44" priority="1">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -40691,7 +41088,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="48" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -41038,7 +41435,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -41383,7 +41780,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -52079,7 +52476,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -52423,7 +52820,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -52758,7 +53155,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -53090,7 +53487,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -53434,7 +53831,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -53778,7 +54175,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -54122,7 +54519,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -54466,7 +54863,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -54810,7 +55207,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -55154,7 +55551,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63191,7 +63588,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63535,7 +63932,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63879,7 +64276,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -64223,7 +64620,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -64567,7 +64964,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -64911,7 +65308,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -65255,7 +65652,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -65599,7 +65996,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -65943,7 +66340,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -66287,7 +66684,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -66652,7 +67049,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="74" priority="1">
+    <cfRule type="expression" dxfId="79" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -66997,7 +67394,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -67341,7 +67738,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -67685,7 +68082,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -68029,7 +68426,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -68373,7 +68770,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -68717,7 +69114,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -69061,7 +69458,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -69405,7 +69802,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -69749,7 +70146,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -69942,7 +70339,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -70304,7 +70701,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="73" priority="1">
+    <cfRule type="expression" dxfId="78" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70646,7 +71043,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -70990,7 +71387,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -71334,7 +71731,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -71678,7 +72075,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -72022,7 +72419,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -72366,7 +72763,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -72725,7 +73122,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -73069,7 +73466,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -73413,7 +73810,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -73757,7 +74154,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -74120,7 +74517,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="72" priority="1">
+    <cfRule type="expression" dxfId="77" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -74156,7 +74553,7 @@
     </row>
     <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="50">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B2" s="51">
         <v>7</v>
@@ -74418,7 +74815,7 @@
       <c r="J8" s="75"/>
       <c r="K8" s="68">
         <f>H8-'Daily Data'!H105</f>
-        <v>2.2799999999999997E-2</v>
+        <v>2.24E-2</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
@@ -74461,7 +74858,1056 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F18BEE35-1847-43BE-AEF0-FC640A65B7D6}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46179</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.4900000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>4.1224853939605843E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR106</f>
+        <v>2.5899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="57">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z106</f>
+        <v>1.0100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.4200000000000003E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.8225997347559368E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.8318177566042645E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.837845475532109E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.8560045880042144E-2</v>
+      </c>
+      <c r="H5" s="57">
+        <v>3.8199999999999998E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.8936923251637001E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ106</f>
+        <v>2.4299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.090778059017687E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>2.29E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.0935342936297952E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.0953344478137657E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.1007473023389494E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.0899999999999998E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.1119323554426916E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>1.0299999999999998E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.6410891892388886E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.6423604592851447E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.6452684422008552E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.6507292567278249E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.6562009787260347E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.672681834941291E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.6400000000000002E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.7068709602530836E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H106</f>
+        <v>2.1900000000000003E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>4.0513484000246666E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>4.052922289982909E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.0565228148374044E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.0632852986788683E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.0700628138462452E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>4.0904859236788139E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>4.1328970092306072E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EF638DD-D47B-4BE9-A415-020C9E62597A}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46180</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.4900000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>4.1224853939605843E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR107</f>
+        <v>2.5700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="57">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z107</f>
+        <v>1.0000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.4200000000000003E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.7224653775365733E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.7312065302985954E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.7369220247494755E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.7541386378962212E-2</v>
+      </c>
+      <c r="H5" s="57">
+        <v>3.7199999999999997E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.7898612814819987E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ107</f>
+        <v>2.1599999999999998E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.090778059017687E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>2.29E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.0935342936297952E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.0953344478137657E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.1007473023389494E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.0899999999999998E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.1119323554426916E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>1.0299999999999998E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.6310832124105845E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.6323475049729645E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.6352395210776788E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.6406703291771501E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.6461119549689336E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.6625019812009267E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.6299999999999999E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.6965018242766767E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H107</f>
+        <v>2.23E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.8712311956318669E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.8726682506561701E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.8759556193956914E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.8821294681477138E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.8883164289896549E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.9069562977386327E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.8699999999999998E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.9456466858355688E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J3 I4:J9 A4:H5 A6:G7 A8:H9">
+    <cfRule type="expression" dxfId="3" priority="5">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6">
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>_xlfn.ISFORMULA(H6)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4">
+      <formula>_xlfn.ISFORMULA(H6)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7">
     <cfRule type="expression" dxfId="0" priority="1">
+      <formula>_xlfn.ISFORMULA(H7)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(H7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC40240A-61FD-43EE-BF2B-4C44E29180D5}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46181</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.4900000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>4.1224853939605843E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR108</f>
+        <v>2.64E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="57">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z108</f>
+        <v>1.0800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.4200000000000003E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:G5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.6824126331346081E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.6909665927788916E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.6965595336695314E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.7134062420906062E-2</v>
+      </c>
+      <c r="H5" s="57">
+        <v>3.6799999999999999E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.7483578454069244E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ108</f>
+        <v>2.3699999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.090778059017687E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>2.29E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.0935342936297952E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.0953344478137657E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.1007473023389494E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.0899999999999998E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.1119323554426916E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>1.0299999999999998E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.6410891892388886E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.6423604592851447E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.6452684422008552E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.6507292567278249E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.6562009787260347E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.672681834941291E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.6400000000000002E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.7068709602530836E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H108</f>
+        <v>2.23E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.8111933116994026E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.8125861385658953E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.8157722919830293E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.8217559021958877E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.8277520231449862E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.8458157450568138E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.8100000000000002E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.88330456106869E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -74819,7 +76265,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="71" priority="1">
+    <cfRule type="expression" dxfId="76" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E403CB86-6FAB-42B7-8176-5E9C84ED939A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2E0361-B06B-42D9-8D4C-CB39027A12F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28965" yWindow="810" windowWidth="29130" windowHeight="17610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="74" activeTab="83" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -96,6 +96,7 @@
     <sheet name="06.06.2026" sheetId="103" r:id="rId81"/>
     <sheet name="07.06.2026" sheetId="104" r:id="rId82"/>
     <sheet name="08.06.2026" sheetId="105" r:id="rId83"/>
+    <sheet name="09.06.2026" sheetId="106" r:id="rId84"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3164,6 +3165,43 @@
 </comments>
 </file>
 
+<file path=xl/comments80.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{42A17E2B-951C-45D0-90CB-0C9E4D075BE2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -3202,7 +3240,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4645" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4658" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -3885,14 +3923,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="80">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="79">
     <dxf>
       <fill>
         <patternFill>
@@ -4470,9 +4501,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>30911</xdr:colOff>
+      <xdr:colOff>27736</xdr:colOff>
       <xdr:row>155</xdr:row>
-      <xdr:rowOff>63975</xdr:rowOff>
+      <xdr:rowOff>67150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -8535,11 +8566,21 @@
       <c r="A161" s="82">
         <v>46182</v>
       </c>
-      <c r="B161" s="83"/>
-      <c r="C161" s="23"/>
-      <c r="D161" s="23"/>
-      <c r="E161" s="23"/>
-      <c r="F161" s="23"/>
+      <c r="B161" s="83">
+        <v>3.6299999999999999E-2</v>
+      </c>
+      <c r="C161" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D161" s="23">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="E161" s="23">
+        <v>3.8100000000000002E-2</v>
+      </c>
+      <c r="F161" s="23">
+        <v>4.2700000000000002E-2</v>
+      </c>
       <c r="G161" s="90"/>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
@@ -9069,7 +9110,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="75" priority="1">
+    <cfRule type="expression" dxfId="74" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9405,7 +9446,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="74" priority="1">
+    <cfRule type="expression" dxfId="73" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9743,7 +9784,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="73" priority="1">
+    <cfRule type="expression" dxfId="72" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10079,7 +10120,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="72" priority="1">
+    <cfRule type="expression" dxfId="71" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10413,7 +10454,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="71" priority="1">
+    <cfRule type="expression" dxfId="70" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10749,7 +10790,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="70" priority="1">
+    <cfRule type="expression" dxfId="69" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11085,7 +11126,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="69" priority="1">
+    <cfRule type="expression" dxfId="68" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11421,7 +11462,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="68" priority="1">
+    <cfRule type="expression" dxfId="67" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11757,7 +11798,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="67" priority="1">
+    <cfRule type="expression" dxfId="66" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12093,7 +12134,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="66" priority="1">
+    <cfRule type="expression" dxfId="65" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12886,7 +12927,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS108" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS109" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -25388,7 +25429,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="BA71" s="13">
-        <f t="shared" ref="BA71:BA108" si="5">AZ71-AR71</f>
+        <f t="shared" ref="BA71:BA109" si="5">AZ71-AR71</f>
         <v>2.6199999999999998E-2</v>
       </c>
       <c r="BC71" s="4">
@@ -26672,7 +26713,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="AI78" s="13">
-        <f t="shared" ref="AI78:AI108" si="6">AH78-Z78</f>
+        <f t="shared" ref="AI78:AI110" si="6">AH78-Z78</f>
         <v>1.1500000000000002E-2</v>
       </c>
       <c r="AK78" s="4">
@@ -32486,7 +32527,9 @@
       <c r="G109" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H109" s="9"/>
+      <c r="H109" s="9">
+        <v>1.3599999999999999E-2</v>
+      </c>
       <c r="I109" s="2">
         <v>46182</v>
       </c>
@@ -32508,10 +32551,12 @@
       <c r="O109" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P109" s="58"/>
+      <c r="P109" s="58">
+        <v>3.5799999999999998E-2</v>
+      </c>
       <c r="Q109" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.2199999999999998E-2</v>
       </c>
       <c r="S109" s="4">
         <v>46182</v>
@@ -32528,11 +32573,15 @@
       <c r="W109" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X109" s="6"/>
+      <c r="X109" s="6">
+        <v>0.03</v>
+      </c>
       <c r="Y109" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z109" s="6"/>
+      <c r="Z109" s="6">
+        <v>1.47E-2</v>
+      </c>
       <c r="AA109" s="2">
         <v>46182</v>
       </c>
@@ -32554,50 +32603,97 @@
       <c r="AG109" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH109" s="58"/>
-      <c r="AI109" s="13"/>
+      <c r="AH109" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AI109" s="13">
+        <f t="shared" si="6"/>
+        <v>1.0300000000000002E-2</v>
+      </c>
       <c r="AK109" s="4">
         <v>46182</v>
       </c>
-      <c r="AL109" s="3"/>
+      <c r="AL109" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM109" s="3"/>
       <c r="AN109" s="3"/>
       <c r="AO109" s="3"/>
-      <c r="AP109" s="3"/>
-      <c r="AQ109" s="6"/>
-      <c r="AR109" s="6"/>
+      <c r="AP109" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ109" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR109" s="6">
+        <v>1.4800000000000001E-2</v>
+      </c>
       <c r="AS109" s="2">
         <v>46182</v>
       </c>
-      <c r="AT109" s="14"/>
-      <c r="AU109" s="14"/>
-      <c r="AV109" s="14"/>
-      <c r="AW109" s="14"/>
-      <c r="AX109" s="14"/>
-      <c r="AY109" s="14"/>
-      <c r="AZ109" s="14"/>
-      <c r="BA109" s="13"/>
+      <c r="AT109" s="14">
+        <v>4.4499999999999998E-2</v>
+      </c>
+      <c r="AU109" s="14">
+        <v>3.9E-2</v>
+      </c>
+      <c r="AV109" s="14">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="AW109" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="AX109" s="14">
+        <v>4.4900000000000002E-2</v>
+      </c>
+      <c r="AY109" s="14">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="AZ109" s="14">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="BA109" s="13">
+        <f t="shared" si="5"/>
+        <v>2.5599999999999998E-2</v>
+      </c>
       <c r="BC109" s="4">
         <v>46182</v>
       </c>
-      <c r="BD109" s="6"/>
-      <c r="BE109" s="6"/>
-      <c r="BF109" s="6"/>
+      <c r="BD109" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE109" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF109" s="6">
+        <v>1.14E-2</v>
+      </c>
       <c r="BG109" s="3"/>
       <c r="BH109" s="3"/>
       <c r="BI109" s="3"/>
-      <c r="BJ109" s="6"/>
+      <c r="BJ109" s="6">
+        <v>1.2699999999999999E-2</v>
+      </c>
       <c r="BK109" s="2">
         <v>46182</v>
       </c>
-      <c r="BL109" s="58"/>
+      <c r="BL109" s="58">
+        <v>4.3799999999999999E-2</v>
+      </c>
       <c r="BM109" s="1"/>
-      <c r="BN109" s="58"/>
+      <c r="BN109" s="58">
+        <v>5.2600000000000001E-2</v>
+      </c>
       <c r="BO109" s="1"/>
       <c r="BP109" s="1"/>
       <c r="BQ109" s="1"/>
-      <c r="BR109" s="58"/>
-      <c r="BS109" s="13"/>
+      <c r="BR109" s="58">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="BS109" s="13">
+        <f t="shared" si="3"/>
+        <v>2.3900000000000001E-2</v>
+      </c>
     </row>
     <row r="110" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A110" s="4">
@@ -32690,7 +32786,10 @@
         <v>33</v>
       </c>
       <c r="AH110" s="58"/>
-      <c r="AI110" s="13"/>
+      <c r="AI110" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AK110" s="4">
         <v>46183</v>
       </c>
@@ -34022,7 +34121,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="65" priority="1">
+    <cfRule type="expression" dxfId="64" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34358,7 +34457,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="64" priority="1">
+    <cfRule type="expression" dxfId="63" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34696,7 +34795,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="63" priority="1">
+    <cfRule type="expression" dxfId="62" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35034,7 +35133,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="62" priority="1">
+    <cfRule type="expression" dxfId="61" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35372,7 +35471,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="61" priority="1">
+    <cfRule type="expression" dxfId="60" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35740,7 +35839,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="60" priority="1">
+    <cfRule type="expression" dxfId="59" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36108,7 +36207,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="59" priority="1">
+    <cfRule type="expression" dxfId="58" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36476,7 +36575,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="58" priority="1">
+    <cfRule type="expression" dxfId="57" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36847,7 +36946,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="57" priority="1">
+    <cfRule type="expression" dxfId="56" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -37228,7 +37327,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="56" priority="1">
+    <cfRule type="expression" dxfId="55" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -38692,7 +38791,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="55" priority="1">
+    <cfRule type="expression" dxfId="54" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -39036,7 +39135,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="54" priority="1">
+    <cfRule type="expression" dxfId="53" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -39380,7 +39479,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="53" priority="1">
+    <cfRule type="expression" dxfId="52" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -39724,7 +39823,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="52" priority="1">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -40068,7 +40167,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="51" priority="1">
+    <cfRule type="expression" dxfId="50" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -40400,7 +40499,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="50" priority="1">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -40744,7 +40843,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="49" priority="1">
+    <cfRule type="expression" dxfId="48" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -41088,7 +41187,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -41435,7 +41534,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -41780,7 +41879,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="46" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -52476,7 +52575,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -52820,7 +52919,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="44" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -53155,7 +53254,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -53487,7 +53586,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -53831,7 +53930,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -54175,7 +54274,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -54519,7 +54618,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -54863,7 +54962,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -55207,7 +55306,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -55551,7 +55650,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63588,7 +63687,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63932,7 +64031,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -64276,7 +64375,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -64620,7 +64719,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -64964,7 +65063,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -65308,7 +65407,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -65652,7 +65751,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -65996,7 +66095,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -66340,7 +66439,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -66684,7 +66783,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -67049,7 +67148,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="79" priority="1">
+    <cfRule type="expression" dxfId="78" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -67394,7 +67493,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -67738,7 +67837,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -68082,7 +68181,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -68426,7 +68525,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -68770,7 +68869,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -69114,7 +69213,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -69458,7 +69557,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -69802,7 +69901,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -70146,7 +70245,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -70339,7 +70438,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -70701,7 +70800,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="78" priority="1">
+    <cfRule type="expression" dxfId="77" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -71043,7 +71142,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -71387,7 +71486,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -71731,7 +71830,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -72075,7 +72174,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -72419,7 +72518,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -72763,7 +72862,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -73122,7 +73221,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -73466,7 +73565,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -73810,7 +73909,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -74154,7 +74253,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -74517,7 +74616,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="77" priority="1">
+    <cfRule type="expression" dxfId="76" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -74858,7 +74957,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -75202,7 +75301,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -75545,28 +75644,12 @@
       <c r="K9" s="69"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:J3 I4:J9 A4:H5 A6:G7 A8:H9">
-    <cfRule type="expression" dxfId="3" priority="5">
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
-    <cfRule type="expression" priority="6">
+    <cfRule type="expression" priority="2">
       <formula>_xlfn.ISFORMULA(A1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H6">
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>_xlfn.ISFORMULA(H6)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4">
-      <formula>_xlfn.ISFORMULA(H6)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>_xlfn.ISFORMULA(H7)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2">
-      <formula>_xlfn.ISFORMULA(H7)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -75907,7 +75990,351 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EA9CB7-58FD-4E92-8F4F-F7F5581F808F}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46182</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>4.4499999999999998E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>0.04</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.4900000000000002E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>4.1224853939605843E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR109</f>
+        <v>2.5599999999999998E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I5)^(B2/365)-1)*365/B2</f>
+        <v>3.6611011922457352E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.6623864748969649E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>3.6653265234805166E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>3.6708475995860898E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>3.6763797642103878E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>3.6930430400372957E-2</v>
+      </c>
+      <c r="H4" s="57">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z109</f>
+        <v>1.0300000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.3799999999999999E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f t="shared" ref="C5:F5" si="2">((1+$I5)^(C2/365)-1)*365/C2</f>
+        <v>3.6623864748969649E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.6708475995860898E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.6763797642103878E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f>((1+$I5)^(G2/365)-1)*365/G2</f>
+        <v>3.6930430400372957E-2</v>
+      </c>
+      <c r="H5" s="57">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.727612334382413E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ109</f>
+        <v>2.3900000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.1007855232316502E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>2.3099999999999999E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.1035682144425177E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.1053856606007598E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.1108505700553632E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.1221434731349964E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>1.0400000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.5810535749577328E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.5822832682856749E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.5850961105459378E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.5903781300481455E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.5956705257407101E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.6116101995444835E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.6446716511065569E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H109</f>
+        <v>2.2199999999999998E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.8111933116994026E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.8125861385658953E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.8157722919830293E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.8217559021958877E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.8277520231449862E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.8458157450568138E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.8100000000000002E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.88330456106869E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -76265,7 +76692,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="76" priority="1">
+    <cfRule type="expression" dxfId="75" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Daily Earn-Borrow Rates.xlsx
+++ b/Daily Earn-Borrow Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eqwpfs01.eliptik.local\fileserver\Department_Data\00-Share\141-BTCTURK _INT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2E0361-B06B-42D9-8D4C-CB39027A12F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE8120B8-BE54-43E9-AFCD-49AE3B7E63EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="17520" firstSheet="74" activeTab="83" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="1830" windowWidth="29040" windowHeight="15720" firstSheet="75" activeTab="84" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin Borrow Rates" sheetId="50" r:id="rId1"/>
@@ -97,6 +97,7 @@
     <sheet name="07.06.2026" sheetId="104" r:id="rId82"/>
     <sheet name="08.06.2026" sheetId="105" r:id="rId83"/>
     <sheet name="09.06.2026" sheetId="106" r:id="rId84"/>
+    <sheet name="10.06.2026" sheetId="107" r:id="rId85"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3202,6 +3203,43 @@
 </comments>
 </file>
 
+<file path=xl/comments81.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Batuhan Helvaci</author>
+  </authors>
+  <commentList>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{E5B63D5C-717D-4E98-A7CC-F6634DD1D8FD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t>Batuhan Helvaci:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="162"/>
+          </rPr>
+          <t xml:space="preserve">
+Margin Borrow Int Rate
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -3240,7 +3278,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4658" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4671" uniqueCount="69">
   <si>
     <t>3.46%</t>
   </si>
@@ -3923,7 +3961,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="79">
+  <dxfs count="80">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4501,9 +4546,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>27736</xdr:colOff>
+      <xdr:colOff>30911</xdr:colOff>
       <xdr:row>155</xdr:row>
-      <xdr:rowOff>67150</xdr:rowOff>
+      <xdr:rowOff>63975</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -8581,46 +8626,107 @@
       <c r="F161" s="23">
         <v>4.2700000000000002E-2</v>
       </c>
-      <c r="G161" s="90"/>
+      <c r="G161" s="90">
+        <v>61685</v>
+      </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="82">
         <v>46183</v>
       </c>
-      <c r="B162" s="83"/>
-      <c r="C162" s="23"/>
-      <c r="D162" s="23"/>
-      <c r="E162" s="23"/>
-      <c r="F162" s="23"/>
+      <c r="B162" s="83">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="C162" s="23">
+        <v>2.47E-2</v>
+      </c>
+      <c r="D162" s="23">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="E162" s="23">
+        <v>3.8600000000000002E-2</v>
+      </c>
+      <c r="F162" s="23">
+        <v>4.3499999999999997E-2</v>
+      </c>
       <c r="G162" s="90"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A163" s="80"/>
-      <c r="B163" s="80"/>
+      <c r="A163" s="82">
+        <v>46184</v>
+      </c>
+      <c r="B163" s="83"/>
+      <c r="C163" s="23"/>
+      <c r="D163" s="23"/>
+      <c r="E163" s="23"/>
+      <c r="F163" s="23"/>
+      <c r="G163" s="90"/>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A164" s="80"/>
-      <c r="B164" s="80"/>
+      <c r="A164" s="82">
+        <v>46185</v>
+      </c>
+      <c r="B164" s="83"/>
+      <c r="C164" s="23"/>
+      <c r="D164" s="23"/>
+      <c r="E164" s="23"/>
+      <c r="F164" s="23"/>
+      <c r="G164" s="90"/>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A165" s="80"/>
-      <c r="B165" s="80"/>
+      <c r="A165" s="82">
+        <v>46186</v>
+      </c>
+      <c r="B165" s="83"/>
+      <c r="C165" s="23"/>
+      <c r="D165" s="23"/>
+      <c r="E165" s="23"/>
+      <c r="F165" s="23"/>
+      <c r="G165" s="90"/>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A166" s="80"/>
-      <c r="B166" s="80"/>
+      <c r="A166" s="82">
+        <v>46187</v>
+      </c>
+      <c r="B166" s="83"/>
+      <c r="C166" s="23"/>
+      <c r="D166" s="23"/>
+      <c r="E166" s="23"/>
+      <c r="F166" s="23"/>
+      <c r="G166" s="90"/>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A167" s="80"/>
-      <c r="B167" s="80"/>
+      <c r="A167" s="82">
+        <v>46188</v>
+      </c>
+      <c r="B167" s="83"/>
+      <c r="C167" s="23"/>
+      <c r="D167" s="23"/>
+      <c r="E167" s="23"/>
+      <c r="F167" s="23"/>
+      <c r="G167" s="90"/>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A168" s="80"/>
-      <c r="B168" s="80"/>
+      <c r="A168" s="82">
+        <v>46189</v>
+      </c>
+      <c r="B168" s="83"/>
+      <c r="C168" s="23"/>
+      <c r="D168" s="23"/>
+      <c r="E168" s="23"/>
+      <c r="F168" s="23"/>
+      <c r="G168" s="90"/>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A169" s="80"/>
-      <c r="B169" s="80"/>
+      <c r="A169" s="82">
+        <v>46190</v>
+      </c>
+      <c r="B169" s="83"/>
+      <c r="C169" s="23"/>
+      <c r="D169" s="23"/>
+      <c r="E169" s="23"/>
+      <c r="F169" s="23"/>
+      <c r="G169" s="90"/>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="80"/>
@@ -9110,7 +9216,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="74" priority="1">
+    <cfRule type="expression" dxfId="75" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9446,7 +9552,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="73" priority="1">
+    <cfRule type="expression" dxfId="74" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9784,7 +9890,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="72" priority="1">
+    <cfRule type="expression" dxfId="73" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10120,7 +10226,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="71" priority="1">
+    <cfRule type="expression" dxfId="72" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10454,7 +10560,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="70" priority="1">
+    <cfRule type="expression" dxfId="71" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10790,7 +10896,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="69" priority="1">
+    <cfRule type="expression" dxfId="70" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11126,7 +11232,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="68" priority="1">
+    <cfRule type="expression" dxfId="69" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11462,7 +11568,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="67" priority="1">
+    <cfRule type="expression" dxfId="68" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11798,7 +11904,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="66" priority="1">
+    <cfRule type="expression" dxfId="67" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12134,7 +12240,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="65" priority="1">
+    <cfRule type="expression" dxfId="66" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12927,7 +13033,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="BS5" s="13">
-        <f t="shared" ref="BS5:BS109" si="3">BR5-BJ5</f>
+        <f t="shared" ref="BS5:BS110" si="3">BR5-BJ5</f>
         <v>2.3100000000000002E-2</v>
       </c>
     </row>
@@ -25429,7 +25535,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="BA71" s="13">
-        <f t="shared" ref="BA71:BA109" si="5">AZ71-AR71</f>
+        <f t="shared" ref="BA71:BA110" si="5">AZ71-AR71</f>
         <v>2.6199999999999998E-2</v>
       </c>
       <c r="BC71" s="4">
@@ -32717,7 +32823,9 @@
       <c r="G110" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H110" s="9"/>
+      <c r="H110" s="9">
+        <v>1.37E-2</v>
+      </c>
       <c r="I110" s="2">
         <v>46183</v>
       </c>
@@ -32739,10 +32847,12 @@
       <c r="O110" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P110" s="58"/>
+      <c r="P110" s="58">
+        <v>3.5799999999999998E-2</v>
+      </c>
       <c r="Q110" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.2099999999999998E-2</v>
       </c>
       <c r="S110" s="4">
         <v>46183</v>
@@ -32759,11 +32869,15 @@
       <c r="W110" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X110" s="6"/>
+      <c r="X110" s="6">
+        <v>0.03</v>
+      </c>
       <c r="Y110" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Z110" s="6"/>
+      <c r="Z110" s="6">
+        <v>1.49E-2</v>
+      </c>
       <c r="AA110" s="2">
         <v>46183</v>
       </c>
@@ -32785,53 +32899,97 @@
       <c r="AG110" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH110" s="58"/>
+      <c r="AH110" s="58">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="AI110" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1.0100000000000001E-2</v>
       </c>
       <c r="AK110" s="4">
         <v>46183</v>
       </c>
-      <c r="AL110" s="3"/>
+      <c r="AL110" s="6">
+        <v>0.02</v>
+      </c>
       <c r="AM110" s="3"/>
       <c r="AN110" s="3"/>
       <c r="AO110" s="3"/>
-      <c r="AP110" s="3"/>
-      <c r="AQ110" s="6"/>
-      <c r="AR110" s="6"/>
+      <c r="AP110" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ110" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR110" s="6">
+        <v>1.4E-2</v>
+      </c>
       <c r="AS110" s="2">
         <v>46183</v>
       </c>
-      <c r="AT110" s="14"/>
-      <c r="AU110" s="14"/>
-      <c r="AV110" s="14"/>
-      <c r="AW110" s="14"/>
-      <c r="AX110" s="14"/>
-      <c r="AY110" s="14"/>
-      <c r="AZ110" s="14"/>
-      <c r="BA110" s="13"/>
+      <c r="AT110" s="14">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="AU110" s="14">
+        <v>3.9E-2</v>
+      </c>
+      <c r="AV110" s="14">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="AW110" s="14">
+        <v>3.9E-2</v>
+      </c>
+      <c r="AX110" s="14">
+        <v>4.5400000000000003E-2</v>
+      </c>
+      <c r="AY110" s="14">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="AZ110" s="14">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="BA110" s="13">
+        <f t="shared" si="5"/>
+        <v>2.6300000000000004E-2</v>
+      </c>
       <c r="BC110" s="4">
         <v>46183</v>
       </c>
-      <c r="BD110" s="6"/>
-      <c r="BE110" s="6"/>
-      <c r="BF110" s="6"/>
+      <c r="BD110" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BE110" s="6">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BF110" s="6">
+        <v>1.14E-2</v>
+      </c>
       <c r="BG110" s="3"/>
       <c r="BH110" s="3"/>
       <c r="BI110" s="3"/>
-      <c r="BJ110" s="6"/>
+      <c r="BJ110" s="6">
+        <v>1.4200000000000001E-2</v>
+      </c>
       <c r="BK110" s="2">
         <v>46183</v>
       </c>
-      <c r="BL110" s="58"/>
+      <c r="BL110" s="58">
+        <v>4.4400000000000002E-2</v>
+      </c>
       <c r="BM110" s="1"/>
-      <c r="BN110" s="58"/>
+      <c r="BN110" s="58">
+        <v>5.3199999999999997E-2</v>
+      </c>
       <c r="BO110" s="1"/>
       <c r="BP110" s="1"/>
       <c r="BQ110" s="1"/>
-      <c r="BR110" s="58"/>
-      <c r="BS110" s="13"/>
+      <c r="BR110" s="58">
+        <v>3.7100000000000001E-2</v>
+      </c>
+      <c r="BS110" s="13">
+        <f t="shared" si="3"/>
+        <v>2.29E-2</v>
+      </c>
     </row>
     <row r="111" spans="1:71" x14ac:dyDescent="0.35">
       <c r="A111" s="4">
@@ -34121,7 +34279,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="64" priority="1">
+    <cfRule type="expression" dxfId="65" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34457,7 +34615,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="63" priority="1">
+    <cfRule type="expression" dxfId="64" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34795,7 +34953,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="62" priority="1">
+    <cfRule type="expression" dxfId="63" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35133,7 +35291,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="61" priority="1">
+    <cfRule type="expression" dxfId="62" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35471,7 +35629,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="60" priority="1">
+    <cfRule type="expression" dxfId="61" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35839,7 +35997,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="59" priority="1">
+    <cfRule type="expression" dxfId="60" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36207,7 +36365,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="58" priority="1">
+    <cfRule type="expression" dxfId="59" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36575,7 +36733,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="57" priority="1">
+    <cfRule type="expression" dxfId="58" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36946,7 +37104,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="56" priority="1">
+    <cfRule type="expression" dxfId="57" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -37327,7 +37485,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9 A10">
-    <cfRule type="expression" dxfId="55" priority="1">
+    <cfRule type="expression" dxfId="56" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -38791,7 +38949,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="54" priority="1">
+    <cfRule type="expression" dxfId="55" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -39135,7 +39293,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="53" priority="1">
+    <cfRule type="expression" dxfId="54" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -39479,7 +39637,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="52" priority="1">
+    <cfRule type="expression" dxfId="53" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -39823,7 +39981,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="51" priority="1">
+    <cfRule type="expression" dxfId="52" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -40167,7 +40325,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="50" priority="1">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -40499,7 +40657,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="49" priority="1">
+    <cfRule type="expression" dxfId="50" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -40843,7 +41001,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -41187,7 +41345,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="48" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -41534,7 +41692,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="46" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -41879,7 +42037,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -52575,7 +52733,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="44" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -52919,7 +53077,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -53254,7 +53412,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J3 A4:H9 J4:J9 I4:I10">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -53586,7 +53744,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -53930,7 +54088,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -54274,7 +54432,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -54618,7 +54776,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -54962,7 +55120,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -55306,7 +55464,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -55650,7 +55808,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -63687,7 +63845,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -64031,7 +64189,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -64375,7 +64533,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -64719,7 +64877,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -65063,7 +65221,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -65407,7 +65565,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -65751,7 +65909,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -66095,7 +66253,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -66439,7 +66597,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -66783,7 +66941,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -67148,7 +67306,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="78" priority="1">
+    <cfRule type="expression" dxfId="79" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -67493,7 +67651,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -67837,7 +67995,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -68181,7 +68339,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -68525,7 +68683,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -68869,7 +69027,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -69213,7 +69371,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -69557,7 +69715,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -69901,7 +70059,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -70245,7 +70403,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -70438,7 +70596,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -70800,7 +70958,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="77" priority="1">
+    <cfRule type="expression" dxfId="78" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -71142,7 +71300,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -71486,7 +71644,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -71830,7 +71988,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -72174,7 +72332,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -72518,7 +72676,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -72862,7 +73020,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -73221,7 +73379,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -73565,7 +73723,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -73909,7 +74067,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -74253,7 +74411,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -74616,7 +74774,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="76" priority="1">
+    <cfRule type="expression" dxfId="77" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -74957,7 +75115,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -75301,7 +75459,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -75645,7 +75803,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -75990,7 +76148,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:J9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
     <cfRule type="expression" priority="2">
@@ -76328,6 +76486,350 @@
       <c r="I9" s="74">
         <f t="shared" si="1"/>
         <v>3.88330456106869E-2</v>
+      </c>
+      <c r="J9" s="75"/>
+      <c r="K9" s="69"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:J9">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>_xlfn.ISFORMULA(A1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98F48FD5-BC9F-412C-B18F-ADC011811169}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="9" width="30.6328125" customWidth="1"/>
+    <col min="10" max="10" width="30.6328125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50">
+        <v>46183</v>
+      </c>
+      <c r="B2" s="51">
+        <v>7</v>
+      </c>
+      <c r="C2" s="51">
+        <v>14</v>
+      </c>
+      <c r="D2" s="51">
+        <v>30</v>
+      </c>
+      <c r="E2" s="51">
+        <v>60</v>
+      </c>
+      <c r="F2" s="51">
+        <v>90</v>
+      </c>
+      <c r="G2" s="51">
+        <v>180</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="55">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D3" s="55">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="E3" s="55">
+        <v>3.9E-2</v>
+      </c>
+      <c r="F3" s="55">
+        <v>4.5400000000000003E-2</v>
+      </c>
+      <c r="G3" s="55">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="H3" s="53">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="I3" s="74">
+        <f>(1+H3/365)^365-1</f>
+        <v>4.1120748168237853E-2</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="K3" s="68">
+        <f>H3-'Daily Data'!AR110</f>
+        <v>2.6300000000000004E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="56">
+        <f>((1+$I4)^(B2/365)-1)*365/B2</f>
+        <v>2.5005137572765568E-2</v>
+      </c>
+      <c r="C4" s="56">
+        <f t="shared" ref="C4:G4" si="0">((1+$I4)^(C2/365)-1)*365/C2</f>
+        <v>2.5011133186924366E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5024844646748073E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5050580654265259E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5076351951623117E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="0"/>
+        <v>2.5153878127579712E-2</v>
+      </c>
+      <c r="H4" s="57">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I4" s="74">
+        <f t="shared" ref="I4:I9" si="1">(1+H4/365)^365-1</f>
+        <v>2.5314242726610869E-2</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="K4" s="68">
+        <f>H4-'Daily Data'!Z110</f>
+        <v>1.0100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="56">
+        <v>4.4400000000000002E-2</v>
+      </c>
+      <c r="C5" s="56">
+        <f>((1+I5)^(C2/365)-1)*365/C2</f>
+        <v>3.7124521379478526E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>5.3199999999999997E-2</v>
+      </c>
+      <c r="E5" s="56">
+        <f>((1+$I5)^(E2/365)-1)*365/E2</f>
+        <v>3.7211463020234627E-2</v>
+      </c>
+      <c r="F5" s="56">
+        <f t="shared" ref="F5:G5" si="2">((1+$I5)^(F2/365)-1)*365/F2</f>
+        <v>3.7268310329474294E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="2"/>
+        <v>3.7439547899246244E-2</v>
+      </c>
+      <c r="H5" s="57">
+        <v>3.7100000000000001E-2</v>
+      </c>
+      <c r="I5" s="74">
+        <f t="shared" si="1"/>
+        <v>3.7794838704558797E-2</v>
+      </c>
+      <c r="J5" s="75"/>
+      <c r="K5" s="68">
+        <f>H5-'Daily Data'!BJ110</f>
+        <v>2.29E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="52">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C6" s="52">
+        <f t="shared" ref="C6:G6" si="3">((1+$I6)^(C2/365)-1)*365/C2</f>
+        <v>3.3720232087598924E-2</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3791952704462558E-2</v>
+      </c>
+      <c r="F6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3838836584806672E-2</v>
+      </c>
+      <c r="G6" s="52">
+        <f t="shared" si="3"/>
+        <v>3.3980009211555737E-2</v>
+      </c>
+      <c r="H6" s="53">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I6" s="74">
+        <f t="shared" si="1"/>
+        <v>3.4272668936467188E-2</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="68">
+        <f>H6-2.3%</f>
+        <v>1.0700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="52">
+        <v>2.23E-2</v>
+      </c>
+      <c r="C7" s="52">
+        <f t="shared" ref="C7:G7" si="4">((1+$I7)^(C2/365)-1)*365/C2</f>
+        <v>2.1208005585827774E-2</v>
+      </c>
+      <c r="D7" s="52">
+        <v>2.3400000000000001E-2</v>
+      </c>
+      <c r="E7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.1236365426236359E-2</v>
+      </c>
+      <c r="F7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.1254888214009424E-2</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" si="4"/>
+        <v>2.1310585918899037E-2</v>
+      </c>
+      <c r="H7" s="53">
+        <v>2.12E-2</v>
+      </c>
+      <c r="I7" s="74">
+        <f t="shared" si="1"/>
+        <v>2.1425687635407309E-2</v>
+      </c>
+      <c r="J7" s="75"/>
+      <c r="K7" s="68">
+        <f>H7-1.06%</f>
+        <v>1.06E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="52">
+        <f>((1+$I8)^(B2/365)-1)*365/B2</f>
+        <v>3.5810535749577328E-2</v>
+      </c>
+      <c r="C8" s="52">
+        <f t="shared" ref="C8:G8" si="5">((1+$I8)^(C2/365)-1)*365/C2</f>
+        <v>3.5822832682856749E-2</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.5850961105459378E-2</v>
+      </c>
+      <c r="E8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.5903781300481455E-2</v>
+      </c>
+      <c r="F8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.5956705257407101E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="5"/>
+        <v>3.6116101995444835E-2</v>
+      </c>
+      <c r="H8" s="53">
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="I8" s="74">
+        <f t="shared" si="1"/>
+        <v>3.6446716511065569E-2</v>
+      </c>
+      <c r="J8" s="75"/>
+      <c r="K8" s="68">
+        <f>H8-'Daily Data'!H110</f>
+        <v>2.2099999999999998E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="56">
+        <f>((1+$I9)^(B2/365)-1)*365/B2</f>
+        <v>3.8612248405269937E-2</v>
+      </c>
+      <c r="C9" s="56">
+        <f t="shared" ref="C9:G9" si="6">((1+$I9)^(C2/365)-1)*365/C2</f>
+        <v>3.8626544761562069E-2</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.8659248656118694E-2</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.8720668005707982E-2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.8782217460826149E-2</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="6"/>
+        <v>3.8967649563848281E-2</v>
+      </c>
+      <c r="H9" s="53">
+        <v>3.8600000000000002E-2</v>
+      </c>
+      <c r="I9" s="74">
+        <f t="shared" si="1"/>
+        <v>3.9352537413389843E-2</v>
       </c>
       <c r="J9" s="75"/>
       <c r="K9" s="69"/>
@@ -76692,7 +77194,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="expression" dxfId="75" priority="1">
+    <cfRule type="expression" dxfId="76" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
